--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
         <v>0.77</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="3">
@@ -513,7 +513,7 @@
         <v>0.62</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>0.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="5">
@@ -565,7 +565,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="6">
@@ -591,7 +591,7 @@
         <v>0.79</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="7">
@@ -617,7 +617,7 @@
         <v>0.67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         <v>0.92</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="9">
@@ -669,7 +669,7 @@
         <v>0.79</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         <v>0.77</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="11">
@@ -721,7 +721,7 @@
         <v>0.97</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="12">
@@ -747,7 +747,7 @@
         <v>0.87</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="13">
@@ -773,7 +773,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="14">
@@ -799,7 +799,7 @@
         <v>0.66</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="15">
@@ -825,7 +825,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="16">
@@ -851,7 +851,7 @@
         <v>0.98</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="17">
@@ -877,7 +877,7 @@
         <v>0.62</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="18">
@@ -903,7 +903,7 @@
         <v>0.82</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="19">
@@ -929,7 +929,7 @@
         <v>0.63</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="20">
@@ -955,7 +955,7 @@
         <v>0.98</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="21">
@@ -981,7 +981,7 @@
         <v>0.68</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="22">
@@ -1007,7 +1007,7 @@
         <v>0.79</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="23">
@@ -1033,7 +1033,7 @@
         <v>0.63</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="24">
@@ -1059,7 +1059,7 @@
         <v>0.66</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="25">
@@ -1085,7 +1085,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="26">
@@ -1111,7 +1111,7 @@
         <v>0.92</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="27">
@@ -1137,7 +1137,7 @@
         <v>0.85</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="28">
@@ -1163,7 +1163,7 @@
         <v>0.96</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="29">
@@ -1189,7 +1189,7 @@
         <v>0.84</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="30">
@@ -1215,7 +1215,7 @@
         <v>0.76</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="31">
@@ -1241,7 +1241,7 @@
         <v>0.91</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="32">
@@ -1267,7 +1267,7 @@
         <v>0.68</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="33">
@@ -1293,7 +1293,7 @@
         <v>0.9</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="34">
@@ -1319,7 +1319,7 @@
         <v>0.74</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="35">
@@ -1345,7 +1345,7 @@
         <v>0.8</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="36">
@@ -1371,7 +1371,7 @@
         <v>0.98</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="37">
@@ -1397,7 +1397,7 @@
         <v>0.96</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="38">
@@ -1423,7 +1423,7 @@
         <v>0.79</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="39">
@@ -1449,7 +1449,7 @@
         <v>0.79</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="40">
@@ -1475,7 +1475,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="41">
@@ -1501,7 +1501,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="42">
@@ -1527,7 +1527,7 @@
         <v>0.73</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="43">
@@ -1553,7 +1553,7 @@
         <v>0.71</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="44">
@@ -1579,7 +1579,7 @@
         <v>0.97</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="45">
@@ -1605,7 +1605,7 @@
         <v>0.83</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="46">
@@ -1631,7 +1631,7 @@
         <v>0.73</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="47">
@@ -1657,7 +1657,7 @@
         <v>0.87</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="48">
@@ -1683,7 +1683,7 @@
         <v>0.73</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="49">
@@ -1709,7 +1709,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="50">
@@ -1735,7 +1735,7 @@
         <v>0.63</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
       </c>
     </row>
     <row r="51">
@@ -1761,7 +1761,1307 @@
         <v>0.68</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>46089.25622588059</v>
+        <v>46089.25622587963</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2ecffa49-6041-4745-8445-b52eb9827bcc</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>e715895a-7a8a-47c1-857c-e87a64fb2118</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>28e0ffff-f1f8-4339-a866-5df71269333f</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>c6d56985-5a6a-49e6-b8e8-860c6dc07e10</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>85ca6879-e8bd-46d3-a691-9517d38c6345</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1a23d3a8-52b9-437e-913e-581a97eee8cc</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>e0de7df4-f8c1-4d52-a541-5a37844d61e9</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>f6081d35-4bc5-4f01-b297-da420817bf42</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>aa8f64db-fc6c-4198-945a-fb89d0b2bef0</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>162938ad-c468-4930-b7f5-9496fa97cb6d</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>99cb8543-7029-411a-973a-5b3207528928</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>d55b4bf2-8aac-4f8e-a876-3066518f442f</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>41ff460e-71d3-4215-849c-8385070af494</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>9588dd77-b44f-4bf3-99f6-007d91bcf8be</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>8ccaea4d-30b0-4c81-bce9-d1c610597f2b</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>20af1d8a-3d5b-492a-a2ce-1c385c06bfef</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>58bc5230-f65c-49fc-b29d-97b1cadb683e</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6877568a-cbe1-48be-a8ae-9a2912009768</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1b3bcb13-314b-4386-90fd-d99753c22133</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>100f9133-3187-40ff-95f7-3381c810ecbe</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>536b7b28-8667-492e-86b3-1a6b6df1c170</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>59668d0a-3955-4b53-ba0f-e278e92dd3eb</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ed9494e5-e0d8-4c83-8602-efaa6df2f0a3</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>3b1ea915-a4cb-46f3-8469-42dee4357ff4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>46e513bf-e6fc-4122-8c7d-0af721aef6f5</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>70e66201-db63-4fa9-ae20-29c7b57463de</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1202db8f-56ea-480e-b226-14dcbafd9f17</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0e7ff1a5-67ac-475b-9d7d-0009a21dd50f</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>a7c34c19-d9b3-43e8-ae7a-cce178840139</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>71c0efec-c333-4ff7-a09b-e7e4545e8f93</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>28525a1b-b6c7-4ef6-9b7c-08da103ecb78</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1e194daa-45ea-4822-b8a8-8e7937ff95bd</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>52a3de08-8bbb-4914-a606-555588a9a22f</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>a2b02321-c657-4cf4-a44c-696320598cbc</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>912fe05b-e7e3-435a-8b56-d084b4e009e8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>75b2ee11-1a96-4125-82e6-3bed8b18d3ec</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>feb25fe5-de14-4a74-872c-9fd250bf4851</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>6c69de8b-13ff-49d1-b8e8-fb733d1441fd</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>773c13c1-a473-498c-9941-892b0a82544c</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>b4b087ef-560f-41de-b9df-394e0ccecbd5</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>a7b3fe06-cc27-4c7f-bf88-5393cdf8513a</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>dd10f970-adb3-439b-a7c0-f782639e5b91</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4af0ab73-f9c7-4164-a00c-c8590a2d464c</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>20f0ca84-badc-4dd4-91e0-ea426296dc34</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4d8d15f4-d974-4256-a6c0-b76d294f82d6</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>061a5d8d-db2c-4eb2-8dab-0d3022a37074</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>a4063195-267e-4198-af57-aca8d32f7d33</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>bb339521-073d-415c-8193-35cd41b24a8a</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>b0e7432f-0526-4aa0-8c00-3f32d965edcf</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>a8eb50ee-b5ff-4191-a0a6-cd163a09d918</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>e94a7e91-acd6-482d-ae63-f9e4e9123fdb</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>066a0461-853e-4d63-8876-8fb3d41a1f54</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>aa488b1f-559d-4f2b-b87b-55ac28c321fe</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>995349d6-0520-40f2-b77d-5734b81dcf25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>dd3a6a6f-569b-4285-a9c2-5c6545c9dff6</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>fe29a209-e7d6-4290-a402-cc0050182210</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>d2e82b04-ee3e-4fe5-a2b4-d9405f81cfdc</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>a9d59163-e9e3-4602-8f6f-d8ee471fc731</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>d0d4445e-d742-4f15-be06-3c2f125e0229</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>98f4be1e-4f41-44ad-84f8-4993472c4f92</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>562c6270-31e8-4c92-8b20-29d66e3db902</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>72c9447c-5584-4d93-ac79-04097139e5cd</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>bb0948e0-420c-40eb-81b1-4caa8423a5db</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>84730c28-9465-4801-8092-05f9cd78cc5b</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2b54806e-a966-4513-922c-cae074aff44b</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>fd499e9e-741b-4826-848a-b0360d2d2cad</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>5273c0e0-cb7d-4674-a9fb-3950289e7890</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>8a7ebb39-c7f9-40fd-a82f-3b4057d25bda</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>e8e953a7-8d80-4a98-8ae2-3bf742fc999a</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>14e8167e-ccf0-4e6a-9c33-3a9f6ecc1a79</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>bf3f7446-9e92-4b3c-8d75-7a79c0273dae</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>24a73fe1-4c8d-4d08-b850-e07a3c653910</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2c2ad67d-8bdf-42c9-b503-2c70e722abb6</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>97556e77-3a71-4e0e-9b49-d84af964b598</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>424737d9-0ada-424d-906e-99e80b2aace0</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>cbee731f-b14d-4743-9b87-fb5aeddf7d84</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>55448c15-7ef0-418e-a65a-204b38ae48fa</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>baed2d45-70d0-467a-a088-f25779fdae91</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>a4d841fb-ea8a-4655-919a-05b31db1978d</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>aeba1ce1-3306-4f81-acb0-b81b4e30925f</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>e64875c2-53f9-4e4d-b5f7-7d75d62d8154</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1a6a020a-171d-4bfe-b6ab-348ae858d2ec</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>91710272-6a66-4f1c-ab42-bea695384340</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>61a36c48-8a6b-44e8-9d99-91cb11828130</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>62a0892a-60cb-4a89-b7ba-1a4e6ef9d13d</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ff77c13e-e11d-47b0-a19e-83a916c763ae</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>adeeedf2-a92f-46c6-9102-6b5e01b9548a</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>34d2e99c-8962-49cb-85a3-f0480403d7e4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>c30464a4-2367-409e-8877-b1bf046ebff4</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>3df449ec-e9f5-4939-9471-b3ba82db3d19</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2acd5f48-cb5a-4783-a463-8030508211ab</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5a2ba8e5-04e6-47d2-93a9-d27736a0a1a4</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>6ee73c27-b8da-41f1-95ad-58475278425a</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>e13a4ded-3395-4fc7-81e8-dc16bcc5f87e</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>68f9adff-8ff7-4e73-8ba5-64f1f6210a88</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>32be64a1-f03c-482a-a52b-4efc49632624</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>037fe10d-f6fd-4622-a95e-84625d59e666</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>c44bcb78-1735-4a9d-b5fb-862fef33f1f9</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46089.26884123853</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1e8f5036-d31a-400c-93dd-e85c148616c7</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>a93c4311-1888-4651-827e-20c3b73c9cd4</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46089.26884123853</v>
       </c>
     </row>
   </sheetData>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:K551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>46074.31505102188</v>
+        <v>46074.31505101852</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>46085.60671769303</v>
+        <v>46085.60671769676</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>46085.3983843631</v>
+        <v>46085.39838436343</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>46075.31505103283</v>
+        <v>46075.31505103009</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46071.64838436958</v>
+        <v>46071.648384375</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>46069.60671770601</v>
+        <v>46069.60671770833</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>46073.64838437577</v>
+        <v>46073.648384375</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>46087.48171771219</v>
+        <v>46087.48171770833</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>46075.44005104923</v>
+        <v>46075.44005105324</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>46075.64838438571</v>
+        <v>46075.64838438657</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>46067.69005105556</v>
+        <v>46067.69005105324</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>46070.48171772561</v>
+        <v>46070.48171771991</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>46073.69005106219</v>
+        <v>46073.69005106481</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>46066.35671773207</v>
+        <v>46066.35671773148</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>46060.60671773522</v>
+        <v>46060.60671773148</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>46067.35671773848</v>
+        <v>46067.35671774305</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46074.52338440831</v>
+        <v>46074.52338440972</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46078.39838441137</v>
+        <v>46078.39838440972</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46088.39838441468</v>
+        <v>46088.39838440972</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46067.4817177511</v>
+        <v>46067.48171775463</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46069.6067177541</v>
+        <v>46069.60671775463</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46064.69005109046</v>
+        <v>46064.69005108796</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46073.48171776073</v>
+        <v>46073.4817177662</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46066.69005109711</v>
+        <v>46066.69005109954</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46084.69005110033</v>
+        <v>46084.69005109954</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46062.64838443667</v>
+        <v>46062.64838443287</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46076.44005110671</v>
+        <v>46076.44005111111</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46083.60671777641</v>
+        <v>46083.60671777778</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46060.48171777962</v>
+        <v>46060.48171777778</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46086.44005111635</v>
+        <v>46086.44005111111</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46076.48171778607</v>
+        <v>46076.48171778935</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46069.60671778907</v>
+        <v>46069.60671778935</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46062.31505112546</v>
+        <v>46062.31505112268</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46075.48171779542</v>
+        <v>46075.48171780093</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46062.60671779846</v>
+        <v>46062.60671780093</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46065.48171780161</v>
+        <v>46065.48171780093</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46066.44005113791</v>
+        <v>46066.44005113426</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46059.44005114168</v>
+        <v>46059.44005114583</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46078.39838447809</v>
+        <v>46078.39838447917</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46084.5650511478</v>
+        <v>46084.56505114583</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46087.31505115115</v>
+        <v>46087.31505114583</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46069.56505115417</v>
+        <v>46069.56505115741</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>46067.35671782727</v>
+        <v>46067.35671782408</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>46068.64838449729</v>
+        <v>46068.64838450232</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>46087.64838450032</v>
+        <v>46087.64838450232</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>46079.60671783668</v>
+        <v>46079.60671783565</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46071.69005117308</v>
+        <v>46071.69005116898</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46068.60671784301</v>
+        <v>46068.60671784722</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46078.31505117936</v>
+        <v>46078.31505118056</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46086.39838451582</v>
+        <v>46086.39838451389</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46078.39838451966</v>
+        <v>46078.39838451389</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46081.60671785609</v>
+        <v>46081.6067178588</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46067.35671785923</v>
+        <v>46067.3567178588</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46069.69005119577</v>
+        <v>46069.69005119213</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46067.64838453226</v>
+        <v>46067.64838453704</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46085.6483845353</v>
+        <v>46085.64838453704</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46078.48171787169</v>
+        <v>46078.48171787037</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46062.31505120802</v>
+        <v>46062.3150512037</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46071.69005121126</v>
+        <v>46071.69005121528</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46074.69005121425</v>
+        <v>46074.69005121528</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46073.35671788396</v>
+        <v>46073.35671788194</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46059.64838455387</v>
+        <v>46059.64838454861</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46066.48171789019</v>
+        <v>46066.48171789352</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46075.48171789325</v>
+        <v>46075.48171789352</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46081.44005122966</v>
+        <v>46081.44005122685</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46066.64838456657</v>
+        <v>46066.64838457176</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46065.44005123671</v>
+        <v>46065.44005123842</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46078.56505123975</v>
+        <v>46078.56505123842</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46059.3150512452</v>
+        <v>46059.31505125</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46080.35671791505</v>
+        <v>46080.35671791666</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46084.39838458481</v>
+        <v>46084.39838458334</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46077.31505125491</v>
+        <v>46077.31505125</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46078.39838459133</v>
+        <v>46078.3983845949</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46080.39838459431</v>
+        <v>46080.3983845949</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46061.69005126404</v>
+        <v>46061.69005126158</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46060.56505126738</v>
+        <v>46060.56505127315</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46059.56505127046</v>
+        <v>46059.56505127315</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46086.64838460687</v>
+        <v>46086.64838460648</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46085.64838461</v>
+        <v>46085.64838460648</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46085.48171794655</v>
+        <v>46085.48171795139</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46065.39838461625</v>
+        <v>46065.39838461806</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46077.35671795269</v>
+        <v>46077.35671795139</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46060.52338462249</v>
+        <v>46060.52338461806</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46066.39838462568</v>
+        <v>46066.39838462963</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46081.64838462888</v>
+        <v>46081.64838462963</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46073.48171796523</v>
+        <v>46073.48171796296</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46068.35671796858</v>
+        <v>46068.35671796296</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46076.69005130504</v>
+        <v>46076.69005130787</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46059.48171797483</v>
+        <v>46059.48171797454</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46085.48171797791</v>
+        <v>46085.48171797454</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46074.39838464774</v>
+        <v>46074.39838465278</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46061.60671798437</v>
+        <v>46061.60671798611</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46082.64838465423</v>
+        <v>46082.64838465278</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46066.4400513239</v>
+        <v>46066.44005131944</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46077.31505132731</v>
+        <v>46077.31505133102</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46063.52338466371</v>
+        <v>46063.52338466435</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46065.44005133356</v>
+        <v>46065.44005133102</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46085.69005133675</v>
+        <v>46085.69005133102</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46083.69005133984</v>
+        <v>46083.69005134259</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46088.60671800959</v>
+        <v>46088.60671800926</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46067.48171801262</v>
+        <v>46067.48171800926</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46072.39838468272</v>
+        <v>46072.3983846875</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46087.60671801919</v>
+        <v>46087.60671802083</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46071.69005135567</v>
+        <v>46071.69005135417</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46066.523384692</v>
+        <v>46066.5233846875</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46063.6483846952</v>
+        <v>46063.64838469907</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46067.64838469839</v>
+        <v>46067.64838469907</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46086.64838470152</v>
+        <v>46086.64838469907</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46084.48171803811</v>
+        <v>46084.48171803241</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46060.69005137448</v>
+        <v>46060.69005137731</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46085.5650513775</v>
+        <v>46085.56505137731</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46063.64838471399</v>
+        <v>46063.64838471065</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46087.52338471733</v>
+        <v>46087.52338472222</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46061.35671805376</v>
+        <v>46061.35671805555</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46088.52338472347</v>
+        <v>46088.52338472222</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46068.48171805985</v>
+        <v>46068.48171805555</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46066.56505139636</v>
+        <v>46066.56505140047</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46060.39838473285</v>
+        <v>46060.39838473379</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46063.56505140255</v>
+        <v>46063.56505140047</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46084.35671807244</v>
+        <v>46084.35671806713</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46075.60671807548</v>
+        <v>46075.60671807871</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46076.39838474516</v>
+        <v>46076.39838474537</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46078.56505141486</v>
+        <v>46078.56505141204</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46077.31505141824</v>
+        <v>46077.31505142361</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>46076.4817180879</v>
+        <v>46076.48171809028</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46079.69005142451</v>
+        <v>46079.69005142361</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46074.60671809423</v>
+        <v>46074.60671809028</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46078.56505143073</v>
+        <v>46078.56505143519</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46060.44005143394</v>
+        <v>46060.44005143519</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46059.35671810369</v>
+        <v>46059.35671810185</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46070.35671810692</v>
+        <v>46070.35671810185</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46077.6483847766</v>
+        <v>46077.64838478009</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46087.44005144636</v>
+        <v>46087.44005144676</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46060.31505144944</v>
+        <v>46060.31505144676</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46065.56505145273</v>
+        <v>46065.56505145833</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46075.31505145579</v>
+        <v>46075.31505145833</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46074.44005145882</v>
+        <v>46074.44005145833</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46061.31505146188</v>
+        <v>46061.31505145833</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46066.3567181317</v>
+        <v>46066.35671813657</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46086.52338480143</v>
+        <v>46086.52338480324</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46071.39838480449</v>
+        <v>46071.39838480324</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46079.6483848076</v>
+        <v>46079.64838480324</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46062.64838481087</v>
+        <v>46062.64838481481</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46073.6067181473</v>
+        <v>46073.60671814815</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46088.56505148367</v>
+        <v>46088.56505148148</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46086.44005148715</v>
+        <v>46086.44005148148</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46088.44005149029</v>
+        <v>46088.44005149305</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46081.56505149352</v>
+        <v>46081.56505149305</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46064.3150514967</v>
+        <v>46064.31505149305</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46083.69005149981</v>
+        <v>46083.69005150463</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46076.35671816971</v>
+        <v>46076.35671817129</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46072.440051507</v>
+        <v>46072.44005150463</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46067.5650515102</v>
+        <v>46067.56505150463</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46078.64838484659</v>
+        <v>46078.64838484953</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46073.69005151631</v>
+        <v>46073.69005151621</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46087.35671818608</v>
+        <v>46087.35671818287</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46087.56505152257</v>
+        <v>46087.56505152778</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46086.64838485909</v>
+        <v>46086.64838486111</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46080.64838486214</v>
+        <v>46080.64838486111</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46087.35671819866</v>
+        <v>46087.35671819445</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46073.69005153531</v>
+        <v>46073.69005153935</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46060.48171820502</v>
+        <v>46060.48171820602</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46070.39838487473</v>
+        <v>46070.39838487269</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46086.56505154462</v>
+        <v>46086.56505153935</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46068.31505154765</v>
+        <v>46068.31505155093</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46059.56505155071</v>
+        <v>46059.56505155093</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46061.48171822039</v>
+        <v>46061.48171821759</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46085.69005155699</v>
+        <v>46085.6900515625</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46072.39838489333</v>
+        <v>46072.39838489583</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46064.52338489651</v>
+        <v>46064.52338489583</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>46086.39838489959</v>
+        <v>46086.39838489583</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>46060.60671823609</v>
+        <v>46060.60671824074</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>46071.52338490596</v>
+        <v>46071.52338490741</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>46082.6900515759</v>
+        <v>46082.69005157407</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>46073.56505157926</v>
+        <v>46073.56505157407</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>46074.35671824907</v>
+        <v>46074.35671825232</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>46086.69005158539</v>
+        <v>46086.69005158565</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>46061.44005158856</v>
+        <v>46061.44005158565</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>46081.39838492509</v>
+        <v>46081.39838493056</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>46088.39838492814</v>
+        <v>46088.39838493056</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>46069.56505159787</v>
+        <v>46069.56505159722</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>46063.31505160087</v>
+        <v>46063.31505159722</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>46081.52338493785</v>
+        <v>46081.52338494213</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>46067.31505160772</v>
+        <v>46067.3150516088</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>46079.35671827758</v>
+        <v>46079.35671827546</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>46079.39838494758</v>
+        <v>46079.39838494213</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="J189" s="2" t="n">
-        <v>46080.64838495065</v>
+        <v>46080.6483849537</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>46063.31505162052</v>
+        <v>46063.31505162037</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         </is>
       </c>
       <c r="J191" s="2" t="n">
-        <v>46066.648384957</v>
+        <v>46066.6483849537</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>46085.39838496036</v>
+        <v>46085.39838496528</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>46070.4817182968</v>
+        <v>46070.48171829861</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>46074.48171830002</v>
+        <v>46074.48171829861</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>46066.48171830327</v>
+        <v>46066.48171829861</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="J196" s="2" t="n">
-        <v>46078.48171830632</v>
+        <v>46078.48171831018</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>46088.44005164288</v>
+        <v>46088.44005164352</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         </is>
       </c>
       <c r="J198" s="2" t="n">
-        <v>46062.31505164604</v>
+        <v>46062.31505164352</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -10579,7 +10579,7 @@
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>46084.6067183161</v>
+        <v>46084.60671832176</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>46078.56505165261</v>
+        <v>46078.5650516551</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         </is>
       </c>
       <c r="J201" s="2" t="n">
-        <v>46076.44005165575</v>
+        <v>46076.4400516551</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>46066.3150516589</v>
+        <v>46066.3150516551</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="J203" s="2" t="n">
-        <v>46067.64838499543</v>
+        <v>46067.648385</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         </is>
       </c>
       <c r="J204" s="2" t="n">
-        <v>46068.52338499867</v>
+        <v>46068.523385</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         </is>
       </c>
       <c r="J205" s="2" t="n">
-        <v>46077.44005166835</v>
+        <v>46077.44005166666</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="J206" s="2" t="n">
-        <v>46081.31505167156</v>
+        <v>46081.31505166666</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="J207" s="2" t="n">
-        <v>46088.35671834138</v>
+        <v>46088.3567183449</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>46083.69005167775</v>
+        <v>46083.69005167824</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="J209" s="2" t="n">
-        <v>46063.56505168096</v>
+        <v>46063.56505167824</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>46080.64838501746</v>
+        <v>46080.64838502315</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>46071.39838502064</v>
+        <v>46071.39838502315</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         </is>
       </c>
       <c r="J212" s="2" t="n">
-        <v>46069.52338502379</v>
+        <v>46069.52338502315</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         </is>
       </c>
       <c r="J213" s="2" t="n">
-        <v>46083.48171836024</v>
+        <v>46083.48171835648</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="J214" s="2" t="n">
-        <v>46070.44005169699</v>
+        <v>46070.44005170139</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="J215" s="2" t="n">
-        <v>46084.31505170002</v>
+        <v>46084.31505170139</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="J216" s="2" t="n">
-        <v>46087.48171836971</v>
+        <v>46087.48171836806</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="J217" s="2" t="n">
-        <v>46060.56505170627</v>
+        <v>46060.56505170139</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="J218" s="2" t="n">
-        <v>46059.31505170945</v>
+        <v>46059.31505171296</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="J219" s="2" t="n">
-        <v>46062.44005171256</v>
+        <v>46062.44005171296</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         </is>
       </c>
       <c r="J220" s="2" t="n">
-        <v>46067.64838504892</v>
+        <v>46067.6483850463</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         </is>
       </c>
       <c r="J221" s="2" t="n">
-        <v>46078.56505171894</v>
+        <v>46078.56505172454</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         </is>
       </c>
       <c r="J222" s="2" t="n">
-        <v>46066.31505172197</v>
+        <v>46066.31505172454</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="J223" s="2" t="n">
-        <v>46085.44005172497</v>
+        <v>46085.44005172454</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="J224" s="2" t="n">
-        <v>46074.31505172802</v>
+        <v>46074.31505172454</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="J225" s="2" t="n">
-        <v>46074.64838506468</v>
+        <v>46074.64838506944</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         </is>
       </c>
       <c r="J226" s="2" t="n">
-        <v>46077.31505173459</v>
+        <v>46077.31505173611</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         </is>
       </c>
       <c r="J227" s="2" t="n">
-        <v>46071.69005173772</v>
+        <v>46071.69005173611</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         </is>
       </c>
       <c r="J228" s="2" t="n">
-        <v>46088.48171840765</v>
+        <v>46088.48171840278</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="J229" s="2" t="n">
-        <v>46062.48171841077</v>
+        <v>46062.48171841435</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         </is>
       </c>
       <c r="J230" s="2" t="n">
-        <v>46066.52338508043</v>
+        <v>46066.52338508102</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="J231" s="2" t="n">
-        <v>46064.31505175013</v>
+        <v>46064.31505174768</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         </is>
       </c>
       <c r="J232" s="2" t="n">
-        <v>46081.5233850868</v>
+        <v>46081.52338508102</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         </is>
       </c>
       <c r="J233" s="2" t="n">
-        <v>46067.35671842333</v>
+        <v>46067.35671842592</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="J234" s="2" t="n">
-        <v>46071.44005175973</v>
+        <v>46071.44005175926</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="J235" s="2" t="n">
-        <v>46079.48171842949</v>
+        <v>46079.48171842592</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="J236" s="2" t="n">
-        <v>46073.64838509941</v>
+        <v>46073.64838510417</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         </is>
       </c>
       <c r="J237" s="2" t="n">
-        <v>46060.35671843585</v>
+        <v>46060.3567184375</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="J238" s="2" t="n">
-        <v>46077.69005177225</v>
+        <v>46077.69005177083</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         </is>
       </c>
       <c r="J239" s="2" t="n">
-        <v>46067.69005177523</v>
+        <v>46067.69005177083</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="J240" s="2" t="n">
-        <v>46080.64838511192</v>
+        <v>46080.64838511574</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="J241" s="2" t="n">
-        <v>46081.69005178177</v>
+        <v>46081.69005178241</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         </is>
       </c>
       <c r="J242" s="2" t="n">
-        <v>46065.48171845142</v>
+        <v>46065.48171844907</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         </is>
       </c>
       <c r="J243" s="2" t="n">
-        <v>46068.6067184548</v>
+        <v>46068.60671844907</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         </is>
       </c>
       <c r="J244" s="2" t="n">
-        <v>46060.31505179115</v>
+        <v>46060.31505179398</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="J245" s="2" t="n">
-        <v>46063.44005179418</v>
+        <v>46063.44005179398</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         </is>
       </c>
       <c r="J246" s="2" t="n">
-        <v>46079.56505179722</v>
+        <v>46079.56505179398</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -13027,7 +13027,7 @@
         </is>
       </c>
       <c r="J247" s="2" t="n">
-        <v>46080.6067184671</v>
+        <v>46080.60671847222</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="J248" s="2" t="n">
-        <v>46063.35671847015</v>
+        <v>46063.35671847222</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         </is>
       </c>
       <c r="J249" s="2" t="n">
-        <v>46060.64838513995</v>
+        <v>46060.64838513889</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
@@ -13180,7 +13180,7 @@
         </is>
       </c>
       <c r="J250" s="2" t="n">
-        <v>46066.64838514305</v>
+        <v>46066.64838513889</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         </is>
       </c>
       <c r="J251" s="2" t="n">
-        <v>46067.6900518129</v>
+        <v>46067.69005181713</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         </is>
       </c>
       <c r="J252" s="2" t="n">
-        <v>46067.3567184826</v>
+        <v>46067.3567184838</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         </is>
       </c>
       <c r="J253" s="2" t="n">
-        <v>46078.3983851523</v>
+        <v>46078.39838515046</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="J254" s="2" t="n">
-        <v>46079.69005182225</v>
+        <v>46079.69005181713</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="J255" s="2" t="n">
-        <v>46087.60671849199</v>
+        <v>46087.60671849537</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="J256" s="2" t="n">
-        <v>46066.35671849499</v>
+        <v>46066.35671849537</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         </is>
       </c>
       <c r="J257" s="2" t="n">
-        <v>46070.64838516464</v>
+        <v>46070.64838516204</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         </is>
       </c>
       <c r="J258" s="2" t="n">
-        <v>46071.48171850132</v>
+        <v>46071.48171850695</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="J259" s="2" t="n">
-        <v>46071.48171850449</v>
+        <v>46071.48171850695</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
@@ -13690,7 +13690,7 @@
         </is>
       </c>
       <c r="J260" s="2" t="n">
-        <v>46065.48171850768</v>
+        <v>46065.48171850695</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         </is>
       </c>
       <c r="J261" s="2" t="n">
-        <v>46065.6067185108</v>
+        <v>46065.60671850695</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         </is>
       </c>
       <c r="J262" s="2" t="n">
-        <v>46080.44005184742</v>
+        <v>46080.44005185185</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -13843,7 +13843,7 @@
         </is>
       </c>
       <c r="J263" s="2" t="n">
-        <v>46066.39838518508</v>
+        <v>46066.39838518519</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         </is>
       </c>
       <c r="J264" s="2" t="n">
-        <v>46061.56505185493</v>
+        <v>46061.56505185185</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         </is>
       </c>
       <c r="J265" s="2" t="n">
-        <v>46082.31505185882</v>
+        <v>46082.31505186343</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         </is>
       </c>
       <c r="J266" s="2" t="n">
-        <v>46080.690051862</v>
+        <v>46080.69005186343</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="J267" s="2" t="n">
-        <v>46061.35671853172</v>
+        <v>46061.35671853009</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         </is>
       </c>
       <c r="J268" s="2" t="n">
-        <v>46082.44005186835</v>
+        <v>46082.44005186343</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         </is>
       </c>
       <c r="J269" s="2" t="n">
-        <v>46063.39838520473</v>
+        <v>46063.39838520833</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46066.56505187455</v>
+        <v>46066.565051875</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46059.48171854456</v>
+        <v>46059.48171854167</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46064.60671854784</v>
+        <v>46064.60671855324</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46068.3150518842</v>
+        <v>46068.31505188657</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46084.64838522072</v>
+        <v>46084.64838521991</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46073.44005189044</v>
+        <v>46073.44005188657</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46082.56505189384</v>
+        <v>46082.56505189815</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46084.69005189706</v>
+        <v>46084.69005189815</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46066.39838523365</v>
+        <v>46066.39838523149</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46081.52338523684</v>
+        <v>46081.52338523149</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46061.69005190658</v>
+        <v>46061.69005190973</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46071.39838524309</v>
+        <v>46071.39838524305</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46066.60671857949</v>
+        <v>46066.60671857639</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46060.315051916</v>
+        <v>46060.31505192129</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46085.39838525236</v>
+        <v>46085.39838525463</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46082.64838525549</v>
+        <v>46082.64838525463</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -15016,7 +15016,7 @@
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46059.35671859181</v>
+        <v>46059.35671858797</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46084.69005192853</v>
+        <v>46084.69005193287</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46060.48171859822</v>
+        <v>46060.48171859953</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46085.64838526789</v>
+        <v>46085.64838526621</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46066.6483852711</v>
+        <v>46066.64838526621</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46076.39838527414</v>
+        <v>46076.39838527777</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46060.64838527722</v>
+        <v>46060.64838527777</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>46065.44005194696</v>
+        <v>46065.44005194445</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         </is>
       </c>
       <c r="J294" s="2" t="n">
-        <v>46060.64838528349</v>
+        <v>46060.64838527777</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         </is>
       </c>
       <c r="J295" s="2" t="n">
-        <v>46079.39838528657</v>
+        <v>46079.39838528935</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         </is>
       </c>
       <c r="J296" s="2" t="n">
-        <v>46066.64838528957</v>
+        <v>46066.64838528935</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>46079.69005195948</v>
+        <v>46079.69005195601</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="J298" s="2" t="n">
-        <v>46080.39838529602</v>
+        <v>46080.39838530093</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         </is>
       </c>
       <c r="J299" s="2" t="n">
-        <v>46065.69005196598</v>
+        <v>46065.69005196759</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         </is>
       </c>
       <c r="J300" s="2" t="n">
-        <v>46076.44005196912</v>
+        <v>46076.44005196759</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="J301" s="2" t="n">
-        <v>46072.52338530582</v>
+        <v>46072.52338530093</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="J302" s="2" t="n">
-        <v>46077.35671864238</v>
+        <v>46077.35671864583</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         </is>
       </c>
       <c r="J303" s="2" t="n">
-        <v>46061.52338531227</v>
+        <v>46061.5233853125</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         </is>
       </c>
       <c r="J304" s="2" t="n">
-        <v>46063.31505198198</v>
+        <v>46063.31505197917</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         </is>
       </c>
       <c r="J305" s="2" t="n">
-        <v>46082.39838531856</v>
+        <v>46082.39838532407</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="J306" s="2" t="n">
-        <v>46067.44005198838</v>
+        <v>46067.44005199074</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         </is>
       </c>
       <c r="J307" s="2" t="n">
-        <v>46082.44005199157</v>
+        <v>46082.44005199074</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="J308" s="2" t="n">
-        <v>46066.52338532791</v>
+        <v>46066.52338532407</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="J309" s="2" t="n">
-        <v>46087.5233853313</v>
+        <v>46087.52338533565</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         </is>
       </c>
       <c r="J310" s="2" t="n">
-        <v>46071.52338533432</v>
+        <v>46071.52338533565</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="J311" s="2" t="n">
-        <v>46077.31505200435</v>
+        <v>46077.31505200231</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         </is>
       </c>
       <c r="J312" s="2" t="n">
-        <v>46067.35671867416</v>
+        <v>46067.35671866898</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="J313" s="2" t="n">
-        <v>46059.39838534386</v>
+        <v>46059.39838534722</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         </is>
       </c>
       <c r="J314" s="2" t="n">
-        <v>46083.35671868041</v>
+        <v>46083.35671868055</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="J315" s="2" t="n">
-        <v>46067.64838535023</v>
+        <v>46067.64838534722</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         </is>
       </c>
       <c r="J316" s="2" t="n">
-        <v>46085.44005202025</v>
+        <v>46085.44005202546</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
@@ -16597,7 +16597,7 @@
         </is>
       </c>
       <c r="J317" s="2" t="n">
-        <v>46073.4400520234</v>
+        <v>46073.44005202546</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         </is>
       </c>
       <c r="J318" s="2" t="n">
-        <v>46067.69005202639</v>
+        <v>46067.69005202546</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
@@ -16699,7 +16699,7 @@
         </is>
       </c>
       <c r="J319" s="2" t="n">
-        <v>46084.48171869614</v>
+        <v>46084.48171869213</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         </is>
       </c>
       <c r="J320" s="2" t="n">
-        <v>46081.3150520327</v>
+        <v>46081.31505203704</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         </is>
       </c>
       <c r="J321" s="2" t="n">
-        <v>46086.39838536912</v>
+        <v>46086.39838537037</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="J322" s="2" t="n">
-        <v>46073.48171870553</v>
+        <v>46073.4817187037</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         </is>
       </c>
       <c r="J323" s="2" t="n">
-        <v>46064.6067187087</v>
+        <v>46064.6067187037</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         </is>
       </c>
       <c r="J324" s="2" t="n">
-        <v>46078.44005204521</v>
+        <v>46078.44005204861</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         </is>
       </c>
       <c r="J325" s="2" t="n">
-        <v>46084.69005204837</v>
+        <v>46084.69005204861</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         </is>
       </c>
       <c r="J326" s="2" t="n">
-        <v>46068.56505205158</v>
+        <v>46068.56505204861</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         </is>
       </c>
       <c r="J327" s="2" t="n">
-        <v>46079.60671872141</v>
+        <v>46079.60671872685</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         </is>
       </c>
       <c r="J328" s="2" t="n">
-        <v>46085.35671872459</v>
+        <v>46085.35671872685</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="J329" s="2" t="n">
-        <v>46064.48171872769</v>
+        <v>46064.48171872685</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         </is>
       </c>
       <c r="J330" s="2" t="n">
-        <v>46088.35671873064</v>
+        <v>46088.35671872685</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="J331" s="2" t="n">
-        <v>46069.4400520673</v>
+        <v>46069.44005207176</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         </is>
       </c>
       <c r="J332" s="2" t="n">
-        <v>46062.64838540367</v>
+        <v>46062.64838540509</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="J333" s="2" t="n">
-        <v>46072.60671874005</v>
+        <v>46072.60671873843</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         </is>
       </c>
       <c r="J334" s="2" t="n">
-        <v>46082.35671874339</v>
+        <v>46082.35671873843</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         </is>
       </c>
       <c r="J335" s="2" t="n">
-        <v>46077.60671874648</v>
+        <v>46077.60671875</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="J336" s="2" t="n">
-        <v>46079.52338541641</v>
+        <v>46079.52338541667</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
@@ -17617,7 +17617,7 @@
         </is>
       </c>
       <c r="J337" s="2" t="n">
-        <v>46065.69005208611</v>
+        <v>46065.69005208334</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="J338" s="2" t="n">
-        <v>46066.69005208947</v>
+        <v>46066.69005209491</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         </is>
       </c>
       <c r="J339" s="2" t="n">
-        <v>46084.60671875925</v>
+        <v>46084.60671876158</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         </is>
       </c>
       <c r="J340" s="2" t="n">
-        <v>46079.3567187623</v>
+        <v>46079.35671876158</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="J341" s="2" t="n">
-        <v>46069.64838543216</v>
+        <v>46069.64838542824</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="J342" s="2" t="n">
-        <v>46085.69005210217</v>
+        <v>46085.69005210648</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="J343" s="2" t="n">
-        <v>46072.35671877191</v>
+        <v>46072.35671877315</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="J344" s="2" t="n">
-        <v>46069.64838544155</v>
+        <v>46069.64838543982</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         </is>
       </c>
       <c r="J345" s="2" t="n">
-        <v>46079.60671877823</v>
+        <v>46079.60671877315</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="J346" s="2" t="n">
-        <v>46088.35671878131</v>
+        <v>46088.35671878472</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         </is>
       </c>
       <c r="J347" s="2" t="n">
-        <v>46059.52338545102</v>
+        <v>46059.52338545139</v>
       </c>
       <c r="K347" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="J348" s="2" t="n">
-        <v>46087.56505212089</v>
+        <v>46087.56505211806</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         </is>
       </c>
       <c r="J349" s="2" t="n">
-        <v>46073.48171879235</v>
+        <v>46073.4817187963</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="J350" s="2" t="n">
-        <v>46084.35671879557</v>
+        <v>46084.3567187963</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="J351" s="2" t="n">
-        <v>46062.56505213195</v>
+        <v>46062.56505212963</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         </is>
       </c>
       <c r="J352" s="2" t="n">
-        <v>46077.6483854686</v>
+        <v>46077.64838546296</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="J353" s="2" t="n">
-        <v>46082.35671880504</v>
+        <v>46082.35671880787</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         </is>
       </c>
       <c r="J354" s="2" t="n">
-        <v>46075.69005214142</v>
+        <v>46075.6900521412</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="J355" s="2" t="n">
-        <v>46078.44005214469</v>
+        <v>46078.4400521412</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         </is>
       </c>
       <c r="J356" s="2" t="n">
-        <v>46071.69005214786</v>
+        <v>46071.69005215278</v>
       </c>
       <c r="K356" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="J357" s="2" t="n">
-        <v>46077.565052151</v>
+        <v>46077.56505215278</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
@@ -18688,7 +18688,7 @@
         </is>
       </c>
       <c r="J358" s="2" t="n">
-        <v>46063.39838548753</v>
+        <v>46063.39838548611</v>
       </c>
       <c r="K358" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="J359" s="2" t="n">
-        <v>46063.64838549082</v>
+        <v>46063.64838548611</v>
       </c>
       <c r="K359" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         </is>
       </c>
       <c r="J360" s="2" t="n">
-        <v>46063.60671882732</v>
+        <v>46063.60671883102</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         </is>
       </c>
       <c r="J361" s="2" t="n">
-        <v>46083.35671883036</v>
+        <v>46083.35671883102</v>
       </c>
       <c r="K361" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         </is>
       </c>
       <c r="J362" s="2" t="n">
-        <v>46075.39838550008</v>
+        <v>46075.39838549768</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         </is>
       </c>
       <c r="J363" s="2" t="n">
-        <v>46066.69005217002</v>
+        <v>46066.69005216435</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         </is>
       </c>
       <c r="J364" s="2" t="n">
-        <v>46067.35671883974</v>
+        <v>46067.3567188426</v>
       </c>
       <c r="K364" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="J365" s="2" t="n">
-        <v>46070.69005217619</v>
+        <v>46070.69005217592</v>
       </c>
       <c r="K365" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="J366" s="2" t="n">
-        <v>46080.52338551251</v>
+        <v>46080.52338550926</v>
       </c>
       <c r="K366" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         </is>
       </c>
       <c r="J367" s="2" t="n">
-        <v>46070.64838551587</v>
+        <v>46070.64838552084</v>
       </c>
       <c r="K367" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         </is>
       </c>
       <c r="J368" s="2" t="n">
-        <v>46064.60671885221</v>
+        <v>46064.60671885416</v>
       </c>
       <c r="K368" t="inlineStr">
         <is>
@@ -19249,7 +19249,7 @@
         </is>
       </c>
       <c r="J369" s="2" t="n">
-        <v>46065.44005218855</v>
+        <v>46065.4400521875</v>
       </c>
       <c r="K369" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="J370" s="2" t="n">
-        <v>46068.4817188583</v>
+        <v>46068.48171885416</v>
       </c>
       <c r="K370" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         </is>
       </c>
       <c r="J371" s="2" t="n">
-        <v>46072.56505219479</v>
+        <v>46072.56505219908</v>
       </c>
       <c r="K371" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         </is>
       </c>
       <c r="J372" s="2" t="n">
-        <v>46070.31505219794</v>
+        <v>46070.31505219908</v>
       </c>
       <c r="K372" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         </is>
       </c>
       <c r="J373" s="2" t="n">
-        <v>46061.69005220095</v>
+        <v>46061.69005219908</v>
       </c>
       <c r="K373" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         </is>
       </c>
       <c r="J374" s="2" t="n">
-        <v>46077.48171887077</v>
+        <v>46077.48171886574</v>
       </c>
       <c r="K374" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         </is>
       </c>
       <c r="J375" s="2" t="n">
-        <v>46088.48171887387</v>
+        <v>46088.48171887732</v>
       </c>
       <c r="K375" t="inlineStr">
         <is>
@@ -19606,7 +19606,7 @@
         </is>
       </c>
       <c r="J376" s="2" t="n">
-        <v>46081.35671887702</v>
+        <v>46081.35671887732</v>
       </c>
       <c r="K376" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="J377" s="2" t="n">
-        <v>46076.64838554677</v>
+        <v>46076.64838554398</v>
       </c>
       <c r="K377" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         </is>
       </c>
       <c r="J378" s="2" t="n">
-        <v>46069.31505221671</v>
+        <v>46069.31505222222</v>
       </c>
       <c r="K378" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         </is>
       </c>
       <c r="J379" s="2" t="n">
-        <v>46075.60671888647</v>
+        <v>46075.60671888889</v>
       </c>
       <c r="K379" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         </is>
       </c>
       <c r="J380" s="2" t="n">
-        <v>46065.60671888952</v>
+        <v>46065.60671888889</v>
       </c>
       <c r="K380" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         </is>
       </c>
       <c r="J381" s="2" t="n">
-        <v>46067.39838555941</v>
+        <v>46067.39838555556</v>
       </c>
       <c r="K381" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         </is>
       </c>
       <c r="J382" s="2" t="n">
-        <v>46072.31505222939</v>
+        <v>46072.3150522338</v>
       </c>
       <c r="K382" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="J383" s="2" t="n">
-        <v>46061.69005223254</v>
+        <v>46061.6900522338</v>
       </c>
       <c r="K383" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         </is>
       </c>
       <c r="J384" s="2" t="n">
-        <v>46069.64838556896</v>
+        <v>46069.64838556713</v>
       </c>
       <c r="K384" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="J385" s="2" t="n">
-        <v>46075.39838557212</v>
+        <v>46075.39838556713</v>
       </c>
       <c r="K385" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         </is>
       </c>
       <c r="J386" s="2" t="n">
-        <v>46066.48171890849</v>
+        <v>46066.48171891204</v>
       </c>
       <c r="K386" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         </is>
       </c>
       <c r="J387" s="2" t="n">
-        <v>46075.52338557821</v>
+        <v>46075.5233855787</v>
       </c>
       <c r="K387" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         </is>
       </c>
       <c r="J388" s="2" t="n">
-        <v>46078.44005224798</v>
+        <v>46078.44005224537</v>
       </c>
       <c r="K388" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         </is>
       </c>
       <c r="J389" s="2" t="n">
-        <v>46076.35671891791</v>
+        <v>46076.35671892361</v>
       </c>
       <c r="K389" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         </is>
       </c>
       <c r="J390" s="2" t="n">
-        <v>46060.31505225433</v>
+        <v>46060.31505225694</v>
       </c>
       <c r="K390" t="inlineStr">
         <is>
@@ -20371,7 +20371,7 @@
         </is>
       </c>
       <c r="J391" s="2" t="n">
-        <v>46073.44005225735</v>
+        <v>46073.44005225694</v>
       </c>
       <c r="K391" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="J392" s="2" t="n">
-        <v>46074.56505226042</v>
+        <v>46074.56505225694</v>
       </c>
       <c r="K392" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         </is>
       </c>
       <c r="J393" s="2" t="n">
-        <v>46063.35671893037</v>
+        <v>46063.35671893518</v>
       </c>
       <c r="K393" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         </is>
       </c>
       <c r="J394" s="2" t="n">
-        <v>46061.39838560009</v>
+        <v>46061.39838560185</v>
       </c>
       <c r="K394" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         </is>
       </c>
       <c r="J395" s="2" t="n">
-        <v>46069.44005226994</v>
+        <v>46069.44005226852</v>
       </c>
       <c r="K395" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         </is>
       </c>
       <c r="J396" s="2" t="n">
-        <v>46070.5650522729</v>
+        <v>46070.56505226852</v>
       </c>
       <c r="K396" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         </is>
       </c>
       <c r="J397" s="2" t="n">
-        <v>46061.44005227617</v>
+        <v>46061.44005228009</v>
       </c>
       <c r="K397" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         </is>
       </c>
       <c r="J398" s="2" t="n">
-        <v>46069.69005227931</v>
+        <v>46069.69005228009</v>
       </c>
       <c r="K398" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         </is>
       </c>
       <c r="J399" s="2" t="n">
-        <v>46070.69005228236</v>
+        <v>46070.69005228009</v>
       </c>
       <c r="K399" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         </is>
       </c>
       <c r="J400" s="2" t="n">
-        <v>46077.6483856189</v>
+        <v>46077.64838561343</v>
       </c>
       <c r="K400" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         </is>
       </c>
       <c r="J401" s="2" t="n">
-        <v>46059.69005228868</v>
+        <v>46059.69005229167</v>
       </c>
       <c r="K401" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         </is>
       </c>
       <c r="J402" s="2" t="n">
-        <v>46082.48171895839</v>
+        <v>46082.48171895833</v>
       </c>
       <c r="K402" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="J403" s="2" t="n">
-        <v>46061.44005229475</v>
+        <v>46061.44005229167</v>
       </c>
       <c r="K403" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         </is>
       </c>
       <c r="J404" s="2" t="n">
-        <v>46073.52338563131</v>
+        <v>46073.52338563657</v>
       </c>
       <c r="K404" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         </is>
       </c>
       <c r="J405" s="2" t="n">
-        <v>46084.64838563434</v>
+        <v>46084.64838563657</v>
       </c>
       <c r="K405" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         </is>
       </c>
       <c r="J406" s="2" t="n">
-        <v>46059.31505230413</v>
+        <v>46059.31505230324</v>
       </c>
       <c r="K406" t="inlineStr">
         <is>
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="J407" s="2" t="n">
-        <v>46075.48171897395</v>
+        <v>46075.48171896991</v>
       </c>
       <c r="K407" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="J408" s="2" t="n">
-        <v>46084.52338564388</v>
+        <v>46084.52338564815</v>
       </c>
       <c r="K408" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         </is>
       </c>
       <c r="J409" s="2" t="n">
-        <v>46065.56505231384</v>
+        <v>46065.56505231481</v>
       </c>
       <c r="K409" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         </is>
       </c>
       <c r="J410" s="2" t="n">
-        <v>46088.44005231684</v>
+        <v>46088.44005231481</v>
       </c>
       <c r="K410" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         </is>
       </c>
       <c r="J411" s="2" t="n">
-        <v>46060.6900523201</v>
+        <v>46060.69005231481</v>
       </c>
       <c r="K411" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         </is>
       </c>
       <c r="J412" s="2" t="n">
-        <v>46087.4817189898</v>
+        <v>46087.48171899305</v>
       </c>
       <c r="K412" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         </is>
       </c>
       <c r="J413" s="2" t="n">
-        <v>46078.39838565941</v>
+        <v>46078.39838565972</v>
       </c>
       <c r="K413" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         </is>
       </c>
       <c r="J414" s="2" t="n">
-        <v>46068.35671899595</v>
+        <v>46068.35671899305</v>
       </c>
       <c r="K414" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         </is>
       </c>
       <c r="J415" s="2" t="n">
-        <v>46061.39838566577</v>
+        <v>46061.39838567129</v>
       </c>
       <c r="K415" t="inlineStr">
         <is>
@@ -21646,7 +21646,7 @@
         </is>
       </c>
       <c r="J416" s="2" t="n">
-        <v>46063.69005233551</v>
+        <v>46063.69005233797</v>
       </c>
       <c r="K416" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         </is>
       </c>
       <c r="J417" s="2" t="n">
-        <v>46088.56505233864</v>
+        <v>46088.56505233797</v>
       </c>
       <c r="K417" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         </is>
       </c>
       <c r="J418" s="2" t="n">
-        <v>46068.48171900912</v>
+        <v>46068.48171900463</v>
       </c>
       <c r="K418" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         </is>
       </c>
       <c r="J419" s="2" t="n">
-        <v>46085.52338567901</v>
+        <v>46085.52338568287</v>
       </c>
       <c r="K419" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         </is>
       </c>
       <c r="J420" s="2" t="n">
-        <v>46063.31505234868</v>
+        <v>46063.31505234954</v>
       </c>
       <c r="K420" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         </is>
       </c>
       <c r="J421" s="2" t="n">
-        <v>46067.44005235183</v>
+        <v>46067.44005234954</v>
       </c>
       <c r="K421" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         </is>
       </c>
       <c r="J422" s="2" t="n">
-        <v>46076.39838568861</v>
+        <v>46076.39838568287</v>
       </c>
       <c r="K422" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         </is>
       </c>
       <c r="J423" s="2" t="n">
-        <v>46064.39838569181</v>
+        <v>46064.39838569445</v>
       </c>
       <c r="K423" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         </is>
       </c>
       <c r="J424" s="2" t="n">
-        <v>46080.64838569484</v>
+        <v>46080.64838569445</v>
       </c>
       <c r="K424" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         </is>
       </c>
       <c r="J425" s="2" t="n">
-        <v>46074.64838569798</v>
+        <v>46074.64838569445</v>
       </c>
       <c r="K425" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         </is>
       </c>
       <c r="J426" s="2" t="n">
-        <v>46082.56505236874</v>
+        <v>46082.56505237269</v>
       </c>
       <c r="K426" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         </is>
       </c>
       <c r="J427" s="2" t="n">
-        <v>46072.64838570528</v>
+        <v>46072.64838570602</v>
       </c>
       <c r="K427" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         </is>
       </c>
       <c r="J428" s="2" t="n">
-        <v>46088.31505237504</v>
+        <v>46088.31505237269</v>
       </c>
       <c r="K428" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         </is>
       </c>
       <c r="J429" s="2" t="n">
-        <v>46077.44005237826</v>
+        <v>46077.44005237269</v>
       </c>
       <c r="K429" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         </is>
       </c>
       <c r="J430" s="2" t="n">
-        <v>46072.481719048</v>
+        <v>46072.48171905093</v>
       </c>
       <c r="K430" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="J431" s="2" t="n">
-        <v>46088.64838571779</v>
+        <v>46088.64838571759</v>
       </c>
       <c r="K431" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         </is>
       </c>
       <c r="J432" s="2" t="n">
-        <v>46066.52338572087</v>
+        <v>46066.52338571759</v>
       </c>
       <c r="K432" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         </is>
       </c>
       <c r="J433" s="2" t="n">
-        <v>46075.4400523908</v>
+        <v>46075.44005239583</v>
       </c>
       <c r="K433" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         </is>
       </c>
       <c r="J434" s="2" t="n">
-        <v>46069.39838572729</v>
+        <v>46069.39838572917</v>
       </c>
       <c r="K434" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         </is>
       </c>
       <c r="J435" s="2" t="n">
-        <v>46066.31505239695</v>
+        <v>46066.31505239583</v>
       </c>
       <c r="K435" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         </is>
       </c>
       <c r="J436" s="2" t="n">
-        <v>46078.35671906667</v>
+        <v>46078.3567190625</v>
       </c>
       <c r="K436" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="J437" s="2" t="n">
-        <v>46064.35671906998</v>
+        <v>46064.35671907407</v>
       </c>
       <c r="K437" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         </is>
       </c>
       <c r="J438" s="2" t="n">
-        <v>46082.39838573973</v>
+        <v>46082.39838574074</v>
       </c>
       <c r="K438" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         </is>
       </c>
       <c r="J439" s="2" t="n">
-        <v>46071.31505240937</v>
+        <v>46071.31505240741</v>
       </c>
       <c r="K439" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         </is>
       </c>
       <c r="J440" s="2" t="n">
-        <v>46062.56505241268</v>
+        <v>46062.56505240741</v>
       </c>
       <c r="K440" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         </is>
       </c>
       <c r="J441" s="2" t="n">
-        <v>46088.60671908261</v>
+        <v>46088.60671908565</v>
       </c>
       <c r="K441" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         </is>
       </c>
       <c r="J442" s="2" t="n">
-        <v>46087.64838575255</v>
+        <v>46087.64838575231</v>
       </c>
       <c r="K442" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         </is>
       </c>
       <c r="J443" s="2" t="n">
-        <v>46076.69005242221</v>
+        <v>46076.69005241898</v>
       </c>
       <c r="K443" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         </is>
       </c>
       <c r="J444" s="2" t="n">
-        <v>46071.48171909206</v>
+        <v>46071.48171909722</v>
       </c>
       <c r="K444" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         </is>
       </c>
       <c r="J445" s="2" t="n">
-        <v>46073.52338576193</v>
+        <v>46073.52338576389</v>
       </c>
       <c r="K445" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="J446" s="2" t="n">
-        <v>46088.69005243176</v>
+        <v>46088.69005243055</v>
       </c>
       <c r="K446" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         </is>
       </c>
       <c r="J447" s="2" t="n">
-        <v>46079.64838576828</v>
+        <v>46079.64838576389</v>
       </c>
       <c r="K447" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         </is>
       </c>
       <c r="J448" s="2" t="n">
-        <v>46068.48171910484</v>
+        <v>46068.48171910879</v>
       </c>
       <c r="K448" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         </is>
       </c>
       <c r="J449" s="2" t="n">
-        <v>46071.35671910786</v>
+        <v>46071.35671910879</v>
       </c>
       <c r="K449" t="inlineStr">
         <is>
@@ -23380,7 +23380,7 @@
         </is>
       </c>
       <c r="J450" s="2" t="n">
-        <v>46083.31505244436</v>
+        <v>46083.31505244213</v>
       </c>
       <c r="K450" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         </is>
       </c>
       <c r="J451" s="2" t="n">
-        <v>46084.39838578107</v>
+        <v>46084.39838577546</v>
       </c>
       <c r="K451" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         </is>
       </c>
       <c r="J452" s="2" t="n">
-        <v>46068.48171911743</v>
+        <v>46068.48171912037</v>
       </c>
       <c r="K452" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         </is>
       </c>
       <c r="J453" s="2" t="n">
-        <v>46077.4817191205</v>
+        <v>46077.48171912037</v>
       </c>
       <c r="K453" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         </is>
       </c>
       <c r="J454" s="2" t="n">
-        <v>46085.60671912351</v>
+        <v>46085.60671912037</v>
       </c>
       <c r="K454" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="J455" s="2" t="n">
-        <v>46065.60671912671</v>
+        <v>46065.60671913195</v>
       </c>
       <c r="K455" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         </is>
       </c>
       <c r="J456" s="2" t="n">
-        <v>46075.64838579653</v>
+        <v>46075.64838579861</v>
       </c>
       <c r="K456" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         </is>
       </c>
       <c r="J457" s="2" t="n">
-        <v>46065.39838579959</v>
+        <v>46065.39838579861</v>
       </c>
       <c r="K457" t="inlineStr">
         <is>
@@ -23788,7 +23788,7 @@
         </is>
       </c>
       <c r="J458" s="2" t="n">
-        <v>46083.4400524693</v>
+        <v>46083.44005246528</v>
       </c>
       <c r="K458" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         </is>
       </c>
       <c r="J459" s="2" t="n">
-        <v>46075.35671913916</v>
+        <v>46075.35671914352</v>
       </c>
       <c r="K459" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         </is>
       </c>
       <c r="J460" s="2" t="n">
-        <v>46087.60671914237</v>
+        <v>46087.60671914352</v>
       </c>
       <c r="K460" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         </is>
       </c>
       <c r="J461" s="2" t="n">
-        <v>46081.52338581206</v>
+        <v>46081.52338581019</v>
       </c>
       <c r="K461" t="inlineStr">
         <is>
@@ -23992,7 +23992,7 @@
         </is>
       </c>
       <c r="J462" s="2" t="n">
-        <v>46081.31505248192</v>
+        <v>46081.31505247685</v>
       </c>
       <c r="K462" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         </is>
       </c>
       <c r="J463" s="2" t="n">
-        <v>46072.44005248515</v>
+        <v>46072.44005248843</v>
       </c>
       <c r="K463" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         </is>
       </c>
       <c r="J464" s="2" t="n">
-        <v>46078.44005248827</v>
+        <v>46078.44005248843</v>
       </c>
       <c r="K464" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         </is>
       </c>
       <c r="J465" s="2" t="n">
-        <v>46075.39838582482</v>
+        <v>46075.39838582176</v>
       </c>
       <c r="K465" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         </is>
       </c>
       <c r="J466" s="2" t="n">
-        <v>46078.56505249478</v>
+        <v>46078.5650525</v>
       </c>
       <c r="K466" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         </is>
       </c>
       <c r="J467" s="2" t="n">
-        <v>46074.31505249801</v>
+        <v>46074.3150525</v>
       </c>
       <c r="K467" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="J468" s="2" t="n">
-        <v>46063.60671916771</v>
+        <v>46063.60671916667</v>
       </c>
       <c r="K468" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         </is>
       </c>
       <c r="J469" s="2" t="n">
-        <v>46073.35671917084</v>
+        <v>46073.35671916667</v>
       </c>
       <c r="K469" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="J470" s="2" t="n">
-        <v>46072.56505250739</v>
+        <v>46072.56505251157</v>
       </c>
       <c r="K470" t="inlineStr">
         <is>
@@ -24451,7 +24451,7 @@
         </is>
       </c>
       <c r="J471" s="2" t="n">
-        <v>46082.56505251038</v>
+        <v>46082.56505251157</v>
       </c>
       <c r="K471" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         </is>
       </c>
       <c r="J472" s="2" t="n">
-        <v>46073.60671918014</v>
+        <v>46073.60671917824</v>
       </c>
       <c r="K472" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         </is>
       </c>
       <c r="J473" s="2" t="n">
-        <v>46087.56505251662</v>
+        <v>46087.56505251157</v>
       </c>
       <c r="K473" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         </is>
       </c>
       <c r="J474" s="2" t="n">
-        <v>46062.60671918631</v>
+        <v>46062.60671918982</v>
       </c>
       <c r="K474" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         </is>
       </c>
       <c r="J475" s="2" t="n">
-        <v>46065.64838585602</v>
+        <v>46065.64838585648</v>
       </c>
       <c r="K475" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         </is>
       </c>
       <c r="J476" s="2" t="n">
-        <v>46077.69005252587</v>
+        <v>46077.69005252315</v>
       </c>
       <c r="K476" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         </is>
       </c>
       <c r="J477" s="2" t="n">
-        <v>46086.52338586249</v>
+        <v>46086.52338586806</v>
       </c>
       <c r="K477" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         </is>
       </c>
       <c r="J478" s="2" t="n">
-        <v>46065.6483858655</v>
+        <v>46065.64838586806</v>
       </c>
       <c r="K478" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         </is>
       </c>
       <c r="J479" s="2" t="n">
-        <v>46074.3150525353</v>
+        <v>46074.31505253472</v>
       </c>
       <c r="K479" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         </is>
       </c>
       <c r="J480" s="2" t="n">
-        <v>46081.35671920499</v>
+        <v>46081.35671920139</v>
       </c>
       <c r="K480" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         </is>
       </c>
       <c r="J481" s="2" t="n">
-        <v>46066.64838587499</v>
+        <v>46066.64838587963</v>
       </c>
       <c r="K481" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         </is>
       </c>
       <c r="J482" s="2" t="n">
-        <v>46078.44005254489</v>
+        <v>46078.4400525463</v>
       </c>
       <c r="K482" t="inlineStr">
         <is>
@@ -25063,7 +25063,7 @@
         </is>
       </c>
       <c r="J483" s="2" t="n">
-        <v>46083.56505254797</v>
+        <v>46083.5650525463</v>
       </c>
       <c r="K483" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="J484" s="2" t="n">
-        <v>46078.3983858845</v>
+        <v>46078.39838587963</v>
       </c>
       <c r="K484" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         </is>
       </c>
       <c r="J485" s="2" t="n">
-        <v>46088.52338588757</v>
+        <v>46088.5233858912</v>
       </c>
       <c r="K485" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         </is>
       </c>
       <c r="J486" s="2" t="n">
-        <v>46073.69005255728</v>
+        <v>46073.69005255787</v>
       </c>
       <c r="K486" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         </is>
       </c>
       <c r="J487" s="2" t="n">
-        <v>46087.39838589379</v>
+        <v>46087.3983858912</v>
       </c>
       <c r="K487" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         </is>
       </c>
       <c r="J488" s="2" t="n">
-        <v>46065.39838589696</v>
+        <v>46065.3983858912</v>
       </c>
       <c r="K488" t="inlineStr">
         <is>
@@ -25369,7 +25369,7 @@
         </is>
       </c>
       <c r="J489" s="2" t="n">
-        <v>46063.31505256666</v>
+        <v>46063.31505256944</v>
       </c>
       <c r="K489" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         </is>
       </c>
       <c r="J490" s="2" t="n">
-        <v>46085.52338590302</v>
+        <v>46085.52338590278</v>
       </c>
       <c r="K490" t="inlineStr">
         <is>
@@ -25471,7 +25471,7 @@
         </is>
       </c>
       <c r="J491" s="2" t="n">
-        <v>46083.48171923935</v>
+        <v>46083.48171923611</v>
       </c>
       <c r="K491" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="J492" s="2" t="n">
-        <v>46073.44005257603</v>
+        <v>46073.44005258102</v>
       </c>
       <c r="K492" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         </is>
       </c>
       <c r="J493" s="2" t="n">
-        <v>46085.39838591238</v>
+        <v>46085.39838591436</v>
       </c>
       <c r="K493" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         </is>
       </c>
       <c r="J494" s="2" t="n">
-        <v>46079.64838591542</v>
+        <v>46079.64838591436</v>
       </c>
       <c r="K494" t="inlineStr">
         <is>
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="J495" s="2" t="n">
-        <v>46066.44005258521</v>
+        <v>46066.44005258102</v>
       </c>
       <c r="K495" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         </is>
       </c>
       <c r="J496" s="2" t="n">
-        <v>46084.60671925507</v>
+        <v>46084.60671925926</v>
       </c>
       <c r="K496" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         </is>
       </c>
       <c r="J497" s="2" t="n">
-        <v>46086.44005259145</v>
+        <v>46086.4400525926</v>
       </c>
       <c r="K497" t="inlineStr">
         <is>
@@ -25828,7 +25828,7 @@
         </is>
       </c>
       <c r="J498" s="2" t="n">
-        <v>46070.44005259447</v>
+        <v>46070.4400525926</v>
       </c>
       <c r="K498" t="inlineStr">
         <is>
@@ -25879,7 +25879,7 @@
         </is>
       </c>
       <c r="J499" s="2" t="n">
-        <v>46086.56505259766</v>
+        <v>46086.5650525926</v>
       </c>
       <c r="K499" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         </is>
       </c>
       <c r="J500" s="2" t="n">
-        <v>46062.48171926735</v>
+        <v>46062.48171927084</v>
       </c>
       <c r="K500" t="inlineStr">
         <is>
@@ -25981,9 +25981,2559 @@
         </is>
       </c>
       <c r="J501" s="2" t="n">
-        <v>46067.44005260373</v>
+        <v>46067.44005260416</v>
       </c>
       <c r="K501" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>eed1cb24-b5d0-4535-bccc-c8ddfe5080fd</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>b08c82bb-4677-4021-8bab-7788d0a276c8</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F502" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>OP-625</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J502" s="2" t="n">
+        <v>46087.53937713445</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>fa882b53-93a5-47a7-b96f-c5ac694deee9</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>30b0cfb4-420c-4cd9-9570-0a8fe1893aef</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F503" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>OP-437</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J503" s="2" t="n">
+        <v>46088.4560438054</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>59a5ea85-6eb8-4bfa-b1df-9671baa64636</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>536c7b76-0b35-47fe-8090-e94300839e5d</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F504" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>OP-762</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J504" s="2" t="n">
+        <v>46064.33104380868</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>9aee12ca-1e9a-4c1d-9a7b-648891d3c248</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>9ea37706-10e4-4525-b363-9770dde6d763</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>OP-564</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J505" s="2" t="n">
+        <v>46065.49771047864</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>02f3c877-d538-41f7-b032-04ec63a47a01</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>1c8ecd1c-d0bb-4630-a2e4-2655f6bdaca3</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F506" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>OP-998</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J506" s="2" t="n">
+        <v>46070.66437714858</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>c9879b0e-0fbc-41ad-9f74-9137054413ed</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>47faa697-70a8-413d-abe3-16d329f90f21</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>OP-117</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J507" s="2" t="n">
+        <v>46059.53937715171</v>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>b9c655a9-3d36-4840-ab2f-54a6c948b8f9</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>acc5d158-3c79-45e9-859f-592a1dee32c3</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>OP-735</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J508" s="2" t="n">
+        <v>46070.53937715492</v>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>18688f79-b7f0-4873-a3da-053071981728</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>61cf9ef7-621e-42d9-8fd9-dcfdf569ac33</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>OP-803</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J509" s="2" t="n">
+        <v>46061.33104382484</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>c0107392-392a-4045-ad6f-1202e5140f97</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>aebbfc87-2e57-4bd8-8b84-8d979a122de3</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>OP-353</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J510" s="2" t="n">
+        <v>46088.41437716169</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>c80c0e23-b760-4296-add2-eec088b2914a</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>caf94a38-e5b1-4a09-ad6a-263e2bdfb05d</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>OP-547</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J511" s="2" t="n">
+        <v>46081.49771049835</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>c45aaf36-115c-45f1-bd28-1a5941f79713</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>9aabe525-6ec2-4c92-b084-1be588dfa603</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>OP-732</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J512" s="2" t="n">
+        <v>46065.4143771681</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>e237ca67-c976-458e-8b57-dede545703aa</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>e342557d-a276-4f10-955b-ec102abce62b</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>OP-298</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J513" s="2" t="n">
+        <v>46085.70604383809</v>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>e69d745e-1861-45ea-a74e-aa73704a6844</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>45edb267-a2bd-4af4-998f-c10c8084c51d</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F514" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>OP-343</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J514" s="2" t="n">
+        <v>46067.37271050802</v>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>b4c3769e-600a-4977-a962-6f3ea19ec352</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2bd70b43-a67f-4fb4-9462-f7266685bf22</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F515" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>OP-126</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J515" s="2" t="n">
+        <v>46088.58104384453</v>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>292514ff-e689-41f3-9572-fd4652383729</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>8df11d50-da85-471b-92ef-0e551f2a2ae9</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F516" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>OP-947</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J516" s="2" t="n">
+        <v>46076.62271051436</v>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>0ae64cde-9487-4e7a-bd2a-5895378bc8d0</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>595d25cd-8e49-4b59-bb7f-535414497cdf</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F517" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>OP-270</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J517" s="2" t="n">
+        <v>46075.37271051761</v>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>3f6e03ab-a7fe-4e1d-9bdd-87a9e42d7391</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>802ce0b6-6807-430d-8d5f-2f61d3e51bb1</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F518" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>OP-988</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J518" s="2" t="n">
+        <v>46066.41437718735</v>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>bd5dd7a6-09e0-446f-89b6-34068afe7075</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>6bd4d6f9-d830-4412-be07-f12d9656d121</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F519" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>OP-405</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J519" s="2" t="n">
+        <v>46067.53937719043</v>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>d4f5096a-488d-4347-845e-202218c8435f</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>ba9b0064-d2c9-4366-88ea-6ee7f5f70bb0</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F520" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>OP-109</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J520" s="2" t="n">
+        <v>46059.33104386034</v>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>0d9b2a58-5f4f-4628-a679-92b14d35e76b</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>85e55dc1-c799-4492-8a6a-fe9bd72323b1</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F521" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>OP-280</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J521" s="2" t="n">
+        <v>46064.4560438634</v>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>11da93e7-787e-4f5d-aca1-4992503eff48</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>ee509a87-34e6-493e-8d00-529ef4fd0759</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F522" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>OP-848</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J522" s="2" t="n">
+        <v>46082.62271053311</v>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>3231b005-ac2b-4342-aefb-e9933cebc898</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>ca327c3c-9a1b-41af-b66f-99d9a0d22cbf</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F523" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>OP-746</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J523" s="2" t="n">
+        <v>46076.45604386947</v>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>d3cde178-5262-49a2-af15-864b184141e5</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>f98000d5-f06a-4f64-b173-0a4e45a69242</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>OP-563</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J524" s="2" t="n">
+        <v>46071.53937720609</v>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>0e18357c-7a58-48b2-be01-12d0c45db875</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>a0ec6fe9-ad94-40e0-bf94-9d4ce7d7ebcc</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>OP-270</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J525" s="2" t="n">
+        <v>46077.66437720925</v>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>99bb8211-49eb-4bae-ac7b-cbd8b776b15c</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>526c8661-27be-4a19-9b0d-f1806a1b4929</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>OP-475</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J526" s="2" t="n">
+        <v>46088.66437721228</v>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>e1f63fd8-a341-4043-ad8e-16a430974e73</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>7bb684f9-d4e1-4d65-8b5b-fd5a72597f68</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>OP-328</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J527" s="2" t="n">
+        <v>46085.53937721553</v>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>0107467f-69d4-40c8-b60b-21361eaef6ad</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>a1617060-221e-4ace-863f-814a4f7df61f</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>OP-391</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J528" s="2" t="n">
+        <v>46079.41437721903</v>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>4a69b1c6-f893-4730-b01d-d9547dcb6a55</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>53748711-6386-4b79-a899-33fb7f1790d6</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>OP-670</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J529" s="2" t="n">
+        <v>46084.49771055547</v>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>db6bcd04-2ff8-4c28-a201-6bd95c994478</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>c8bfd8e2-fc2d-4a1d-88dd-6385d1e56223</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>OP-781</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J530" s="2" t="n">
+        <v>46061.37271055861</v>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>0747d30f-7d2f-4e8b-bdcd-6026d1dffcff</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>92093c53-a175-4a9f-a1d3-c47dc1f5f59c</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F531" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>OP-703</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J531" s="2" t="n">
+        <v>46078.66437722873</v>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>5e7ea68c-6929-41f7-ace4-dfbb7886fbeb</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>3f6a66f6-0cc4-4faf-9a9a-a6ca6da5f49e</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F532" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>OP-611</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J532" s="2" t="n">
+        <v>46061.62271056515</v>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>4ad46340-a3ae-4f5e-8779-c53241fddee3</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>6c74d833-67e4-4ba1-9201-e106355fa46a</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F533" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>OP-833</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J533" s="2" t="n">
+        <v>46069.3727105682</v>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>d52bd17e-cc58-4184-b0f4-886d2e12f617</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>847c524c-b2f1-4938-a7f4-8bd5798ed010</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>OP-596</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J534" s="2" t="n">
+        <v>46076.33104390463</v>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>49424790-2fde-4cac-85a6-fcce6e65ab42</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>9774cb84-086c-40db-865b-c976b64475a2</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>OP-992</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J535" s="2" t="n">
+        <v>46071.49771057453</v>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>c2dec9fc-bc7b-4f01-8676-2c9dbe838ee6</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>0d779aa8-c4f0-45da-8844-f567af0f8547</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F536" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>OP-222</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J536" s="2" t="n">
+        <v>46082.70604391103</v>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>3929357a-10bc-4780-b02e-7d71ee163d17</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>726a1bdc-4d06-41fb-a09e-4a3d8c5e7e2d</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>OP-444</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J537" s="2" t="n">
+        <v>46062.33104391408</v>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>3929f10e-431f-429d-9c18-535d6fd059fd</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>908ff0e0-f310-40fe-8b84-bcb2d57ad229</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F538" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>OP-713</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J538" s="2" t="n">
+        <v>46068.41437725046</v>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>7fb8df24-3308-4a2d-9ada-8086cde38285</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>135ff89b-d2fc-4935-9b2e-93553ce79319</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>OP-642</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J539" s="2" t="n">
+        <v>46061.33104392058</v>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>9e9f0586-9ca6-40fa-8bd4-9dbd0f5412a6</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>1e969486-84aa-4a88-b040-ac5139d7e23a</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F540" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>OP-164</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J540" s="2" t="n">
+        <v>46064.33104392376</v>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>f1ce5517-5e8c-4f7f-b9dc-dffba2f18bfd</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>f033f3d2-1684-411f-86ff-0d627471bfc3</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F541" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>OP-222</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J541" s="2" t="n">
+        <v>46073.7060439268</v>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>6c706df7-d3ec-46e5-85ad-10e56a9d671c</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>8a90a5d8-615a-414d-b948-ef092bb3d01f</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>OP-278</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J542" s="2" t="n">
+        <v>46072.53937726333</v>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>ed2e7b62-9589-4aa0-94fc-801d813515de</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>8bc3055e-1d7a-470f-939d-71683953f6c2</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F543" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>OP-903</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J543" s="2" t="n">
+        <v>46078.70604393321</v>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>5b15bebf-ee21-433b-be55-65ad392018a3</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>42c94772-d4d2-48c3-a8ad-338a048d326e</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F544" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>OP-544</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J544" s="2" t="n">
+        <v>46070.4143772696</v>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>5abee073-6424-40f6-92a4-86a375aa3485</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>aa2007bf-5feb-46c8-94fe-bc80c14947be</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F545" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>OP-184</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J545" s="2" t="n">
+        <v>46070.3310439393</v>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>ee2e7917-1d0c-455c-8583-85293af28bd1</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>c4175400-89a6-4a00-83d2-a5b72a96bb72</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>OP-997</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J546" s="2" t="n">
+        <v>46060.66437727593</v>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>a4dc06d5-1415-48df-a63b-2e4eb3bdfaa6</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>01e09385-4abb-4812-b1ea-404f354439d1</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F547" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>OP-614</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J547" s="2" t="n">
+        <v>46071.4977106123</v>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>322bc9ad-e75f-48e1-bc3a-70470bd70f65</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>7fa8ff52-3eee-464e-8f49-19665668962a</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F548" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>OP-999</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J548" s="2" t="n">
+        <v>46080.45604394881</v>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2b24ded7-94b1-475e-8d91-55e83969a1e0</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>c5e5ec90-e2a0-4736-9a78-a7a000a7d918</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F549" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>OP-351</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J549" s="2" t="n">
+        <v>46084.45604395191</v>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>96d94829-927e-4ba3-acf2-ad4b614f1d7a</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>0bb29069-9141-4a52-b71b-a2f6cae240de</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>OP-447</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J550" s="2" t="n">
+        <v>46066.62271062179</v>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>7c3443ad-bdd1-49cd-a537-1134d149c345</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>e79ed416-2b36-485d-b7a8-c2747f1b5ebb</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>OP-134</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J551" s="2" t="n">
+        <v>46061.33104395819</v>
+      </c>
+      <c r="K551" t="inlineStr">
         <is>
           <t>poor</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K551"/>
+  <dimension ref="A1:K601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26032,7 +26032,7 @@
         </is>
       </c>
       <c r="J502" s="2" t="n">
-        <v>46087.53937713445</v>
+        <v>46087.53937712963</v>
       </c>
       <c r="K502" t="inlineStr">
         <is>
@@ -26083,7 +26083,7 @@
         </is>
       </c>
       <c r="J503" s="2" t="n">
-        <v>46088.4560438054</v>
+        <v>46088.45604380787</v>
       </c>
       <c r="K503" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         </is>
       </c>
       <c r="J504" s="2" t="n">
-        <v>46064.33104380868</v>
+        <v>46064.33104380787</v>
       </c>
       <c r="K504" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         </is>
       </c>
       <c r="J505" s="2" t="n">
-        <v>46065.49771047864</v>
+        <v>46065.49771047453</v>
       </c>
       <c r="K505" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         </is>
       </c>
       <c r="J506" s="2" t="n">
-        <v>46070.66437714858</v>
+        <v>46070.66437715277</v>
       </c>
       <c r="K506" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         </is>
       </c>
       <c r="J507" s="2" t="n">
-        <v>46059.53937715171</v>
+        <v>46059.53937715277</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         </is>
       </c>
       <c r="J508" s="2" t="n">
-        <v>46070.53937715492</v>
+        <v>46070.53937715277</v>
       </c>
       <c r="K508" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         </is>
       </c>
       <c r="J509" s="2" t="n">
-        <v>46061.33104382484</v>
+        <v>46061.33104381945</v>
       </c>
       <c r="K509" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         </is>
       </c>
       <c r="J510" s="2" t="n">
-        <v>46088.41437716169</v>
+        <v>46088.41437716435</v>
       </c>
       <c r="K510" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         </is>
       </c>
       <c r="J511" s="2" t="n">
-        <v>46081.49771049835</v>
+        <v>46081.49771049769</v>
       </c>
       <c r="K511" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         </is>
       </c>
       <c r="J512" s="2" t="n">
-        <v>46065.4143771681</v>
+        <v>46065.41437716435</v>
       </c>
       <c r="K512" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         </is>
       </c>
       <c r="J513" s="2" t="n">
-        <v>46085.70604383809</v>
+        <v>46085.70604384259</v>
       </c>
       <c r="K513" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         </is>
       </c>
       <c r="J514" s="2" t="n">
-        <v>46067.37271050802</v>
+        <v>46067.37271050926</v>
       </c>
       <c r="K514" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         </is>
       </c>
       <c r="J515" s="2" t="n">
-        <v>46088.58104384453</v>
+        <v>46088.58104384259</v>
       </c>
       <c r="K515" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         </is>
       </c>
       <c r="J516" s="2" t="n">
-        <v>46076.62271051436</v>
+        <v>46076.62271050926</v>
       </c>
       <c r="K516" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         </is>
       </c>
       <c r="J517" s="2" t="n">
-        <v>46075.37271051761</v>
+        <v>46075.37271052083</v>
       </c>
       <c r="K517" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         </is>
       </c>
       <c r="J518" s="2" t="n">
-        <v>46066.41437718735</v>
+        <v>46066.4143771875</v>
       </c>
       <c r="K518" t="inlineStr">
         <is>
@@ -26899,7 +26899,7 @@
         </is>
       </c>
       <c r="J519" s="2" t="n">
-        <v>46067.53937719043</v>
+        <v>46067.5393771875</v>
       </c>
       <c r="K519" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         </is>
       </c>
       <c r="J520" s="2" t="n">
-        <v>46059.33104386034</v>
+        <v>46059.33104386574</v>
       </c>
       <c r="K520" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         </is>
       </c>
       <c r="J521" s="2" t="n">
-        <v>46064.4560438634</v>
+        <v>46064.45604386574</v>
       </c>
       <c r="K521" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="J522" s="2" t="n">
-        <v>46082.62271053311</v>
+        <v>46082.62271053241</v>
       </c>
       <c r="K522" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         </is>
       </c>
       <c r="J523" s="2" t="n">
-        <v>46076.45604386947</v>
+        <v>46076.45604386574</v>
       </c>
       <c r="K523" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="J524" s="2" t="n">
-        <v>46071.53937720609</v>
+        <v>46071.53937721065</v>
       </c>
       <c r="K524" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         </is>
       </c>
       <c r="J525" s="2" t="n">
-        <v>46077.66437720925</v>
+        <v>46077.66437721065</v>
       </c>
       <c r="K525" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         </is>
       </c>
       <c r="J526" s="2" t="n">
-        <v>46088.66437721228</v>
+        <v>46088.66437721065</v>
       </c>
       <c r="K526" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         </is>
       </c>
       <c r="J527" s="2" t="n">
-        <v>46085.53937721553</v>
+        <v>46085.53937721065</v>
       </c>
       <c r="K527" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         </is>
       </c>
       <c r="J528" s="2" t="n">
-        <v>46079.41437721903</v>
+        <v>46079.41437722222</v>
       </c>
       <c r="K528" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="J529" s="2" t="n">
-        <v>46084.49771055547</v>
+        <v>46084.49771055556</v>
       </c>
       <c r="K529" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         </is>
       </c>
       <c r="J530" s="2" t="n">
-        <v>46061.37271055861</v>
+        <v>46061.37271055556</v>
       </c>
       <c r="K530" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         </is>
       </c>
       <c r="J531" s="2" t="n">
-        <v>46078.66437722873</v>
+        <v>46078.6643772338</v>
       </c>
       <c r="K531" t="inlineStr">
         <is>
@@ -27562,7 +27562,7 @@
         </is>
       </c>
       <c r="J532" s="2" t="n">
-        <v>46061.62271056515</v>
+        <v>46061.62271056713</v>
       </c>
       <c r="K532" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         </is>
       </c>
       <c r="J533" s="2" t="n">
-        <v>46069.3727105682</v>
+        <v>46069.37271056713</v>
       </c>
       <c r="K533" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         </is>
       </c>
       <c r="J534" s="2" t="n">
-        <v>46076.33104390463</v>
+        <v>46076.33104390046</v>
       </c>
       <c r="K534" t="inlineStr">
         <is>
@@ -27715,7 +27715,7 @@
         </is>
       </c>
       <c r="J535" s="2" t="n">
-        <v>46071.49771057453</v>
+        <v>46071.4977105787</v>
       </c>
       <c r="K535" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         </is>
       </c>
       <c r="J536" s="2" t="n">
-        <v>46082.70604391103</v>
+        <v>46082.70604391204</v>
       </c>
       <c r="K536" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         </is>
       </c>
       <c r="J537" s="2" t="n">
-        <v>46062.33104391408</v>
+        <v>46062.33104391204</v>
       </c>
       <c r="K537" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         </is>
       </c>
       <c r="J538" s="2" t="n">
-        <v>46068.41437725046</v>
+        <v>46068.41437724537</v>
       </c>
       <c r="K538" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         </is>
       </c>
       <c r="J539" s="2" t="n">
-        <v>46061.33104392058</v>
+        <v>46061.33104392361</v>
       </c>
       <c r="K539" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         </is>
       </c>
       <c r="J540" s="2" t="n">
-        <v>46064.33104392376</v>
+        <v>46064.33104392361</v>
       </c>
       <c r="K540" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         </is>
       </c>
       <c r="J541" s="2" t="n">
-        <v>46073.7060439268</v>
+        <v>46073.70604392361</v>
       </c>
       <c r="K541" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         </is>
       </c>
       <c r="J542" s="2" t="n">
-        <v>46072.53937726333</v>
+        <v>46072.53937726852</v>
       </c>
       <c r="K542" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         </is>
       </c>
       <c r="J543" s="2" t="n">
-        <v>46078.70604393321</v>
+        <v>46078.70604393518</v>
       </c>
       <c r="K543" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         </is>
       </c>
       <c r="J544" s="2" t="n">
-        <v>46070.4143772696</v>
+        <v>46070.41437726852</v>
       </c>
       <c r="K544" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         </is>
       </c>
       <c r="J545" s="2" t="n">
-        <v>46070.3310439393</v>
+        <v>46070.33104393518</v>
       </c>
       <c r="K545" t="inlineStr">
         <is>
@@ -28276,7 +28276,7 @@
         </is>
       </c>
       <c r="J546" s="2" t="n">
-        <v>46060.66437727593</v>
+        <v>46060.66437728009</v>
       </c>
       <c r="K546" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         </is>
       </c>
       <c r="J547" s="2" t="n">
-        <v>46071.4977106123</v>
+        <v>46071.49771061342</v>
       </c>
       <c r="K547" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         </is>
       </c>
       <c r="J548" s="2" t="n">
-        <v>46080.45604394881</v>
+        <v>46080.45604394676</v>
       </c>
       <c r="K548" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         </is>
       </c>
       <c r="J549" s="2" t="n">
-        <v>46084.45604395191</v>
+        <v>46084.45604394676</v>
       </c>
       <c r="K549" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         </is>
       </c>
       <c r="J550" s="2" t="n">
-        <v>46066.62271062179</v>
+        <v>46066.622710625</v>
       </c>
       <c r="K550" t="inlineStr">
         <is>
@@ -28531,11 +28531,2561 @@
         </is>
       </c>
       <c r="J551" s="2" t="n">
-        <v>46061.33104395819</v>
+        <v>46061.33104395834</v>
       </c>
       <c r="K551" t="inlineStr">
         <is>
           <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>24815e3c-61d8-42d3-8f88-c131984358a2</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>857d0806-0f10-4330-b2ed-de37b27b20a9</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F552" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>OP-352</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J552" s="2" t="n">
+        <v>46060.7129640142</v>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>fae86374-d5b0-420a-a523-28571025cd18</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>eb4f135f-8fa3-4324-93b0-bf69a241c5ac</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>OP-981</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J553" s="2" t="n">
+        <v>46081.87963068551</v>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>83b0d62c-93d7-4cc4-abf7-1d641576bdd1</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>6c633a38-fa58-48b4-84a9-cde12968c4af</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>OP-120</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J554" s="2" t="n">
+        <v>46067.79629735544</v>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>e489e479-5a0c-497b-9d90-affe88219713</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>d7f36b98-11ed-4cbb-bb59-667f7df12f6a</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F555" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>OP-932</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J555" s="2" t="n">
+        <v>46069.62963069205</v>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>52a587ad-7ec3-43f5-a0a6-d0b609abf526</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>b74b4d9e-99cc-49de-9026-9be19d543019</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>OP-710</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J556" s="2" t="n">
+        <v>46079.96296402877</v>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>3e40673d-d1ac-4930-b7bf-50f41467bb5b</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>9445f8fd-7161-4c7f-8fea-4db374579ad8</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>OP-988</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J557" s="2" t="n">
+        <v>46064.7962973658</v>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>7e298f86-f90b-43be-bc93-137a9415c00c</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>f6fed973-70e2-4efe-a175-86f338d5d1b4</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>OP-444</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J558" s="2" t="n">
+        <v>46076.75463070224</v>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>42038056-12d0-4d66-aad3-ef6daa90a89c</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>51628fa4-128b-42ab-9dfa-66d55d3213f1</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>OP-115</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J559" s="2" t="n">
+        <v>46077.67129737206</v>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>05c868e8-03c2-422f-81fa-e8d2662229c1</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>b1c8d170-cc99-40af-a96d-6635ca9be7d2</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>OP-860</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J560" s="2" t="n">
+        <v>46088.67129737534</v>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>93803369-433b-4414-958a-35bf790e9ffa</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>61360ffd-a88c-4ad0-a464-3a300c2c0aab</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F561" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>OP-567</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J561" s="2" t="n">
+        <v>46069.79629737847</v>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>f7ccb211-b2ea-4957-a530-3a0bbeb9c352</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>09a58def-7756-4ede-9f0a-af3b60374bd7</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F562" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>OP-354</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J562" s="2" t="n">
+        <v>46077.87963071529</v>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>c716eabc-5253-4abd-9eb4-089d0aa24d37</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>c0bb005f-031d-45b9-ae7b-7849d437915c</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>OP-532</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J563" s="2" t="n">
+        <v>46059.62963071837</v>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>c8bd0d0c-d716-4767-ab9b-46168ae1528c</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>71bad39d-82c4-4838-8ba5-50e0e33b7f01</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>OP-553</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J564" s="2" t="n">
+        <v>46071.79629738865</v>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>d31bbcb7-5737-4bcf-b299-789d6ea1ab3c</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>b875e5c8-7728-412d-9b81-f2e669aa7ff0</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>OP-846</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J565" s="2" t="n">
+        <v>46079.7129640584</v>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>e97182b7-d6ec-4606-91d6-8bdcadaf3f3d</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>fa40a6ee-08f8-417d-a633-a760fad3092b</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>OP-293</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J566" s="2" t="n">
+        <v>46087.6712973949</v>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>e0410413-8bd9-4edc-bc81-d5d50ac7fb72</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>e4333b0f-b2a4-4be8-9efb-44e28f82761e</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>OP-579</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J567" s="2" t="n">
+        <v>46067.96296406501</v>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>013a9320-8eeb-40fc-93b8-5f68b1166b49</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>f88ba1b0-f075-43ff-8aa2-4f366bf9b2eb</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F568" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>OP-918</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J568" s="2" t="n">
+        <v>46084.75463073562</v>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>f6b5275c-803b-43d7-9bc4-53d72107c388</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>fd95471f-48b8-4311-a108-ed46dca8e2b2</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F569" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>OP-332</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J569" s="2" t="n">
+        <v>46073.6712974054</v>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>bd16bc06-8c11-4273-9bc5-b67fa76b4aaa</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>11e37fbf-706a-4ad0-b9bd-134a2bbdcf03</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F570" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>OP-209</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J570" s="2" t="n">
+        <v>46075.9629640752</v>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>ccaa21a1-918e-451f-b45b-d5a1953a2b60</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>050659a0-ca13-4690-bd39-f6d0fe86ccbc</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F571" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>OP-363</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J571" s="2" t="n">
+        <v>46059.79629741182</v>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>b2f766d3-54ea-4dea-8788-a1987cf3ea90</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>3decbe6f-feb8-4242-9aac-1efb05f7a6ed</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F572" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>OP-126</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J572" s="2" t="n">
+        <v>46071.75463074828</v>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>7381c3ce-c847-40e6-81d7-60b96e1f0610</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>75620955-b8a1-4cfd-b93d-3737aa4e4ca1</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F573" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>OP-230</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J573" s="2" t="n">
+        <v>46084.58796408487</v>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>dbe1fee2-e72d-4dba-aa36-544c6d6fc249</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>cf99d64b-36dd-4621-9f62-d18c7be066c1</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>OP-382</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J574" s="2" t="n">
+        <v>46083.87963075478</v>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>7670eb57-217c-400d-ae35-21e7255f4647</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>43351dfe-fa9b-4f09-be50-a716542d3a47</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>OP-632</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J575" s="2" t="n">
+        <v>46067.71296409134</v>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>322fac2c-352f-402e-9a42-d176e4ce1370</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>0be1c8d4-3702-47dd-a82d-9014c688e352</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>OP-928</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J576" s="2" t="n">
+        <v>46069.96296409442</v>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>ac3e77d5-307c-4a66-8389-3c9c104179af</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>352bc9c0-e473-4f44-9c4e-34e92f74c107</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>OP-538</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J577" s="2" t="n">
+        <v>46079.58796409767</v>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>695c982e-0a1e-467d-b679-6a87a4e8fe4a</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>c1353d4a-e856-4a88-98f9-f735cab6e869</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>OP-510</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J578" s="2" t="n">
+        <v>46071.83796410132</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>0f5bf304-edff-4527-8c9a-393c36a471aa</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>87626a0e-0c5e-4d23-8538-1eb671eaa3a7</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>OP-205</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J579" s="2" t="n">
+        <v>46067.83796410452</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>b3160cbb-48cc-4d17-9107-0aac477cef39</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>5e2d5d1c-9749-4099-829b-fcf41f7754cb</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>OP-922</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J580" s="2" t="n">
+        <v>46086.71296410758</v>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2bb584b6-3b9d-4fa5-94cc-2b05155f636b</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>7a3042fb-ac42-468c-ae74-471addfd3050</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>OP-347</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J581" s="2" t="n">
+        <v>46066.83796411066</v>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>b2aeec7a-08c1-498f-a2be-d76e12b5031d</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>a2b947cd-5653-42d6-933d-dd5fdecb4f6c</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>OP-766</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J582" s="2" t="n">
+        <v>46088.62963078083</v>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2ebfd676-5ffb-42b9-af30-c15a0ff89ae3</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>642f472d-2963-4870-a708-3e6cfe013157</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>OP-608</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J583" s="2" t="n">
+        <v>46076.67129745054</v>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>f31a5a64-b3df-4a30-93eb-1fc2624b5c37</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>d78c8701-5c91-491d-960e-fa7e50fc5f95</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>OP-445</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J584" s="2" t="n">
+        <v>46067.62963078706</v>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>a1c8f1fc-9db5-4077-91a4-35b2559b357d</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>3c4bda8b-4d61-470f-81bc-ac3410ffb05a</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>OP-400</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J585" s="2" t="n">
+        <v>46073.83796412372</v>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>6209319f-c786-46b5-89ca-ba83040af8c4</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>b39f60fd-2d5e-4745-a505-349e3c08912b</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>OP-162</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J586" s="2" t="n">
+        <v>46075.8796307936</v>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>24e13c69-03f4-47ef-bf01-e07345571403</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>3bad2eb8-0e7a-4958-a82e-45ee1cfa3e75</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>OP-839</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J587" s="2" t="n">
+        <v>46062.83796413003</v>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>bd2b9f33-9c3d-4a8d-9026-d48319b5bdce</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>4c0c5e7f-1307-49b9-a3fc-37bafcd1ec64</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>OP-717</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="n">
+        <v>46069.9212974664</v>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2f01fcbe-1430-40dc-b76c-db5103d11a56</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>fc1bb941-e2a7-434a-86fb-c9d476559f3f</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>OP-107</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J589" s="2" t="n">
+        <v>46074.58796413642</v>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>5fa92fab-217e-437d-ac30-830e4a10823d</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2743224a-c38b-45fe-b4af-bd238ef77cdb</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>OP-964</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J590" s="2" t="n">
+        <v>46088.96296413954</v>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>8f8e5955-11aa-4528-9bb7-b93018f5f2f2</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>0d34b840-4a4b-42cc-8f1a-25de96dc0458</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>OP-397</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J591" s="2" t="n">
+        <v>46075.96296414261</v>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>3724593d-a100-4627-999f-808ccb621b3c</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>953f8dd7-1efc-4020-bbc7-4f1fab2a68ee</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>OP-176</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J592" s="2" t="n">
+        <v>46083.62963081271</v>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>f77c014f-9fbb-48ae-89ef-494f3ff02134</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>55744d16-dd40-4b24-a479-2241a1e83a67</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F593" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>OP-910</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J593" s="2" t="n">
+        <v>46062.79629748264</v>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2b6e1817-ea08-47a3-9a68-0877271acf1d</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>77beae8d-b1ff-449c-9e6c-ee5fe115b020</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>OP-284</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J594" s="2" t="n">
+        <v>46073.79629748569</v>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>c0023e09-2b6c-4f35-9027-73e30f4d7a66</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>cc659dc5-0296-485a-979d-074e4b27294d</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>OP-494</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J595" s="2" t="n">
+        <v>46075.75463082219</v>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>27cd7466-9774-4f57-abd4-2137cb1b18af</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>669b8b1a-0341-428d-97a3-b4e7169f7cd0</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>OP-485</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J596" s="2" t="n">
+        <v>46078.71296415881</v>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>f88a5af1-38ea-44d4-be96-8e36ec8597c9</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>4524f329-85e0-4838-99ef-063f2d97aec9</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>OP-442</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J597" s="2" t="n">
+        <v>46077.67129749537</v>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>90cc32d4-6068-4ac3-a118-120c37a4c8b7</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>7e358781-1a40-4444-a375-286af92691c0</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>OP-401</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J598" s="2" t="n">
+        <v>46087.75463083173</v>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>ef359209-83db-4ba2-a1f0-dee7e7186a34</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>0e3b467c-d658-4c4d-ab9b-f395d55ef1f8</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>OP-216</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J599" s="2" t="n">
+        <v>46064.75463083493</v>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>06de7f58-9a97-4058-9636-0b0d3b67270b</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>d328b2dc-a7de-4b46-83f1-1808496a8d0c</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F600" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>OP-669</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J600" s="2" t="n">
+        <v>46065.71296417165</v>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>88b39549-474c-4365-9209-894b792aa0a2</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>a2b32d8e-f6fb-4f74-bd5d-9ea01cf17cdb</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F601" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>OP-238</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J601" s="2" t="n">
+        <v>46079.83796417471</v>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K601"/>
+  <dimension ref="A1:K651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="J552" s="2" t="n">
-        <v>46060.7129640142</v>
+        <v>46060.7129640162</v>
       </c>
       <c r="K552" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="J553" s="2" t="n">
-        <v>46081.87963068551</v>
+        <v>46081.87963068287</v>
       </c>
       <c r="K553" t="inlineStr">
         <is>
@@ -28684,7 +28684,7 @@
         </is>
       </c>
       <c r="J554" s="2" t="n">
-        <v>46067.79629735544</v>
+        <v>46067.79629736111</v>
       </c>
       <c r="K554" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="J555" s="2" t="n">
-        <v>46069.62963069205</v>
+        <v>46069.62963069444</v>
       </c>
       <c r="K555" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         </is>
       </c>
       <c r="J556" s="2" t="n">
-        <v>46079.96296402877</v>
+        <v>46079.96296402778</v>
       </c>
       <c r="K556" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         </is>
       </c>
       <c r="J557" s="2" t="n">
-        <v>46064.7962973658</v>
+        <v>46064.79629736111</v>
       </c>
       <c r="K557" t="inlineStr">
         <is>
@@ -28888,7 +28888,7 @@
         </is>
       </c>
       <c r="J558" s="2" t="n">
-        <v>46076.75463070224</v>
+        <v>46076.75463070602</v>
       </c>
       <c r="K558" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         </is>
       </c>
       <c r="J559" s="2" t="n">
-        <v>46077.67129737206</v>
+        <v>46077.67129737268</v>
       </c>
       <c r="K559" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         </is>
       </c>
       <c r="J560" s="2" t="n">
-        <v>46088.67129737534</v>
+        <v>46088.67129737268</v>
       </c>
       <c r="K560" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         </is>
       </c>
       <c r="J561" s="2" t="n">
-        <v>46069.79629737847</v>
+        <v>46069.79629737268</v>
       </c>
       <c r="K561" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         </is>
       </c>
       <c r="J562" s="2" t="n">
-        <v>46077.87963071529</v>
+        <v>46077.87963071759</v>
       </c>
       <c r="K562" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         </is>
       </c>
       <c r="J563" s="2" t="n">
-        <v>46059.62963071837</v>
+        <v>46059.62963071759</v>
       </c>
       <c r="K563" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         </is>
       </c>
       <c r="J564" s="2" t="n">
-        <v>46071.79629738865</v>
+        <v>46071.79629738426</v>
       </c>
       <c r="K564" t="inlineStr">
         <is>
@@ -29245,7 +29245,7 @@
         </is>
       </c>
       <c r="J565" s="2" t="n">
-        <v>46079.7129640584</v>
+        <v>46079.7129640625</v>
       </c>
       <c r="K565" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         </is>
       </c>
       <c r="J566" s="2" t="n">
-        <v>46087.6712973949</v>
+        <v>46087.67129739583</v>
       </c>
       <c r="K566" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         </is>
       </c>
       <c r="J567" s="2" t="n">
-        <v>46067.96296406501</v>
+        <v>46067.9629640625</v>
       </c>
       <c r="K567" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         </is>
       </c>
       <c r="J568" s="2" t="n">
-        <v>46084.75463073562</v>
+        <v>46084.75463074074</v>
       </c>
       <c r="K568" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         </is>
       </c>
       <c r="J569" s="2" t="n">
-        <v>46073.6712974054</v>
+        <v>46073.67129740741</v>
       </c>
       <c r="K569" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         </is>
       </c>
       <c r="J570" s="2" t="n">
-        <v>46075.9629640752</v>
+        <v>46075.96296407407</v>
       </c>
       <c r="K570" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         </is>
       </c>
       <c r="J571" s="2" t="n">
-        <v>46059.79629741182</v>
+        <v>46059.79629740741</v>
       </c>
       <c r="K571" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         </is>
       </c>
       <c r="J572" s="2" t="n">
-        <v>46071.75463074828</v>
+        <v>46071.75463075232</v>
       </c>
       <c r="K572" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         </is>
       </c>
       <c r="J573" s="2" t="n">
-        <v>46084.58796408487</v>
+        <v>46084.58796408565</v>
       </c>
       <c r="K573" t="inlineStr">
         <is>
@@ -29704,7 +29704,7 @@
         </is>
       </c>
       <c r="J574" s="2" t="n">
-        <v>46083.87963075478</v>
+        <v>46083.87963075232</v>
       </c>
       <c r="K574" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         </is>
       </c>
       <c r="J575" s="2" t="n">
-        <v>46067.71296409134</v>
+        <v>46067.71296408565</v>
       </c>
       <c r="K575" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="J576" s="2" t="n">
-        <v>46069.96296409442</v>
+        <v>46069.96296409722</v>
       </c>
       <c r="K576" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="J577" s="2" t="n">
-        <v>46079.58796409767</v>
+        <v>46079.58796409722</v>
       </c>
       <c r="K577" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         </is>
       </c>
       <c r="J578" s="2" t="n">
-        <v>46071.83796410132</v>
+        <v>46071.83796409722</v>
       </c>
       <c r="K578" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         </is>
       </c>
       <c r="J579" s="2" t="n">
-        <v>46067.83796410452</v>
+        <v>46067.8379641088</v>
       </c>
       <c r="K579" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         </is>
       </c>
       <c r="J580" s="2" t="n">
-        <v>46086.71296410758</v>
+        <v>46086.7129641088</v>
       </c>
       <c r="K580" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         </is>
       </c>
       <c r="J581" s="2" t="n">
-        <v>46066.83796411066</v>
+        <v>46066.8379641088</v>
       </c>
       <c r="K581" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         </is>
       </c>
       <c r="J582" s="2" t="n">
-        <v>46088.62963078083</v>
+        <v>46088.62963077546</v>
       </c>
       <c r="K582" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         </is>
       </c>
       <c r="J583" s="2" t="n">
-        <v>46076.67129745054</v>
+        <v>46076.6712974537</v>
       </c>
       <c r="K583" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         </is>
       </c>
       <c r="J584" s="2" t="n">
-        <v>46067.62963078706</v>
+        <v>46067.62963078704</v>
       </c>
       <c r="K584" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         </is>
       </c>
       <c r="J585" s="2" t="n">
-        <v>46073.83796412372</v>
+        <v>46073.83796412037</v>
       </c>
       <c r="K585" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         </is>
       </c>
       <c r="J586" s="2" t="n">
-        <v>46075.8796307936</v>
+        <v>46075.87963079861</v>
       </c>
       <c r="K586" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         </is>
       </c>
       <c r="J587" s="2" t="n">
-        <v>46062.83796413003</v>
+        <v>46062.83796413195</v>
       </c>
       <c r="K587" t="inlineStr">
         <is>
@@ -30418,7 +30418,7 @@
         </is>
       </c>
       <c r="J588" s="2" t="n">
-        <v>46069.9212974664</v>
+        <v>46069.92129746528</v>
       </c>
       <c r="K588" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         </is>
       </c>
       <c r="J589" s="2" t="n">
-        <v>46074.58796413642</v>
+        <v>46074.58796413195</v>
       </c>
       <c r="K589" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="J590" s="2" t="n">
-        <v>46088.96296413954</v>
+        <v>46088.96296414352</v>
       </c>
       <c r="K590" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         </is>
       </c>
       <c r="J591" s="2" t="n">
-        <v>46075.96296414261</v>
+        <v>46075.96296414352</v>
       </c>
       <c r="K591" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         </is>
       </c>
       <c r="J592" s="2" t="n">
-        <v>46083.62963081271</v>
+        <v>46083.62963081019</v>
       </c>
       <c r="K592" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         </is>
       </c>
       <c r="J593" s="2" t="n">
-        <v>46062.79629748264</v>
+        <v>46062.79629747685</v>
       </c>
       <c r="K593" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         </is>
       </c>
       <c r="J594" s="2" t="n">
-        <v>46073.79629748569</v>
+        <v>46073.79629748843</v>
       </c>
       <c r="K594" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         </is>
       </c>
       <c r="J595" s="2" t="n">
-        <v>46075.75463082219</v>
+        <v>46075.75463082176</v>
       </c>
       <c r="K595" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         </is>
       </c>
       <c r="J596" s="2" t="n">
-        <v>46078.71296415881</v>
+        <v>46078.71296415509</v>
       </c>
       <c r="K596" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         </is>
       </c>
       <c r="J597" s="2" t="n">
-        <v>46077.67129749537</v>
+        <v>46077.6712975</v>
       </c>
       <c r="K597" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         </is>
       </c>
       <c r="J598" s="2" t="n">
-        <v>46087.75463083173</v>
+        <v>46087.75463083333</v>
       </c>
       <c r="K598" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         </is>
       </c>
       <c r="J599" s="2" t="n">
-        <v>46064.75463083493</v>
+        <v>46064.75463083333</v>
       </c>
       <c r="K599" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         </is>
       </c>
       <c r="J600" s="2" t="n">
-        <v>46065.71296417165</v>
+        <v>46065.71296416667</v>
       </c>
       <c r="K600" t="inlineStr">
         <is>
@@ -31081,9 +31081,2559 @@
         </is>
       </c>
       <c r="J601" s="2" t="n">
-        <v>46079.83796417471</v>
+        <v>46079.83796417824</v>
       </c>
       <c r="K601" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>e8d1b22a-2d57-4935-a626-db72937336a5</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>baa7ed4a-8c68-4e77-aa14-524f47a81a93</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F602" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>OP-765</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J602" s="2" t="n">
+        <v>46067.01275399435</v>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>22bf4196-5215-4492-9865-d9cb45ae6d64</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>4c59bf3e-035d-4908-9763-6d5ec796f45c</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F603" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>OP-504</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J603" s="2" t="n">
+        <v>46079.67942066523</v>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>d1dd183c-928e-4407-9364-ad13521479ad</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>29f2432f-2ed0-4ba2-b0b6-7b4a407aeb59</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F604" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>OP-868</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J604" s="2" t="n">
+        <v>46081.76275400197</v>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>825df84b-33c0-47bd-ae13-47d2644f5e88</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>61e7dcd8-aeb7-4992-9db3-d06e9ab7cf61</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E605" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F605" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>OP-284</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J605" s="2" t="n">
+        <v>46063.88775400534</v>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>c28a52c9-13ff-4f64-8c96-6c971f7e21b3</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>41107f68-3a74-4c9c-823c-daeeca3f891a</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E606" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F606" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>OP-452</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J606" s="2" t="n">
+        <v>46086.01275400844</v>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>951c7b2d-2806-4c6b-9700-b46e9834f01a</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>b0976afb-6758-4dd8-a226-184be379d329</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E607" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F607" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>OP-451</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J607" s="2" t="n">
+        <v>46062.7210873451</v>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>16c797b6-e523-4f7b-8f10-819e63b8dc1e</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>68ada10e-146b-4b24-889a-e9d0b30756cb</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E608" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>OP-966</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J608" s="2" t="n">
+        <v>46072.72108734838</v>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>c6c4fbc1-8ac7-446a-9a0d-1c6016554eb0</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>dcd2491e-29ba-4405-981d-8df9b2ecb71b</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E609" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>OP-327</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J609" s="2" t="n">
+        <v>46081.76275401821</v>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>8b0bd95a-1fc8-4778-883b-4e422f786ffc</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>f1de66b3-f38c-43fa-bead-8cff6084d01c</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E610" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>OP-685</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J610" s="2" t="n">
+        <v>46060.97108735476</v>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>a92a23d7-54e3-4184-89c9-3581c7715302</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>a33344f8-d610-43c2-a475-fd55e64ccfb4</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E611" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F611" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>OP-636</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J611" s="2" t="n">
+        <v>46067.92942069126</v>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>f13469d3-f3b2-4c27-b066-970292c1d81a</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>9d88e637-9ff3-4fd6-874c-0aba4f9b3275</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E612" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>OP-786</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J612" s="2" t="n">
+        <v>46086.80442069457</v>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>7303ea4e-5c6c-408c-9276-3072c6e26946</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>adcdabae-b7cf-4d5b-9f69-52978aeef469</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E613" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F613" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>OP-301</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J613" s="2" t="n">
+        <v>46077.88775403112</v>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>1e6988f8-3943-4722-8e4b-07663dc8a259</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>4ba1722b-390e-4c3d-9142-1b8f5755a988</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E614" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F614" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>OP-674</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J614" s="2" t="n">
+        <v>46070.72108736759</v>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>32569310-d48f-49b6-adec-82cd7ff66032</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>ac0483b3-194a-4dfc-8079-85023b436f98</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E615" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F615" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>OP-468</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J615" s="2" t="n">
+        <v>46060.97108737077</v>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>42de9771-1daa-4733-9c7e-731c4c4f853d</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>fb96b029-8c21-4453-b234-a0276c3a8a59</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E616" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F616" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>OP-229</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J616" s="2" t="n">
+        <v>46088.63775404098</v>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>a264a1ad-0cb9-4894-901e-d7de1b173899</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>c0609d05-9aef-4938-9534-6d10ba871786</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E617" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F617" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>OP-641</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J617" s="2" t="n">
+        <v>46068.92942071068</v>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>ef493dcd-d4cd-4bb5-bce7-ca1b01ed37cb</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>7370c5a6-8f21-41ad-a2ee-ab44036e761f</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E618" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F618" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>OP-419</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J618" s="2" t="n">
+        <v>46085.88775404709</v>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>50c77d33-102b-490b-a990-f10eddfc5f28</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>72bf69ad-02ae-4718-8921-564c5b8037d4</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E619" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F619" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>OP-648</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J619" s="2" t="n">
+        <v>46075.72108738368</v>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>00abc7c9-48a0-4c8d-bd71-41c6c75d97dc</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>97f693f5-f0d1-403d-8a52-890a47f47cf4</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E620" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F620" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>OP-847</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J620" s="2" t="n">
+        <v>46066.67942072012</v>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>0edc5575-7263-4eed-adff-16f686dcba27</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>22d307d5-d678-4305-bdf6-f4ae79d29b68</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E621" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F621" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>OP-770</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J621" s="2" t="n">
+        <v>46067.9294207233</v>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>a1553558-ed7e-4dc5-9652-17e7446a9f5b</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>7af6b38f-e383-48d6-8ad7-71aeb4ebef90</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E622" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F622" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>OP-275</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J622" s="2" t="n">
+        <v>46084.97108739295</v>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>31e3b6df-8090-45fc-9cab-f83ef4603754</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>5d6c6746-0f34-430c-b84a-6b2575338f46</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E623" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F623" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>OP-842</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J623" s="2" t="n">
+        <v>46087.76275406285</v>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>44757df5-b234-4164-add9-e7e5ef4d4e9d</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>82ecfcad-7a3a-4a83-a42a-443cd817740c</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E624" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F624" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>OP-401</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J624" s="2" t="n">
+        <v>46060.92942073266</v>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>c36bb13f-0424-4980-9474-45d023212c1b</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>1165e8f2-28ab-43bd-b674-fae44f057c04</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E625" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F625" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>OP-562</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J625" s="2" t="n">
+        <v>46085.72108740231</v>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>6b207bb2-997b-437f-867c-f5ab32edfe1e</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>26af686a-b539-47c3-abb2-f355aecd3e82</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E626" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F626" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>OP-946</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J626" s="2" t="n">
+        <v>46072.88775407209</v>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>d0e17594-1e76-44ce-8a7d-b5cb8d20e77c</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>81f276ed-7123-4305-97f9-69112175e560</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E627" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F627" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>OP-142</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J627" s="2" t="n">
+        <v>46078.80442074213</v>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>056cbdf8-127b-4459-8e68-bd28b90633d8</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>d61729d3-61ce-421c-a487-8fad73eed802</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E628" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F628" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>OP-677</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J628" s="2" t="n">
+        <v>46069.97108741204</v>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>0fab2fc4-4c40-4ccb-8f7d-44b8a598be86</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>c35738d5-c36d-4f1b-a63c-0316fc7f54c3</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E629" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F629" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>OP-795</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J629" s="2" t="n">
+        <v>46067.01275408173</v>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>a283ade0-be91-477f-888d-127aecf265f5</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>b44b84a0-2a4a-446a-85e3-e9876384cf05</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E630" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F630" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>OP-523</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J630" s="2" t="n">
+        <v>46081.76275408504</v>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>5e56e802-1f9c-4ece-8703-cbaa6218c2c9</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>97ec28a1-4680-48f2-9f72-04d3b3d0b9fe</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E631" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F631" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>OP-244</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J631" s="2" t="n">
+        <v>46062.92942075507</v>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>f5609bb7-ceaf-4a29-842f-424b15f5baff</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>3dfe2580-5fd7-48ff-8b31-71433ae784c8</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E632" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F632" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>OP-228</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J632" s="2" t="n">
+        <v>46066.80442075834</v>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2bb96c11-ab52-401b-be17-f00f3639bc80</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>0e0173eb-459d-43ed-bca7-c54dc8c9bcef</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E633" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F633" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>OP-449</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J633" s="2" t="n">
+        <v>46083.9294207614</v>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>33be4c7b-cbe1-4f4b-8c8d-a7c6b758a3fa</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>ae59944b-181d-4187-b886-a1e6b05df5a8</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E634" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F634" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>OP-493</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J634" s="2" t="n">
+        <v>46065.97108743135</v>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>91c4b533-ef11-4093-9c76-bec200d9912e</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>523cf0a8-0e7c-4952-afa2-d2314c99fa35</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E635" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F635" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>OP-541</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J635" s="2" t="n">
+        <v>46075.01275410113</v>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>53f84759-f179-4306-9b99-ba9f8d8aaa86</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>c1e06220-dba5-4cef-9a7d-f0e6a18b86c8</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E636" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F636" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>OP-930</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J636" s="2" t="n">
+        <v>46084.63775410426</v>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>7ba10b6e-897c-4855-8dc0-24888e7563a8</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>fa700996-3763-4bdc-b464-bee1e3fff5b4</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E637" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F637" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>OP-412</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J637" s="2" t="n">
+        <v>46081.01275410748</v>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>ecc045bd-c2ce-45ad-ab2c-713b24c3ac26</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>22212b79-aa1e-49f8-bac3-84feebe30114</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E638" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F638" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>OP-162</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J638" s="2" t="n">
+        <v>46079.72108744404</v>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>6af71a34-3a8c-409b-bb76-65bbf6dbc67d</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>a648b3b3-ea19-48ff-824d-8c137a79086d</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E639" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F639" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>OP-644</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J639" s="2" t="n">
+        <v>46074.80442078054</v>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>a3e97427-d32b-49c3-9da8-f634cb3df687</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>c92240f0-3e68-424c-8f73-01df622bbb1e</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E640" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F640" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>OP-163</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J640" s="2" t="n">
+        <v>46085.63775411702</v>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>7e295119-73f3-4d91-a163-09dba01d7f01</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>6909372d-c959-4d73-a0aa-7c4129adc2a7</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E641" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F641" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>OP-253</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J641" s="2" t="n">
+        <v>46060.84608745373</v>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>9274eda0-689c-41fb-8dd6-348c16d8eb1c</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>25114fce-f940-4e56-b657-c9c19741a6ce</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E642" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F642" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>OP-418</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J642" s="2" t="n">
+        <v>46068.72108745688</v>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>ca4c1f82-9d3e-48d7-b34d-8c3f9e920bfd</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>5fe61a1f-f21e-4469-9717-1f6f45471fb5</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E643" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F643" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>OP-622</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J643" s="2" t="n">
+        <v>46059.72108745999</v>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>6573cc39-e2a9-40d2-a2ae-ee28e62d1539</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>51e0b758-950f-4a4a-ab93-0835fe84b9f8</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E644" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F644" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>OP-306</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J644" s="2" t="n">
+        <v>46064.76275412977</v>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>a4aaf6b2-903a-4d16-a711-ff71a23ab89a</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>b8d917ff-d52f-461b-9dac-b93d845ec257</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E645" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F645" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>OP-231</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J645" s="2" t="n">
+        <v>46088.887754133</v>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>66823398-671a-441b-9383-05310e5b9f31</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>6c80f053-815c-4aca-9f83-31f1b2d0e592</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E646" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F646" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>OP-381</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J646" s="2" t="n">
+        <v>46076.7627541361</v>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>797dff14-612b-4494-9ebe-178e93bc97ff</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>8a8b9b44-f54f-4413-8c50-8ceb0ea9abdc</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E647" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F647" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>OP-932</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J647" s="2" t="n">
+        <v>46080.88775413912</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>e3c6ab6f-555c-40b6-adb0-d05a501d95e9</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>bdf75d57-ba5d-4d13-914a-bc8398b6de57</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E648" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F648" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>OP-368</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J648" s="2" t="n">
+        <v>46085.67942080899</v>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>9b1aa644-acc5-4926-a7db-8e0cef303c33</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>e306753e-620e-4d67-a040-73c65dca1210</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E649" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F649" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>OP-373</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J649" s="2" t="n">
+        <v>46074.76275414553</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>52c996da-9f2d-421c-8049-27e8e97a0ac8</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>0a5e8503-5cd4-4982-86ef-ecd8f50fcd98</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E650" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F650" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>OP-116</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J650" s="2" t="n">
+        <v>46075.97108748208</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>5e2b7442-e0cd-44c9-a7ce-057d5dbdbeba</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>c0829025-9725-4f56-ba50-d752ed12d42b</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E651" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F651" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>OP-340</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J651" s="2" t="n">
+        <v>46062.92942081861</v>
+      </c>
+      <c r="K651" t="inlineStr">
         <is>
           <t>good</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K651"/>
+  <dimension ref="A1:K701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31132,7 +31132,7 @@
         </is>
       </c>
       <c r="J602" s="2" t="n">
-        <v>46067.01275399435</v>
+        <v>46067.01275399305</v>
       </c>
       <c r="K602" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         </is>
       </c>
       <c r="J603" s="2" t="n">
-        <v>46079.67942066523</v>
+        <v>46079.67942065972</v>
       </c>
       <c r="K603" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         </is>
       </c>
       <c r="J604" s="2" t="n">
-        <v>46081.76275400197</v>
+        <v>46081.76275400463</v>
       </c>
       <c r="K604" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         </is>
       </c>
       <c r="J605" s="2" t="n">
-        <v>46063.88775400534</v>
+        <v>46063.88775400463</v>
       </c>
       <c r="K605" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         </is>
       </c>
       <c r="J606" s="2" t="n">
-        <v>46086.01275400844</v>
+        <v>46086.01275400463</v>
       </c>
       <c r="K606" t="inlineStr">
         <is>
@@ -31387,7 +31387,7 @@
         </is>
       </c>
       <c r="J607" s="2" t="n">
-        <v>46062.7210873451</v>
+        <v>46062.72108734954</v>
       </c>
       <c r="K607" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         </is>
       </c>
       <c r="J608" s="2" t="n">
-        <v>46072.72108734838</v>
+        <v>46072.72108734954</v>
       </c>
       <c r="K608" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         </is>
       </c>
       <c r="J609" s="2" t="n">
-        <v>46081.76275401821</v>
+        <v>46081.76275401621</v>
       </c>
       <c r="K609" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         </is>
       </c>
       <c r="J610" s="2" t="n">
-        <v>46060.97108735476</v>
+        <v>46060.97108734954</v>
       </c>
       <c r="K610" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         </is>
       </c>
       <c r="J611" s="2" t="n">
-        <v>46067.92942069126</v>
+        <v>46067.92942069445</v>
       </c>
       <c r="K611" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         </is>
       </c>
       <c r="J612" s="2" t="n">
-        <v>46086.80442069457</v>
+        <v>46086.80442069445</v>
       </c>
       <c r="K612" t="inlineStr">
         <is>
@@ -31693,7 +31693,7 @@
         </is>
       </c>
       <c r="J613" s="2" t="n">
-        <v>46077.88775403112</v>
+        <v>46077.88775402778</v>
       </c>
       <c r="K613" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="J614" s="2" t="n">
-        <v>46070.72108736759</v>
+        <v>46070.72108737269</v>
       </c>
       <c r="K614" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         </is>
       </c>
       <c r="J615" s="2" t="n">
-        <v>46060.97108737077</v>
+        <v>46060.97108737269</v>
       </c>
       <c r="K615" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         </is>
       </c>
       <c r="J616" s="2" t="n">
-        <v>46088.63775404098</v>
+        <v>46088.63775403935</v>
       </c>
       <c r="K616" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         </is>
       </c>
       <c r="J617" s="2" t="n">
-        <v>46068.92942071068</v>
+        <v>46068.92942070602</v>
       </c>
       <c r="K617" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         </is>
       </c>
       <c r="J618" s="2" t="n">
-        <v>46085.88775404709</v>
+        <v>46085.88775405093</v>
       </c>
       <c r="K618" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         </is>
       </c>
       <c r="J619" s="2" t="n">
-        <v>46075.72108738368</v>
+        <v>46075.72108738426</v>
       </c>
       <c r="K619" t="inlineStr">
         <is>
@@ -32050,7 +32050,7 @@
         </is>
       </c>
       <c r="J620" s="2" t="n">
-        <v>46066.67942072012</v>
+        <v>46066.67942071759</v>
       </c>
       <c r="K620" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         </is>
       </c>
       <c r="J621" s="2" t="n">
-        <v>46067.9294207233</v>
+        <v>46067.92942071759</v>
       </c>
       <c r="K621" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         </is>
       </c>
       <c r="J622" s="2" t="n">
-        <v>46084.97108739295</v>
+        <v>46084.97108739583</v>
       </c>
       <c r="K622" t="inlineStr">
         <is>
@@ -32203,7 +32203,7 @@
         </is>
       </c>
       <c r="J623" s="2" t="n">
-        <v>46087.76275406285</v>
+        <v>46087.7627540625</v>
       </c>
       <c r="K623" t="inlineStr">
         <is>
@@ -32254,7 +32254,7 @@
         </is>
       </c>
       <c r="J624" s="2" t="n">
-        <v>46060.92942073266</v>
+        <v>46060.92942072917</v>
       </c>
       <c r="K624" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         </is>
       </c>
       <c r="J625" s="2" t="n">
-        <v>46085.72108740231</v>
+        <v>46085.72108740741</v>
       </c>
       <c r="K625" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         </is>
       </c>
       <c r="J626" s="2" t="n">
-        <v>46072.88775407209</v>
+        <v>46072.88775407407</v>
       </c>
       <c r="K626" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         </is>
       </c>
       <c r="J627" s="2" t="n">
-        <v>46078.80442074213</v>
+        <v>46078.80442074074</v>
       </c>
       <c r="K627" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         </is>
       </c>
       <c r="J628" s="2" t="n">
-        <v>46069.97108741204</v>
+        <v>46069.97108740741</v>
       </c>
       <c r="K628" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         </is>
       </c>
       <c r="J629" s="2" t="n">
-        <v>46067.01275408173</v>
+        <v>46067.01275408565</v>
       </c>
       <c r="K629" t="inlineStr">
         <is>
@@ -32560,7 +32560,7 @@
         </is>
       </c>
       <c r="J630" s="2" t="n">
-        <v>46081.76275408504</v>
+        <v>46081.76275408565</v>
       </c>
       <c r="K630" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         </is>
       </c>
       <c r="J631" s="2" t="n">
-        <v>46062.92942075507</v>
+        <v>46062.92942075231</v>
       </c>
       <c r="K631" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         </is>
       </c>
       <c r="J632" s="2" t="n">
-        <v>46066.80442075834</v>
+        <v>46066.80442076389</v>
       </c>
       <c r="K632" t="inlineStr">
         <is>
@@ -32713,7 +32713,7 @@
         </is>
       </c>
       <c r="J633" s="2" t="n">
-        <v>46083.9294207614</v>
+        <v>46083.92942076389</v>
       </c>
       <c r="K633" t="inlineStr">
         <is>
@@ -32764,7 +32764,7 @@
         </is>
       </c>
       <c r="J634" s="2" t="n">
-        <v>46065.97108743135</v>
+        <v>46065.97108743055</v>
       </c>
       <c r="K634" t="inlineStr">
         <is>
@@ -32815,7 +32815,7 @@
         </is>
       </c>
       <c r="J635" s="2" t="n">
-        <v>46075.01275410113</v>
+        <v>46075.01275409722</v>
       </c>
       <c r="K635" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         </is>
       </c>
       <c r="J636" s="2" t="n">
-        <v>46084.63775410426</v>
+        <v>46084.63775410879</v>
       </c>
       <c r="K636" t="inlineStr">
         <is>
@@ -32917,7 +32917,7 @@
         </is>
       </c>
       <c r="J637" s="2" t="n">
-        <v>46081.01275410748</v>
+        <v>46081.01275410879</v>
       </c>
       <c r="K637" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         </is>
       </c>
       <c r="J638" s="2" t="n">
-        <v>46079.72108744404</v>
+        <v>46079.72108744213</v>
       </c>
       <c r="K638" t="inlineStr">
         <is>
@@ -33019,7 +33019,7 @@
         </is>
       </c>
       <c r="J639" s="2" t="n">
-        <v>46074.80442078054</v>
+        <v>46074.80442077546</v>
       </c>
       <c r="K639" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         </is>
       </c>
       <c r="J640" s="2" t="n">
-        <v>46085.63775411702</v>
+        <v>46085.63775412037</v>
       </c>
       <c r="K640" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         </is>
       </c>
       <c r="J641" s="2" t="n">
-        <v>46060.84608745373</v>
+        <v>46060.8460874537</v>
       </c>
       <c r="K641" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         </is>
       </c>
       <c r="J642" s="2" t="n">
-        <v>46068.72108745688</v>
+        <v>46068.7210874537</v>
       </c>
       <c r="K642" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         </is>
       </c>
       <c r="J643" s="2" t="n">
-        <v>46059.72108745999</v>
+        <v>46059.72108746528</v>
       </c>
       <c r="K643" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         </is>
       </c>
       <c r="J644" s="2" t="n">
-        <v>46064.76275412977</v>
+        <v>46064.76275413195</v>
       </c>
       <c r="K644" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         </is>
       </c>
       <c r="J645" s="2" t="n">
-        <v>46088.887754133</v>
+        <v>46088.88775413195</v>
       </c>
       <c r="K645" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
         </is>
       </c>
       <c r="J646" s="2" t="n">
-        <v>46076.7627541361</v>
+        <v>46076.76275413195</v>
       </c>
       <c r="K646" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         </is>
       </c>
       <c r="J647" s="2" t="n">
-        <v>46080.88775413912</v>
+        <v>46080.88775414352</v>
       </c>
       <c r="K647" t="inlineStr">
         <is>
@@ -33478,7 +33478,7 @@
         </is>
       </c>
       <c r="J648" s="2" t="n">
-        <v>46085.67942080899</v>
+        <v>46085.67942081019</v>
       </c>
       <c r="K648" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         </is>
       </c>
       <c r="J649" s="2" t="n">
-        <v>46074.76275414553</v>
+        <v>46074.76275414352</v>
       </c>
       <c r="K649" t="inlineStr">
         <is>
@@ -33580,7 +33580,7 @@
         </is>
       </c>
       <c r="J650" s="2" t="n">
-        <v>46075.97108748208</v>
+        <v>46075.97108747685</v>
       </c>
       <c r="K650" t="inlineStr">
         <is>
@@ -33631,11 +33631,2561 @@
         </is>
       </c>
       <c r="J651" s="2" t="n">
-        <v>46062.92942081861</v>
+        <v>46062.92942082176</v>
       </c>
       <c r="K651" t="inlineStr">
         <is>
           <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>919b6980-b404-487f-b747-c78ee1144ede</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>50b7255d-476e-4238-9d70-2c720e2eaeef</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E652" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F652" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>OP-844</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J652" s="2" t="n">
+        <v>46075.86179396173</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2c66b641-c9cb-434a-b71f-57e6f9eff7be</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>d016f671-bfe6-44da-9864-f40b52009548</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E653" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F653" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>OP-814</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J653" s="2" t="n">
+        <v>46073.73679396624</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>a7795f55-dbe1-423c-b97f-57ac0c797d61</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>d0493c70-feee-44b3-904a-c2d49a899a65</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E654" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F654" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>OP-124</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J654" s="2" t="n">
+        <v>46063.9034606361</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>e1e7d44b-e011-479e-9f8f-c5b4d1ff53e2</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>58eaca07-7f6e-469e-82ee-ef26f1d55147</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E655" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F655" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>OP-254</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J655" s="2" t="n">
+        <v>46069.6534606394</v>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>5db74229-509e-4c72-b0d3-b1b7ec37395e</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>64cb6a25-ce39-44de-b7dd-1aea65360e0a</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E656" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F656" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>OP-229</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J656" s="2" t="n">
+        <v>46060.73679397591</v>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>c3ef4fe2-d92f-4a2b-85b6-b833824e1f69</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>7b45770b-97a7-4f27-acd7-b0a83f233805</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E657" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F657" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>OP-975</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J657" s="2" t="n">
+        <v>46069.77846064592</v>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>802e22f4-ff30-4308-8e9a-41682bd21529</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>ae8d9832-1820-4576-88fb-7c759e1304a6</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E658" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F658" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>OP-741</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J658" s="2" t="n">
+        <v>46059.90346064902</v>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>66ef3535-60f7-43be-9346-e537fdf8785a</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>837840d4-088d-4771-8ed8-80e491829998</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E659" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F659" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>OP-227</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J659" s="2" t="n">
+        <v>46066.02846065208</v>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>ec215157-719d-4fd0-9d5a-285f35432104</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>53658452-c234-44ab-96c8-521fb8f20a1f</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E660" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F660" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>OP-787</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J660" s="2" t="n">
+        <v>46065.65346065519</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>ff15d70c-c436-491b-bfeb-3cda75b3a303</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>e82d9af5-b28e-4046-b142-278d1dedb31b</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E661" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F661" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>OP-117</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J661" s="2" t="n">
+        <v>46066.69512732551</v>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>3ea7d121-be0b-4cfa-9eaa-b9c296444bf0</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>7faad09f-5b0e-4eb1-9823-f094399c0bdd</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E662" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F662" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>OP-376</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J662" s="2" t="n">
+        <v>46063.82012732871</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>3786c408-6e61-47b2-8392-cd1787f57622</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>55a27469-0140-4719-935f-d997cea4de36</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F663" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>OP-300</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J663" s="2" t="n">
+        <v>46068.9451273318</v>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>985fbba8-2e44-4b78-8900-606fd6db1810</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>e452e18f-55b0-4a77-b265-679a6f1068b9</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E664" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F664" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>OP-522</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J664" s="2" t="n">
+        <v>46073.94512733544</v>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>9254258a-9043-45f5-b865-59eef8ee43da</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>89f8d0ff-245a-4035-ac17-001d9714ef1f</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E665" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F665" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>OP-284</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J665" s="2" t="n">
+        <v>46060.69512733862</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>026a8cd3-23f4-450c-8829-b4aee3954122</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>4285c4d1-fdac-4a52-ae33-79cb4da4b3c2</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E666" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F666" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>OP-884</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J666" s="2" t="n">
+        <v>46077.77846067508</v>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>6b30c613-e925-4fac-a1c4-37e9536b8aba</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>37a7dcb1-7521-4007-a711-357c1f1adb77</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E667" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F667" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>OP-518</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J667" s="2" t="n">
+        <v>46079.65346067814</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>1d1db1c7-2cae-44dc-9bee-d9dc161f045f</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>6f81e737-1bd6-4d70-95e2-2e2f7a796e33</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E668" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F668" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>OP-689</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J668" s="2" t="n">
+        <v>46059.73679401483</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>d4ca1aa2-5fe5-4d0c-b1b7-eb8a01e8d2da</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>b6676b5d-9e7e-4dad-a651-a4c11c1ee04a</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F669" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>OP-665</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J669" s="2" t="n">
+        <v>46063.86179401798</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>a1434c78-dcee-4ea9-8189-d1c597949fd0</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>7eed7d97-ca1c-4408-90d9-a0e0d45a8cea</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F670" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>OP-492</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J670" s="2" t="n">
+        <v>46083.02846068775</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>df954051-215c-4d0e-a490-d5ee2a427a30</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>31f9bf89-f3bb-468e-b22c-d99c6352888f</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F671" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>OP-274</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J671" s="2" t="n">
+        <v>46088.69512735761</v>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>ffa72356-6801-4c77-9ce6-7ff4df022d66</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>3d31031a-5fce-42ad-a7f6-0b8f60b8368a</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F672" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>OP-373</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J672" s="2" t="n">
+        <v>46075.82012736078</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>cc76681d-70bd-4a4e-b499-39ef927c5c8a</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>ffe2d4d6-7edc-442f-a591-2adb63399103</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F673" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>OP-301</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J673" s="2" t="n">
+        <v>46086.90346069721</v>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>daeb4415-d61b-4c30-876c-60f9b4aca0cc</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>7b11a2c9-c127-430c-aba9-874b0d7d60a1</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F674" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>OP-598</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J674" s="2" t="n">
+        <v>46070.86179403355</v>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>0ae0b644-3d0a-4176-960b-035d1e3f991c</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>d8af2d27-ffd6-400f-9909-8bca54261334</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F675" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>OP-370</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J675" s="2" t="n">
+        <v>46080.7784607034</v>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>ecdf4851-3e4e-4d14-8af5-82efd6ad6457</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>a5f4bb36-2e0b-40ee-9979-2836680e6bf3</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F676" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>OP-598</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J676" s="2" t="n">
+        <v>46079.77846070646</v>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>0f6d5b9b-5cff-41d0-94f8-8a25f3cbf0c7</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>d3445bbe-07e6-4b31-afa2-f316de4e88bd</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>1</v>
+      </c>
+      <c r="F677" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>OP-822</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J677" s="2" t="n">
+        <v>46081.90346070952</v>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>03870d03-7938-4f88-8405-31d555ab5677</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>a786efb3-2d5e-4338-bb26-aa2c6b07e303</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F678" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>OP-269</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J678" s="2" t="n">
+        <v>46064.69512737934</v>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>31da13c2-9905-4e98-bdfb-b6fa22e26977</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>ab35d860-c8ba-42ff-b36e-8c5b4712c812</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F679" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>OP-678</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J679" s="2" t="n">
+        <v>46067.7367940496</v>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>807f4b84-21de-42f7-9ab1-c525650a97fb</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>24c1f530-8b3a-4895-a21f-f1baacf639d1</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F680" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>OP-259</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J680" s="2" t="n">
+        <v>46083.77846071951</v>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>0a6ed282-fa81-4691-991d-8312013f3c39</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>caee9bdb-f0ed-41bc-b363-1679b4bf92b4</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F681" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>OP-626</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J681" s="2" t="n">
+        <v>46084.8201273895</v>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>61639d9a-2ad1-4c1b-9696-581630f7c789</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>3fc6c417-6242-4987-a29f-f0816aac8cdb</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E682" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F682" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>OP-444</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J682" s="2" t="n">
+        <v>46067.9034607261</v>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>c8b33302-c8ea-47e3-9f31-d018155a9ab4</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>722acc51-a7ad-4e31-a890-834bf2b52348</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E683" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F683" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>OP-465</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J683" s="2" t="n">
+        <v>46085.90346072913</v>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>805fd142-b9df-4b7a-a8c7-e0bf712f6a6f</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>dc4c3c5a-6a72-4c80-b014-1db0d28b8ab3</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E684" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F684" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>OP-212</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J684" s="2" t="n">
+        <v>46083.86179406563</v>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>43d2cd09-955e-46fa-95a8-7fb4c329c0cd</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>d6e1ae04-ef81-4183-9c0c-0410a911b306</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E685" t="n">
+        <v>0</v>
+      </c>
+      <c r="F685" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>OP-171</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J685" s="2" t="n">
+        <v>46073.94512740221</v>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>41d286c0-1e20-43e1-a7bf-f313cf9ffb08</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>50a27a7b-9ff6-4da6-8ade-41375578fa90</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E686" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F686" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>OP-995</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J686" s="2" t="n">
+        <v>46081.7784607387</v>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>6135d4c3-2f2e-4a54-8d49-4b3f58b88c42</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>4f058fa4-0986-4766-a63e-5854c724ce2e</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E687" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F687" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>OP-661</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J687" s="2" t="n">
+        <v>46076.77846074195</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>bc411d12-f881-4cb7-ab7a-fd9a01cb6bfb</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>b5abcdaa-8f1d-405e-bc26-e8539c96a86f</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E688" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F688" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>OP-782</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J688" s="2" t="n">
+        <v>46083.6534607451</v>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>aef8ba31-f656-47b3-b21f-3c5f71240a78</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>095b74d7-13d1-432f-ae1f-1210cc566b7d</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E689" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F689" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>OP-332</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J689" s="2" t="n">
+        <v>46087.82012741495</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>616f00ba-b656-4996-889a-47652c59b4b2</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>c2811e74-9dd6-4c43-8775-2445557a6d14</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E690" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F690" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>OP-247</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J690" s="2" t="n">
+        <v>46060.86179408475</v>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>8444cf50-3ef5-4720-86c0-0db8c558bad7</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>7639bc2c-b8d2-4908-a6e3-4e43360c06b9</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E691" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F691" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>OP-106</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J691" s="2" t="n">
+        <v>46076.94512742122</v>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>96e92430-ba04-4718-a64c-56cbb9e41cc3</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>adf08da6-1507-48f4-985b-6428905f5d80</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E692" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F692" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>OP-339</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J692" s="2" t="n">
+        <v>46077.90346075765</v>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>a3b21185-ca73-404b-a41b-6ccb5c2be89a</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>3a24274c-68c3-4368-a7d4-f93885bfc531</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E693" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F693" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>OP-676</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J693" s="2" t="n">
+        <v>46070.820127428</v>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>a744332f-f7a6-4a08-893c-72c7b69d6cef</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>af50c5b4-88d4-472d-8dfc-c2c700b7ca8a</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E694" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F694" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>OP-190</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J694" s="2" t="n">
+        <v>46059.86179409815</v>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>72927d1b-d9dd-4e7b-a401-453c940262b3</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>165e8d0a-3ac1-45d7-a734-af1eed6bfd95</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E695" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F695" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>OP-324</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J695" s="2" t="n">
+        <v>46070.65346076785</v>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>46c48701-7231-4694-95ef-b10e438ae577</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>3cc9a3a8-c5dd-49f9-8dbb-dd3fed0c405e</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E696" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F696" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>OP-722</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J696" s="2" t="n">
+        <v>46063.02846077086</v>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>ed29410b-916c-4316-886a-5f38852a5f06</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>c90d96ca-e9ab-40ff-b2af-ed3144a590a5</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E697" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F697" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>OP-527</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J697" s="2" t="n">
+        <v>46082.90346077413</v>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2d4a1f93-fac9-4180-b34a-3299cecdd167</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>da65f702-8f71-46a3-9eb8-c03e65c831ee</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E698" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F698" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>OP-189</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J698" s="2" t="n">
+        <v>46073.82012744399</v>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>cd6ae15e-621b-4e86-9190-159139207102</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>042d8ec2-dfe2-4a2a-a566-e46a10688be8</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E699" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F699" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>OP-391</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J699" s="2" t="n">
+        <v>46069.73679411387</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>668c49ad-0632-42a6-b311-680416c56d05</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>e3bf582c-17ef-4b04-8385-194b5152b866</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E700" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F700" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>OP-623</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J700" s="2" t="n">
+        <v>46072.94512745036</v>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>d4c3d4ac-f9f5-4858-8168-f73c2215f210</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>0e84fbd8-daa6-46f4-b937-24dc76d64f61</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E701" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F701" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>OP-476</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J701" s="2" t="n">
+        <v>46076.9867941203</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>poor</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K701"/>
+  <dimension ref="A1:K751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33682,7 +33682,7 @@
         </is>
       </c>
       <c r="J652" s="2" t="n">
-        <v>46075.86179396173</v>
+        <v>46075.86179395833</v>
       </c>
       <c r="K652" t="inlineStr">
         <is>
@@ -33733,7 +33733,7 @@
         </is>
       </c>
       <c r="J653" s="2" t="n">
-        <v>46073.73679396624</v>
+        <v>46073.73679396991</v>
       </c>
       <c r="K653" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         </is>
       </c>
       <c r="J654" s="2" t="n">
-        <v>46063.9034606361</v>
+        <v>46063.90346063657</v>
       </c>
       <c r="K654" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         </is>
       </c>
       <c r="J655" s="2" t="n">
-        <v>46069.6534606394</v>
+        <v>46069.65346063657</v>
       </c>
       <c r="K655" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         </is>
       </c>
       <c r="J656" s="2" t="n">
-        <v>46060.73679397591</v>
+        <v>46060.73679398148</v>
       </c>
       <c r="K656" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         </is>
       </c>
       <c r="J657" s="2" t="n">
-        <v>46069.77846064592</v>
+        <v>46069.77846064815</v>
       </c>
       <c r="K657" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         </is>
       </c>
       <c r="J658" s="2" t="n">
-        <v>46059.90346064902</v>
+        <v>46059.90346064815</v>
       </c>
       <c r="K658" t="inlineStr">
         <is>
@@ -34039,7 +34039,7 @@
         </is>
       </c>
       <c r="J659" s="2" t="n">
-        <v>46066.02846065208</v>
+        <v>46066.02846064815</v>
       </c>
       <c r="K659" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         </is>
       </c>
       <c r="J660" s="2" t="n">
-        <v>46065.65346065519</v>
+        <v>46065.65346065972</v>
       </c>
       <c r="K660" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         </is>
       </c>
       <c r="J661" s="2" t="n">
-        <v>46066.69512732551</v>
+        <v>46066.69512732639</v>
       </c>
       <c r="K661" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         </is>
       </c>
       <c r="J662" s="2" t="n">
-        <v>46063.82012732871</v>
+        <v>46063.82012732639</v>
       </c>
       <c r="K662" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         </is>
       </c>
       <c r="J663" s="2" t="n">
-        <v>46068.9451273318</v>
+        <v>46068.94512732639</v>
       </c>
       <c r="K663" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         </is>
       </c>
       <c r="J664" s="2" t="n">
-        <v>46073.94512733544</v>
+        <v>46073.94512733796</v>
       </c>
       <c r="K664" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="J665" s="2" t="n">
-        <v>46060.69512733862</v>
+        <v>46060.69512733796</v>
       </c>
       <c r="K665" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         </is>
       </c>
       <c r="J666" s="2" t="n">
-        <v>46077.77846067508</v>
+        <v>46077.7784606713</v>
       </c>
       <c r="K666" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         </is>
       </c>
       <c r="J667" s="2" t="n">
-        <v>46079.65346067814</v>
+        <v>46079.65346068287</v>
       </c>
       <c r="K667" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         </is>
       </c>
       <c r="J668" s="2" t="n">
-        <v>46059.73679401483</v>
+        <v>46059.7367940162</v>
       </c>
       <c r="K668" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         </is>
       </c>
       <c r="J669" s="2" t="n">
-        <v>46063.86179401798</v>
+        <v>46063.8617940162</v>
       </c>
       <c r="K669" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         </is>
       </c>
       <c r="J670" s="2" t="n">
-        <v>46083.02846068775</v>
+        <v>46083.02846068287</v>
       </c>
       <c r="K670" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         </is>
       </c>
       <c r="J671" s="2" t="n">
-        <v>46088.69512735761</v>
+        <v>46088.69512736111</v>
       </c>
       <c r="K671" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         </is>
       </c>
       <c r="J672" s="2" t="n">
-        <v>46075.82012736078</v>
+        <v>46075.82012736111</v>
       </c>
       <c r="K672" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         </is>
       </c>
       <c r="J673" s="2" t="n">
-        <v>46086.90346069721</v>
+        <v>46086.90346069445</v>
       </c>
       <c r="K673" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         </is>
       </c>
       <c r="J674" s="2" t="n">
-        <v>46070.86179403355</v>
+        <v>46070.86179402778</v>
       </c>
       <c r="K674" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="J675" s="2" t="n">
-        <v>46080.7784607034</v>
+        <v>46080.77846070602</v>
       </c>
       <c r="K675" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         </is>
       </c>
       <c r="J676" s="2" t="n">
-        <v>46079.77846070646</v>
+        <v>46079.77846070602</v>
       </c>
       <c r="K676" t="inlineStr">
         <is>
@@ -34957,7 +34957,7 @@
         </is>
       </c>
       <c r="J677" s="2" t="n">
-        <v>46081.90346070952</v>
+        <v>46081.90346070602</v>
       </c>
       <c r="K677" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         </is>
       </c>
       <c r="J678" s="2" t="n">
-        <v>46064.69512737934</v>
+        <v>46064.69512738426</v>
       </c>
       <c r="K678" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         </is>
       </c>
       <c r="J679" s="2" t="n">
-        <v>46067.7367940496</v>
+        <v>46067.73679405093</v>
       </c>
       <c r="K679" t="inlineStr">
         <is>
@@ -35110,7 +35110,7 @@
         </is>
       </c>
       <c r="J680" s="2" t="n">
-        <v>46083.77846071951</v>
+        <v>46083.77846071759</v>
       </c>
       <c r="K680" t="inlineStr">
         <is>
@@ -35161,7 +35161,7 @@
         </is>
       </c>
       <c r="J681" s="2" t="n">
-        <v>46084.8201273895</v>
+        <v>46084.82012738426</v>
       </c>
       <c r="K681" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         </is>
       </c>
       <c r="J682" s="2" t="n">
-        <v>46067.9034607261</v>
+        <v>46067.90346072917</v>
       </c>
       <c r="K682" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         </is>
       </c>
       <c r="J683" s="2" t="n">
-        <v>46085.90346072913</v>
+        <v>46085.90346072917</v>
       </c>
       <c r="K683" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         </is>
       </c>
       <c r="J684" s="2" t="n">
-        <v>46083.86179406563</v>
+        <v>46083.8617940625</v>
       </c>
       <c r="K684" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         </is>
       </c>
       <c r="J685" s="2" t="n">
-        <v>46073.94512740221</v>
+        <v>46073.94512740741</v>
       </c>
       <c r="K685" t="inlineStr">
         <is>
@@ -35416,7 +35416,7 @@
         </is>
       </c>
       <c r="J686" s="2" t="n">
-        <v>46081.7784607387</v>
+        <v>46081.77846074074</v>
       </c>
       <c r="K686" t="inlineStr">
         <is>
@@ -35467,7 +35467,7 @@
         </is>
       </c>
       <c r="J687" s="2" t="n">
-        <v>46076.77846074195</v>
+        <v>46076.77846074074</v>
       </c>
       <c r="K687" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         </is>
       </c>
       <c r="J688" s="2" t="n">
-        <v>46083.6534607451</v>
+        <v>46083.65346074074</v>
       </c>
       <c r="K688" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         </is>
       </c>
       <c r="J689" s="2" t="n">
-        <v>46087.82012741495</v>
+        <v>46087.82012741899</v>
       </c>
       <c r="K689" t="inlineStr">
         <is>
@@ -35620,7 +35620,7 @@
         </is>
       </c>
       <c r="J690" s="2" t="n">
-        <v>46060.86179408475</v>
+        <v>46060.86179408565</v>
       </c>
       <c r="K690" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         </is>
       </c>
       <c r="J691" s="2" t="n">
-        <v>46076.94512742122</v>
+        <v>46076.94512741899</v>
       </c>
       <c r="K691" t="inlineStr">
         <is>
@@ -35722,7 +35722,7 @@
         </is>
       </c>
       <c r="J692" s="2" t="n">
-        <v>46077.90346075765</v>
+        <v>46077.90346075231</v>
       </c>
       <c r="K692" t="inlineStr">
         <is>
@@ -35773,7 +35773,7 @@
         </is>
       </c>
       <c r="J693" s="2" t="n">
-        <v>46070.820127428</v>
+        <v>46070.82012743055</v>
       </c>
       <c r="K693" t="inlineStr">
         <is>
@@ -35824,7 +35824,7 @@
         </is>
       </c>
       <c r="J694" s="2" t="n">
-        <v>46059.86179409815</v>
+        <v>46059.86179409723</v>
       </c>
       <c r="K694" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         </is>
       </c>
       <c r="J695" s="2" t="n">
-        <v>46070.65346076785</v>
+        <v>46070.65346076389</v>
       </c>
       <c r="K695" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         </is>
       </c>
       <c r="J696" s="2" t="n">
-        <v>46063.02846077086</v>
+        <v>46063.02846077547</v>
       </c>
       <c r="K696" t="inlineStr">
         <is>
@@ -35977,7 +35977,7 @@
         </is>
       </c>
       <c r="J697" s="2" t="n">
-        <v>46082.90346077413</v>
+        <v>46082.90346077547</v>
       </c>
       <c r="K697" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         </is>
       </c>
       <c r="J698" s="2" t="n">
-        <v>46073.82012744399</v>
+        <v>46073.82012744213</v>
       </c>
       <c r="K698" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="J699" s="2" t="n">
-        <v>46069.73679411387</v>
+        <v>46069.73679410879</v>
       </c>
       <c r="K699" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         </is>
       </c>
       <c r="J700" s="2" t="n">
-        <v>46072.94512745036</v>
+        <v>46072.94512745371</v>
       </c>
       <c r="K700" t="inlineStr">
         <is>
@@ -36181,11 +36181,2561 @@
         </is>
       </c>
       <c r="J701" s="2" t="n">
-        <v>46076.9867941203</v>
+        <v>46076.98679412037</v>
       </c>
       <c r="K701" t="inlineStr">
         <is>
           <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>ab115894-0dc7-4556-b63d-a044d0f50549</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>35aa2688-4610-4dac-8329-49519fb81a39</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E702" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F702" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>OP-830</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J702" s="2" t="n">
+        <v>46077.05318133988</v>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>64fafeaf-0d7d-4ae6-8227-e811554b9292</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>5b89f551-babc-4982-8875-556751dc288e</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E703" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F703" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>OP-296</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J703" s="2" t="n">
+        <v>46083.6781813441</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>0618bb32-f5e7-4849-a562-b55213829eb7</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>5786831b-8a66-44f2-aa16-e7492c82926b</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E704" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F704" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>OP-932</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J704" s="2" t="n">
+        <v>46087.88651468074</v>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2fcef5bb-1254-4841-8712-197b096ea646</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>8fdb9fdb-afef-437f-a2cd-08565e8a0480</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E705" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F705" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>OP-290</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J705" s="2" t="n">
+        <v>46069.84484801729</v>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>c50cbe5c-4c57-441a-b30a-05338a516634</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>b35949de-3dfb-4ba6-821e-ea840ebe883a</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E706" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F706" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>OP-123</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J706" s="2" t="n">
+        <v>46087.0115146868</v>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>d20cf049-a870-44a6-bcb9-c61f757f7baf</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>f7c6ebe6-e509-497f-9cbe-7b705b7272b5</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E707" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F707" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>OP-286</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J707" s="2" t="n">
+        <v>46077.96984802309</v>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>fb27533a-9db4-4690-871a-8ac129d903df</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>f79ad350-2ad4-495a-9723-309aa26a9a56</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E708" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F708" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>OP-584</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J708" s="2" t="n">
+        <v>46082.05318135941</v>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>71372a63-9530-45ca-b560-4d808b608a45</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>6cfc439b-196e-4a2d-a26f-27d348483dd3</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E709" t="n">
+        <v>0</v>
+      </c>
+      <c r="F709" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>OP-382</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J709" s="2" t="n">
+        <v>46063.0115146957</v>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>7a4d94b2-d1d8-4ca3-9141-b249c84bda4d</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>ade4dfbf-d42b-40f7-99a5-a1d5b733f301</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E710" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F710" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>OP-361</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J710" s="2" t="n">
+        <v>46061.92818136549</v>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>eb1a2d9b-1130-4566-af10-5a7ef20ac841</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>7eb34511-5578-4724-b6fa-49fb9727f7f8</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E711" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F711" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>OP-206</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J711" s="2" t="n">
+        <v>46069.67818136839</v>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>94545cb8-d365-4e13-b99d-645db23b41ce</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>e8d84f66-4034-44c4-8d21-6de99927041d</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E712" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F712" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>OP-532</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J712" s="2" t="n">
+        <v>46069.80318137155</v>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>5d74dc07-ea5e-42ee-bd7a-f7355b6b7db5</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>2a1bc2c5-77cd-4203-9045-38933e5efd81</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E713" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F713" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>OP-367</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J713" s="2" t="n">
+        <v>46060.76151470779</v>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>770d2b25-cfb6-4128-ab97-8d2a11b14ebd</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>01677c6b-8d51-43d1-863d-0619175f13fa</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E714" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F714" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>OP-134</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J714" s="2" t="n">
+        <v>46067.01151471069</v>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>ceb19eca-e4d8-4ebf-8b4a-60a2e842f8a7</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>628714d0-ef00-4a6b-a2d0-30c82040a3e4</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E715" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F715" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>OP-395</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J715" s="2" t="n">
+        <v>46061.96984804693</v>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>de02c99f-9836-4b71-9351-047bfbe743b8</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>f7a5e412-964d-47c8-b1bd-9d705a0018c6</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E716" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F716" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>OP-647</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J716" s="2" t="n">
+        <v>46085.01151471637</v>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>65148668-edff-4a46-aba1-fec71490448d</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>a5baf645-5c6a-47dd-be45-4b96104ee25b</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E717" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F717" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>OP-392</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J717" s="2" t="n">
+        <v>46068.80318138587</v>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>636e4852-8ce0-4be1-b2f0-2a4a63720d75</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>d9ba2d5c-e81d-4dda-959f-8da6cf67c3e2</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E718" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F718" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>OP-371</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J718" s="2" t="n">
+        <v>46088.80318138881</v>
+      </c>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>e023f302-7678-4dc6-b62a-cdbb76db84a1</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>ad575945-0ffb-4bcc-8d2b-98ee38a0753e</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E719" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F719" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>OP-127</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J719" s="2" t="n">
+        <v>46064.01151472513</v>
+      </c>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>8dd011aa-1763-4671-b8de-c670ba2a6d13</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>6eb031f5-7aad-44b8-8e09-3111ccad9cd5</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E720" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F720" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>OP-633</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J720" s="2" t="n">
+        <v>46080.01151472817</v>
+      </c>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>01aae85f-193e-42d2-a812-6afcd9778519</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>52f04c7f-62b1-4b1f-bcb1-6cdfd5196825</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E721" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F721" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>OP-117</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J721" s="2" t="n">
+        <v>46077.84484806438</v>
+      </c>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>9d468221-f796-4257-9716-64261706835e</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>20cf546d-c0cd-4544-bc1f-5141b26749ef</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E722" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F722" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>OP-500</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J722" s="2" t="n">
+        <v>46075.92818140052</v>
+      </c>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2eeac431-5a0d-4585-9a21-67a30d525e17</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>3332f984-c78d-43c4-a9f6-d8ccd68f975b</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E723" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F723" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>OP-936</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J723" s="2" t="n">
+        <v>46079.01151473675</v>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>6fec910e-9a66-4108-bde8-3cedf57418b0</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>c75a6c59-e493-4467-b660-dad12e3401ac</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>OP-935</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J724" s="2" t="n">
+        <v>46080.88651473955</v>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>9518fe1b-1f48-464f-aa4e-0f1a77d9a380</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>e940d1e4-0acf-4d9e-b5e1-d8b10596b24a</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F725" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>OP-831</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J725" s="2" t="n">
+        <v>46082.84484807581</v>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>1f0d4fc6-5fbc-4e67-9691-03d33fbf8bf1</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>c9028daa-5f41-4c46-b87b-9cc5609f5b31</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F726" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>OP-841</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J726" s="2" t="n">
+        <v>46073.67818141205</v>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>581490fc-6647-4717-93af-190b3a3b24a5</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>079105b9-cef6-453e-88f8-2bf4491273ce</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F727" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>OP-970</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J727" s="2" t="n">
+        <v>46060.05318141505</v>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>e83ad3ee-49f8-4924-b13e-236b1359dc8d</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>facfe198-cdd9-4503-829e-39fa06644086</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E728" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F728" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>OP-364</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J728" s="2" t="n">
+        <v>46080.92818141806</v>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>8ad90062-3a35-4145-8d02-a1ae44aedfa3</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>8760a690-8a67-4ee4-bcbd-52aa87117a45</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E729" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F729" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>OP-605</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J729" s="2" t="n">
+        <v>46081.88651475419</v>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>f7531649-8dab-4a90-972c-513f5b42100a</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>f574277e-a113-41ef-9013-10321d51cf7c</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E730" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F730" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>OP-608</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J730" s="2" t="n">
+        <v>46064.88651475698</v>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>be95a961-d835-4402-b76f-6eeb235428a4</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>c537c210-f6ad-4224-bdd3-4a8f57e1f605</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E731" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F731" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>OP-406</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J731" s="2" t="n">
+        <v>46086.67818142667</v>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>3b7d9f88-cd5d-4e07-b22b-5e3e6e05d8a0</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>ad5afe57-d10d-4e1d-9073-4b427096c69e</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E732" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F732" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>OP-724</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J732" s="2" t="n">
+        <v>46080.71984809622</v>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>ca9028a3-365a-4f0b-8189-f24e04fb4c59</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>298f2a77-ae3d-4bd9-a39f-1fa781eb3261</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E733" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F733" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>OP-116</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J733" s="2" t="n">
+        <v>46077.88651476572</v>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>f29c7541-2115-46c8-ae7a-e6628252c3df</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>eb60a40c-d999-428e-b81a-3c9737a07930</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E734" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F734" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>OP-931</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J734" s="2" t="n">
+        <v>46076.05318143526</v>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>ca552392-6439-4592-85b4-489158419f0a</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>fe2f7ddf-c47f-4b59-85d9-cc1be9488a26</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E735" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F735" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>OP-370</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J735" s="2" t="n">
+        <v>46077.84484810499</v>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>e2f26816-c364-4ce8-9acf-bf70b424374d</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>81e9aba8-d0af-4dbc-af74-e25b3e84817e</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E736" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F736" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>OP-544</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J736" s="2" t="n">
+        <v>46087.76151477442</v>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>6f6a1960-f774-4f5e-bd1f-7cbef3867399</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>ece9f276-5821-4901-b49d-2f942b3471f8</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E737" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F737" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>OP-526</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J737" s="2" t="n">
+        <v>46077.9698481106</v>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>6409f4a8-7125-4134-b0a8-2aad71d4ed41</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>5d7787cb-7f5f-45f1-942d-a99b6564d550</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E738" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F738" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>OP-549</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J738" s="2" t="n">
+        <v>46082.01151478009</v>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>1d694479-46af-41ef-a565-90134034705f</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>fec6a825-caf6-44df-bfce-d992e57deaf6</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E739" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F739" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>OP-209</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J739" s="2" t="n">
+        <v>46070.80318144978</v>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>86ea1dba-42d4-4133-9ce3-00319f10101b</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>dde62b51-867f-4cae-b258-d99052e21b62</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E740" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F740" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>OP-524</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J740" s="2" t="n">
+        <v>46082.92818145256</v>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>da36842f-994e-43cf-8300-047e4e715263</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>06d2f2d5-9c46-49eb-819c-6fa3c6cac829</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E741" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F741" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>OP-519</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J741" s="2" t="n">
+        <v>46067.84484812206</v>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>32db8a78-9bba-43de-a240-fc3f82bda08f</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>cf047088-b027-4b5e-ba75-59a492210609</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E742" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F742" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>OP-809</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J742" s="2" t="n">
+        <v>46077.84484812486</v>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>c24ab201-510b-4ded-8d5a-25aad13f319b</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>0a09acdd-3439-413f-9023-581788539b59</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E743" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F743" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>OP-327</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J743" s="2" t="n">
+        <v>46072.67818146103</v>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>edb2f52b-b9a2-4435-86bd-0fe7f6d0439d</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>41d345fe-73b0-4957-979b-7e6d1892a6dc</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E744" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F744" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>OP-242</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J744" s="2" t="n">
+        <v>46085.92818146426</v>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>0d73856a-e127-40c9-8f1a-6fdfa0ed801c</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>71b3478f-44d1-4729-aef1-4795e2514d29</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E745" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F745" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>OP-131</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J745" s="2" t="n">
+        <v>46060.05318146706</v>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>e28107d4-f179-4a67-b4e5-013b2d024bf7</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>c3679b77-77d2-45f1-8375-d8741acce97a</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E746" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F746" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>OP-756</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J746" s="2" t="n">
+        <v>46084.80318146988</v>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>4abc9b95-5176-487c-89a6-01d943a3de5f</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>e1ad3d75-e7fa-4904-823d-a69a086b704e</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E747" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F747" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>OP-551</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J747" s="2" t="n">
+        <v>46063.71984813941</v>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>dd8e8625-2bcb-442d-9fd8-e8095de8757f</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>bbf6d2c2-5c02-474e-acce-1fa06ac68ada</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E748" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F748" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>OP-536</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J748" s="2" t="n">
+        <v>46072.011514809</v>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>dc89a74f-5fd5-4b47-a0c2-e762c0334cd7</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>e1efef48-47b6-4a2e-9fad-571b4cab21ea</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E749" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F749" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>OP-482</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J749" s="2" t="n">
+        <v>46071.71984814527</v>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>93c3fd66-7bee-45c3-81da-2d2df0f67552</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>1f18f7f9-09ea-4e33-835d-5889fb7739f4</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E750" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F750" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>OP-660</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J750" s="2" t="n">
+        <v>46071.84484814803</v>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>b47a1cb1-7a2a-4930-a427-2ab708fea150</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>c571bdcd-200b-4cda-8f28-8c1f4e4ec856</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E751" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F751" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>OP-285</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J751" s="2" t="n">
+        <v>46071.84484815088</v>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K751"/>
+  <dimension ref="A1:K801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36232,7 +36232,7 @@
         </is>
       </c>
       <c r="J702" s="2" t="n">
-        <v>46077.05318133988</v>
+        <v>46077.05318134259</v>
       </c>
       <c r="K702" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         </is>
       </c>
       <c r="J703" s="2" t="n">
-        <v>46083.6781813441</v>
+        <v>46083.67818134259</v>
       </c>
       <c r="K703" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         </is>
       </c>
       <c r="J704" s="2" t="n">
-        <v>46087.88651468074</v>
+        <v>46087.88651467593</v>
       </c>
       <c r="K704" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         </is>
       </c>
       <c r="J705" s="2" t="n">
-        <v>46069.84484801729</v>
+        <v>46069.84484802083</v>
       </c>
       <c r="K705" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         </is>
       </c>
       <c r="J706" s="2" t="n">
-        <v>46087.0115146868</v>
+        <v>46087.0115146875</v>
       </c>
       <c r="K706" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         </is>
       </c>
       <c r="J707" s="2" t="n">
-        <v>46077.96984802309</v>
+        <v>46077.96984802083</v>
       </c>
       <c r="K707" t="inlineStr">
         <is>
@@ -36538,7 +36538,7 @@
         </is>
       </c>
       <c r="J708" s="2" t="n">
-        <v>46082.05318135941</v>
+        <v>46082.05318135417</v>
       </c>
       <c r="K708" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         </is>
       </c>
       <c r="J709" s="2" t="n">
-        <v>46063.0115146957</v>
+        <v>46063.01151469907</v>
       </c>
       <c r="K709" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         </is>
       </c>
       <c r="J710" s="2" t="n">
-        <v>46061.92818136549</v>
+        <v>46061.92818136574</v>
       </c>
       <c r="K710" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         </is>
       </c>
       <c r="J711" s="2" t="n">
-        <v>46069.67818136839</v>
+        <v>46069.67818136574</v>
       </c>
       <c r="K711" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         </is>
       </c>
       <c r="J712" s="2" t="n">
-        <v>46069.80318137155</v>
+        <v>46069.80318137731</v>
       </c>
       <c r="K712" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         </is>
       </c>
       <c r="J713" s="2" t="n">
-        <v>46060.76151470779</v>
+        <v>46060.76151471065</v>
       </c>
       <c r="K713" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         </is>
       </c>
       <c r="J714" s="2" t="n">
-        <v>46067.01151471069</v>
+        <v>46067.01151471065</v>
       </c>
       <c r="K714" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         </is>
       </c>
       <c r="J715" s="2" t="n">
-        <v>46061.96984804693</v>
+        <v>46061.96984804398</v>
       </c>
       <c r="K715" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         </is>
       </c>
       <c r="J716" s="2" t="n">
-        <v>46085.01151471637</v>
+        <v>46085.01151471065</v>
       </c>
       <c r="K716" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         </is>
       </c>
       <c r="J717" s="2" t="n">
-        <v>46068.80318138587</v>
+        <v>46068.80318138889</v>
       </c>
       <c r="K717" t="inlineStr">
         <is>
@@ -37048,7 +37048,7 @@
         </is>
       </c>
       <c r="J718" s="2" t="n">
-        <v>46088.80318138881</v>
+        <v>46088.80318138889</v>
       </c>
       <c r="K718" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         </is>
       </c>
       <c r="J719" s="2" t="n">
-        <v>46064.01151472513</v>
+        <v>46064.01151472222</v>
       </c>
       <c r="K719" t="inlineStr">
         <is>
@@ -37150,7 +37150,7 @@
         </is>
       </c>
       <c r="J720" s="2" t="n">
-        <v>46080.01151472817</v>
+        <v>46080.01151473379</v>
       </c>
       <c r="K720" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         </is>
       </c>
       <c r="J721" s="2" t="n">
-        <v>46077.84484806438</v>
+        <v>46077.84484806713</v>
       </c>
       <c r="K721" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         </is>
       </c>
       <c r="J722" s="2" t="n">
-        <v>46075.92818140052</v>
+        <v>46075.92818140046</v>
       </c>
       <c r="K722" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         </is>
       </c>
       <c r="J723" s="2" t="n">
-        <v>46079.01151473675</v>
+        <v>46079.01151473379</v>
       </c>
       <c r="K723" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         </is>
       </c>
       <c r="J724" s="2" t="n">
-        <v>46080.88651473955</v>
+        <v>46080.88651473379</v>
       </c>
       <c r="K724" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         </is>
       </c>
       <c r="J725" s="2" t="n">
-        <v>46082.84484807581</v>
+        <v>46082.8448480787</v>
       </c>
       <c r="K725" t="inlineStr">
         <is>
@@ -37456,7 +37456,7 @@
         </is>
       </c>
       <c r="J726" s="2" t="n">
-        <v>46073.67818141205</v>
+        <v>46073.67818141204</v>
       </c>
       <c r="K726" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         </is>
       </c>
       <c r="J727" s="2" t="n">
-        <v>46060.05318141505</v>
+        <v>46060.05318141204</v>
       </c>
       <c r="K727" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         </is>
       </c>
       <c r="J728" s="2" t="n">
-        <v>46080.92818141806</v>
+        <v>46080.92818142361</v>
       </c>
       <c r="K728" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         </is>
       </c>
       <c r="J729" s="2" t="n">
-        <v>46081.88651475419</v>
+        <v>46081.88651475694</v>
       </c>
       <c r="K729" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         </is>
       </c>
       <c r="J730" s="2" t="n">
-        <v>46064.88651475698</v>
+        <v>46064.88651475694</v>
       </c>
       <c r="K730" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         </is>
       </c>
       <c r="J731" s="2" t="n">
-        <v>46086.67818142667</v>
+        <v>46086.67818142361</v>
       </c>
       <c r="K731" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         </is>
       </c>
       <c r="J732" s="2" t="n">
-        <v>46080.71984809622</v>
+        <v>46080.71984810185</v>
       </c>
       <c r="K732" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         </is>
       </c>
       <c r="J733" s="2" t="n">
-        <v>46077.88651476572</v>
+        <v>46077.88651476852</v>
       </c>
       <c r="K733" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         </is>
       </c>
       <c r="J734" s="2" t="n">
-        <v>46076.05318143526</v>
+        <v>46076.05318143519</v>
       </c>
       <c r="K734" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         </is>
       </c>
       <c r="J735" s="2" t="n">
-        <v>46077.84484810499</v>
+        <v>46077.84484810185</v>
       </c>
       <c r="K735" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="J736" s="2" t="n">
-        <v>46087.76151477442</v>
+        <v>46087.76151478009</v>
       </c>
       <c r="K736" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         </is>
       </c>
       <c r="J737" s="2" t="n">
-        <v>46077.9698481106</v>
+        <v>46077.96984811343</v>
       </c>
       <c r="K737" t="inlineStr">
         <is>
@@ -38119,7 +38119,7 @@
         </is>
       </c>
       <c r="J739" s="2" t="n">
-        <v>46070.80318144978</v>
+        <v>46070.80318144676</v>
       </c>
       <c r="K739" t="inlineStr">
         <is>
@@ -38170,7 +38170,7 @@
         </is>
       </c>
       <c r="J740" s="2" t="n">
-        <v>46082.92818145256</v>
+        <v>46082.92818145833</v>
       </c>
       <c r="K740" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         </is>
       </c>
       <c r="J741" s="2" t="n">
-        <v>46067.84484812206</v>
+        <v>46067.844848125</v>
       </c>
       <c r="K741" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         </is>
       </c>
       <c r="J742" s="2" t="n">
-        <v>46077.84484812486</v>
+        <v>46077.844848125</v>
       </c>
       <c r="K742" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         </is>
       </c>
       <c r="J743" s="2" t="n">
-        <v>46072.67818146103</v>
+        <v>46072.67818145833</v>
       </c>
       <c r="K743" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         </is>
       </c>
       <c r="J744" s="2" t="n">
-        <v>46085.92818146426</v>
+        <v>46085.92818146991</v>
       </c>
       <c r="K744" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         </is>
       </c>
       <c r="J745" s="2" t="n">
-        <v>46060.05318146706</v>
+        <v>46060.05318146991</v>
       </c>
       <c r="K745" t="inlineStr">
         <is>
@@ -38476,7 +38476,7 @@
         </is>
       </c>
       <c r="J746" s="2" t="n">
-        <v>46084.80318146988</v>
+        <v>46084.80318146991</v>
       </c>
       <c r="K746" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         </is>
       </c>
       <c r="J747" s="2" t="n">
-        <v>46063.71984813941</v>
+        <v>46063.71984813658</v>
       </c>
       <c r="K747" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         </is>
       </c>
       <c r="J748" s="2" t="n">
-        <v>46072.011514809</v>
+        <v>46072.01151480324</v>
       </c>
       <c r="K748" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         </is>
       </c>
       <c r="J749" s="2" t="n">
-        <v>46071.71984814527</v>
+        <v>46071.71984814815</v>
       </c>
       <c r="K749" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         </is>
       </c>
       <c r="J750" s="2" t="n">
-        <v>46071.84484814803</v>
+        <v>46071.84484814815</v>
       </c>
       <c r="K750" t="inlineStr">
         <is>
@@ -38731,9 +38731,2559 @@
         </is>
       </c>
       <c r="J751" s="2" t="n">
-        <v>46071.84484815088</v>
+        <v>46071.84484814815</v>
       </c>
       <c r="K751" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>29e82235-e6ef-4008-88be-87f5037da7d0</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>def882b6-def6-42c6-938c-1495d06a3c3c</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E752" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F752" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>OP-714</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J752" s="2" t="n">
+        <v>46068.76314900327</v>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>41ecc12a-8cca-4bd8-9fee-7e08b410344c</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>c92629df-3759-41d5-9132-d27d52263f12</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E753" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F753" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>OP-456</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J753" s="2" t="n">
+        <v>46084.01314900742</v>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>fe66df70-c7f1-4542-bc40-94c460eb3dcb</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>948c1d3d-efdb-40fc-bf6e-f4b39a551456</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E754" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F754" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>OP-194</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J754" s="2" t="n">
+        <v>46067.92981567739</v>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>a70bbb35-c13f-409a-8370-e6cf932b7161</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>061a9842-e334-492e-9e57-10f6a9533380</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E755" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F755" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>OP-823</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J755" s="2" t="n">
+        <v>46061.7631490142</v>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>b7d38239-d104-4322-87cc-d0893d60a19f</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>e39f1e89-dc85-4722-a75c-334d615ebb78</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E756" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F756" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>OP-565</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J756" s="2" t="n">
+        <v>46064.09648235074</v>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>49e945b6-c35e-4875-908a-d78746a8945a</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>17229131-e051-4a61-b82a-9f83bc45863e</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E757" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F757" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>OP-952</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J757" s="2" t="n">
+        <v>46069.01314902051</v>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>8920d2a9-6c9c-4d70-bb09-526eeb894378</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>da2964a6-47c4-40ed-8ab2-5d7da5806f08</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E758" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F758" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>OP-139</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J758" s="2" t="n">
+        <v>46060.846482357</v>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>bf5773d6-9afa-4ce5-b597-88dbd1570f9a</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>dd9508fa-da1a-4b66-b2f7-dfb81cc98eaf</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E759" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F759" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>OP-193</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J759" s="2" t="n">
+        <v>46068.76314902697</v>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>f30876fa-4ac9-4985-adc2-657ea529a515</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>d24cf199-935a-44d4-ada6-a3a992c8c71c</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E760" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F760" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>OP-836</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J760" s="2" t="n">
+        <v>46082.97148236335</v>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>ae067ea7-0236-451c-8a48-76266ba838dc</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>1d1ef314-52f0-4082-9862-13108c87437b</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E761" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F761" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>OP-748</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J761" s="2" t="n">
+        <v>46076.72148236653</v>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>91745605-981c-498d-bb2b-56a98a27dae5</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>4ae48d55-eb7f-4c10-a390-9dd89386963c</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E762" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F762" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>OP-251</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J762" s="2" t="n">
+        <v>46062.76314903648</v>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>c3f08d42-b75a-4f35-be8e-a87ebad0e4e1</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>b9fcfad8-fdeb-457a-a843-8df49df72a02</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E763" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F763" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>OP-610</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J763" s="2" t="n">
+        <v>46068.80481570633</v>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>a7ad04f0-8539-4d01-9c02-e1ec06a76140</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>bcd1dd37-a81a-4eb5-80a3-554f841982a2</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E764" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F764" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>OP-980</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J764" s="2" t="n">
+        <v>46077.76314904271</v>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>becd5abc-3802-460c-92d3-9b1176ca2cf7</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>53ff8292-39e0-42be-b2cd-674b6c8237c0</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E765" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F765" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>OP-542</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J765" s="2" t="n">
+        <v>46073.09648237905</v>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>7e37800c-9dba-4aa2-8e89-ee0c425d811e</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>ee5bd2f6-4903-4311-bb1d-bfc80a97cc86</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E766" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F766" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>OP-990</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J766" s="2" t="n">
+        <v>46085.92981571573</v>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>122d85ca-4921-4a66-99d0-a77e1c9c1976</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>e683cdb2-169d-427f-9988-a1882ec49376</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E767" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F767" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>OP-381</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J767" s="2" t="n">
+        <v>46082.92981571893</v>
+      </c>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>c04d7923-e159-4532-98bb-499a870c0daa</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>ee252fdb-4dab-44ae-a49d-a9f0ecfeafa0</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E768" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F768" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>OP-983</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J768" s="2" t="n">
+        <v>46086.05481572195</v>
+      </c>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>bba71236-3635-4f85-8693-b1a1439484f7</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>48f1e553-b8bf-4462-833e-a9143dd2553c</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E769" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F769" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>OP-512</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J769" s="2" t="n">
+        <v>46072.92981572494</v>
+      </c>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>37896022-e721-41ef-b679-558ea7947319</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>a5121bc6-b739-4ca2-8f6f-35d6f2615db4</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E770" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F770" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>OP-855</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J770" s="2" t="n">
+        <v>46064.0964823948</v>
+      </c>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>7a08b513-d8fb-4d33-b2f8-910f6eda24aa</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>eb1f00ff-1fe1-4943-9f2f-d5743c621a19</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E771" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F771" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>OP-779</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J771" s="2" t="n">
+        <v>46065.92981573135</v>
+      </c>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>dea6d31b-7dae-442f-92dd-0654faf8c3c7</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>ec102bf8-b99f-42c4-a6ab-1216097b7d19</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E772" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F772" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>OP-321</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J772" s="2" t="n">
+        <v>46063.01314906787</v>
+      </c>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>df207a34-1f3f-4383-bb63-94af5f47dffd</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>0173642e-3ca4-45f9-b7b3-e7a8252f38cd</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E773" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F773" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>OP-293</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J773" s="2" t="n">
+        <v>46064.72148240438</v>
+      </c>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>870eff02-b89a-48af-b4f1-af60e68d94b9</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>8183ea22-9000-4f57-b3da-a02cebc5b2ea</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E774" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F774" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>OP-102</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J774" s="2" t="n">
+        <v>46072.09648240746</v>
+      </c>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>8a347091-3308-43ce-a88c-8b3b68d7b24c</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>639a7382-e74b-47f4-b1f7-d3f037edde05</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E775" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F775" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>OP-511</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J775" s="2" t="n">
+        <v>46068.05481574377</v>
+      </c>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>996581bf-cce6-46f8-8372-4294bbe7f53c</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>d8006394-103b-4106-9a7c-fce11b677073</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E776" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F776" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>OP-592</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J776" s="2" t="n">
+        <v>46079.84648241346</v>
+      </c>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>eaee08a7-f8d0-4b12-9b8b-7b23048ecf93</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>88f6f350-56b4-4456-b412-2b48c8714cf3</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E777" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F777" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>OP-870</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J777" s="2" t="n">
+        <v>46066.97148241686</v>
+      </c>
+      <c r="K777" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>1a2caff2-ba94-4841-8e02-5299dbb45f45</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>e4889755-bad3-44fd-a814-2ba395fff6ef</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E778" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F778" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>OP-250</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J778" s="2" t="n">
+        <v>46080.8048157534</v>
+      </c>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>0b53eba1-4123-4e22-a88c-8a59ceb35f7d</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>429319d8-196b-4125-af5c-a90afd03818d</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E779" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F779" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>OP-890</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J779" s="2" t="n">
+        <v>46074.76314908981</v>
+      </c>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>bb2eee2a-1de9-4091-85f1-382647381cd0</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>aeaef3db-23e4-4af5-9d22-85653f916edb</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E780" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F780" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>OP-582</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J780" s="2" t="n">
+        <v>46061.09648242627</v>
+      </c>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>bde931bf-c78f-42c3-827f-bf7d9df5a9aa</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>67483aeb-f661-433a-8026-dc1a19d04a40</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E781" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F781" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>OP-885</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J781" s="2" t="n">
+        <v>46084.92981576294</v>
+      </c>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>1fbbfe29-7bc9-4b03-99a3-ab390851ebb0</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>95d456b7-4823-4913-970a-8967073748d1</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E782" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F782" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>OP-502</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J782" s="2" t="n">
+        <v>46085.0548157663</v>
+      </c>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>006d72cd-8e0a-4999-95f7-7cd425b55fad</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>0418ae8f-6703-4a6c-b83e-b0fe9fd037e4</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E783" t="n">
+        <v>0</v>
+      </c>
+      <c r="F783" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>OP-719</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J783" s="2" t="n">
+        <v>46069.05481576944</v>
+      </c>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>f3bbf1aa-f53c-4d33-9db4-85639f839a94</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>5b41e7cc-006e-4c63-8a1d-85dfff1cc10e</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E784" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F784" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>OP-144</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J784" s="2" t="n">
+        <v>46083.97148243945</v>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>e4ad2fd4-e665-49c4-8c8e-d2ce1a257d00</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>04395110-3b3d-4b75-8f8b-6502f948c986</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E785" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F785" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>OP-263</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J785" s="2" t="n">
+        <v>46077.72148244249</v>
+      </c>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>aaaf9da1-2309-4b85-a5d2-7c3c68a037ef</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>784d086b-aa3b-4aa0-8ad9-4d8f0e1c4d5a</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E786" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F786" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>OP-160</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J786" s="2" t="n">
+        <v>46062.05481577884</v>
+      </c>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>046334f8-6468-456c-8434-bbcdf31cd714</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>9d772244-7f72-4a63-93d9-b46f6536dfbd</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E787" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F787" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>OP-736</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J787" s="2" t="n">
+        <v>46076.0131491154</v>
+      </c>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>f9dbe275-2851-4de8-b092-fd253c805f8a</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>1752cca5-ce66-48aa-8ad0-b583c45e3cf4</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E788" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F788" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>OP-668</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J788" s="2" t="n">
+        <v>46065.01314911868</v>
+      </c>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>102c0ae4-5534-4542-b1be-7a05a8eee24a</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>92a43823-016b-4402-9f11-123ef62af4f9</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E789" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F789" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>OP-968</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J789" s="2" t="n">
+        <v>46074.92981578839</v>
+      </c>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>d48ebe8e-d2ef-48a4-825f-9a28c91da1da</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>d03a8487-3061-4bc7-b510-eff9d3910d1d</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E790" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F790" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>OP-477</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J790" s="2" t="n">
+        <v>46082.9298157914</v>
+      </c>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>3b743979-b28e-466f-92a1-7733e4c2be3d</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>a06ded3f-56ec-457e-aa98-750bbd584cf7</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E791" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F791" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>OP-239</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J791" s="2" t="n">
+        <v>46071.80481579489</v>
+      </c>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>20430339-3c28-48cc-9792-cf72b1af3b07</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>fa8bc42b-413a-444f-953c-1e8e954d680c</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E792" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F792" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>OP-677</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J792" s="2" t="n">
+        <v>46079.72148246464</v>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>d957c05a-a2f1-46f9-8b03-b27deb05bc7e</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>2a30d9c7-fe48-47a5-b02c-62036ea6212a</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E793" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F793" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>OP-145</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J793" s="2" t="n">
+        <v>46085.88814913433</v>
+      </c>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>f9e12d06-c6cd-4639-896a-708283450ccf</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>dc2dcf9c-646c-4875-800f-75faf2c477af</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E794" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F794" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>OP-896</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J794" s="2" t="n">
+        <v>46086.97148247073</v>
+      </c>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>98087abb-8480-4289-a93d-cb1a63f44a7b</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>3a17ede1-b206-455b-9cf9-2c400522dcb6</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E795" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F795" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>OP-409</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J795" s="2" t="n">
+        <v>46076.88814914069</v>
+      </c>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>07d4cfde-ee89-4554-adba-657b97dd52a9</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>21b19f56-3bea-46b9-af6a-58e810292df8</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E796" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F796" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>OP-139</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J796" s="2" t="n">
+        <v>46060.88814914373</v>
+      </c>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>f31452f1-dc21-4287-b5c2-c929c07aef87</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>98621bb2-d51c-4362-83d6-8fb319ee80da</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E797" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F797" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>OP-614</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J797" s="2" t="n">
+        <v>46088.88814914692</v>
+      </c>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>5c018907-477f-4253-8c91-5e03c16da7c2</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>7b041b20-4548-4d01-9dea-f30c710ef3da</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E798" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F798" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>OP-761</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J798" s="2" t="n">
+        <v>46085.05481581675</v>
+      </c>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>ea4a1efa-ca51-4775-8560-abe6aba357a5</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>559699cf-6ee3-4045-a124-0f566ce5a841</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E799" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F799" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>OP-676</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J799" s="2" t="n">
+        <v>46065.88814915333</v>
+      </c>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>7f048083-e244-49cd-b50c-19be48e00056</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>b84a2a61-3d0c-4680-b66b-e827f4dd39de</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E800" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F800" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>OP-243</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J800" s="2" t="n">
+        <v>46069.09648248982</v>
+      </c>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>71e9cd78-29f2-45b8-8052-c187832ec02a</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>ca46c94f-9fa0-4bb3-b7dc-a9726f10abce</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E801" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F801" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>OP-100</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J801" s="2" t="n">
+        <v>46083.9714824929</v>
+      </c>
+      <c r="K801" t="inlineStr">
         <is>
           <t>good</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K801"/>
+  <dimension ref="A1:K851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38782,7 +38782,7 @@
         </is>
       </c>
       <c r="J752" s="2" t="n">
-        <v>46068.76314900327</v>
+        <v>46068.76314900463</v>
       </c>
       <c r="K752" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         </is>
       </c>
       <c r="J753" s="2" t="n">
-        <v>46084.01314900742</v>
+        <v>46084.01314900463</v>
       </c>
       <c r="K753" t="inlineStr">
         <is>
@@ -38884,7 +38884,7 @@
         </is>
       </c>
       <c r="J754" s="2" t="n">
-        <v>46067.92981567739</v>
+        <v>46067.92981568287</v>
       </c>
       <c r="K754" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         </is>
       </c>
       <c r="J755" s="2" t="n">
-        <v>46061.7631490142</v>
+        <v>46061.7631490162</v>
       </c>
       <c r="K755" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         </is>
       </c>
       <c r="J756" s="2" t="n">
-        <v>46064.09648235074</v>
+        <v>46064.09648234954</v>
       </c>
       <c r="K756" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         </is>
       </c>
       <c r="J757" s="2" t="n">
-        <v>46069.01314902051</v>
+        <v>46069.0131490162</v>
       </c>
       <c r="K757" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         </is>
       </c>
       <c r="J758" s="2" t="n">
-        <v>46060.846482357</v>
+        <v>46060.84648236111</v>
       </c>
       <c r="K758" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         </is>
       </c>
       <c r="J759" s="2" t="n">
-        <v>46068.76314902697</v>
+        <v>46068.76314902778</v>
       </c>
       <c r="K759" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         </is>
       </c>
       <c r="J760" s="2" t="n">
-        <v>46082.97148236335</v>
+        <v>46082.97148236111</v>
       </c>
       <c r="K760" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         </is>
       </c>
       <c r="J761" s="2" t="n">
-        <v>46076.72148236653</v>
+        <v>46076.72148236111</v>
       </c>
       <c r="K761" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         </is>
       </c>
       <c r="J762" s="2" t="n">
-        <v>46062.76314903648</v>
+        <v>46062.76314903935</v>
       </c>
       <c r="K762" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         </is>
       </c>
       <c r="J763" s="2" t="n">
-        <v>46068.80481570633</v>
+        <v>46068.80481570602</v>
       </c>
       <c r="K763" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         </is>
       </c>
       <c r="J764" s="2" t="n">
-        <v>46077.76314904271</v>
+        <v>46077.76314903935</v>
       </c>
       <c r="K764" t="inlineStr">
         <is>
@@ -39445,7 +39445,7 @@
         </is>
       </c>
       <c r="J765" s="2" t="n">
-        <v>46073.09648237905</v>
+        <v>46073.09648238426</v>
       </c>
       <c r="K765" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         </is>
       </c>
       <c r="J766" s="2" t="n">
-        <v>46085.92981571573</v>
+        <v>46085.92981571759</v>
       </c>
       <c r="K766" t="inlineStr">
         <is>
@@ -39547,7 +39547,7 @@
         </is>
       </c>
       <c r="J767" s="2" t="n">
-        <v>46082.92981571893</v>
+        <v>46082.92981571759</v>
       </c>
       <c r="K767" t="inlineStr">
         <is>
@@ -39598,7 +39598,7 @@
         </is>
       </c>
       <c r="J768" s="2" t="n">
-        <v>46086.05481572195</v>
+        <v>46086.05481571759</v>
       </c>
       <c r="K768" t="inlineStr">
         <is>
@@ -39649,7 +39649,7 @@
         </is>
       </c>
       <c r="J769" s="2" t="n">
-        <v>46072.92981572494</v>
+        <v>46072.92981572916</v>
       </c>
       <c r="K769" t="inlineStr">
         <is>
@@ -39700,7 +39700,7 @@
         </is>
       </c>
       <c r="J770" s="2" t="n">
-        <v>46064.0964823948</v>
+        <v>46064.09648239583</v>
       </c>
       <c r="K770" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         </is>
       </c>
       <c r="J771" s="2" t="n">
-        <v>46065.92981573135</v>
+        <v>46065.92981572916</v>
       </c>
       <c r="K771" t="inlineStr">
         <is>
@@ -39802,7 +39802,7 @@
         </is>
       </c>
       <c r="J772" s="2" t="n">
-        <v>46063.01314906787</v>
+        <v>46063.0131490625</v>
       </c>
       <c r="K772" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         </is>
       </c>
       <c r="J773" s="2" t="n">
-        <v>46064.72148240438</v>
+        <v>46064.72148240741</v>
       </c>
       <c r="K773" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         </is>
       </c>
       <c r="J774" s="2" t="n">
-        <v>46072.09648240746</v>
+        <v>46072.09648240741</v>
       </c>
       <c r="K774" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         </is>
       </c>
       <c r="J775" s="2" t="n">
-        <v>46068.05481574377</v>
+        <v>46068.05481574074</v>
       </c>
       <c r="K775" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         </is>
       </c>
       <c r="J776" s="2" t="n">
-        <v>46079.84648241346</v>
+        <v>46079.84648241898</v>
       </c>
       <c r="K776" t="inlineStr">
         <is>
@@ -40057,7 +40057,7 @@
         </is>
       </c>
       <c r="J777" s="2" t="n">
-        <v>46066.97148241686</v>
+        <v>46066.97148241898</v>
       </c>
       <c r="K777" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         </is>
       </c>
       <c r="J778" s="2" t="n">
-        <v>46080.8048157534</v>
+        <v>46080.80481575232</v>
       </c>
       <c r="K778" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         </is>
       </c>
       <c r="J779" s="2" t="n">
-        <v>46074.76314908981</v>
+        <v>46074.76314908565</v>
       </c>
       <c r="K779" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         </is>
       </c>
       <c r="J780" s="2" t="n">
-        <v>46061.09648242627</v>
+        <v>46061.09648243056</v>
       </c>
       <c r="K780" t="inlineStr">
         <is>
@@ -40261,7 +40261,7 @@
         </is>
       </c>
       <c r="J781" s="2" t="n">
-        <v>46084.92981576294</v>
+        <v>46084.92981576389</v>
       </c>
       <c r="K781" t="inlineStr">
         <is>
@@ -40312,7 +40312,7 @@
         </is>
       </c>
       <c r="J782" s="2" t="n">
-        <v>46085.0548157663</v>
+        <v>46085.05481576389</v>
       </c>
       <c r="K782" t="inlineStr">
         <is>
@@ -40363,7 +40363,7 @@
         </is>
       </c>
       <c r="J783" s="2" t="n">
-        <v>46069.05481576944</v>
+        <v>46069.05481576389</v>
       </c>
       <c r="K783" t="inlineStr">
         <is>
@@ -40414,7 +40414,7 @@
         </is>
       </c>
       <c r="J784" s="2" t="n">
-        <v>46083.97148243945</v>
+        <v>46083.97148244213</v>
       </c>
       <c r="K784" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         </is>
       </c>
       <c r="J785" s="2" t="n">
-        <v>46077.72148244249</v>
+        <v>46077.72148244213</v>
       </c>
       <c r="K785" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         </is>
       </c>
       <c r="J786" s="2" t="n">
-        <v>46062.05481577884</v>
+        <v>46062.05481577546</v>
       </c>
       <c r="K786" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         </is>
       </c>
       <c r="J787" s="2" t="n">
-        <v>46076.0131491154</v>
+        <v>46076.01314912037</v>
       </c>
       <c r="K787" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         </is>
       </c>
       <c r="J788" s="2" t="n">
-        <v>46065.01314911868</v>
+        <v>46065.01314912037</v>
       </c>
       <c r="K788" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         </is>
       </c>
       <c r="J789" s="2" t="n">
-        <v>46074.92981578839</v>
+        <v>46074.92981578704</v>
       </c>
       <c r="K789" t="inlineStr">
         <is>
@@ -40720,7 +40720,7 @@
         </is>
       </c>
       <c r="J790" s="2" t="n">
-        <v>46082.9298157914</v>
+        <v>46082.92981578704</v>
       </c>
       <c r="K790" t="inlineStr">
         <is>
@@ -40771,7 +40771,7 @@
         </is>
       </c>
       <c r="J791" s="2" t="n">
-        <v>46071.80481579489</v>
+        <v>46071.80481579861</v>
       </c>
       <c r="K791" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         </is>
       </c>
       <c r="J792" s="2" t="n">
-        <v>46079.72148246464</v>
+        <v>46079.72148246528</v>
       </c>
       <c r="K792" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         </is>
       </c>
       <c r="J793" s="2" t="n">
-        <v>46085.88814913433</v>
+        <v>46085.88814913195</v>
       </c>
       <c r="K793" t="inlineStr">
         <is>
@@ -40924,7 +40924,7 @@
         </is>
       </c>
       <c r="J794" s="2" t="n">
-        <v>46086.97148247073</v>
+        <v>46086.97148246528</v>
       </c>
       <c r="K794" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         </is>
       </c>
       <c r="J795" s="2" t="n">
-        <v>46076.88814914069</v>
+        <v>46076.88814914352</v>
       </c>
       <c r="K795" t="inlineStr">
         <is>
@@ -41026,7 +41026,7 @@
         </is>
       </c>
       <c r="J796" s="2" t="n">
-        <v>46060.88814914373</v>
+        <v>46060.88814914352</v>
       </c>
       <c r="K796" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="J797" s="2" t="n">
-        <v>46088.88814914692</v>
+        <v>46088.88814914352</v>
       </c>
       <c r="K797" t="inlineStr">
         <is>
@@ -41128,7 +41128,7 @@
         </is>
       </c>
       <c r="J798" s="2" t="n">
-        <v>46085.05481581675</v>
+        <v>46085.05481582176</v>
       </c>
       <c r="K798" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         </is>
       </c>
       <c r="J799" s="2" t="n">
-        <v>46065.88814915333</v>
+        <v>46065.88814915509</v>
       </c>
       <c r="K799" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         </is>
       </c>
       <c r="J800" s="2" t="n">
-        <v>46069.09648248982</v>
+        <v>46069.09648248843</v>
       </c>
       <c r="K800" t="inlineStr">
         <is>
@@ -41281,11 +41281,2561 @@
         </is>
       </c>
       <c r="J801" s="2" t="n">
-        <v>46083.9714824929</v>
+        <v>46083.97148248843</v>
       </c>
       <c r="K801" t="inlineStr">
         <is>
           <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>599962a0-65b4-4f81-a8c0-40188e4c5355</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>b1280636-e3ce-4fd4-83fb-2003c154a453</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E802" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F802" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>OP-344</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J802" s="2" t="n">
+        <v>46062.01184223553</v>
+      </c>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>de020897-5858-4b54-84e9-e153b6559f1c</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>c6a4dbc1-f752-41da-8749-21a410731bfa</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E803" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F803" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>OP-479</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J803" s="2" t="n">
+        <v>46079.80350890655</v>
+      </c>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>393367f1-a0b9-4d27-91ca-7c1edf43ee9d</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>6b719db8-d872-4401-b8b7-cff1f1a8cbdc</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E804" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F804" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>OP-207</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J804" s="2" t="n">
+        <v>46084.76184224326</v>
+      </c>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>b93c2ca3-ca80-4c1a-a952-5d28256bceaa</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>37cdf58e-e19b-43f7-a2e2-b68fa6a4e9f3</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E805" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F805" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>OP-928</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J805" s="2" t="n">
+        <v>46082.97017557982</v>
+      </c>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>96ebf568-eec4-4d82-8895-f3ebd284f539</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>7934b399-37d5-45b6-a6b9-88ab62284696</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E806" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F806" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>OP-698</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J806" s="2" t="n">
+        <v>46082.84517558294</v>
+      </c>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>a113c2e1-efa6-41fd-bc7e-b31f95943620</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>215dac92-3b8a-4048-9492-afcbb38b6741</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E807" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F807" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>OP-863</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J807" s="2" t="n">
+        <v>46078.09517558666</v>
+      </c>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>140b23fa-84a2-4eea-9dcf-9719b2454893</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>03185e8e-1460-4bf0-94e5-ac5bef028002</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E808" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F808" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>OP-491</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J808" s="2" t="n">
+        <v>46072.97017558973</v>
+      </c>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>0922025a-d5a1-42c8-9b4e-cfb028535137</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>09a00b98-2a99-482d-bf63-db20b449c231</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E809" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F809" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>OP-640</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J809" s="2" t="n">
+        <v>46072.97017559287</v>
+      </c>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>ad9ed5d5-a40f-4460-a4e3-bf755814fd90</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>db0bb19c-1b2b-466e-a2e7-fb1fcbdfa089</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E810" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F810" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>OP-539</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J810" s="2" t="n">
+        <v>46062.84517559685</v>
+      </c>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>a93abe0d-f558-423e-9073-858a42bec133</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>0a62276d-a1a8-477a-9b9e-4e36075570d4</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E811" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F811" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>OP-557</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J811" s="2" t="n">
+        <v>46063.97017560013</v>
+      </c>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>46040bc4-9936-4d08-b055-b9c8eb233e42</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>bece8b1d-7d8e-4589-a5e7-66a1213fa737</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E812" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F812" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>OP-692</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J812" s="2" t="n">
+        <v>46066.88684227015</v>
+      </c>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>fe73b568-957c-476a-a1c1-572906d200fe</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>79dffc75-b06a-49a7-938f-65f7da965b17</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E813" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F813" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>OP-445</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J813" s="2" t="n">
+        <v>46083.0118422736</v>
+      </c>
+      <c r="K813" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>039350a6-fa94-491d-9fd3-56eaae8476a4</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>da953338-d740-4e2e-9aec-31ca59b1f3b1</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E814" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F814" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>OP-557</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J814" s="2" t="n">
+        <v>46076.76184227677</v>
+      </c>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2298d754-b97c-47b8-96b5-71ce479a8726</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>2e0fb77e-5499-421b-996d-2aea1fe4ae10</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E815" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F815" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>OP-645</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J815" s="2" t="n">
+        <v>46071.13684227983</v>
+      </c>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>b806dbe0-017b-4efe-a4a5-b144ea918c05</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>40a698cc-ad4b-48a2-8242-35f0dea4083c</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E816" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F816" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>OP-771</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J816" s="2" t="n">
+        <v>46066.84517561622</v>
+      </c>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>3fd4bd8c-3e2f-4ba7-b523-2b81f942838e</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>de3df5c4-c47e-4a7c-8c62-10124aba11bb</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E817" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F817" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>OP-659</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J817" s="2" t="n">
+        <v>46075.84517561949</v>
+      </c>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>c06bc7c5-92ff-45b9-86bc-bea74ea5cd42</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>c5ea309c-4537-438f-8cd8-cdbc21cd9ddd</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E818" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F818" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>OP-182</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J818" s="2" t="n">
+        <v>46087.84517562253</v>
+      </c>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>10b64d67-1061-467d-8539-26d656c684fc</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>0f0fd362-0345-4d85-9d1a-8b0c18e939e0</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E819" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F819" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>OP-240</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J819" s="2" t="n">
+        <v>46073.05350895908</v>
+      </c>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>80277205-e97e-47bf-856b-ebdb274e7e51</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>b49bcc59-b5e9-4a3e-ba45-2e6e8c077cc0</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E820" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F820" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>OP-249</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J820" s="2" t="n">
+        <v>46072.76184229548</v>
+      </c>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>eb921169-b18d-447e-95ba-af8ac742282d</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>4dfd08ec-de9e-4737-86af-8fbda7edc363</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E821" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F821" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>OP-734</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J821" s="2" t="n">
+        <v>46083.01184229885</v>
+      </c>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>b3f44dc7-2c3a-4198-bcde-c6ebd1ee12a1</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>bd09e1c4-7972-47bd-ad09-d707e6358385</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E822" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F822" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>OP-785</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J822" s="2" t="n">
+        <v>46070.92850896858</v>
+      </c>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>49893667-d265-447f-9af0-5802f995bf10</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>deea15e2-8f12-4453-b6d1-8de07a91dd81</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E823" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F823" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>OP-887</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J823" s="2" t="n">
+        <v>46078.09517563834</v>
+      </c>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>0db29ada-047e-433b-83eb-bfe1fb6eb0b6</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>1a9d9071-6d5b-4907-b755-30980f2aa9ea</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E824" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F824" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>OP-208</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J824" s="2" t="n">
+        <v>46075.01184230853</v>
+      </c>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>41f35079-f344-41bd-9b1b-5722fb44201a</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>7918a951-f712-43d8-82da-29c50f53b2d4</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E825" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F825" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>OP-106</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J825" s="2" t="n">
+        <v>46068.01184231164</v>
+      </c>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>4509fc8c-48be-42f7-b718-4cec53d24e70</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>aa0d1ca4-0bdd-40e3-916d-4c8ccd6263da</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E826" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F826" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>OP-150</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J826" s="2" t="n">
+        <v>46083.01184231482</v>
+      </c>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>5c3ca286-bc59-41b6-9abf-108d8aec8df8</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>04b4622d-0934-4bde-ad68-378e5cba3bee</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E827" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F827" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>OP-706</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J827" s="2" t="n">
+        <v>46063.84517565139</v>
+      </c>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>0e9806eb-b325-4986-bb62-0d6114faa8ea</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>7d55820e-b500-4be6-aba6-6e1b54e699f2</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E828" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F828" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>OP-580</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J828" s="2" t="n">
+        <v>46065.92850898793</v>
+      </c>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>7fc83ae7-cd40-4c5b-91a9-f2b59193cc85</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>6cc32273-1b7f-462c-8b65-057dbdda68f0</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E829" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F829" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>OP-998</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J829" s="2" t="n">
+        <v>46084.05350899104</v>
+      </c>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>729ce3c9-3fa4-4248-8eff-4497f26a423c</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>acf20933-63e8-438e-835c-c9ca7c2630b2</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E830" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F830" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>OP-214</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J830" s="2" t="n">
+        <v>46084.92850899405</v>
+      </c>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>4615e259-5e27-4457-8d1f-bed59bbcf647</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>60f472af-3772-4903-a82f-dbd7aa94ff17</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E831" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F831" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>OP-132</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J831" s="2" t="n">
+        <v>46077.09517566382</v>
+      </c>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>63b23fd8-af26-4fb9-af29-9150ef7fe68f</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>40af0366-d9ad-4dd8-b8c6-929bdea9de0e</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E832" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F832" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>OP-358</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J832" s="2" t="n">
+        <v>46088.97017566721</v>
+      </c>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>51f591a0-7b49-4ba7-a0fa-a7881c093114</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>a67911c6-8945-43ce-90b8-254bb38e13d8</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E833" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F833" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>OP-827</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J833" s="2" t="n">
+        <v>46087.13684233694</v>
+      </c>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>470c688d-a9a1-4af0-a649-2eaaff2e5b46</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>d93f8dd0-5fd0-4035-b2ec-18e9a72a6db4</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E834" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F834" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>OP-674</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J834" s="2" t="n">
+        <v>46080.01184234017</v>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>bd9da07c-118f-4f31-a10f-85562b3172e4</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>410d510e-bd75-4122-9725-f0f4f426d478</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E835" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F835" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>OP-740</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J835" s="2" t="n">
+        <v>46084.88684234352</v>
+      </c>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>8b3214d1-d3f1-4fd4-9a6f-9590f6a7fbf1</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>fcc520fd-a135-41ba-a89b-ef711524ac6b</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E836" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F836" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>OP-550</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J836" s="2" t="n">
+        <v>46082.1368423465</v>
+      </c>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>fd9ce9d0-9c4a-425f-bd69-e75956056f24</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>4e9d9df4-65ac-4cbc-97e5-d95bce1106a2</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E837" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F837" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>OP-317</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J837" s="2" t="n">
+        <v>46085.0118423496</v>
+      </c>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>037681cc-c287-457b-b80a-eb4cff927775</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>7e764c48-99d5-4fe8-bb41-74f0455719ff</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E838" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F838" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>OP-844</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J838" s="2" t="n">
+        <v>46076.09517568597</v>
+      </c>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>ee7df9e2-aa69-4a34-bcae-90b3166358be</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>3dfb7c84-20de-41bd-a508-c1ec5f108d6a</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E839" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F839" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>OP-578</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J839" s="2" t="n">
+        <v>46067.76184235626</v>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>62bcdefd-5f5b-4161-a995-e24bdc74a0c3</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>83db7dae-edd6-46b6-9a59-ea31a80cec6c</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E840" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F840" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>OP-118</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J840" s="2" t="n">
+        <v>46068.97017569275</v>
+      </c>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>355481a6-d9c9-4c45-b3dd-34cf89d1e990</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>50409910-90a5-40ef-8968-8132feff19ac</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E841" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F841" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>OP-653</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J841" s="2" t="n">
+        <v>46068.76184236252</v>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>f9639147-04b7-4749-9b9f-451a5cfb95c5</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>8a589903-e137-4a60-82d7-fc0b1da76393</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E842" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F842" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>OP-663</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J842" s="2" t="n">
+        <v>46084.80350903234</v>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>b03008a0-6290-4cb2-9556-713c1047ade5</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>94c8fcd4-f6cc-403f-b81d-2c34859f3312</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E843" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F843" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>OP-114</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J843" s="2" t="n">
+        <v>46062.88684236901</v>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>fcd78d1e-c56c-487f-8c65-ee6fa6be1a34</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>fb82b25e-5718-4a9f-bb2c-8e97185fec6f</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E844" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F844" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>OP-251</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J844" s="2" t="n">
+        <v>46066.92850903874</v>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>ee6240fc-41cf-461b-ac89-f7faffa31692</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>e21d4a4a-d2fb-4d97-a357-22cae8ddf31f</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E845" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F845" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>OP-786</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J845" s="2" t="n">
+        <v>46070.09517570846</v>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>6d786e65-3bfb-4a63-a0fd-d589e02b9836</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>59c74d3e-af1c-4cc5-be6a-be9b340d2fc5</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E846" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F846" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>OP-241</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J846" s="2" t="n">
+        <v>46082.09517571172</v>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>aebc0eb2-3804-44ba-a162-4af9066b9410</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>c3d88499-ee91-486f-8905-9ab7d20ac1aa</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E847" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F847" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>OP-600</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J847" s="2" t="n">
+        <v>46082.84517571703</v>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>e91f1c99-da0a-4ff4-b6a8-d0c3d085ee8c</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>85601bfa-b688-4964-8b0b-a7f8115652ef</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E848" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F848" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>OP-332</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J848" s="2" t="n">
+        <v>46068.84517572085</v>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2a38565a-aa77-4e72-ac13-e3aadaba6bf0</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>bce2ac2a-7daa-446e-9388-63b75860ecac</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E849" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F849" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>OP-583</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J849" s="2" t="n">
+        <v>46065.88684239129</v>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>59097148-c628-4db5-bcb5-2aa961429d14</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>68169296-4328-41f4-a64a-1665ecca8a70</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E850" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F850" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>OP-438</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J850" s="2" t="n">
+        <v>46084.76184239432</v>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>383db848-3836-4477-b4cb-ea73aaa3f4a3</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>3ab75ca7-e7fd-418d-9e7b-80f4bbc48ce4</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E851" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F851" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>OP-110</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J851" s="2" t="n">
+        <v>46074.76184239736</v>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>poor</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K851"/>
+  <dimension ref="A1:K901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41332,7 +41332,7 @@
         </is>
       </c>
       <c r="J802" s="2" t="n">
-        <v>46062.01184223553</v>
+        <v>46062.0118422338</v>
       </c>
       <c r="K802" t="inlineStr">
         <is>
@@ -41383,7 +41383,7 @@
         </is>
       </c>
       <c r="J803" s="2" t="n">
-        <v>46079.80350890655</v>
+        <v>46079.80350891204</v>
       </c>
       <c r="K803" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         </is>
       </c>
       <c r="J804" s="2" t="n">
-        <v>46084.76184224326</v>
+        <v>46084.76184224537</v>
       </c>
       <c r="K804" t="inlineStr">
         <is>
@@ -41485,7 +41485,7 @@
         </is>
       </c>
       <c r="J805" s="2" t="n">
-        <v>46082.97017557982</v>
+        <v>46082.9701755787</v>
       </c>
       <c r="K805" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         </is>
       </c>
       <c r="J806" s="2" t="n">
-        <v>46082.84517558294</v>
+        <v>46082.8451755787</v>
       </c>
       <c r="K806" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         </is>
       </c>
       <c r="J807" s="2" t="n">
-        <v>46078.09517558666</v>
+        <v>46078.09517559028</v>
       </c>
       <c r="K807" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         </is>
       </c>
       <c r="J808" s="2" t="n">
-        <v>46072.97017558973</v>
+        <v>46072.97017559028</v>
       </c>
       <c r="K808" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         </is>
       </c>
       <c r="J809" s="2" t="n">
-        <v>46072.97017559287</v>
+        <v>46072.97017559028</v>
       </c>
       <c r="K809" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         </is>
       </c>
       <c r="J810" s="2" t="n">
-        <v>46062.84517559685</v>
+        <v>46062.84517560185</v>
       </c>
       <c r="K810" t="inlineStr">
         <is>
@@ -41791,7 +41791,7 @@
         </is>
       </c>
       <c r="J811" s="2" t="n">
-        <v>46063.97017560013</v>
+        <v>46063.97017560185</v>
       </c>
       <c r="K811" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         </is>
       </c>
       <c r="J812" s="2" t="n">
-        <v>46066.88684227015</v>
+        <v>46066.88684226852</v>
       </c>
       <c r="K812" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         </is>
       </c>
       <c r="J813" s="2" t="n">
-        <v>46083.0118422736</v>
+        <v>46083.01184226852</v>
       </c>
       <c r="K813" t="inlineStr">
         <is>
@@ -41944,7 +41944,7 @@
         </is>
       </c>
       <c r="J814" s="2" t="n">
-        <v>46076.76184227677</v>
+        <v>46076.7618422801</v>
       </c>
       <c r="K814" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         </is>
       </c>
       <c r="J815" s="2" t="n">
-        <v>46071.13684227983</v>
+        <v>46071.1368422801</v>
       </c>
       <c r="K815" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         </is>
       </c>
       <c r="J816" s="2" t="n">
-        <v>46066.84517561622</v>
+        <v>46066.84517561342</v>
       </c>
       <c r="K816" t="inlineStr">
         <is>
@@ -42097,7 +42097,7 @@
         </is>
       </c>
       <c r="J817" s="2" t="n">
-        <v>46075.84517561949</v>
+        <v>46075.845175625</v>
       </c>
       <c r="K817" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         </is>
       </c>
       <c r="J818" s="2" t="n">
-        <v>46087.84517562253</v>
+        <v>46087.845175625</v>
       </c>
       <c r="K818" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         </is>
       </c>
       <c r="J819" s="2" t="n">
-        <v>46073.05350895908</v>
+        <v>46073.05350895834</v>
       </c>
       <c r="K819" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         </is>
       </c>
       <c r="J820" s="2" t="n">
-        <v>46072.76184229548</v>
+        <v>46072.76184229166</v>
       </c>
       <c r="K820" t="inlineStr">
         <is>
@@ -42301,7 +42301,7 @@
         </is>
       </c>
       <c r="J821" s="2" t="n">
-        <v>46083.01184229885</v>
+        <v>46083.01184230324</v>
       </c>
       <c r="K821" t="inlineStr">
         <is>
@@ -42352,7 +42352,7 @@
         </is>
       </c>
       <c r="J822" s="2" t="n">
-        <v>46070.92850896858</v>
+        <v>46070.9285089699</v>
       </c>
       <c r="K822" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         </is>
       </c>
       <c r="J823" s="2" t="n">
-        <v>46078.09517563834</v>
+        <v>46078.09517563658</v>
       </c>
       <c r="K823" t="inlineStr">
         <is>
@@ -42454,7 +42454,7 @@
         </is>
       </c>
       <c r="J824" s="2" t="n">
-        <v>46075.01184230853</v>
+        <v>46075.01184230324</v>
       </c>
       <c r="K824" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         </is>
       </c>
       <c r="J825" s="2" t="n">
-        <v>46068.01184231164</v>
+        <v>46068.01184231482</v>
       </c>
       <c r="K825" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         </is>
       </c>
       <c r="J827" s="2" t="n">
-        <v>46063.84517565139</v>
+        <v>46063.84517564815</v>
       </c>
       <c r="K827" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         </is>
       </c>
       <c r="J828" s="2" t="n">
-        <v>46065.92850898793</v>
+        <v>46065.92850899306</v>
       </c>
       <c r="K828" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         </is>
       </c>
       <c r="J829" s="2" t="n">
-        <v>46084.05350899104</v>
+        <v>46084.05350899306</v>
       </c>
       <c r="K829" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         </is>
       </c>
       <c r="J830" s="2" t="n">
-        <v>46084.92850899405</v>
+        <v>46084.92850899306</v>
       </c>
       <c r="K830" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         </is>
       </c>
       <c r="J831" s="2" t="n">
-        <v>46077.09517566382</v>
+        <v>46077.09517565972</v>
       </c>
       <c r="K831" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         </is>
       </c>
       <c r="J832" s="2" t="n">
-        <v>46088.97017566721</v>
+        <v>46088.9701756713</v>
       </c>
       <c r="K832" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         </is>
       </c>
       <c r="J833" s="2" t="n">
-        <v>46087.13684233694</v>
+        <v>46087.13684233796</v>
       </c>
       <c r="K833" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         </is>
       </c>
       <c r="J834" s="2" t="n">
-        <v>46080.01184234017</v>
+        <v>46080.01184233796</v>
       </c>
       <c r="K834" t="inlineStr">
         <is>
@@ -43015,7 +43015,7 @@
         </is>
       </c>
       <c r="J835" s="2" t="n">
-        <v>46084.88684234352</v>
+        <v>46084.88684233796</v>
       </c>
       <c r="K835" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         </is>
       </c>
       <c r="J836" s="2" t="n">
-        <v>46082.1368423465</v>
+        <v>46082.13684234954</v>
       </c>
       <c r="K836" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         </is>
       </c>
       <c r="J837" s="2" t="n">
-        <v>46085.0118423496</v>
+        <v>46085.01184234954</v>
       </c>
       <c r="K837" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         </is>
       </c>
       <c r="J838" s="2" t="n">
-        <v>46076.09517568597</v>
+        <v>46076.09517568287</v>
       </c>
       <c r="K838" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         </is>
       </c>
       <c r="J839" s="2" t="n">
-        <v>46067.76184235626</v>
+        <v>46067.76184236111</v>
       </c>
       <c r="K839" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         </is>
       </c>
       <c r="J840" s="2" t="n">
-        <v>46068.97017569275</v>
+        <v>46068.97017569444</v>
       </c>
       <c r="K840" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         </is>
       </c>
       <c r="J841" s="2" t="n">
-        <v>46068.76184236252</v>
+        <v>46068.76184236111</v>
       </c>
       <c r="K841" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         </is>
       </c>
       <c r="J842" s="2" t="n">
-        <v>46084.80350903234</v>
+        <v>46084.80350902778</v>
       </c>
       <c r="K842" t="inlineStr">
         <is>
@@ -43423,7 +43423,7 @@
         </is>
       </c>
       <c r="J843" s="2" t="n">
-        <v>46062.88684236901</v>
+        <v>46062.88684237268</v>
       </c>
       <c r="K843" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         </is>
       </c>
       <c r="J844" s="2" t="n">
-        <v>46066.92850903874</v>
+        <v>46066.92850903935</v>
       </c>
       <c r="K844" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         </is>
       </c>
       <c r="J845" s="2" t="n">
-        <v>46070.09517570846</v>
+        <v>46070.09517570602</v>
       </c>
       <c r="K845" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         </is>
       </c>
       <c r="J846" s="2" t="n">
-        <v>46082.09517571172</v>
+        <v>46082.09517570602</v>
       </c>
       <c r="K846" t="inlineStr">
         <is>
@@ -43627,7 +43627,7 @@
         </is>
       </c>
       <c r="J847" s="2" t="n">
-        <v>46082.84517571703</v>
+        <v>46082.84517571759</v>
       </c>
       <c r="K847" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         </is>
       </c>
       <c r="J848" s="2" t="n">
-        <v>46068.84517572085</v>
+        <v>46068.84517571759</v>
       </c>
       <c r="K848" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         </is>
       </c>
       <c r="J849" s="2" t="n">
-        <v>46065.88684239129</v>
+        <v>46065.88684239583</v>
       </c>
       <c r="K849" t="inlineStr">
         <is>
@@ -43780,7 +43780,7 @@
         </is>
       </c>
       <c r="J850" s="2" t="n">
-        <v>46084.76184239432</v>
+        <v>46084.76184239583</v>
       </c>
       <c r="K850" t="inlineStr">
         <is>
@@ -43831,9 +43831,2559 @@
         </is>
       </c>
       <c r="J851" s="2" t="n">
-        <v>46074.76184239736</v>
+        <v>46074.76184239583</v>
       </c>
       <c r="K851" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>b498776b-7889-4989-9367-5aae4c4b2144</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>93668fa5-91f9-4fbd-945f-71f23ce3b2ca</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E852" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F852" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>OP-233</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J852" s="2" t="n">
+        <v>46073.09905100625</v>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>44a7febe-994e-4131-bad0-fc1d3f3b8934</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>4d8b9348-02ef-4ca3-b880-fd5c9170d4b1</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E853" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F853" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>OP-824</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J853" s="2" t="n">
+        <v>46085.89071767736</v>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>43bdb853-e3e4-4c65-a27e-7dc76ea72087</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>8c51aa49-b13d-4c72-8707-9d7877b32082</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E854" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F854" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>OP-939</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J854" s="2" t="n">
+        <v>46074.93238434723</v>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>90409315-b375-4ff9-84f4-8ca523fb7eb0</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>22e49c19-5e98-4b93-985c-aaac85522b33</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E855" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F855" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>OP-977</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J855" s="2" t="n">
+        <v>46086.97405101722</v>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>0a8ed00e-5619-4e21-9075-c90242c946be</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>bb47010d-05d2-41f9-96f0-bb1398fcd8a6</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E856" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F856" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>OP-637</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J856" s="2" t="n">
+        <v>46080.80738435365</v>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>540c3ed0-c189-43b9-acea-b30b30db9b47</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>bac3db48-92c3-4b37-8bdf-18c85c77f64d</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E857" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F857" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>OP-237</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J857" s="2" t="n">
+        <v>46063.01571769036</v>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>cca78616-ef21-4f1e-988a-44bc77a1bd64</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>70e4f9f8-888d-4677-a074-e4ec5cbd24de</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E858" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F858" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>OP-453</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J858" s="2" t="n">
+        <v>46081.89071769344</v>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>298b213d-1fee-41ba-8d46-22b4ab6c8f39</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>2f9f8ba5-ea34-44f1-bf03-9f9610a4a3a3</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E859" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F859" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>OP-652</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J859" s="2" t="n">
+        <v>46063.05738436332</v>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>112937b2-5de0-45a1-8d91-e92e6694557e</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>adf072be-aa9c-4b75-b361-a2deb1c68e3a</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E860" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F860" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>OP-681</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J860" s="2" t="n">
+        <v>46074.80738436677</v>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2e8b3f26-0b87-437d-be75-64807085765e</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>2822993d-b582-4212-9052-61dcba6a5fd7</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E861" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F861" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>OP-534</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J861" s="2" t="n">
+        <v>46065.97405103675</v>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>0fa7fe59-72f2-4a08-8e44-5431358ed5ca</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>8d5c1327-c2bf-448f-9715-c6af231009a9</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E862" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F862" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>OP-109</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J862" s="2" t="n">
+        <v>46082.93238437319</v>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>255adfda-06a8-40ea-ab58-4d212d3d2987</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>4ee5deb4-c40a-4db2-9037-d166971fc2f5</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E863" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F863" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>OP-533</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J863" s="2" t="n">
+        <v>46063.97405104302</v>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>c90305f1-b550-4e30-979e-76ae16e9f48c</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>0e5b1f8e-4c02-43d8-87de-7ccf21a6fd01</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E864" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F864" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>OP-148</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J864" s="2" t="n">
+        <v>46060.01571771291</v>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>68a3fe97-ccc5-4f37-b6b7-429a3ff6ac35</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>c8d8740b-92fd-4cc8-bf7c-fbc94e8b1aed</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E865" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F865" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>OP-356</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J865" s="2" t="n">
+        <v>46071.09905104936</v>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>4820ac8c-2a1f-4013-ae37-663e04ecefdc</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>1f76e152-f8dd-41e8-9cbe-b641309c7665</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E866" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F866" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>OP-826</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J866" s="2" t="n">
+        <v>46065.1407177192</v>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>d93b35a1-134d-4071-8ab1-a85e396a87b4</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>d5ca044a-b92a-40ab-8be4-b5550db9ef3d</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E867" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F867" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>OP-600</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J867" s="2" t="n">
+        <v>46081.97405105564</v>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>16e3ed86-dd65-4de1-b214-2152cfdfca70</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>d15ab7b6-a885-42ef-b999-58cf8bcd720f</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E868" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F868" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>OP-554</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J868" s="2" t="n">
+        <v>46077.05738439228</v>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>fb3f45b2-ddbb-49e8-9637-d30eb4f898f0</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>859bccbb-3738-499d-a559-c907174e29f2</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E869" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F869" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>OP-694</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J869" s="2" t="n">
+        <v>46072.18238439545</v>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>046bbf90-683b-42b3-a583-76a875864fec</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>fa383ea1-aa85-4241-8259-e6c5ec39316f</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E870" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F870" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>OP-301</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J870" s="2" t="n">
+        <v>46088.89071773209</v>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>a5ec7ea9-c154-48f2-8be0-ff446d07e414</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>15f2fe6f-23b3-4aa7-8317-29a90be625ca</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E871" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F871" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>OP-846</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J871" s="2" t="n">
+        <v>46076.97405106876</v>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2037c364-32ae-4253-bf5f-03feb2875352</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>7d01bdb8-2b6f-4993-acd1-d2fe9c427d29</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E872" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F872" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>OP-242</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J872" s="2" t="n">
+        <v>46073.93238440518</v>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>306c6b11-51b0-4353-8a18-7ee3f29a6723</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>3ce0ea1a-7bc7-4a29-8446-49643ce3befd</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E873" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F873" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>OP-348</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J873" s="2" t="n">
+        <v>46078.05738440833</v>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>8c23c09c-7d25-45f3-9bec-c9009152a301</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>9c640618-38e5-4498-a62b-476e6cc2baf4</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E874" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F874" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>OP-993</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J874" s="2" t="n">
+        <v>46075.18238441141</v>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>21657884-0aae-483b-adca-ab6258489b9a</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>1396f573-b493-4000-8639-0639db89579b</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E875" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F875" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>OP-241</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J875" s="2" t="n">
+        <v>46082.89071774812</v>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>7dfc6d7f-1931-4c67-a51f-d2249ebb6b48</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>dde0639a-19e2-4378-96a4-878adfb5231d</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E876" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F876" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>OP-413</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J876" s="2" t="n">
+        <v>46063.14071775116</v>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>a96160aa-0f86-4bfa-99d5-1cc8eb97b3f8</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>8bfd4ec0-fa09-4d9f-bfc4-f1d35a9b754c</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E877" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F877" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>OP-532</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J877" s="2" t="n">
+        <v>46085.89071775427</v>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>8e7e5704-568d-4df0-bd08-f9ce8f62b527</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>28c2f6c1-244a-4737-95c3-cbdab592de14</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E878" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F878" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>OP-305</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J878" s="2" t="n">
+        <v>46088.01571775743</v>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>684b4aa6-43a2-414c-8791-59ea014eb46e</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>6efcc097-1e3e-4397-82bc-75515e7c1806</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E879" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F879" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>OP-628</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J879" s="2" t="n">
+        <v>46080.18238442737</v>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>58f6dad4-a088-447b-93aa-35f393234a98</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>f3e7d1ad-2cb8-448d-90af-3006b02cf41f</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E880" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F880" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>OP-352</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J880" s="2" t="n">
+        <v>46078.01571776376</v>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>f0d92136-baff-40ad-8dac-ade4905c887f</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>b33a2863-e166-4891-b579-c2023352f1ee</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E881" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F881" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>OP-324</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J881" s="2" t="n">
+        <v>46061.05738443347</v>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>9553f5b4-9d15-4b4e-9736-b9afb1d8aa6a</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>191fe4b7-5573-4747-b498-4e2581d7e30c</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E882" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F882" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>OP-726</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J882" s="2" t="n">
+        <v>46075.93238443685</v>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>efea8e13-8325-4112-916e-ec6d38f34d8a</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>2fdfeff1-05b7-4bbb-8824-96d8e84187a7</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E883" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F883" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>OP-595</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J883" s="2" t="n">
+        <v>46062.84905110669</v>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>3daf9fd2-4aee-496b-a20a-badae4dd1471</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>068ae17a-d416-4013-b953-9e16fc556ee5</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E884" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F884" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>OP-233</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J884" s="2" t="n">
+        <v>46079.80738444321</v>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>b8e4e96b-619f-491d-9ed2-bbe894671d58</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>bfa5aa0e-1a5d-4bc6-82e0-ce9bbdf6061e</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E885" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F885" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>OP-386</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J885" s="2" t="n">
+        <v>46069.93238444682</v>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>538135fe-91c1-4c59-a2c0-6690c197a790</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>2beed69d-35c1-4546-a31f-4229ddecc147</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E886" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F886" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>OP-544</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J886" s="2" t="n">
+        <v>46075.93238445005</v>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>e5eba397-fbfa-4a81-84f0-a5b1bf9e8abb</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>aa6a2c46-ed3a-4048-a634-311b21bf6e9e</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E887" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F887" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>OP-997</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J887" s="2" t="n">
+        <v>46085.97405111973</v>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>22fdd0da-5341-487e-af9a-45fd811d6d7a</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>6d72c8f9-867a-4322-8ef0-68fe741a411c</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E888" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F888" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>OP-322</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J888" s="2" t="n">
+        <v>46082.18238445608</v>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>c443538d-ea9e-4a46-9fb0-f2cb3bcc8996</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>8c87d06b-52c1-463d-9147-99e2638a174c</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E889" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F889" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>OP-412</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J889" s="2" t="n">
+        <v>46084.93238445929</v>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>93d6fccc-eb8f-4ced-9ebf-287535709fc7</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>c8e6f612-589f-4d79-897e-c57d4d81506c</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E890" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F890" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>OP-172</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J890" s="2" t="n">
+        <v>46072.97405112901</v>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>7c370e9b-46b9-407f-8bc1-93f60a0a9292</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>c7cd60f3-2608-4c7a-bf34-0245032684a9</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E891" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F891" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>OP-687</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J891" s="2" t="n">
+        <v>46087.93238446539</v>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>a572b1b7-313d-435c-bfbc-e2b33873682f</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>c01171f0-ce05-4ae4-88db-2392f58aecac</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E892" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F892" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>OP-497</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J892" s="2" t="n">
+        <v>46064.97405113518</v>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>0c94c0b9-1d91-4294-ab77-498bb676c9bb</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>b6d8c20c-91c8-4b1f-afaa-83e5ddb8900f</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E893" t="n">
+        <v>0</v>
+      </c>
+      <c r="F893" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>OP-492</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J893" s="2" t="n">
+        <v>46076.09905113853</v>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>a8ffa4de-883e-457c-927f-1289fd2098db</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>80dcd774-783e-4909-b51f-571d70f7b635</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E894" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F894" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>OP-525</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J894" s="2" t="n">
+        <v>46077.18238447489</v>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>ace32a65-1db1-4e18-ad9c-c94867b3d9a7</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>42792fb1-b396-404e-95a9-db12a2e833f6</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E895" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F895" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>OP-294</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J895" s="2" t="n">
+        <v>46064.18238447808</v>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>d69211e6-1f38-40cf-bf1d-6b69a31fbdfb</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>5e355f22-61bc-4fca-a051-894897e522fd</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E896" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F896" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>OP-766</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J896" s="2" t="n">
+        <v>46074.18238448128</v>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>f41564dc-9a19-418c-9289-f44e39c931df</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>aed45ccf-bfdb-42db-9d6b-0a21456cfd21</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E897" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F897" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>OP-695</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J897" s="2" t="n">
+        <v>46068.01571781791</v>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>709a4bc6-af00-4bf8-9587-7aeb05cee1b8</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>c485f3c2-4b42-4bfa-98ed-a7d9e16f8e75</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E898" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F898" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>OP-653</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J898" s="2" t="n">
+        <v>46064.89071782095</v>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>bca8799d-ec7e-42a5-8ae4-0d1ae4267f7d</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>e0fef902-3f0a-4795-a65b-90575ccd6f3c</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E899" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F899" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>OP-278</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J899" s="2" t="n">
+        <v>46063.01571782405</v>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>0112b94a-0c29-4977-99c4-1683f0186ed9</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>40b123b9-bfba-47d6-a6b0-cf70b4c9e259</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E900" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F900" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>OP-773</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J900" s="2" t="n">
+        <v>46081.05738449386</v>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>33f76a8e-a293-4b44-8c82-65d55e79f37f</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>ad841e60-97c5-40a6-8bc3-d950b61f54f6</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E901" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F901" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>OP-341</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J901" s="2" t="n">
+        <v>46085.89071783039</v>
+      </c>
+      <c r="K901" t="inlineStr">
         <is>
           <t>poor</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K901"/>
+  <dimension ref="A1:K951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43882,7 +43882,7 @@
         </is>
       </c>
       <c r="J852" s="2" t="n">
-        <v>46073.09905100625</v>
+        <v>46073.09905100695</v>
       </c>
       <c r="K852" t="inlineStr">
         <is>
@@ -43933,7 +43933,7 @@
         </is>
       </c>
       <c r="J853" s="2" t="n">
-        <v>46085.89071767736</v>
+        <v>46085.89071767361</v>
       </c>
       <c r="K853" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         </is>
       </c>
       <c r="J854" s="2" t="n">
-        <v>46074.93238434723</v>
+        <v>46074.93238435185</v>
       </c>
       <c r="K854" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         </is>
       </c>
       <c r="J855" s="2" t="n">
-        <v>46086.97405101722</v>
+        <v>46086.97405101852</v>
       </c>
       <c r="K855" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         </is>
       </c>
       <c r="J856" s="2" t="n">
-        <v>46080.80738435365</v>
+        <v>46080.80738435185</v>
       </c>
       <c r="K856" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         </is>
       </c>
       <c r="J857" s="2" t="n">
-        <v>46063.01571769036</v>
+        <v>46063.01571768519</v>
       </c>
       <c r="K857" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="J858" s="2" t="n">
-        <v>46081.89071769344</v>
+        <v>46081.89071769676</v>
       </c>
       <c r="K858" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         </is>
       </c>
       <c r="J859" s="2" t="n">
-        <v>46063.05738436332</v>
+        <v>46063.05738436343</v>
       </c>
       <c r="K859" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         </is>
       </c>
       <c r="J860" s="2" t="n">
-        <v>46074.80738436677</v>
+        <v>46074.80738436343</v>
       </c>
       <c r="K860" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         </is>
       </c>
       <c r="J861" s="2" t="n">
-        <v>46065.97405103675</v>
+        <v>46065.97405104167</v>
       </c>
       <c r="K861" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         </is>
       </c>
       <c r="J862" s="2" t="n">
-        <v>46082.93238437319</v>
+        <v>46082.932384375</v>
       </c>
       <c r="K862" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         </is>
       </c>
       <c r="J863" s="2" t="n">
-        <v>46063.97405104302</v>
+        <v>46063.97405104167</v>
       </c>
       <c r="K863" t="inlineStr">
         <is>
@@ -44494,7 +44494,7 @@
         </is>
       </c>
       <c r="J864" s="2" t="n">
-        <v>46060.01571771291</v>
+        <v>46060.01571770833</v>
       </c>
       <c r="K864" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         </is>
       </c>
       <c r="J865" s="2" t="n">
-        <v>46071.09905104936</v>
+        <v>46071.09905105324</v>
       </c>
       <c r="K865" t="inlineStr">
         <is>
@@ -44596,7 +44596,7 @@
         </is>
       </c>
       <c r="J866" s="2" t="n">
-        <v>46065.1407177192</v>
+        <v>46065.14071771991</v>
       </c>
       <c r="K866" t="inlineStr">
         <is>
@@ -44647,7 +44647,7 @@
         </is>
       </c>
       <c r="J867" s="2" t="n">
-        <v>46081.97405105564</v>
+        <v>46081.97405105324</v>
       </c>
       <c r="K867" t="inlineStr">
         <is>
@@ -44698,7 +44698,7 @@
         </is>
       </c>
       <c r="J868" s="2" t="n">
-        <v>46077.05738439228</v>
+        <v>46077.05738438657</v>
       </c>
       <c r="K868" t="inlineStr">
         <is>
@@ -44749,7 +44749,7 @@
         </is>
       </c>
       <c r="J869" s="2" t="n">
-        <v>46072.18238439545</v>
+        <v>46072.18238439815</v>
       </c>
       <c r="K869" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         </is>
       </c>
       <c r="J870" s="2" t="n">
-        <v>46088.89071773209</v>
+        <v>46088.89071773148</v>
       </c>
       <c r="K870" t="inlineStr">
         <is>
@@ -44851,7 +44851,7 @@
         </is>
       </c>
       <c r="J871" s="2" t="n">
-        <v>46076.97405106876</v>
+        <v>46076.97405106481</v>
       </c>
       <c r="K871" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         </is>
       </c>
       <c r="J872" s="2" t="n">
-        <v>46073.93238440518</v>
+        <v>46073.93238440972</v>
       </c>
       <c r="K872" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         </is>
       </c>
       <c r="J873" s="2" t="n">
-        <v>46078.05738440833</v>
+        <v>46078.05738440972</v>
       </c>
       <c r="K873" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         </is>
       </c>
       <c r="J874" s="2" t="n">
-        <v>46075.18238441141</v>
+        <v>46075.18238440972</v>
       </c>
       <c r="K874" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         </is>
       </c>
       <c r="J875" s="2" t="n">
-        <v>46082.89071774812</v>
+        <v>46082.89071774305</v>
       </c>
       <c r="K875" t="inlineStr">
         <is>
@@ -45106,7 +45106,7 @@
         </is>
       </c>
       <c r="J876" s="2" t="n">
-        <v>46063.14071775116</v>
+        <v>46063.14071775463</v>
       </c>
       <c r="K876" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         </is>
       </c>
       <c r="J877" s="2" t="n">
-        <v>46085.89071775427</v>
+        <v>46085.89071775463</v>
       </c>
       <c r="K877" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         </is>
       </c>
       <c r="J878" s="2" t="n">
-        <v>46088.01571775743</v>
+        <v>46088.01571775463</v>
       </c>
       <c r="K878" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         </is>
       </c>
       <c r="J879" s="2" t="n">
-        <v>46080.18238442737</v>
+        <v>46080.18238443287</v>
       </c>
       <c r="K879" t="inlineStr">
         <is>
@@ -45310,7 +45310,7 @@
         </is>
       </c>
       <c r="J880" s="2" t="n">
-        <v>46078.01571776376</v>
+        <v>46078.0157177662</v>
       </c>
       <c r="K880" t="inlineStr">
         <is>
@@ -45361,7 +45361,7 @@
         </is>
       </c>
       <c r="J881" s="2" t="n">
-        <v>46061.05738443347</v>
+        <v>46061.05738443287</v>
       </c>
       <c r="K881" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="J882" s="2" t="n">
-        <v>46075.93238443685</v>
+        <v>46075.93238443287</v>
       </c>
       <c r="K882" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         </is>
       </c>
       <c r="J883" s="2" t="n">
-        <v>46062.84905110669</v>
+        <v>46062.84905111111</v>
       </c>
       <c r="K883" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         </is>
       </c>
       <c r="J884" s="2" t="n">
-        <v>46079.80738444321</v>
+        <v>46079.80738444444</v>
       </c>
       <c r="K884" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         </is>
       </c>
       <c r="J885" s="2" t="n">
-        <v>46069.93238444682</v>
+        <v>46069.93238444444</v>
       </c>
       <c r="K885" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         </is>
       </c>
       <c r="J886" s="2" t="n">
-        <v>46075.93238445005</v>
+        <v>46075.93238444444</v>
       </c>
       <c r="K886" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         </is>
       </c>
       <c r="J887" s="2" t="n">
-        <v>46085.97405111973</v>
+        <v>46085.97405112268</v>
       </c>
       <c r="K887" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         </is>
       </c>
       <c r="J888" s="2" t="n">
-        <v>46082.18238445608</v>
+        <v>46082.18238445602</v>
       </c>
       <c r="K888" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         </is>
       </c>
       <c r="J889" s="2" t="n">
-        <v>46084.93238445929</v>
+        <v>46084.93238445602</v>
       </c>
       <c r="K889" t="inlineStr">
         <is>
@@ -45820,7 +45820,7 @@
         </is>
       </c>
       <c r="J890" s="2" t="n">
-        <v>46072.97405112901</v>
+        <v>46072.97405113426</v>
       </c>
       <c r="K890" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         </is>
       </c>
       <c r="J891" s="2" t="n">
-        <v>46087.93238446539</v>
+        <v>46087.93238446759</v>
       </c>
       <c r="K891" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         </is>
       </c>
       <c r="J892" s="2" t="n">
-        <v>46064.97405113518</v>
+        <v>46064.97405113426</v>
       </c>
       <c r="K892" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         </is>
       </c>
       <c r="J893" s="2" t="n">
-        <v>46076.09905113853</v>
+        <v>46076.09905113426</v>
       </c>
       <c r="K893" t="inlineStr">
         <is>
@@ -46024,7 +46024,7 @@
         </is>
       </c>
       <c r="J894" s="2" t="n">
-        <v>46077.18238447489</v>
+        <v>46077.18238447917</v>
       </c>
       <c r="K894" t="inlineStr">
         <is>
@@ -46075,7 +46075,7 @@
         </is>
       </c>
       <c r="J895" s="2" t="n">
-        <v>46064.18238447808</v>
+        <v>46064.18238447917</v>
       </c>
       <c r="K895" t="inlineStr">
         <is>
@@ -46126,7 +46126,7 @@
         </is>
       </c>
       <c r="J896" s="2" t="n">
-        <v>46074.18238448128</v>
+        <v>46074.18238447917</v>
       </c>
       <c r="K896" t="inlineStr">
         <is>
@@ -46177,7 +46177,7 @@
         </is>
       </c>
       <c r="J897" s="2" t="n">
-        <v>46068.01571781791</v>
+        <v>46068.0157178125</v>
       </c>
       <c r="K897" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         </is>
       </c>
       <c r="J898" s="2" t="n">
-        <v>46064.89071782095</v>
+        <v>46064.89071782408</v>
       </c>
       <c r="K898" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         </is>
       </c>
       <c r="J899" s="2" t="n">
-        <v>46063.01571782405</v>
+        <v>46063.01571782408</v>
       </c>
       <c r="K899" t="inlineStr">
         <is>
@@ -46330,7 +46330,7 @@
         </is>
       </c>
       <c r="J900" s="2" t="n">
-        <v>46081.05738449386</v>
+        <v>46081.05738449074</v>
       </c>
       <c r="K900" t="inlineStr">
         <is>
@@ -46381,9 +46381,2559 @@
         </is>
       </c>
       <c r="J901" s="2" t="n">
-        <v>46085.89071783039</v>
+        <v>46085.89071783565</v>
       </c>
       <c r="K901" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>33332aaf-27d3-4d56-bfb0-31135fc447a1</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>faee317d-6923-4612-8d8a-988b09c13bef</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E902" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F902" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>OP-691</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J902" s="2" t="n">
+        <v>46087.01273969707</v>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>550a3982-3b42-4a50-8020-9ed9233e1d05</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>66a1fa9b-36e4-4c86-9863-e5ee6997ca94</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E903" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F903" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>OP-176</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J903" s="2" t="n">
+        <v>46075.05440636795</v>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>94d9ef46-4de9-42cc-a078-86a7b63a967a</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>f36f0b64-f83e-4f26-95d6-b2fedc4e3b6c</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E904" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F904" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>OP-620</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J904" s="2" t="n">
+        <v>46060.22107303803</v>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>eac9a013-f311-478d-9ef8-c640cf7ead2a</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>b8c15e58-e7ec-49af-a166-4cea197fd8b6</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E905" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F905" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>OP-626</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J905" s="2" t="n">
+        <v>46064.9294063749</v>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>6cec2126-b40b-4917-89ca-72f8804ccdca</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>7652c18e-722d-4640-8301-6948d24fb23d</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E906" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F906" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>OP-714</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J906" s="2" t="n">
+        <v>46082.13773971156</v>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>8ad54c91-b119-45f9-97bd-cf9bf9173248</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>79ca0b75-f950-4059-9c37-eb170fc83240</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E907" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F907" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>OP-330</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J907" s="2" t="n">
+        <v>46061.22107304826</v>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>1aebb24e-a825-4ea3-a6fe-b4e1341bec32</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>96547d68-e41b-47d2-9756-7d0769b43924</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E908" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F908" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>OP-881</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J908" s="2" t="n">
+        <v>46063.88773971801</v>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>3fe22964-3eed-4731-b279-a3b50b4e506a</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>a53df51c-a547-4ebe-9807-1555247cc5f1</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E909" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F909" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>OP-966</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J909" s="2" t="n">
+        <v>46088.9710730549</v>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>cda2e237-0bd4-4fc7-86ac-2406797d8bae</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>3c8fb256-6a9d-49ea-8646-32ce0d81e579</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E910" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F910" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>OP-239</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J910" s="2" t="n">
+        <v>46075.88773972491</v>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>a23433c0-abb4-428c-a026-1c5100e5dda8</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>22df145d-4831-4d54-88a5-e8b583c14286</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E911" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F911" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>OP-918</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J911" s="2" t="n">
+        <v>46084.17940639487</v>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>d5cbf28f-8a56-4aab-8c1d-207556598678</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>902bcfe6-d7f2-4e96-9655-4cc9010bcb4f</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E912" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F912" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>OP-727</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J912" s="2" t="n">
+        <v>46085.97107306532</v>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>96998d9e-3273-41c9-8fb6-4b23af103d18</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>8c871962-2965-4819-9753-2ba6ff553a98</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E913" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F913" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>OP-979</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J913" s="2" t="n">
+        <v>46070.01273973526</v>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>8eb39318-8bdb-43e2-81d4-32b41ef89a7b</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>227c6139-b6a5-437f-ad06-7f41241e2965</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E914" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F914" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>OP-662</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J914" s="2" t="n">
+        <v>46073.05440640528</v>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>4afdee60-f87c-4b6c-a9b6-6b55cef2e30e</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>a114eb37-6b79-4a3d-9482-37b9402bd77e</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E915" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F915" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>OP-194</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J915" s="2" t="n">
+        <v>46065.22107307528</v>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>91f60051-5022-4008-814d-092fbaebac07</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>c9da8397-2620-4d0b-b0b1-74e91520491c</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E916" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F916" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>OP-159</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J916" s="2" t="n">
+        <v>46061.05440641173</v>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>419e05e6-8b42-4621-ade3-170fbc5c1386</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>327fe8d7-1088-40e5-8cdb-c3d45b511ec7</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E917" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F917" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>OP-220</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J917" s="2" t="n">
+        <v>46088.05440641504</v>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>91eb815c-8179-4472-a9f0-eccd591a85e3</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>b8d6314f-b5bc-4647-8d3d-86fbdf91f497</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E918" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F918" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>OP-162</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J918" s="2" t="n">
+        <v>46085.97107308496</v>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>416d4017-7958-4437-bc0a-bdacce6354a3</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>784b7953-0cb8-4573-b0dc-f0092bfb94b7</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E919" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F919" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>OP-872</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J919" s="2" t="n">
+        <v>46067.05440642161</v>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>36bee048-8f87-4957-9b68-ea1dedb0be28</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>205343d9-57cb-43b7-b9d3-bb5bba7f02d3</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E920" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F920" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>OP-821</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J920" s="2" t="n">
+        <v>46076.01273975807</v>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>d20b8745-f6a6-42a6-8d14-3d4b16c294bb</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>cf32270a-6acc-4a50-8afc-9a8bbaaf5776</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E921" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F921" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>OP-180</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J921" s="2" t="n">
+        <v>46072.84607309463</v>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>350c47df-f6c9-4635-a739-08a68d55a5d5</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>278420f9-a71d-4ff9-bf8e-36c42d011f66</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E922" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F922" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>OP-465</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J922" s="2" t="n">
+        <v>46071.05440643107</v>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>7a5edbc1-40be-4d83-aebb-d6aad55ff63a</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>1996a631-8c6c-47a2-bf95-71a3790c1ba9</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E923" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F923" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>OP-726</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J923" s="2" t="n">
+        <v>46067.01273976838</v>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>646b5c77-ccd0-4720-9b02-e295f8d20e3a</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>79ae80d8-a741-408a-b426-1045dd5f901f</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E924" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F924" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>OP-723</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J924" s="2" t="n">
+        <v>46066.01273977158</v>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>f8319b34-80a1-465d-b3a7-3ae3c938c8ad</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>cc6cb5f9-497e-4ae2-8243-025efb78c913</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E925" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F925" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>OP-660</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J925" s="2" t="n">
+        <v>46060.22107310814</v>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>1665b044-fd90-4b7e-8aa4-bf54f8abd389</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>a244c00d-80aa-4979-a99e-de973e1f385d</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E926" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F926" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>OP-201</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J926" s="2" t="n">
+        <v>46088.92940644494</v>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>68519636-0ff9-4d1e-b4bb-02c4ff666d5a</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>6404c7eb-8486-484f-9cd3-f6c05f20ab1e</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E927" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F927" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>OP-778</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J927" s="2" t="n">
+        <v>46069.92940644809</v>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>61ae1467-075c-4495-bdbf-ab81e2d7d9dd</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>c101efbf-9d21-440d-acee-14718f324e41</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E928" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F928" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>OP-673</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J928" s="2" t="n">
+        <v>46067.84607311786</v>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>86f80a6c-7cb0-4a2e-a9f7-7021a83a6575</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>d813f0b1-a2bc-4704-a01a-dcfac48ecdc8</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E929" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F929" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>OP-774</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J929" s="2" t="n">
+        <v>46077.05440645434</v>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>543404d7-bfbc-4abd-a7bf-6d11aa8e82d9</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>4b5dcbfe-17f1-4847-bcf4-683026e1371d</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E930" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F930" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>OP-719</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J930" s="2" t="n">
+        <v>46081.88773979095</v>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>ac2922d8-b720-4475-9ec5-48e1fd9f1a6b</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>9272b8f7-149d-47b4-b746-9551e91eca22</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E931" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F931" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>OP-114</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J931" s="2" t="n">
+        <v>46088.05440646079</v>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>bb19f0d7-10e1-4cb3-8b96-473a3298c9cf</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>122ed255-e344-4d28-bfc5-f984cdd5896d</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E932" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F932" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>OP-105</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J932" s="2" t="n">
+        <v>46069.17940646412</v>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>c85fd28c-a8e9-45e6-8d81-6bd911dcd9b7</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>4fe6469b-0aed-486c-a504-ad08459d70a6</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E933" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F933" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>OP-202</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J933" s="2" t="n">
+        <v>46079.84607313409</v>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>f3afe85a-74a3-48e1-aa00-731a6ca7e8d9</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>fee0bceb-82a6-4201-94e4-42d1aa3dc818</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E934" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F934" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>OP-782</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J934" s="2" t="n">
+        <v>46088.84607313721</v>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>21c50fb3-ad31-413c-9905-f53b277f42a1</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>6768216a-3cea-4658-9583-8910e44fd9d8</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E935" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F935" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>OP-670</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J935" s="2" t="n">
+        <v>46063.17940647375</v>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>823277d1-c081-43d3-ad4b-2119143541df</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>e976e11c-07e0-468a-bfe0-393a35101eb6</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E936" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F936" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>OP-714</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J936" s="2" t="n">
+        <v>46083.8460731435</v>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>f5d0ca22-cd20-4522-8683-01d6c1c7bc47</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>823c63ea-d079-4cc1-b547-51c3bc93dcac</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E937" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F937" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>OP-513</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J937" s="2" t="n">
+        <v>46078.05440648029</v>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>0955fa8e-2f7d-48e2-b153-6bbeeb09e2df</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>26083769-e9c1-45a4-9c19-a02cec237d0a</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E938" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F938" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>OP-432</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J938" s="2" t="n">
+        <v>46060.88773981721</v>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2a030dd4-363a-4fc2-a690-4f5d135bcfa6</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>21718b80-07fc-441e-883b-38f0ffc958a8</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E939" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F939" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>OP-165</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J939" s="2" t="n">
+        <v>46064.01273982049</v>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>edceb2e6-43cd-4997-9da9-0cb837aa193e</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>98e8ecd1-d581-41c6-b608-802dab97fc82</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E940" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F940" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>OP-578</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J940" s="2" t="n">
+        <v>46074.97107315713</v>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>ff798a03-22e2-4287-966c-cf719a1bb86e</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>3a5f7e93-03e2-4ffd-b905-f58e1a57fc99</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E941" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F941" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>OP-727</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J941" s="2" t="n">
+        <v>46065.13773982701</v>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>25c3017f-3a6f-418d-bb6b-00fea2c1da44</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>391956ce-a1c5-4e36-844e-9a756b23c3d7</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E942" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F942" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>OP-473</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J942" s="2" t="n">
+        <v>46061.22107316341</v>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>526a5a55-e152-4878-9b19-9e6cce6e25be</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>2a4dadd3-7f75-4936-abe0-e52ee0bd42b2</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E943" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F943" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>OP-148</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J943" s="2" t="n">
+        <v>46078.01273983334</v>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>ee8dfb85-c21b-48bd-94d1-ae7cb436a8f0</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>2d01e1ee-28b0-4ef1-bda4-21d336441ccd</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E944" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F944" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>OP-656</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J944" s="2" t="n">
+        <v>46065.22107317</v>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>69556956-6e21-4625-a3e2-ca406e0cc7c8</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>d837b880-4ea0-42da-97b5-0c3a078fdd43</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E945" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F945" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>OP-347</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J945" s="2" t="n">
+        <v>46084.92940650639</v>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>a8b514d7-1bee-4363-b24c-f19df51b5d10</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>c6f7006f-f43a-461c-ad47-e41b19c1f14d</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E946" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F946" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>OP-568</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J946" s="2" t="n">
+        <v>46061.9710731763</v>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>c808dd95-9014-4055-9ae1-b44c306a6c97</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>760239e4-e7af-4e92-86c9-53c238f76eef</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E947" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F947" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>OP-840</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J947" s="2" t="n">
+        <v>46080.92940651299</v>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>d9ef8cbd-d7ea-48b5-8d5e-403883ec48a5</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>2eca3f95-9c63-498f-8b10-3506a12aa77b</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E948" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F948" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>OP-135</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J948" s="2" t="n">
+        <v>46085.17940651625</v>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>3affca97-a9f3-4af8-870f-030f5e06bbbf</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>827ec653-76d9-4241-89e5-3a14d915a1cf</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E949" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F949" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>OP-575</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J949" s="2" t="n">
+        <v>46087.13773985283</v>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>ae660166-ed32-4012-b471-4abed33225f9</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>b08d9958-573f-49f6-85f9-807f938ba9ca</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E950" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F950" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>OP-775</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J950" s="2" t="n">
+        <v>46076.92940652255</v>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>de45d011-1ee1-43d3-a1e3-0e486a207ad6</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>c0cfba62-af52-4eec-89d9-a6b32cbc6829</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E951" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F951" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>OP-677</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J951" s="2" t="n">
+        <v>46069.8460731926</v>
+      </c>
+      <c r="K951" t="inlineStr">
         <is>
           <t>poor</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K951"/>
+  <dimension ref="A1:K1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46432,7 +46432,7 @@
         </is>
       </c>
       <c r="J902" s="2" t="n">
-        <v>46087.01273969707</v>
+        <v>46087.01273969907</v>
       </c>
       <c r="K902" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         </is>
       </c>
       <c r="J903" s="2" t="n">
-        <v>46075.05440636795</v>
+        <v>46075.05440636574</v>
       </c>
       <c r="K903" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         </is>
       </c>
       <c r="J904" s="2" t="n">
-        <v>46060.22107303803</v>
+        <v>46060.22107303241</v>
       </c>
       <c r="K904" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         </is>
       </c>
       <c r="J905" s="2" t="n">
-        <v>46064.9294063749</v>
+        <v>46064.92940637731</v>
       </c>
       <c r="K905" t="inlineStr">
         <is>
@@ -46636,7 +46636,7 @@
         </is>
       </c>
       <c r="J906" s="2" t="n">
-        <v>46082.13773971156</v>
+        <v>46082.13773971065</v>
       </c>
       <c r="K906" t="inlineStr">
         <is>
@@ -46687,7 +46687,7 @@
         </is>
       </c>
       <c r="J907" s="2" t="n">
-        <v>46061.22107304826</v>
+        <v>46061.22107304398</v>
       </c>
       <c r="K907" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         </is>
       </c>
       <c r="J908" s="2" t="n">
-        <v>46063.88773971801</v>
+        <v>46063.88773972222</v>
       </c>
       <c r="K908" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         </is>
       </c>
       <c r="J909" s="2" t="n">
-        <v>46088.9710730549</v>
+        <v>46088.97107305555</v>
       </c>
       <c r="K909" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         </is>
       </c>
       <c r="J910" s="2" t="n">
-        <v>46075.88773972491</v>
+        <v>46075.88773972222</v>
       </c>
       <c r="K910" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         </is>
       </c>
       <c r="J911" s="2" t="n">
-        <v>46084.17940639487</v>
+        <v>46084.17940640046</v>
       </c>
       <c r="K911" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         </is>
       </c>
       <c r="J912" s="2" t="n">
-        <v>46085.97107306532</v>
+        <v>46085.97107306713</v>
       </c>
       <c r="K912" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         </is>
       </c>
       <c r="J913" s="2" t="n">
-        <v>46070.01273973526</v>
+        <v>46070.01273973379</v>
       </c>
       <c r="K913" t="inlineStr">
         <is>
@@ -47044,7 +47044,7 @@
         </is>
       </c>
       <c r="J914" s="2" t="n">
-        <v>46073.05440640528</v>
+        <v>46073.05440640046</v>
       </c>
       <c r="K914" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         </is>
       </c>
       <c r="J915" s="2" t="n">
-        <v>46065.22107307528</v>
+        <v>46065.2210730787</v>
       </c>
       <c r="K915" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         </is>
       </c>
       <c r="J916" s="2" t="n">
-        <v>46061.05440641173</v>
+        <v>46061.05440641204</v>
       </c>
       <c r="K916" t="inlineStr">
         <is>
@@ -47197,7 +47197,7 @@
         </is>
       </c>
       <c r="J917" s="2" t="n">
-        <v>46088.05440641504</v>
+        <v>46088.05440641204</v>
       </c>
       <c r="K917" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         </is>
       </c>
       <c r="J918" s="2" t="n">
-        <v>46085.97107308496</v>
+        <v>46085.97107309028</v>
       </c>
       <c r="K918" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         </is>
       </c>
       <c r="J919" s="2" t="n">
-        <v>46067.05440642161</v>
+        <v>46067.05440642361</v>
       </c>
       <c r="K919" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         </is>
       </c>
       <c r="J920" s="2" t="n">
-        <v>46076.01273975807</v>
+        <v>46076.01273975694</v>
       </c>
       <c r="K920" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         </is>
       </c>
       <c r="J921" s="2" t="n">
-        <v>46072.84607309463</v>
+        <v>46072.84607309028</v>
       </c>
       <c r="K921" t="inlineStr">
         <is>
@@ -47452,7 +47452,7 @@
         </is>
       </c>
       <c r="J922" s="2" t="n">
-        <v>46071.05440643107</v>
+        <v>46071.05440643519</v>
       </c>
       <c r="K922" t="inlineStr">
         <is>
@@ -47503,7 +47503,7 @@
         </is>
       </c>
       <c r="J923" s="2" t="n">
-        <v>46067.01273976838</v>
+        <v>46067.01273976852</v>
       </c>
       <c r="K923" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         </is>
       </c>
       <c r="J924" s="2" t="n">
-        <v>46066.01273977158</v>
+        <v>46066.01273976852</v>
       </c>
       <c r="K924" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         </is>
       </c>
       <c r="J925" s="2" t="n">
-        <v>46060.22107310814</v>
+        <v>46060.22107311343</v>
       </c>
       <c r="K925" t="inlineStr">
         <is>
@@ -47656,7 +47656,7 @@
         </is>
       </c>
       <c r="J926" s="2" t="n">
-        <v>46088.92940644494</v>
+        <v>46088.92940644676</v>
       </c>
       <c r="K926" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         </is>
       </c>
       <c r="J927" s="2" t="n">
-        <v>46069.92940644809</v>
+        <v>46069.92940644676</v>
       </c>
       <c r="K927" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         </is>
       </c>
       <c r="J928" s="2" t="n">
-        <v>46067.84607311786</v>
+        <v>46067.84607311343</v>
       </c>
       <c r="K928" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         </is>
       </c>
       <c r="J929" s="2" t="n">
-        <v>46077.05440645434</v>
+        <v>46077.05440645833</v>
       </c>
       <c r="K929" t="inlineStr">
         <is>
@@ -47860,7 +47860,7 @@
         </is>
       </c>
       <c r="J930" s="2" t="n">
-        <v>46081.88773979095</v>
+        <v>46081.88773979167</v>
       </c>
       <c r="K930" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         </is>
       </c>
       <c r="J931" s="2" t="n">
-        <v>46088.05440646079</v>
+        <v>46088.05440645833</v>
       </c>
       <c r="K931" t="inlineStr">
         <is>
@@ -47962,7 +47962,7 @@
         </is>
       </c>
       <c r="J932" s="2" t="n">
-        <v>46069.17940646412</v>
+        <v>46069.17940646991</v>
       </c>
       <c r="K932" t="inlineStr">
         <is>
@@ -48013,7 +48013,7 @@
         </is>
       </c>
       <c r="J933" s="2" t="n">
-        <v>46079.84607313409</v>
+        <v>46079.84607313658</v>
       </c>
       <c r="K933" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         </is>
       </c>
       <c r="J934" s="2" t="n">
-        <v>46088.84607313721</v>
+        <v>46088.84607313658</v>
       </c>
       <c r="K934" t="inlineStr">
         <is>
@@ -48115,7 +48115,7 @@
         </is>
       </c>
       <c r="J935" s="2" t="n">
-        <v>46063.17940647375</v>
+        <v>46063.17940646991</v>
       </c>
       <c r="K935" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         </is>
       </c>
       <c r="J936" s="2" t="n">
-        <v>46083.8460731435</v>
+        <v>46083.84607314815</v>
       </c>
       <c r="K936" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         </is>
       </c>
       <c r="J937" s="2" t="n">
-        <v>46078.05440648029</v>
+        <v>46078.05440648148</v>
       </c>
       <c r="K937" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         </is>
       </c>
       <c r="J938" s="2" t="n">
-        <v>46060.88773981721</v>
+        <v>46060.88773981482</v>
       </c>
       <c r="K938" t="inlineStr">
         <is>
@@ -48319,7 +48319,7 @@
         </is>
       </c>
       <c r="J939" s="2" t="n">
-        <v>46064.01273982049</v>
+        <v>46064.01273981482</v>
       </c>
       <c r="K939" t="inlineStr">
         <is>
@@ -48370,7 +48370,7 @@
         </is>
       </c>
       <c r="J940" s="2" t="n">
-        <v>46074.97107315713</v>
+        <v>46074.97107315972</v>
       </c>
       <c r="K940" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         </is>
       </c>
       <c r="J941" s="2" t="n">
-        <v>46065.13773982701</v>
+        <v>46065.13773982639</v>
       </c>
       <c r="K941" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         </is>
       </c>
       <c r="J942" s="2" t="n">
-        <v>46061.22107316341</v>
+        <v>46061.22107315972</v>
       </c>
       <c r="K942" t="inlineStr">
         <is>
@@ -48523,7 +48523,7 @@
         </is>
       </c>
       <c r="J943" s="2" t="n">
-        <v>46078.01273983334</v>
+        <v>46078.01273983796</v>
       </c>
       <c r="K943" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         </is>
       </c>
       <c r="J944" s="2" t="n">
-        <v>46065.22107317</v>
+        <v>46065.2210731713</v>
       </c>
       <c r="K944" t="inlineStr">
         <is>
@@ -48625,7 +48625,7 @@
         </is>
       </c>
       <c r="J945" s="2" t="n">
-        <v>46084.92940650639</v>
+        <v>46084.92940650463</v>
       </c>
       <c r="K945" t="inlineStr">
         <is>
@@ -48676,7 +48676,7 @@
         </is>
       </c>
       <c r="J946" s="2" t="n">
-        <v>46061.9710731763</v>
+        <v>46061.9710731713</v>
       </c>
       <c r="K946" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         </is>
       </c>
       <c r="J947" s="2" t="n">
-        <v>46080.92940651299</v>
+        <v>46080.9294065162</v>
       </c>
       <c r="K947" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         </is>
       </c>
       <c r="J948" s="2" t="n">
-        <v>46085.17940651625</v>
+        <v>46085.1794065162</v>
       </c>
       <c r="K948" t="inlineStr">
         <is>
@@ -48829,7 +48829,7 @@
         </is>
       </c>
       <c r="J949" s="2" t="n">
-        <v>46087.13773985283</v>
+        <v>46087.13773984954</v>
       </c>
       <c r="K949" t="inlineStr">
         <is>
@@ -48880,7 +48880,7 @@
         </is>
       </c>
       <c r="J950" s="2" t="n">
-        <v>46076.92940652255</v>
+        <v>46076.92940652778</v>
       </c>
       <c r="K950" t="inlineStr">
         <is>
@@ -48931,11 +48931,2561 @@
         </is>
       </c>
       <c r="J951" s="2" t="n">
-        <v>46069.8460731926</v>
+        <v>46069.84607319444</v>
       </c>
       <c r="K951" t="inlineStr">
         <is>
           <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>68dbb8ee-bace-4ba5-8be5-82ad633f03fd</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>a02685a3-06d6-44f7-8ea3-dc4588f6c547</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E952" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F952" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>OP-138</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J952" s="2" t="n">
+        <v>46064.26159728926</v>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>42c3ce9b-26da-4e28-ba30-7167cce2fbda</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>304cf696-fdda-4cff-b693-bd08f6a45d2d</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E953" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F953" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>OP-213</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J953" s="2" t="n">
+        <v>46087.969930627</v>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>b16c6612-6e63-4278-b61f-4f9c259a8425</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>b7399f78-afe6-4d4c-8b73-131fc07e692b</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E954" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F954" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>OP-831</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J954" s="2" t="n">
+        <v>46082.09493063045</v>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>07c4b377-77ca-44d6-a2cf-883b85d5fcf2</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>47b425cf-bf57-45e4-8111-32e7b3face78</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E955" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F955" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>OP-243</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J955" s="2" t="n">
+        <v>46062.0949306342</v>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>25fcf62b-688f-41b1-a9f0-ea3bce1404c9</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>965ec4c0-6e8d-48c7-a87c-f39796e78c12</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E956" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F956" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>OP-714</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J956" s="2" t="n">
+        <v>46077.05326397062</v>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>b23afea2-d845-45f4-9151-ef0311b8b6c3</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>b5295492-2520-4373-bb3e-a3fb01f98a8f</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E957" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F957" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>OP-875</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J957" s="2" t="n">
+        <v>46060.9282639739</v>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>050d6e01-c4c9-41f7-a21d-8e7e4eba97d2</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>a8e216dc-a773-4d4d-b0c8-c4c52e979300</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E958" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F958" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>OP-985</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J958" s="2" t="n">
+        <v>46089.13659731088</v>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>c6dbecd2-631e-4eac-ab98-3d3497dbda86</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>c4ad7838-72b7-4b00-83eb-abe6019300d0</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E959" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F959" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>OP-298</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J959" s="2" t="n">
+        <v>46072.92826398079</v>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>e9a3870d-899c-476d-9cbb-32d01ae23fa8</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>1b2493fe-1e16-4136-a930-639e79debe08</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E960" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F960" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>OP-110</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J960" s="2" t="n">
+        <v>46068.01159731727</v>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>f5f2d81c-11aa-459c-9b70-05f8ec6c2616</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>11a96b3b-ba33-4765-8c3d-2c27efc88d75</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E961" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F961" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>OP-543</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J961" s="2" t="n">
+        <v>46063.05326398729</v>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>d655e1b2-d577-4e94-8be4-376ce9c773bc</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>790b43a1-147d-4da1-9c99-dfd6e10961ac</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E962" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F962" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>OP-705</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J962" s="2" t="n">
+        <v>46082.1365973241</v>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>9ec8c6c0-ce92-44b3-9de3-efa786d833be</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>f0d987e5-7cf8-4d53-acc8-8586c7471d51</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E963" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F963" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>OP-657</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J963" s="2" t="n">
+        <v>46075.21993066058</v>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>30f8e843-4356-4e9a-a0c0-6fab636f1588</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>f33e0e7b-3c18-4892-95d1-1b9df8c2e7a7</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E964" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F964" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>OP-820</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J964" s="2" t="n">
+        <v>46078.92826399709</v>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>674e6052-93fa-4a85-807e-dbda6437c26d</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>e0e16ca1-3de2-4638-b0a2-10a853767c26</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E965" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F965" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>OP-582</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J965" s="2" t="n">
+        <v>46065.13659733423</v>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>e37937dd-d963-4107-8b1e-b9a6eb2ffdad</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>392bf59a-f913-4032-a826-4679f6282e07</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E966" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F966" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>OP-811</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J966" s="2" t="n">
+        <v>46071.92826400405</v>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>86ea9f18-fd6e-4236-a659-7b9b07ea13b5</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>c0d2b5f6-cbcb-4d70-8f49-9fddb9bbf7ae</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E967" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F967" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>OP-284</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J967" s="2" t="n">
+        <v>46074.88659734046</v>
+      </c>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>076d2acc-b932-4d00-89c8-1390f6b1387f</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>0c1f8b65-9504-405d-a705-2d026fa3c8bc</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E968" t="n">
+        <v>1</v>
+      </c>
+      <c r="F968" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>OP-277</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J968" s="2" t="n">
+        <v>46078.26159734357</v>
+      </c>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>d4af8537-1f13-4244-8f1d-f7b14a9c651a</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>ead207e9-1408-4986-bd6e-0e94afe16d3d</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E969" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F969" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>OP-933</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J969" s="2" t="n">
+        <v>46086.17826401374</v>
+      </c>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>c54ef89f-e21b-4786-ab0b-bf23db7e30b0</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>338c6d71-a408-4308-869a-3436a0c91e83</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E970" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F970" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>OP-981</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J970" s="2" t="n">
+        <v>46067.05326401692</v>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>5c3e463d-18b7-4391-ac36-b0e03032eb29</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>0a10f249-13da-4371-a199-75c2ad82d491</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E971" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F971" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>OP-598</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J971" s="2" t="n">
+        <v>46076.05326401995</v>
+      </c>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>762123f7-f435-4cc9-be8b-d13183b10a68</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>1fa7119d-faf3-4ffb-8b83-393a06318af2</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E972" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F972" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>OP-102</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J972" s="2" t="n">
+        <v>46080.17826402338</v>
+      </c>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>c570de60-51b3-4976-bcd3-7330f3c6225a</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>2a21b7cc-3384-4997-8661-e6758f68394f</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E973" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F973" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>OP-456</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J973" s="2" t="n">
+        <v>46073.88659735984</v>
+      </c>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>021c6950-462b-4422-9b1f-066342437625</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>a99acec5-6416-4490-a246-eb2ec8d719d7</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E974" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F974" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>OP-536</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J974" s="2" t="n">
+        <v>46073.92826402955</v>
+      </c>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>e7060703-0003-4bf3-a559-92acf62de90f</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>0f25cd74-4a8a-4231-805b-c3c7663cc5b1</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E975" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F975" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>OP-802</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J975" s="2" t="n">
+        <v>46089.09493069941</v>
+      </c>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>68f8b745-f2f1-4f3a-856b-7118460c8257</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>5efd4503-96f5-4fb2-824f-e667ac52c10b</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E976" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F976" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>OP-870</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J976" s="2" t="n">
+        <v>46084.928264036</v>
+      </c>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>94904b27-8d10-4d3b-add6-975d76b5ddff</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>9af21df8-cd51-4502-94ce-f3553d0928a4</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E977" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F977" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>OP-131</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J977" s="2" t="n">
+        <v>46068.09493070588</v>
+      </c>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>f7f4c559-335e-4bc3-a2b2-d9c6c8f24867</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>8319d142-4654-4038-ae44-51c3cb160448</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E978" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F978" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>OP-877</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J978" s="2" t="n">
+        <v>46083.13659737563</v>
+      </c>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>ee4fe0d0-e5ed-4a6c-85cf-1c5f0f56d015</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>135adb38-7f11-4675-965f-d978a472b278</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E979" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F979" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>OP-219</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J979" s="2" t="n">
+        <v>46088.09493071212</v>
+      </c>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>103d0e8b-966c-40f8-9222-05756bff466e</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>5f288a9f-0801-4d04-bc47-937e6ebfa0a3</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E980" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F980" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>OP-813</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J980" s="2" t="n">
+        <v>46064.92826404905</v>
+      </c>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>6a54ec52-83ad-44b1-934a-545dae18f54a</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>079795f7-bd4d-4e1b-ae9c-d39e2ef2904b</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E981" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F981" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>OP-317</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J981" s="2" t="n">
+        <v>46076.8865973857</v>
+      </c>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>5c01ca59-e16a-457c-ae52-480f1ded0882</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>3b70566f-9d15-4d01-9994-1ccffe8e9f0e</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E982" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F982" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>OP-785</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J982" s="2" t="n">
+        <v>46063.0115973888</v>
+      </c>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>47b5acdd-858a-42ee-9edb-186982e8b520</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>b2cd0119-099a-4406-89ca-34cbb74ffaf4</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E983" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F983" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>OP-585</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J983" s="2" t="n">
+        <v>46087.13659739216</v>
+      </c>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>671efe5e-e415-45a5-988d-5ad4344c9bdd</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>1b415b2a-42ab-4c43-a205-2a2e67a566e4</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E984" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F984" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>OP-578</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J984" s="2" t="n">
+        <v>46087.05326406204</v>
+      </c>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>eb45ca68-a2b1-4bb7-9efb-035a78c920f5</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>15589b64-caec-4170-8f0e-27ef9bcdcd14</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E985" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F985" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>OP-735</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J985" s="2" t="n">
+        <v>46085.21993073195</v>
+      </c>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>b7d0aaee-138d-48cf-9be9-1f7836b32b4c</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>af9ee15b-eb37-401b-a7df-624a933df8f8</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E986" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F986" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>OP-532</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J986" s="2" t="n">
+        <v>46070.92826406829</v>
+      </c>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>092836cc-6eb6-4bca-88f9-4baab2e6433e</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>041865dc-2220-400d-ac7e-c94b308542a3</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E987" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F987" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>OP-866</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J987" s="2" t="n">
+        <v>46074.21993073834</v>
+      </c>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>a47051f8-dfa7-41ec-b7ed-e95de7a16e42</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>5bfe573b-451d-477f-bbe1-8fbe1e39daf8</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E988" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F988" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>OP-928</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J988" s="2" t="n">
+        <v>46083.01159740809</v>
+      </c>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>7cca1438-478b-4873-b497-22cb2d997803</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>53ef4842-e00b-4f4b-8768-707b0a2a6370</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E989" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F989" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>OP-434</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J989" s="2" t="n">
+        <v>46066.92826407785</v>
+      </c>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>14363440-3343-4aaa-9010-8e753430bab7</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>4ac33e31-b837-4db2-a3fb-818d4181dbb4</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E990" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F990" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>OP-453</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J990" s="2" t="n">
+        <v>46063.96993074784</v>
+      </c>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>e3ab527e-93d4-44df-8426-a55db00096c9</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>96a62cd2-1fbb-42e7-a6c6-80117f8b68e6</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E991" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F991" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>OP-687</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J991" s="2" t="n">
+        <v>46066.92826408425</v>
+      </c>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>9b2f900e-c9dc-41ba-a07f-db462642aabc</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>3d31088d-2f2a-4efd-9a69-b795777050d9</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E992" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F992" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>OP-106</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J992" s="2" t="n">
+        <v>46084.09493075535</v>
+      </c>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>9f31b954-169d-4617-96bf-1d6672588ff9</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>7634b231-a06c-4835-a6d1-12120884b16a</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E993" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F993" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>OP-518</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J993" s="2" t="n">
+        <v>46086.0532640918</v>
+      </c>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>3c96c8b6-f6ec-44c0-8dda-f0bf2adaad7b</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>83471ce2-d99b-4d0a-8ca8-78d4573296b6</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E994" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F994" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>OP-937</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J994" s="2" t="n">
+        <v>46063.17826409538</v>
+      </c>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>02f12fc6-c800-43ed-a7c8-3ab712afa81c</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>4f6ded20-4a22-40ac-9cfd-0e734d4892f3</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E995" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F995" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>OP-143</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J995" s="2" t="n">
+        <v>46072.92826409846</v>
+      </c>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>8caa9e18-abaa-49b6-8d25-1325bf79c2a0</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>be961253-cc99-42aa-8fca-b11a974c87ba</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E996" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F996" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>OP-912</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J996" s="2" t="n">
+        <v>46072.21993076826</v>
+      </c>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>a39404db-608e-4320-bf1a-cf5e36ecc19c</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>1fb8479e-4e53-4969-900d-0172a0a877a1</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E997" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F997" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>OP-744</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J997" s="2" t="n">
+        <v>46078.09493077166</v>
+      </c>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>c740971d-8c3a-4e00-b5a4-368a73b75476</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>1fc1e725-31ae-4d22-b93a-45c1aa8f6f42</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E998" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F998" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>OP-826</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J998" s="2" t="n">
+        <v>46081.8865974414</v>
+      </c>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>d37713ac-c241-48a1-bbd1-c3f5f832d6e8</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>809465fc-383a-4da2-81e1-852e4f415c41</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E999" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F999" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>OP-695</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J999" s="2" t="n">
+        <v>46062.21993077818</v>
+      </c>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>a87ba963-fe1c-43c4-8512-3d4ab844596f</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>1b3b5cd2-a1c7-4e9d-97f1-950018875e4e</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1000" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>OP-556</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1000" s="2" t="n">
+        <v>46066.17826411465</v>
+      </c>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>db270105-b4ff-40cb-9040-f89637b011ad</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>d316f029-e54a-4b26-bbdc-9f2b631a56a2</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1001" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>OP-363</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1001" s="2" t="n">
+        <v>46075.96993078457</v>
+      </c>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1001"/>
+  <dimension ref="A1:K1051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48982,7 +48982,7 @@
         </is>
       </c>
       <c r="J952" s="2" t="n">
-        <v>46064.26159728926</v>
+        <v>46064.26159729167</v>
       </c>
       <c r="K952" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         </is>
       </c>
       <c r="J953" s="2" t="n">
-        <v>46087.969930627</v>
+        <v>46087.969930625</v>
       </c>
       <c r="K953" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         </is>
       </c>
       <c r="J954" s="2" t="n">
-        <v>46082.09493063045</v>
+        <v>46082.094930625</v>
       </c>
       <c r="K954" t="inlineStr">
         <is>
@@ -49135,7 +49135,7 @@
         </is>
       </c>
       <c r="J955" s="2" t="n">
-        <v>46062.0949306342</v>
+        <v>46062.09493063657</v>
       </c>
       <c r="K955" t="inlineStr">
         <is>
@@ -49186,7 +49186,7 @@
         </is>
       </c>
       <c r="J956" s="2" t="n">
-        <v>46077.05326397062</v>
+        <v>46077.05326396991</v>
       </c>
       <c r="K956" t="inlineStr">
         <is>
@@ -49237,7 +49237,7 @@
         </is>
       </c>
       <c r="J957" s="2" t="n">
-        <v>46060.9282639739</v>
+        <v>46060.92826396991</v>
       </c>
       <c r="K957" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         </is>
       </c>
       <c r="J958" s="2" t="n">
-        <v>46089.13659731088</v>
+        <v>46089.13659731481</v>
       </c>
       <c r="K958" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         </is>
       </c>
       <c r="J959" s="2" t="n">
-        <v>46072.92826398079</v>
+        <v>46072.92826398148</v>
       </c>
       <c r="K959" t="inlineStr">
         <is>
@@ -49390,7 +49390,7 @@
         </is>
       </c>
       <c r="J960" s="2" t="n">
-        <v>46068.01159731727</v>
+        <v>46068.01159731481</v>
       </c>
       <c r="K960" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         </is>
       </c>
       <c r="J961" s="2" t="n">
-        <v>46063.05326398729</v>
+        <v>46063.05326399305</v>
       </c>
       <c r="K961" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         </is>
       </c>
       <c r="J962" s="2" t="n">
-        <v>46082.1365973241</v>
+        <v>46082.13659732639</v>
       </c>
       <c r="K962" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         </is>
       </c>
       <c r="J963" s="2" t="n">
-        <v>46075.21993066058</v>
+        <v>46075.21993065972</v>
       </c>
       <c r="K963" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         </is>
       </c>
       <c r="J964" s="2" t="n">
-        <v>46078.92826399709</v>
+        <v>46078.92826399305</v>
       </c>
       <c r="K964" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         </is>
       </c>
       <c r="J965" s="2" t="n">
-        <v>46065.13659733423</v>
+        <v>46065.13659733797</v>
       </c>
       <c r="K965" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         </is>
       </c>
       <c r="J966" s="2" t="n">
-        <v>46071.92826400405</v>
+        <v>46071.92826400463</v>
       </c>
       <c r="K966" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         </is>
       </c>
       <c r="J967" s="2" t="n">
-        <v>46074.88659734046</v>
+        <v>46074.88659733797</v>
       </c>
       <c r="K967" t="inlineStr">
         <is>
@@ -49798,7 +49798,7 @@
         </is>
       </c>
       <c r="J968" s="2" t="n">
-        <v>46078.26159734357</v>
+        <v>46078.26159733797</v>
       </c>
       <c r="K968" t="inlineStr">
         <is>
@@ -49849,7 +49849,7 @@
         </is>
       </c>
       <c r="J969" s="2" t="n">
-        <v>46086.17826401374</v>
+        <v>46086.17826401621</v>
       </c>
       <c r="K969" t="inlineStr">
         <is>
@@ -49900,7 +49900,7 @@
         </is>
       </c>
       <c r="J970" s="2" t="n">
-        <v>46067.05326401692</v>
+        <v>46067.05326401621</v>
       </c>
       <c r="K970" t="inlineStr">
         <is>
@@ -49951,7 +49951,7 @@
         </is>
       </c>
       <c r="J971" s="2" t="n">
-        <v>46076.05326401995</v>
+        <v>46076.05326401621</v>
       </c>
       <c r="K971" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         </is>
       </c>
       <c r="J972" s="2" t="n">
-        <v>46080.17826402338</v>
+        <v>46080.17826402777</v>
       </c>
       <c r="K972" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         </is>
       </c>
       <c r="J973" s="2" t="n">
-        <v>46073.88659735984</v>
+        <v>46073.88659736111</v>
       </c>
       <c r="K973" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         </is>
       </c>
       <c r="J974" s="2" t="n">
-        <v>46073.92826402955</v>
+        <v>46073.92826402777</v>
       </c>
       <c r="K974" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         </is>
       </c>
       <c r="J975" s="2" t="n">
-        <v>46089.09493069941</v>
+        <v>46089.09493069445</v>
       </c>
       <c r="K975" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         </is>
       </c>
       <c r="J976" s="2" t="n">
-        <v>46084.928264036</v>
+        <v>46084.92826403935</v>
       </c>
       <c r="K976" t="inlineStr">
         <is>
@@ -50257,7 +50257,7 @@
         </is>
       </c>
       <c r="J977" s="2" t="n">
-        <v>46068.09493070588</v>
+        <v>46068.09493070602</v>
       </c>
       <c r="K977" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         </is>
       </c>
       <c r="J978" s="2" t="n">
-        <v>46083.13659737563</v>
+        <v>46083.13659737269</v>
       </c>
       <c r="K978" t="inlineStr">
         <is>
@@ -50359,7 +50359,7 @@
         </is>
       </c>
       <c r="J979" s="2" t="n">
-        <v>46088.09493071212</v>
+        <v>46088.09493071759</v>
       </c>
       <c r="K979" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         </is>
       </c>
       <c r="J980" s="2" t="n">
-        <v>46064.92826404905</v>
+        <v>46064.92826405093</v>
       </c>
       <c r="K980" t="inlineStr">
         <is>
@@ -50461,7 +50461,7 @@
         </is>
       </c>
       <c r="J981" s="2" t="n">
-        <v>46076.8865973857</v>
+        <v>46076.88659738426</v>
       </c>
       <c r="K981" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         </is>
       </c>
       <c r="J982" s="2" t="n">
-        <v>46063.0115973888</v>
+        <v>46063.01159738426</v>
       </c>
       <c r="K982" t="inlineStr">
         <is>
@@ -50563,7 +50563,7 @@
         </is>
       </c>
       <c r="J983" s="2" t="n">
-        <v>46087.13659739216</v>
+        <v>46087.13659739583</v>
       </c>
       <c r="K983" t="inlineStr">
         <is>
@@ -50614,7 +50614,7 @@
         </is>
       </c>
       <c r="J984" s="2" t="n">
-        <v>46087.05326406204</v>
+        <v>46087.0532640625</v>
       </c>
       <c r="K984" t="inlineStr">
         <is>
@@ -50665,7 +50665,7 @@
         </is>
       </c>
       <c r="J985" s="2" t="n">
-        <v>46085.21993073195</v>
+        <v>46085.21993072917</v>
       </c>
       <c r="K985" t="inlineStr">
         <is>
@@ -50716,7 +50716,7 @@
         </is>
       </c>
       <c r="J986" s="2" t="n">
-        <v>46070.92826406829</v>
+        <v>46070.9282640625</v>
       </c>
       <c r="K986" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         </is>
       </c>
       <c r="J987" s="2" t="n">
-        <v>46074.21993073834</v>
+        <v>46074.21993074074</v>
       </c>
       <c r="K987" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         </is>
       </c>
       <c r="J988" s="2" t="n">
-        <v>46083.01159740809</v>
+        <v>46083.01159740741</v>
       </c>
       <c r="K988" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         </is>
       </c>
       <c r="J989" s="2" t="n">
-        <v>46066.92826407785</v>
+        <v>46066.92826407407</v>
       </c>
       <c r="K989" t="inlineStr">
         <is>
@@ -50920,7 +50920,7 @@
         </is>
       </c>
       <c r="J990" s="2" t="n">
-        <v>46063.96993074784</v>
+        <v>46063.96993075231</v>
       </c>
       <c r="K990" t="inlineStr">
         <is>
@@ -50971,7 +50971,7 @@
         </is>
       </c>
       <c r="J991" s="2" t="n">
-        <v>46066.92826408425</v>
+        <v>46066.92826408565</v>
       </c>
       <c r="K991" t="inlineStr">
         <is>
@@ -51022,7 +51022,7 @@
         </is>
       </c>
       <c r="J992" s="2" t="n">
-        <v>46084.09493075535</v>
+        <v>46084.09493075231</v>
       </c>
       <c r="K992" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         </is>
       </c>
       <c r="J993" s="2" t="n">
-        <v>46086.0532640918</v>
+        <v>46086.05326409722</v>
       </c>
       <c r="K993" t="inlineStr">
         <is>
@@ -51124,7 +51124,7 @@
         </is>
       </c>
       <c r="J994" s="2" t="n">
-        <v>46063.17826409538</v>
+        <v>46063.17826409722</v>
       </c>
       <c r="K994" t="inlineStr">
         <is>
@@ -51175,7 +51175,7 @@
         </is>
       </c>
       <c r="J995" s="2" t="n">
-        <v>46072.92826409846</v>
+        <v>46072.92826409722</v>
       </c>
       <c r="K995" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         </is>
       </c>
       <c r="J996" s="2" t="n">
-        <v>46072.21993076826</v>
+        <v>46072.21993076389</v>
       </c>
       <c r="K996" t="inlineStr">
         <is>
@@ -51277,7 +51277,7 @@
         </is>
       </c>
       <c r="J997" s="2" t="n">
-        <v>46078.09493077166</v>
+        <v>46078.09493077546</v>
       </c>
       <c r="K997" t="inlineStr">
         <is>
@@ -51328,7 +51328,7 @@
         </is>
       </c>
       <c r="J998" s="2" t="n">
-        <v>46081.8865974414</v>
+        <v>46081.88659744213</v>
       </c>
       <c r="K998" t="inlineStr">
         <is>
@@ -51379,7 +51379,7 @@
         </is>
       </c>
       <c r="J999" s="2" t="n">
-        <v>46062.21993077818</v>
+        <v>46062.21993077546</v>
       </c>
       <c r="K999" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         </is>
       </c>
       <c r="J1000" s="2" t="n">
-        <v>46066.17826411465</v>
+        <v>46066.17826412037</v>
       </c>
       <c r="K1000" t="inlineStr">
         <is>
@@ -51481,11 +51481,2561 @@
         </is>
       </c>
       <c r="J1001" s="2" t="n">
-        <v>46075.96993078457</v>
+        <v>46075.96993078704</v>
       </c>
       <c r="K1001" t="inlineStr">
         <is>
           <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>ce0b7020-740c-4df3-8d3a-1ae61e77c3a0</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>875050a1-b0ef-4e94-86df-99e81c6c7ac8</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1002" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>OP-962</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1002" s="2" t="n">
+        <v>46065.13617045216</v>
+      </c>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>497c340f-ee98-42c8-9af4-42ca258d407f</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>f3362f22-aeca-4338-ba01-0fd14eab7ebc</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1003" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>OP-511</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1003" s="2" t="n">
+        <v>46060.13617045641</v>
+      </c>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>96d778a9-4d65-44b6-a643-4e959378996d</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>d17de870-ea0d-4ca1-981f-7a372f1cc3ed</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1004" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>OP-970</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1004" s="2" t="n">
+        <v>46083.09450379279</v>
+      </c>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>1edf0e2b-dbef-47f8-97fa-5baa5aa1a0c1</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>085d94d0-bba5-4ede-8990-ac9d7715c717</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1005" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>OP-226</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1005" s="2" t="n">
+        <v>46063.05283712977</v>
+      </c>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>fbf50432-fa82-4202-9070-c252c37fe482</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>dfc41205-7812-4be0-b610-292704959829</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1006" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>OP-881</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1006" s="2" t="n">
+        <v>46073.05283713271</v>
+      </c>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>efb4197a-3522-4aa8-83ec-bd9f11839cea</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>34e52add-1e4c-4f41-9352-cb81d8e52b35</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1007" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>OP-182</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1007" s="2" t="n">
+        <v>46078.21950380237</v>
+      </c>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>70dfdfba-2ea0-43a8-b66f-165c0f831fb1</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>03be5c79-3899-4ed0-8795-ce3f154a3fc3</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1008" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>OP-365</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1008" s="2" t="n">
+        <v>46076.17783713874</v>
+      </c>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>6e92aebc-e0c1-4ed8-ac21-627a743a447e</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>cd51a6aa-170b-4a6e-957b-c1a47c6b694e</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1009" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>OP-402</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1009" s="2" t="n">
+        <v>46081.09450380848</v>
+      </c>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>856186f4-1d3b-4c03-8803-e3abd96cfaea</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>55eae441-a279-4cc0-85e1-b065a1b05edb</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1010" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>OP-671</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1010" s="2" t="n">
+        <v>46069.01117047802</v>
+      </c>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>e2cf152f-8982-4e14-86c7-514eb5ef0af9</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>f4a7d138-c478-4311-a08b-20a94c868aec</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1011" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>OP-742</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1011" s="2" t="n">
+        <v>46071.0945038142</v>
+      </c>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>be55b968-89c7-4691-aa99-995fe9b77f13</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>74257408-7a9f-4c95-978a-026cadefec3e</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1012" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>OP-992</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1012" s="2" t="n">
+        <v>46067.96950381716</v>
+      </c>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>31e74252-01da-4e8c-95be-68a4d1b437ea</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>f2bc2587-8dfc-4747-8f1b-4f93a4a4b188</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1013" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>OP-840</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1013" s="2" t="n">
+        <v>46066.92783715348</v>
+      </c>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>7709cd7d-541a-4c76-9551-621919d0e4b8</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>45c2bb71-eb62-4e4a-9282-2cafa0d9d95a</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1014" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>OP-230</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1014" s="2" t="n">
+        <v>46088.05283715648</v>
+      </c>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>b3ec9f7e-3f64-40b9-93ca-0878d97991c6</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>5c13ff06-e031-42b0-9395-8136eb255c62</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1015" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>OP-758</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1015" s="2" t="n">
+        <v>46061.01117049275</v>
+      </c>
+      <c r="K1015" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>aadc9a0e-1fc7-4898-a2cd-0ab596a506b9</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>32f54874-ada2-4f62-8679-58e497aa4a82</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1016" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>OP-569</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1016" s="2" t="n">
+        <v>46073.30283716234</v>
+      </c>
+      <c r="K1016" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>38ee4f7b-af5b-4ace-87d4-90228e9935c9</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>54588a3b-e495-4748-a156-7f1eefb878ad</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1017" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>OP-296</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1017" s="2" t="n">
+        <v>46065.05283716535</v>
+      </c>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>4f45c36b-4e9f-47fd-bf29-3a1a2ac01e9e</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>e4ee32e5-7e60-45eb-a213-c679be87c8bf</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1018" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>OP-673</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1018" s="2" t="n">
+        <v>46078.13617050152</v>
+      </c>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>1e6863df-1b90-41a2-8864-a82e33485da9</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>3c7f8b0c-0c18-4be1-9f2a-2025c68e1257</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1019" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>OP-836</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1019" s="2" t="n">
+        <v>46088.05283717124</v>
+      </c>
+      <c r="K1019" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>eb80522e-9361-4cdc-8b32-c45c36ed148b</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>81deb3c4-c0a5-4a5f-b5c4-3576d080737e</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1020" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>OP-203</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1020" s="2" t="n">
+        <v>46061.09450384099</v>
+      </c>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>d63151ae-04f5-4454-984d-a1b55f440db5</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>e6d9ae79-3ecf-4735-bd91-f7bb2e52b5a3</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1021" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>OP-498</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1021" s="2" t="n">
+        <v>46078.05283717714</v>
+      </c>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>86360bfd-16cd-415e-9b37-81993ae0dda3</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>480b6348-d27b-421f-a0f2-08e1c021db70</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1022" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>OP-293</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1022" s="2" t="n">
+        <v>46074.96950384663</v>
+      </c>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>7d3eb690-9018-4b1c-935f-a3ce15e06b56</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>415db6e1-e911-403d-848a-949773067834</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1023" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>OP-776</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1023" s="2" t="n">
+        <v>46070.05283718283</v>
+      </c>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>0fd8d085-3f35-4f6d-afc5-f23f49b06c73</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>ab24f9d3-e916-4b00-8d41-19126de3f241</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1024" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>OP-392</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1024" s="2" t="n">
+        <v>46060.01117051918</v>
+      </c>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>385ddecf-7bcc-43c5-985b-017b16adcd1d</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>a3d3aadc-5143-4b43-ac28-e76e9f4d6e06</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1025" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>OP-422</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1025" s="2" t="n">
+        <v>46080.09450385535</v>
+      </c>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>e61ec3ff-b335-4c98-b59f-f86ba61c3a96</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>2fbdead1-9d5c-499f-af78-1bf7785c6052</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1026" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>OP-296</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1026" s="2" t="n">
+        <v>46071.26117052481</v>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>b9658acc-9e1f-40d2-8b52-e8a04d9e87a2</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>7ba5b19f-ee0e-4d03-b8fd-c9107a28308e</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1027" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>OP-301</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1027" s="2" t="n">
+        <v>46066.96950386113</v>
+      </c>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>4ddaf31e-c842-4a2e-8946-110674187824</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>871552f8-cbb3-463f-9db0-e3aba46857ec</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1028" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>OP-537</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1028" s="2" t="n">
+        <v>46067.01117053084</v>
+      </c>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>ab4edc3c-2d0e-4fba-8dd1-2c42fedc2232</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>32624650-aba6-436c-86dd-200e54a8f336</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1029" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>OP-608</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1029" s="2" t="n">
+        <v>46080.30283720052</v>
+      </c>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>98d94b44-3fb6-48ae-8fa9-ece267d3a6f0</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>ceb9a8fb-089a-4db7-9ecf-e7ff7bd42b95</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1030" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>OP-178</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1030" s="2" t="n">
+        <v>46072.26117053667</v>
+      </c>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>cd0f9ee2-1214-47f3-afdc-94b1e7638462</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>85529bde-7020-4411-afb1-c1de2aee00a2</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1031" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>OP-107</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1031" s="2" t="n">
+        <v>46075.26117053944</v>
+      </c>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>198a12be-3c22-42e3-988d-9a5177345664</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>04993d78-9dd2-4545-b5af-6d94a67541d9</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1032" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>OP-741</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1032" s="2" t="n">
+        <v>46077.05283720926</v>
+      </c>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>16566d33-4544-49f9-8c01-aed0417ce7be</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>43d41146-64a8-4730-84e5-1f233298a0f2</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1033" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>OP-866</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1033" s="2" t="n">
+        <v>46060.05283721206</v>
+      </c>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>33a81465-092b-4396-85b5-cd504e61259b</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>da4fcc85-22ac-481b-addf-21e4047018ac</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1034" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>OP-166</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1034" s="2" t="n">
+        <v>46078.1778372149</v>
+      </c>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>dd99f405-918c-471e-b33f-b8900c184d20</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>8c099825-0e00-42ab-aed1-9bcc3ce88c9c</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1035" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>OP-251</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1035" s="2" t="n">
+        <v>46088.17783721782</v>
+      </c>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>b4c8282b-3282-4b3c-95e7-f9f479cd8677</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>0fa0c178-3331-4262-b3b0-2cecb4f0129f</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1036" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>OP-481</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1036" s="2" t="n">
+        <v>46065.05283722082</v>
+      </c>
+      <c r="K1036" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>fc274a81-988a-4000-83c2-e0cd877e1794</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>e6b70cec-a923-431b-9ae6-3bd1d9a5012a</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1037" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>OP-876</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1037" s="2" t="n">
+        <v>46088.01117055702</v>
+      </c>
+      <c r="K1037" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>f063fc6e-e368-4457-95e2-c4cf705c35c2</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>73fc9a67-9098-4274-86cf-310aa345714e</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1038" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>OP-245</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1038" s="2" t="n">
+        <v>46077.26117055984</v>
+      </c>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>cfba88ca-38fa-4021-9c03-ecf5cace6c8f</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>bcc971a8-905a-4f4b-b4aa-d274c37721f4</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1039" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>OP-286</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1039" s="2" t="n">
+        <v>46075.09450389617</v>
+      </c>
+      <c r="K1039" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>658cb14f-d466-476b-929b-158745ee4587</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>b9d3e107-be28-4d4d-a16d-f3c09866bdb8</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1040" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>OP-991</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1040" s="2" t="n">
+        <v>46067.01117056587</v>
+      </c>
+      <c r="K1040" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>9a5903e0-ebb1-447b-8b77-b15a7d3b595b</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>c206dd25-25cb-48f8-8fb2-f2e135c6db25</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1041" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>OP-583</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1041" s="2" t="n">
+        <v>46081.30283723534</v>
+      </c>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>80b9dd71-70b7-444e-9169-6e7c6b150632</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>61cbdc40-c5de-482d-ab85-16f77a521bae</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1042" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>OP-872</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1042" s="2" t="n">
+        <v>46076.92783723839</v>
+      </c>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>fef6dcb2-26f3-4293-bfe8-c03db6934767</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>90ff5adf-5551-458a-b72f-334fa6cdb1ea</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1043" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>OP-925</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1043" s="2" t="n">
+        <v>46069.01117057456</v>
+      </c>
+      <c r="K1043" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>9f224115-5e0a-44d2-888f-7a454a20cdaa</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>45ec2436-9667-4e3c-abbd-8aee014e4f70</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1044" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>OP-861</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1044" s="2" t="n">
+        <v>46061.26117057751</v>
+      </c>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>9029dac6-8977-4517-b419-446ba4cc5817</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>cd540633-7ba7-4907-9339-c0c06ee5d9af</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1045" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>OP-273</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1045" s="2" t="n">
+        <v>46071.21950391366</v>
+      </c>
+      <c r="K1045" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>43f6ec5f-622f-4403-8cc5-c4b9b78fbcb4</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>1ce6cef6-2824-4c10-9906-cda4277265e1</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1046" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>OP-642</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1046" s="2" t="n">
+        <v>46060.21950391652</v>
+      </c>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>b81a0147-fb47-4fb4-872f-d7aec6f7e7de</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>ea18cdc6-44ec-4839-8a92-88e7dea25555</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1047" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>OP-652</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1047" s="2" t="n">
+        <v>46063.92783725271</v>
+      </c>
+      <c r="K1047" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>c4a04f6c-db4d-4a4d-8237-445804eaab08</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>e3705764-7a95-4cca-9546-4cc768c99e09</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1048" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>OP-251</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1048" s="2" t="n">
+        <v>46071.92783725577</v>
+      </c>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>5ba8c9bb-1ad9-40a7-a334-f808badd4c78</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>514839d7-a1bd-43bf-938e-012c877db275</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1049" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>OP-529</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1049" s="2" t="n">
+        <v>46077.26117059199</v>
+      </c>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>0cd0283f-a0cb-423f-8506-2ec32765eb7c</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>033f7bb8-f6c4-4624-ac08-cac683c3d702</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1050" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>OP-173</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1050" s="2" t="n">
+        <v>46073.30283726156</v>
+      </c>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>8d40e7a1-d140-4de4-aabb-475d268a9f90</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>b391d8c4-66f0-4f6a-b27d-48a27a466082</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1051" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>OP-956</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1051" s="2" t="n">
+        <v>46083.09450393117</v>
+      </c>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>poor</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1051"/>
+  <dimension ref="A1:K1101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51532,7 +51532,7 @@
         </is>
       </c>
       <c r="J1002" s="2" t="n">
-        <v>46065.13617045216</v>
+        <v>46065.13617045139</v>
       </c>
       <c r="K1002" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         </is>
       </c>
       <c r="J1003" s="2" t="n">
-        <v>46060.13617045641</v>
+        <v>46060.13617045139</v>
       </c>
       <c r="K1003" t="inlineStr">
         <is>
@@ -51634,7 +51634,7 @@
         </is>
       </c>
       <c r="J1004" s="2" t="n">
-        <v>46083.09450379279</v>
+        <v>46083.0945037963</v>
       </c>
       <c r="K1004" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         </is>
       </c>
       <c r="J1005" s="2" t="n">
-        <v>46063.05283712977</v>
+        <v>46063.05283712963</v>
       </c>
       <c r="K1005" t="inlineStr">
         <is>
@@ -51736,7 +51736,7 @@
         </is>
       </c>
       <c r="J1006" s="2" t="n">
-        <v>46073.05283713271</v>
+        <v>46073.05283712963</v>
       </c>
       <c r="K1006" t="inlineStr">
         <is>
@@ -51787,7 +51787,7 @@
         </is>
       </c>
       <c r="J1007" s="2" t="n">
-        <v>46078.21950380237</v>
+        <v>46078.21950380787</v>
       </c>
       <c r="K1007" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         </is>
       </c>
       <c r="J1008" s="2" t="n">
-        <v>46076.17783713874</v>
+        <v>46076.1778371412</v>
       </c>
       <c r="K1008" t="inlineStr">
         <is>
@@ -51889,7 +51889,7 @@
         </is>
       </c>
       <c r="J1009" s="2" t="n">
-        <v>46081.09450380848</v>
+        <v>46081.09450380787</v>
       </c>
       <c r="K1009" t="inlineStr">
         <is>
@@ -51940,7 +51940,7 @@
         </is>
       </c>
       <c r="J1010" s="2" t="n">
-        <v>46069.01117047802</v>
+        <v>46069.01117047454</v>
       </c>
       <c r="K1010" t="inlineStr">
         <is>
@@ -51991,7 +51991,7 @@
         </is>
       </c>
       <c r="J1011" s="2" t="n">
-        <v>46071.0945038142</v>
+        <v>46071.09450381945</v>
       </c>
       <c r="K1011" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         </is>
       </c>
       <c r="J1012" s="2" t="n">
-        <v>46067.96950381716</v>
+        <v>46067.96950381945</v>
       </c>
       <c r="K1012" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         </is>
       </c>
       <c r="J1013" s="2" t="n">
-        <v>46066.92783715348</v>
+        <v>46066.92783715278</v>
       </c>
       <c r="K1013" t="inlineStr">
         <is>
@@ -52144,7 +52144,7 @@
         </is>
       </c>
       <c r="J1014" s="2" t="n">
-        <v>46088.05283715648</v>
+        <v>46088.05283715278</v>
       </c>
       <c r="K1014" t="inlineStr">
         <is>
@@ -52195,7 +52195,7 @@
         </is>
       </c>
       <c r="J1015" s="2" t="n">
-        <v>46061.01117049275</v>
+        <v>46061.01117049769</v>
       </c>
       <c r="K1015" t="inlineStr">
         <is>
@@ -52246,7 +52246,7 @@
         </is>
       </c>
       <c r="J1016" s="2" t="n">
-        <v>46073.30283716234</v>
+        <v>46073.30283716435</v>
       </c>
       <c r="K1016" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         </is>
       </c>
       <c r="J1017" s="2" t="n">
-        <v>46065.05283716535</v>
+        <v>46065.05283716435</v>
       </c>
       <c r="K1017" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         </is>
       </c>
       <c r="J1018" s="2" t="n">
-        <v>46078.13617050152</v>
+        <v>46078.13617049769</v>
       </c>
       <c r="K1018" t="inlineStr">
         <is>
@@ -52399,7 +52399,7 @@
         </is>
       </c>
       <c r="J1019" s="2" t="n">
-        <v>46088.05283717124</v>
+        <v>46088.05283717593</v>
       </c>
       <c r="K1019" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         </is>
       </c>
       <c r="J1020" s="2" t="n">
-        <v>46061.09450384099</v>
+        <v>46061.09450384259</v>
       </c>
       <c r="K1020" t="inlineStr">
         <is>
@@ -52501,7 +52501,7 @@
         </is>
       </c>
       <c r="J1021" s="2" t="n">
-        <v>46078.05283717714</v>
+        <v>46078.05283717593</v>
       </c>
       <c r="K1021" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         </is>
       </c>
       <c r="J1022" s="2" t="n">
-        <v>46074.96950384663</v>
+        <v>46074.96950384259</v>
       </c>
       <c r="K1022" t="inlineStr">
         <is>
@@ -52603,7 +52603,7 @@
         </is>
       </c>
       <c r="J1023" s="2" t="n">
-        <v>46070.05283718283</v>
+        <v>46070.0528371875</v>
       </c>
       <c r="K1023" t="inlineStr">
         <is>
@@ -52654,7 +52654,7 @@
         </is>
       </c>
       <c r="J1024" s="2" t="n">
-        <v>46060.01117051918</v>
+        <v>46060.01117052083</v>
       </c>
       <c r="K1024" t="inlineStr">
         <is>
@@ -52705,7 +52705,7 @@
         </is>
       </c>
       <c r="J1025" s="2" t="n">
-        <v>46080.09450385535</v>
+        <v>46080.09450385417</v>
       </c>
       <c r="K1025" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         </is>
       </c>
       <c r="J1026" s="2" t="n">
-        <v>46071.26117052481</v>
+        <v>46071.26117052083</v>
       </c>
       <c r="K1026" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         </is>
       </c>
       <c r="J1027" s="2" t="n">
-        <v>46066.96950386113</v>
+        <v>46066.96950386574</v>
       </c>
       <c r="K1027" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         </is>
       </c>
       <c r="J1028" s="2" t="n">
-        <v>46067.01117053084</v>
+        <v>46067.01117053241</v>
       </c>
       <c r="K1028" t="inlineStr">
         <is>
@@ -52909,7 +52909,7 @@
         </is>
       </c>
       <c r="J1029" s="2" t="n">
-        <v>46080.30283720052</v>
+        <v>46080.30283719907</v>
       </c>
       <c r="K1029" t="inlineStr">
         <is>
@@ -52960,7 +52960,7 @@
         </is>
       </c>
       <c r="J1030" s="2" t="n">
-        <v>46072.26117053667</v>
+        <v>46072.26117053241</v>
       </c>
       <c r="K1030" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         </is>
       </c>
       <c r="J1031" s="2" t="n">
-        <v>46075.26117053944</v>
+        <v>46075.26117054398</v>
       </c>
       <c r="K1031" t="inlineStr">
         <is>
@@ -53062,7 +53062,7 @@
         </is>
       </c>
       <c r="J1032" s="2" t="n">
-        <v>46077.05283720926</v>
+        <v>46077.05283721065</v>
       </c>
       <c r="K1032" t="inlineStr">
         <is>
@@ -53113,7 +53113,7 @@
         </is>
       </c>
       <c r="J1033" s="2" t="n">
-        <v>46060.05283721206</v>
+        <v>46060.05283721065</v>
       </c>
       <c r="K1033" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         </is>
       </c>
       <c r="J1034" s="2" t="n">
-        <v>46078.1778372149</v>
+        <v>46078.17783721065</v>
       </c>
       <c r="K1034" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         </is>
       </c>
       <c r="J1035" s="2" t="n">
-        <v>46088.17783721782</v>
+        <v>46088.17783722223</v>
       </c>
       <c r="K1035" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         </is>
       </c>
       <c r="J1036" s="2" t="n">
-        <v>46065.05283722082</v>
+        <v>46065.05283722223</v>
       </c>
       <c r="K1036" t="inlineStr">
         <is>
@@ -53317,7 +53317,7 @@
         </is>
       </c>
       <c r="J1037" s="2" t="n">
-        <v>46088.01117055702</v>
+        <v>46088.01117055555</v>
       </c>
       <c r="K1037" t="inlineStr">
         <is>
@@ -53368,7 +53368,7 @@
         </is>
       </c>
       <c r="J1038" s="2" t="n">
-        <v>46077.26117055984</v>
+        <v>46077.26117055555</v>
       </c>
       <c r="K1038" t="inlineStr">
         <is>
@@ -53419,7 +53419,7 @@
         </is>
       </c>
       <c r="J1039" s="2" t="n">
-        <v>46075.09450389617</v>
+        <v>46075.09450390047</v>
       </c>
       <c r="K1039" t="inlineStr">
         <is>
@@ -53470,7 +53470,7 @@
         </is>
       </c>
       <c r="J1040" s="2" t="n">
-        <v>46067.01117056587</v>
+        <v>46067.01117056713</v>
       </c>
       <c r="K1040" t="inlineStr">
         <is>
@@ -53521,7 +53521,7 @@
         </is>
       </c>
       <c r="J1041" s="2" t="n">
-        <v>46081.30283723534</v>
+        <v>46081.30283723379</v>
       </c>
       <c r="K1041" t="inlineStr">
         <is>
@@ -53572,7 +53572,7 @@
         </is>
       </c>
       <c r="J1042" s="2" t="n">
-        <v>46076.92783723839</v>
+        <v>46076.92783723379</v>
       </c>
       <c r="K1042" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         </is>
       </c>
       <c r="J1043" s="2" t="n">
-        <v>46069.01117057456</v>
+        <v>46069.01117057871</v>
       </c>
       <c r="K1043" t="inlineStr">
         <is>
@@ -53674,7 +53674,7 @@
         </is>
       </c>
       <c r="J1044" s="2" t="n">
-        <v>46061.26117057751</v>
+        <v>46061.26117057871</v>
       </c>
       <c r="K1044" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         </is>
       </c>
       <c r="J1045" s="2" t="n">
-        <v>46071.21950391366</v>
+        <v>46071.21950391203</v>
       </c>
       <c r="K1045" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         </is>
       </c>
       <c r="J1046" s="2" t="n">
-        <v>46060.21950391652</v>
+        <v>46060.21950391203</v>
       </c>
       <c r="K1046" t="inlineStr">
         <is>
@@ -53827,7 +53827,7 @@
         </is>
       </c>
       <c r="J1047" s="2" t="n">
-        <v>46063.92783725271</v>
+        <v>46063.92783725695</v>
       </c>
       <c r="K1047" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         </is>
       </c>
       <c r="J1048" s="2" t="n">
-        <v>46071.92783725577</v>
+        <v>46071.92783725695</v>
       </c>
       <c r="K1048" t="inlineStr">
         <is>
@@ -53929,7 +53929,7 @@
         </is>
       </c>
       <c r="J1049" s="2" t="n">
-        <v>46077.26117059199</v>
+        <v>46077.26117059027</v>
       </c>
       <c r="K1049" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         </is>
       </c>
       <c r="J1050" s="2" t="n">
-        <v>46073.30283726156</v>
+        <v>46073.30283725695</v>
       </c>
       <c r="K1050" t="inlineStr">
         <is>
@@ -54031,9 +54031,2559 @@
         </is>
       </c>
       <c r="J1051" s="2" t="n">
-        <v>46083.09450393117</v>
+        <v>46083.09450393519</v>
       </c>
       <c r="K1051" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>0e2c6b7c-1ed7-4ece-95c6-326e7f245f82</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>e16dabbd-1d2f-4339-b1cc-80a62f94afdf</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1052" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>OP-497</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1052" s="2" t="n">
+        <v>46088.17765186141</v>
+      </c>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>a62feb81-cd1e-4f10-bf88-7e060399dfe7</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>8f839f88-f48b-488a-a964-44395f0703cf</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1053" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>OP-676</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1053" s="2" t="n">
+        <v>46076.34431853263</v>
+      </c>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>880e3e00-28b6-4213-8025-289cc3ac1775</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>75590bbb-a494-4465-808f-fb6b375fdadc</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1054" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>OP-226</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1054" s="2" t="n">
+        <v>46065.26098520249</v>
+      </c>
+      <c r="K1054" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>e04f9d23-4f3d-4dca-ad8e-d095b1f38cd0</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>c05580c4-7618-4be4-bd64-e4761cfbd829</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1055" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>OP-381</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1055" s="2" t="n">
+        <v>46078.96931853918</v>
+      </c>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>029a4c5f-09c7-4c0f-8d8d-833790cd9543</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>5c262d93-398c-47a2-aaec-f5b18e59b71c</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1056" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>OP-821</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1056" s="2" t="n">
+        <v>46074.0109852091</v>
+      </c>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>665fa95b-56a8-4028-852a-d442a9c9826b</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>3a1e969f-61d3-4dfb-af1d-5f71b64e4e69</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1057" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>OP-740</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1057" s="2" t="n">
+        <v>46064.13598521262</v>
+      </c>
+      <c r="K1057" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>e8e0c121-d745-48f6-9350-8308b3ed9598</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>4c69d7c4-4f6b-494a-a86f-5c2db622892c</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1058" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>OP-684</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1058" s="2" t="n">
+        <v>46062.09431854916</v>
+      </c>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>ccdd921d-cfd1-4443-837e-8313fedf93b0</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>a1a0e509-e7f5-4cfa-ac65-796dee233ff3</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1059" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>OP-764</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1059" s="2" t="n">
+        <v>46066.09431855227</v>
+      </c>
+      <c r="K1059" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>059e9956-67ae-4e92-8032-8a7c326aa1b9</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>7e5f596b-c489-4bd7-bfc2-a71c88138893</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1060" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>OP-611</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1060" s="2" t="n">
+        <v>46069.30265188897</v>
+      </c>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>cf74a1d2-73b9-445a-b229-2b30dfadff57</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>a5f22db9-f22c-48bf-8821-f090f0715fdc</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1061" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>OP-695</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1061" s="2" t="n">
+        <v>46064.34431855869</v>
+      </c>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>d7eb4da1-90ef-4989-a16a-10e38103f4ec</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>a0fc3a9a-6d1d-4ceb-a400-06e51faa868d</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1062" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>OP-254</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1062" s="2" t="n">
+        <v>46073.34431856214</v>
+      </c>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>7b9fc9c3-b409-4d3d-9008-0e0ee3ab9387</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>94a7a421-2c32-4eba-b98f-00028e8790ec</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1063" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>OP-124</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1063" s="2" t="n">
+        <v>46069.96931856536</v>
+      </c>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>a6028a22-5517-4624-9e4a-3390078698a0</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>e2bf5eb7-0b52-4bfb-bd7c-6f9307596561</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1064" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>OP-195</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1064" s="2" t="n">
+        <v>46079.01098523559</v>
+      </c>
+      <c r="K1064" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>895061fd-d2d6-4d1c-a19f-37bc98121870</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>2462299b-6b78-4a77-a0c9-eb548d12cbd8</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1065" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>OP-927</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1065" s="2" t="n">
+        <v>46084.96931857229</v>
+      </c>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>63293899-c0f9-4b01-b0a2-d26fbfc85345</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>2a80a252-8f36-4a58-b2a7-12b46645d3dc</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1066" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>OP-552</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1066" s="2" t="n">
+        <v>46062.96931857547</v>
+      </c>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>544fe5a2-6457-4ab5-bbdb-d66e077d090d</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>93cdd32c-822a-41a4-9bca-2ca6611ee24e</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1067" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>OP-611</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1067" s="2" t="n">
+        <v>46070.2193185788</v>
+      </c>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>91dc4bc8-3a73-4849-951e-50afad1ff3e5</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>50bfdb89-c1b3-496e-9e23-7255dffdd35c</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1068" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>OP-108</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1068" s="2" t="n">
+        <v>46061.17765191532</v>
+      </c>
+      <c r="K1068" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>5d610880-df55-4262-801d-1060880eb480</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>2a4f75df-ddc8-4388-a4a0-3580f3b3bc3e</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1069" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>OP-449</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1069" s="2" t="n">
+        <v>46077.30265191841</v>
+      </c>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>38aaff30-5a2c-4e23-bd84-788c174d2e5e</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>fa54045f-c307-44c2-9cb2-4da9b00ace67</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1070" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>OP-178</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1070" s="2" t="n">
+        <v>46077.05265192151</v>
+      </c>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>525506d2-e034-4cf3-a2e2-0b74107f6c0b</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>d95cb3e8-2d42-4707-bf30-ba372af93d33</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1071" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>OP-532</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1071" s="2" t="n">
+        <v>46065.21931859138</v>
+      </c>
+      <c r="K1071" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>bd352cdd-9dbd-4243-b984-b95e0016d27c</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>fd7e06d8-23a0-49fa-85f5-bf223431a177</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1072" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>OP-612</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1072" s="2" t="n">
+        <v>46079.96931859444</v>
+      </c>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>281b9b5a-762e-44f4-a931-97753d93193e</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>8bf7ce47-f41d-4170-aab9-3483db575959</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1073" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>OP-493</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1073" s="2" t="n">
+        <v>46072.13598526415</v>
+      </c>
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>f07bd42b-9532-4f35-9e9c-c255963a92cd</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>d75a70de-9895-4467-9f7a-1bdbe489d936</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1074" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>OP-550</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1074" s="2" t="n">
+        <v>46082.05265193393</v>
+      </c>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>26ac6573-9803-4c09-8829-c7fb4c613964</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>1d50234b-0f7f-410c-8b0e-74ac6adae46b</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1075" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>OP-974</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1075" s="2" t="n">
+        <v>46079.30265193714</v>
+      </c>
+      <c r="K1075" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>c4996072-705c-43f8-b10c-3298100d0772</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>93c7e2e9-e4c5-45dd-8616-427bf268accb</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1076" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>OP-970</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1076" s="2" t="n">
+        <v>46083.05265194014</v>
+      </c>
+      <c r="K1076" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>a6c96bfa-d982-4e8d-b32b-366026be26e0</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>3d654124-fe83-462a-b82d-21e7a83e7995</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1077" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>OP-875</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1077" s="2" t="n">
+        <v>46082.17765194343</v>
+      </c>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>ca5a8dcd-445d-4f5a-b9f9-cae89700d167</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>b2374eb8-5dca-4d23-86d0-74ec5777924d</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1078" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>OP-858</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1078" s="2" t="n">
+        <v>46081.13598528024</v>
+      </c>
+      <c r="K1078" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>80a0e4af-2246-40ec-afe0-aa9a9e8615fa</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>0ea8d3dc-64a0-4309-ac80-8bc1f52c869e</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1079" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>OP-273</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1079" s="2" t="n">
+        <v>46064.17765195003</v>
+      </c>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>6750f81b-9569-4be2-a763-7a9e075973b0</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>c7bbcccf-4817-4cce-a4d4-edb90dedd086</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1080" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>OP-768</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1080" s="2" t="n">
+        <v>46062.26098528643</v>
+      </c>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>12b36aa8-00c4-47be-95eb-675d92f95b60</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>1ef489b9-c0a7-4c55-802a-cf1b486c0db6</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1081" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>OP-496</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1081" s="2" t="n">
+        <v>46074.13598528948</v>
+      </c>
+      <c r="K1081" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>0dc24cb5-9356-4319-afb0-083a9209f279</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>84d4c225-14b3-4210-a713-ce6c3e0fadee</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1082" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>OP-656</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1082" s="2" t="n">
+        <v>46080.30265195961</v>
+      </c>
+      <c r="K1082" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>aa6f8d91-3fbb-49b1-b415-0ac45c1740f1</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>63a26f9a-9e9b-4368-9f9b-bd08332ec7a8</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1083" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>OP-537</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1083" s="2" t="n">
+        <v>46074.21931863141</v>
+      </c>
+      <c r="K1083" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>cdedfdee-1889-460a-91c8-b5c9df0ff9be</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>60b90ee6-b3ae-40ef-bdab-ec0bdd121f56</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1084" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>OP-882</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1084" s="2" t="n">
+        <v>46072.01098530144</v>
+      </c>
+      <c r="K1084" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>9abe5c6c-34c9-49f0-99ac-97dd8abf3dfd</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>43687e84-6d98-4596-94cb-826f028b3542</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1085" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>OP-447</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1085" s="2" t="n">
+        <v>46089.34431863848</v>
+      </c>
+      <c r="K1085" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>3bd7de9b-34e8-4d78-a552-8abd4c3bf382</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>55b1e94d-9df6-4841-b5ee-5b412113e0bf</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1086" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>OP-356</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1086" s="2" t="n">
+        <v>46070.26098530818</v>
+      </c>
+      <c r="K1086" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>c1b0ffc2-8866-4300-b288-6801e64528c0</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>28d1062a-61f9-4818-8c75-4d8bee485c68</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1087" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>OP-989</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1087" s="2" t="n">
+        <v>46071.34431864475</v>
+      </c>
+      <c r="K1087" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>9f38e4f1-58e7-4797-837e-ea17840b2f41</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>1f8b29aa-a9bd-4f76-b8d7-833c35008aaa</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1088" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>OP-713</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1088" s="2" t="n">
+        <v>46075.34431864801</v>
+      </c>
+      <c r="K1088" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>86c17b52-479d-4c8f-8237-0db1c049daa4</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>eb796adf-6fff-4250-9bce-7f3a9570c6de</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1089" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>OP-628</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1089" s="2" t="n">
+        <v>46060.96931865127</v>
+      </c>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>be89f713-1415-43ff-b567-86eca720e183</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>1a87ac9c-baa7-406b-9aff-83ff08e44c5c</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1090" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>OP-693</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1090" s="2" t="n">
+        <v>46069.34431865447</v>
+      </c>
+      <c r="K1090" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>ee30f1ea-503e-48ac-a5c1-062088dddaaf</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>a3f4c2da-40ae-41fd-9ffe-4936e50fb01f</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>OP-869</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1091" s="2" t="n">
+        <v>46071.17765199098</v>
+      </c>
+      <c r="K1091" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>aa7a9d33-2393-4542-b30f-d1ae2cd1f2ec</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>3a903d55-0e13-45e3-8d8d-e28bbe73d6b6</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1092" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>OP-268</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1092" s="2" t="n">
+        <v>46082.34431866101</v>
+      </c>
+      <c r="K1092" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>6bddec7f-b6a0-40fc-abf4-4d6930362bd5</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>b2c3c351-caf6-4ce5-9fc6-2d9a8d2e6d46</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1093" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>OP-177</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1093" s="2" t="n">
+        <v>46082.26098533093</v>
+      </c>
+      <c r="K1093" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>ef1dc6e4-dbd0-4705-8f77-453421916222</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>93b274b8-690e-4871-a1c3-36862a74250c</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1094" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>OP-994</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1094" s="2" t="n">
+        <v>46062.09431866756</v>
+      </c>
+      <c r="K1094" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>8d12e93f-152e-4b3d-97e8-95757025cabf</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>355c8edc-4a3f-47a4-91ba-28bdbe68d261</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1095" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>OP-551</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1095" s="2" t="n">
+        <v>46060.30265200423</v>
+      </c>
+      <c r="K1095" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>7a687121-ef6b-45ed-ab28-7de120bf765a</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>ef4e1cc5-1f3e-4126-bc4f-0c0a79bf15c4</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1096" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>OP-941</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1096" s="2" t="n">
+        <v>46062.34431867412</v>
+      </c>
+      <c r="K1096" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>d2e4b007-a026-421a-b57f-fa0661dbf232</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>71e58d7e-5dad-4317-a9ee-e67e85c09a63</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1097" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>OP-777</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1097" s="2" t="n">
+        <v>46077.26098534398</v>
+      </c>
+      <c r="K1097" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>86216374-9759-4d36-9eb5-203b959e5cd1</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>c0dae086-5d8b-49e4-a166-551828cb440d</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1098" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>OP-554</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1098" s="2" t="n">
+        <v>46060.34431868041</v>
+      </c>
+      <c r="K1098" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2831bf1a-4574-40f3-af7a-1c1f2dd5e487</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>6a5abde0-66d5-4855-bdcf-adfda2dd7fa9</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1099" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>OP-633</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1099" s="2" t="n">
+        <v>46067.96931868397</v>
+      </c>
+      <c r="K1099" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>b07e697a-ca43-4265-94cd-5fc3a0ef0baa</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>6a356440-8ea9-4a73-90c3-1051799f93dd</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1100" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>OP-277</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1100" s="2" t="n">
+        <v>46064.21931868714</v>
+      </c>
+      <c r="K1100" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>8fcb06a9-4cb9-4b0b-a468-eb78ee179ca9</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>f514f02e-5ac1-4e8f-b47b-3a1cf2c2a90c</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1101" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>OP-489</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1101" s="2" t="n">
+        <v>46076.01098535689</v>
+      </c>
+      <c r="K1101" t="inlineStr">
         <is>
           <t>poor</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1101"/>
+  <dimension ref="A1:K1151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54082,7 +54082,7 @@
         </is>
       </c>
       <c r="J1052" s="2" t="n">
-        <v>46088.17765186141</v>
+        <v>46088.17765186343</v>
       </c>
       <c r="K1052" t="inlineStr">
         <is>
@@ -54133,7 +54133,7 @@
         </is>
       </c>
       <c r="J1053" s="2" t="n">
-        <v>46076.34431853263</v>
+        <v>46076.34431853009</v>
       </c>
       <c r="K1053" t="inlineStr">
         <is>
@@ -54184,7 +54184,7 @@
         </is>
       </c>
       <c r="J1054" s="2" t="n">
-        <v>46065.26098520249</v>
+        <v>46065.26098519676</v>
       </c>
       <c r="K1054" t="inlineStr">
         <is>
@@ -54235,7 +54235,7 @@
         </is>
       </c>
       <c r="J1055" s="2" t="n">
-        <v>46078.96931853918</v>
+        <v>46078.96931854167</v>
       </c>
       <c r="K1055" t="inlineStr">
         <is>
@@ -54286,7 +54286,7 @@
         </is>
       </c>
       <c r="J1056" s="2" t="n">
-        <v>46074.0109852091</v>
+        <v>46074.01098520833</v>
       </c>
       <c r="K1056" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         </is>
       </c>
       <c r="J1057" s="2" t="n">
-        <v>46064.13598521262</v>
+        <v>46064.13598520833</v>
       </c>
       <c r="K1057" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         </is>
       </c>
       <c r="J1058" s="2" t="n">
-        <v>46062.09431854916</v>
+        <v>46062.09431855324</v>
       </c>
       <c r="K1058" t="inlineStr">
         <is>
@@ -54439,7 +54439,7 @@
         </is>
       </c>
       <c r="J1059" s="2" t="n">
-        <v>46066.09431855227</v>
+        <v>46066.09431855324</v>
       </c>
       <c r="K1059" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         </is>
       </c>
       <c r="J1060" s="2" t="n">
-        <v>46069.30265188897</v>
+        <v>46069.30265188657</v>
       </c>
       <c r="K1060" t="inlineStr">
         <is>
@@ -54541,7 +54541,7 @@
         </is>
       </c>
       <c r="J1061" s="2" t="n">
-        <v>46064.34431855869</v>
+        <v>46064.34431855324</v>
       </c>
       <c r="K1061" t="inlineStr">
         <is>
@@ -54592,7 +54592,7 @@
         </is>
       </c>
       <c r="J1062" s="2" t="n">
-        <v>46073.34431856214</v>
+        <v>46073.34431856481</v>
       </c>
       <c r="K1062" t="inlineStr">
         <is>
@@ -54643,7 +54643,7 @@
         </is>
       </c>
       <c r="J1063" s="2" t="n">
-        <v>46069.96931856536</v>
+        <v>46069.96931856481</v>
       </c>
       <c r="K1063" t="inlineStr">
         <is>
@@ -54694,7 +54694,7 @@
         </is>
       </c>
       <c r="J1064" s="2" t="n">
-        <v>46079.01098523559</v>
+        <v>46079.01098523148</v>
       </c>
       <c r="K1064" t="inlineStr">
         <is>
@@ -54745,7 +54745,7 @@
         </is>
       </c>
       <c r="J1065" s="2" t="n">
-        <v>46084.96931857229</v>
+        <v>46084.96931857639</v>
       </c>
       <c r="K1065" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         </is>
       </c>
       <c r="J1066" s="2" t="n">
-        <v>46062.96931857547</v>
+        <v>46062.96931857639</v>
       </c>
       <c r="K1066" t="inlineStr">
         <is>
@@ -54847,7 +54847,7 @@
         </is>
       </c>
       <c r="J1067" s="2" t="n">
-        <v>46070.2193185788</v>
+        <v>46070.21931857639</v>
       </c>
       <c r="K1067" t="inlineStr">
         <is>
@@ -54898,7 +54898,7 @@
         </is>
       </c>
       <c r="J1068" s="2" t="n">
-        <v>46061.17765191532</v>
+        <v>46061.17765190973</v>
       </c>
       <c r="K1068" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         </is>
       </c>
       <c r="J1069" s="2" t="n">
-        <v>46077.30265191841</v>
+        <v>46077.30265192129</v>
       </c>
       <c r="K1069" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         </is>
       </c>
       <c r="J1070" s="2" t="n">
-        <v>46077.05265192151</v>
+        <v>46077.05265192129</v>
       </c>
       <c r="K1070" t="inlineStr">
         <is>
@@ -55051,7 +55051,7 @@
         </is>
       </c>
       <c r="J1071" s="2" t="n">
-        <v>46065.21931859138</v>
+        <v>46065.21931858797</v>
       </c>
       <c r="K1071" t="inlineStr">
         <is>
@@ -55102,7 +55102,7 @@
         </is>
       </c>
       <c r="J1072" s="2" t="n">
-        <v>46079.96931859444</v>
+        <v>46079.96931859953</v>
       </c>
       <c r="K1072" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         </is>
       </c>
       <c r="J1073" s="2" t="n">
-        <v>46072.13598526415</v>
+        <v>46072.13598526621</v>
       </c>
       <c r="K1073" t="inlineStr">
         <is>
@@ -55204,7 +55204,7 @@
         </is>
       </c>
       <c r="J1074" s="2" t="n">
-        <v>46082.05265193393</v>
+        <v>46082.05265193287</v>
       </c>
       <c r="K1074" t="inlineStr">
         <is>
@@ -55255,7 +55255,7 @@
         </is>
       </c>
       <c r="J1075" s="2" t="n">
-        <v>46079.30265193714</v>
+        <v>46079.30265193287</v>
       </c>
       <c r="K1075" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         </is>
       </c>
       <c r="J1076" s="2" t="n">
-        <v>46083.05265194014</v>
+        <v>46083.05265194445</v>
       </c>
       <c r="K1076" t="inlineStr">
         <is>
@@ -55357,7 +55357,7 @@
         </is>
       </c>
       <c r="J1077" s="2" t="n">
-        <v>46082.17765194343</v>
+        <v>46082.17765194445</v>
       </c>
       <c r="K1077" t="inlineStr">
         <is>
@@ -55408,7 +55408,7 @@
         </is>
       </c>
       <c r="J1078" s="2" t="n">
-        <v>46081.13598528024</v>
+        <v>46081.13598527778</v>
       </c>
       <c r="K1078" t="inlineStr">
         <is>
@@ -55459,7 +55459,7 @@
         </is>
       </c>
       <c r="J1079" s="2" t="n">
-        <v>46064.17765195003</v>
+        <v>46064.17765194445</v>
       </c>
       <c r="K1079" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         </is>
       </c>
       <c r="J1080" s="2" t="n">
-        <v>46062.26098528643</v>
+        <v>46062.26098528935</v>
       </c>
       <c r="K1080" t="inlineStr">
         <is>
@@ -55561,7 +55561,7 @@
         </is>
       </c>
       <c r="J1081" s="2" t="n">
-        <v>46074.13598528948</v>
+        <v>46074.13598528935</v>
       </c>
       <c r="K1081" t="inlineStr">
         <is>
@@ -55612,7 +55612,7 @@
         </is>
       </c>
       <c r="J1082" s="2" t="n">
-        <v>46080.30265195961</v>
+        <v>46080.30265195602</v>
       </c>
       <c r="K1082" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         </is>
       </c>
       <c r="J1083" s="2" t="n">
-        <v>46074.21931863141</v>
+        <v>46074.21931863426</v>
       </c>
       <c r="K1083" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         </is>
       </c>
       <c r="J1084" s="2" t="n">
-        <v>46072.01098530144</v>
+        <v>46072.01098530093</v>
       </c>
       <c r="K1084" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         </is>
       </c>
       <c r="J1085" s="2" t="n">
-        <v>46089.34431863848</v>
+        <v>46089.34431863426</v>
       </c>
       <c r="K1085" t="inlineStr">
         <is>
@@ -55816,7 +55816,7 @@
         </is>
       </c>
       <c r="J1086" s="2" t="n">
-        <v>46070.26098530818</v>
+        <v>46070.2609853125</v>
       </c>
       <c r="K1086" t="inlineStr">
         <is>
@@ -55867,7 +55867,7 @@
         </is>
       </c>
       <c r="J1087" s="2" t="n">
-        <v>46071.34431864475</v>
+        <v>46071.34431864583</v>
       </c>
       <c r="K1087" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         </is>
       </c>
       <c r="J1088" s="2" t="n">
-        <v>46075.34431864801</v>
+        <v>46075.34431864583</v>
       </c>
       <c r="K1088" t="inlineStr">
         <is>
@@ -55969,7 +55969,7 @@
         </is>
       </c>
       <c r="J1089" s="2" t="n">
-        <v>46060.96931865127</v>
+        <v>46060.96931864583</v>
       </c>
       <c r="K1089" t="inlineStr">
         <is>
@@ -56020,7 +56020,7 @@
         </is>
       </c>
       <c r="J1090" s="2" t="n">
-        <v>46069.34431865447</v>
+        <v>46069.34431865741</v>
       </c>
       <c r="K1090" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         </is>
       </c>
       <c r="J1091" s="2" t="n">
-        <v>46071.17765199098</v>
+        <v>46071.17765199074</v>
       </c>
       <c r="K1091" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         </is>
       </c>
       <c r="J1092" s="2" t="n">
-        <v>46082.34431866101</v>
+        <v>46082.34431865741</v>
       </c>
       <c r="K1092" t="inlineStr">
         <is>
@@ -56173,7 +56173,7 @@
         </is>
       </c>
       <c r="J1093" s="2" t="n">
-        <v>46082.26098533093</v>
+        <v>46082.26098533565</v>
       </c>
       <c r="K1093" t="inlineStr">
         <is>
@@ -56224,7 +56224,7 @@
         </is>
       </c>
       <c r="J1094" s="2" t="n">
-        <v>46062.09431866756</v>
+        <v>46062.09431866898</v>
       </c>
       <c r="K1094" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         </is>
       </c>
       <c r="J1095" s="2" t="n">
-        <v>46060.30265200423</v>
+        <v>46060.30265200231</v>
       </c>
       <c r="K1095" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         </is>
       </c>
       <c r="J1096" s="2" t="n">
-        <v>46062.34431867412</v>
+        <v>46062.34431866898</v>
       </c>
       <c r="K1096" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         </is>
       </c>
       <c r="J1097" s="2" t="n">
-        <v>46077.26098534398</v>
+        <v>46077.26098534722</v>
       </c>
       <c r="K1097" t="inlineStr">
         <is>
@@ -56428,7 +56428,7 @@
         </is>
       </c>
       <c r="J1098" s="2" t="n">
-        <v>46060.34431868041</v>
+        <v>46060.34431868055</v>
       </c>
       <c r="K1098" t="inlineStr">
         <is>
@@ -56479,7 +56479,7 @@
         </is>
       </c>
       <c r="J1099" s="2" t="n">
-        <v>46067.96931868397</v>
+        <v>46067.96931868055</v>
       </c>
       <c r="K1099" t="inlineStr">
         <is>
@@ -56530,7 +56530,7 @@
         </is>
       </c>
       <c r="J1100" s="2" t="n">
-        <v>46064.21931868714</v>
+        <v>46064.21931869213</v>
       </c>
       <c r="K1100" t="inlineStr">
         <is>
@@ -56581,11 +56581,2561 @@
         </is>
       </c>
       <c r="J1101" s="2" t="n">
-        <v>46076.01098535689</v>
+        <v>46076.01098535879</v>
       </c>
       <c r="K1101" t="inlineStr">
         <is>
           <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>b5721354-5f9f-4088-8a44-371fafcaca35</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>d2ccf7f0-9de1-443e-b26f-285a4a5c9f4e</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1102" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>OP-567</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1102" s="2" t="n">
+        <v>46072.38618255092</v>
+      </c>
+      <c r="K1102" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>6afcdb33-b5ad-4294-933b-b190741f4677</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>625f52a0-1520-4bd3-97b6-b0c003143539</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1103" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>OP-412</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1103" s="2" t="n">
+        <v>46063.21951588847</v>
+      </c>
+      <c r="K1103" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2ab65706-b34d-4e25-81d7-4b536d858c93</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>791d9521-49ea-412f-94ec-3f834affd71a</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1104" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>OP-368</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1104" s="2" t="n">
+        <v>46067.05284922545</v>
+      </c>
+      <c r="K1104" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>5ec0143d-0c9d-4ae7-ab79-892dbeae4504</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>07b46a48-c32d-491a-9210-a12786071a4a</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1105" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>OP-964</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1105" s="2" t="n">
+        <v>46075.34451589531</v>
+      </c>
+      <c r="K1105" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>b39ffbcf-215f-4849-8303-633f57e26c20</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>21597957-c0db-41d6-bb3f-ac139cb59066</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1106" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>OP-712</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1106" s="2" t="n">
+        <v>46063.26118256528</v>
+      </c>
+      <c r="K1106" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>bdd3bdd7-89e3-4108-9a99-9673ba6d2a0e</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>5b0af28d-a0bc-4436-bd85-97ebd102ca81</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1107" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>OP-408</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1107" s="2" t="n">
+        <v>46068.09451590214</v>
+      </c>
+      <c r="K1107" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>1d2a33c7-1438-4ced-abfe-e6b19100aef5</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>8ed4a7ac-c2b0-4df3-8f21-fd1cd62b1d69</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1108" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>OP-469</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1108" s="2" t="n">
+        <v>46068.17784923852</v>
+      </c>
+      <c r="K1108" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>bc3af18f-ecdc-40de-89ec-1794b4b280b0</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>1fc9a28b-19ff-4118-a7c0-cd9d3c1d62be</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1109" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>OP-843</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1109" s="2" t="n">
+        <v>46083.09451590843</v>
+      </c>
+      <c r="K1109" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>a0189c5b-94c7-4963-8b34-97ca28a757ac</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>97b54d8b-aa2b-4bef-bc40-1356eeb269a8</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1110" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>OP-975</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1110" s="2" t="n">
+        <v>46088.05284924486</v>
+      </c>
+      <c r="K1110" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>66a89c84-ea2f-433b-9fd2-5a6146cb9c2a</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>c21bb342-4ef3-496e-8d68-0524a60aff18</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1111" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>OP-108</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1111" s="2" t="n">
+        <v>46082.26118258166</v>
+      </c>
+      <c r="K1111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>114a2279-9425-4c5b-b8e3-b1beaed66025</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>b458fe90-081c-4487-9d3c-18c13a5ba00c</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1112" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>OP-766</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1112" s="2" t="n">
+        <v>46063.26118258501</v>
+      </c>
+      <c r="K1112" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>92be6935-35a8-4e2c-a356-e97a3d5a3645</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>5ddc5d20-f011-4602-96f7-97fea21579ca</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1113" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>OP-128</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1113" s="2" t="n">
+        <v>46072.09451592155</v>
+      </c>
+      <c r="K1113" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>708ab784-18bb-4404-9c46-06d91d96ee3a</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>7247395f-ae70-4d17-869d-ba90f4071ca3</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1114" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>OP-791</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1114" s="2" t="n">
+        <v>46066.05284925872</v>
+      </c>
+      <c r="K1114" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>6a373f41-aa10-446e-b5b0-369cddd46d11</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>8e5661d9-114a-41c9-aefd-06f82e213f68</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1115" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>OP-636</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1115" s="2" t="n">
+        <v>46084.38618259532</v>
+      </c>
+      <c r="K1115" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>baaa134d-e8a4-4a00-8a5d-5b83e76d4d0e</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>cf206d23-9f64-404c-993c-d06f37941bf4</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1116" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>OP-452</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1116" s="2" t="n">
+        <v>46066.09451593187</v>
+      </c>
+      <c r="K1116" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>1472eb74-1958-4e04-8427-019ac668c934</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>4120ab62-081e-46e2-841a-b1c488ff23a1</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>OP-480</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1117" s="2" t="n">
+        <v>46086.3861826019</v>
+      </c>
+      <c r="K1117" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>80d8dbf3-a022-428e-8392-2dc53bb61540</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>5b982147-9f97-4af5-a031-6330dd1e6fa3</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1118" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>OP-170</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1118" s="2" t="n">
+        <v>46072.34451593849</v>
+      </c>
+      <c r="K1118" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>bf695517-602c-4f57-a5da-aa60eedcdd58</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>2a7e856a-a4d4-4689-9fb8-5b8ba31b3756</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1119" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>OP-330</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1119" s="2" t="n">
+        <v>46077.05284927483</v>
+      </c>
+      <c r="K1119" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>0a553219-8643-4b8e-baf0-c264cbe57776</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>a1229b92-505f-4ab9-b33d-c478f6308440</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1120" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>OP-584</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1120" s="2" t="n">
+        <v>46083.01118261142</v>
+      </c>
+      <c r="K1120" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>cd545272-2114-4098-965e-6a84d291a75d</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>e14b5a01-a9d3-494e-8a27-25ba8b85ee8e</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1121" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>OP-772</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1121" s="2" t="n">
+        <v>46078.30284928159</v>
+      </c>
+      <c r="K1121" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>419e351f-5128-4bef-805c-6c2dd5a8e88e</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>2e65af93-0eae-451b-9fb3-7912b544f47d</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1122" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>OP-903</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1122" s="2" t="n">
+        <v>46073.13618261818</v>
+      </c>
+      <c r="K1122" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>ea88d44e-fe41-4c87-b8c7-b44edc7168a8</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>1947735c-99fb-4591-8515-4199ab7ae856</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>OP-835</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1123" s="2" t="n">
+        <v>46070.01118262145</v>
+      </c>
+      <c r="K1123" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>f9cd9d69-341e-46b5-99c6-8e9f2296ba73</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>05cb4225-a92a-4b1c-ad0e-e6b4530089e8</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1124" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>OP-865</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1124" s="2" t="n">
+        <v>46084.05284929121</v>
+      </c>
+      <c r="K1124" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>6284b8a6-d697-4949-a91c-fa83ef5d1d22</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>b4ddff6e-c535-4e12-85ba-f6b94c9ddddc</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1125" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>OP-163</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1125" s="2" t="n">
+        <v>46081.3445159614</v>
+      </c>
+      <c r="K1125" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>ce155132-ebe6-4cad-8c9c-f88e5dc328de</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>ab22b40c-6d45-4e73-a538-89c7cf7d755b</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1126" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>OP-672</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1126" s="2" t="n">
+        <v>46086.30284929779</v>
+      </c>
+      <c r="K1126" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>200dc75a-772c-4c3d-bcc8-1bd047d3f5d4</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>6dc962e0-af41-4d57-8529-0ebf8d4b407f</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1127" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>OP-852</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1127" s="2" t="n">
+        <v>46061.13618263436</v>
+      </c>
+      <c r="K1127" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>fef8a49c-4a8b-47fb-869f-b4cfcdb07bad</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>0fcdccd1-01f3-4b93-a474-c9848e91901d</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1128" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>OP-945</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1128" s="2" t="n">
+        <v>46061.0528493048</v>
+      </c>
+      <c r="K1128" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>bc00974b-fc33-45d3-a418-d78fcf8b51cf</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>443d6df9-8566-47a9-824d-5d34e62427cb</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1129" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>OP-614</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1129" s="2" t="n">
+        <v>46071.38618264139</v>
+      </c>
+      <c r="K1129" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>b618d03b-6be0-4a73-9d3c-16a52ab53df1</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>c62bf95e-c6c8-439b-b4cb-6e309c8411e4</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1130" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>OP-491</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1130" s="2" t="n">
+        <v>46073.26118264463</v>
+      </c>
+      <c r="K1130" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>8135e575-6f8b-4755-abe1-101de87c6018</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>83a0780e-a8b1-466f-97ca-bb74c956ea67</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1131" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>OP-939</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1131" s="2" t="n">
+        <v>46078.21951598113</v>
+      </c>
+      <c r="K1131" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>46c36e2a-bb7e-4448-abcf-9b0086d827b0</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>72575689-3a34-4a48-99e6-dc1d5ae8ef7d</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>OP-208</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1132" s="2" t="n">
+        <v>46081.21951598463</v>
+      </c>
+      <c r="K1132" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>acb71b3c-43e3-49a1-aec2-d9f421ae33d3</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>9b20e40b-700b-4b39-a46b-ab9c2b223a71</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1133" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>OP-233</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1133" s="2" t="n">
+        <v>46075.21951598772</v>
+      </c>
+      <c r="K1133" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>e60b4df7-6212-4d23-85f1-391d050c920e</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>129b97e9-ebb1-4bf0-b2f4-0eb5ccb772b6</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>OP-490</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1134" s="2" t="n">
+        <v>46062.09451599094</v>
+      </c>
+      <c r="K1134" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>4f083b3f-c002-4c9d-9e06-885562a1f8c5</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>57d32540-b995-4982-b7e5-1a21fcfeda45</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1135" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>OP-260</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1135" s="2" t="n">
+        <v>46067.01118266105</v>
+      </c>
+      <c r="K1135" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>c9261025-c4a8-4afc-917d-02e5467f5280</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>6c145f29-0bab-49d8-9a4b-334f4c9d20b3</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1136" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>OP-543</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1136" s="2" t="n">
+        <v>46062.21951599737</v>
+      </c>
+      <c r="K1136" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>4661df80-e26d-4986-9564-4c4ebfe90675</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>ba3e8f8c-a625-4c79-9af0-ade85a184a53</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1137" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>OP-901</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1137" s="2" t="n">
+        <v>46066.26118266714</v>
+      </c>
+      <c r="K1137" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>b9c208ef-ab24-447d-8e3a-192ef1ad9d03</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>7b860a4a-3b9d-44d3-8d59-89a0019578da</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1138" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>OP-733</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1138" s="2" t="n">
+        <v>46084.17784933686</v>
+      </c>
+      <c r="K1138" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>f50b0b0e-c3bb-497e-a63c-e95179f76418</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>e31a35e5-4a85-45f3-9102-4681e89d57f7</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1139" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>OP-164</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1139" s="2" t="n">
+        <v>46071.13618267373</v>
+      </c>
+      <c r="K1139" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>84cf636a-c09c-41f6-a1a0-2467bff8dff4</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>2d4f2c47-efb3-405c-961e-8222f25fe1f9</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1140" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>OP-445</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1140" s="2" t="n">
+        <v>46065.3028493436</v>
+      </c>
+      <c r="K1140" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>aeb63f31-608d-4710-8e15-60ff7eda8291</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>e0a0e00e-d2cd-4ef6-8f55-04489fbd210b</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1141" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>OP-116</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1141" s="2" t="n">
+        <v>46065.34451601349</v>
+      </c>
+      <c r="K1141" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>29ed0f3b-33c0-4756-b10c-99a8132c562c</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>4f9bd536-2a22-48f1-b5f7-81168938ffa5</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1142" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>OP-476</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1142" s="2" t="n">
+        <v>46063.09451601723</v>
+      </c>
+      <c r="K1142" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>1dc32de8-82cb-4be2-83d2-987c6f3e2937</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>982e3ed0-02c7-4a05-a41e-bc7c5473beba</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1143" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>OP-470</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1143" s="2" t="n">
+        <v>46073.38618268719</v>
+      </c>
+      <c r="K1143" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>09cbb415-8471-4036-b566-18308dbf7c40</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>acf8f7b3-e498-4c4e-b99f-6f2aae17caf3</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1144" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>OP-667</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1144" s="2" t="n">
+        <v>46083.30284935699</v>
+      </c>
+      <c r="K1144" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>eb3e3576-6ade-45a3-92ae-d2b7cfef0180</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>2202438b-1dff-42c1-9b7b-7c61b98889fc</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1145" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>OP-148</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1145" s="2" t="n">
+        <v>46067.09451602664</v>
+      </c>
+      <c r="K1145" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>33aebfaa-7653-46da-8d6d-346f974fda5b</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>89576101-332f-4f69-939f-096d83372f1e</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1146" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>OP-143</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1146" s="2" t="n">
+        <v>46060.26118269685</v>
+      </c>
+      <c r="K1146" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>e4eef52f-e303-4e9e-92ba-84555d528522</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>b73e16af-cad5-4701-aca0-c9ffb38a9fee</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1147" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>OP-778</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1147" s="2" t="n">
+        <v>46071.30284936668</v>
+      </c>
+      <c r="K1147" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>5b2688d2-bcbe-44b0-a5d2-03ee51fd338e</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>3b59f533-a9a2-4c4e-b5a8-0da877858b8d</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1148" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>OP-869</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1148" s="2" t="n">
+        <v>46068.05284936976</v>
+      </c>
+      <c r="K1148" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>802babcf-26d8-4852-80fa-7b857e98a7df</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>f1c14c1a-2da4-4d81-aae1-924627ac801c</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1149" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>OP-153</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1149" s="2" t="n">
+        <v>46067.01118270647</v>
+      </c>
+      <c r="K1149" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>f1b7cefa-e252-475a-be6c-140c084bf969</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>2672a97f-59d8-4e78-bf25-a674091cded1</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1150" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>OP-626</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1150" s="2" t="n">
+        <v>46084.34451604296</v>
+      </c>
+      <c r="K1150" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>0f2c1707-891b-4cad-ac21-59558a036716</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>d26d6c86-f71f-43f1-9755-3fdfea12200a</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1151" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>OP-287</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1151" s="2" t="n">
+        <v>46066.05284937933</v>
+      </c>
+      <c r="K1151" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1151"/>
+  <dimension ref="A1:K1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56632,7 +56632,7 @@
         </is>
       </c>
       <c r="J1102" s="2" t="n">
-        <v>46072.38618255092</v>
+        <v>46072.3861825463</v>
       </c>
       <c r="K1102" t="inlineStr">
         <is>
@@ -56683,7 +56683,7 @@
         </is>
       </c>
       <c r="J1103" s="2" t="n">
-        <v>46063.21951588847</v>
+        <v>46063.21951589121</v>
       </c>
       <c r="K1103" t="inlineStr">
         <is>
@@ -56734,7 +56734,7 @@
         </is>
       </c>
       <c r="J1104" s="2" t="n">
-        <v>46067.05284922545</v>
+        <v>46067.05284922454</v>
       </c>
       <c r="K1104" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         </is>
       </c>
       <c r="J1105" s="2" t="n">
-        <v>46075.34451589531</v>
+        <v>46075.34451589121</v>
       </c>
       <c r="K1105" t="inlineStr">
         <is>
@@ -56836,7 +56836,7 @@
         </is>
       </c>
       <c r="J1106" s="2" t="n">
-        <v>46063.26118256528</v>
+        <v>46063.26118256945</v>
       </c>
       <c r="K1106" t="inlineStr">
         <is>
@@ -56887,7 +56887,7 @@
         </is>
       </c>
       <c r="J1107" s="2" t="n">
-        <v>46068.09451590214</v>
+        <v>46068.09451590278</v>
       </c>
       <c r="K1107" t="inlineStr">
         <is>
@@ -56938,7 +56938,7 @@
         </is>
       </c>
       <c r="J1108" s="2" t="n">
-        <v>46068.17784923852</v>
+        <v>46068.17784923611</v>
       </c>
       <c r="K1108" t="inlineStr">
         <is>
@@ -56989,7 +56989,7 @@
         </is>
       </c>
       <c r="J1109" s="2" t="n">
-        <v>46083.09451590843</v>
+        <v>46083.09451590278</v>
       </c>
       <c r="K1109" t="inlineStr">
         <is>
@@ -57040,7 +57040,7 @@
         </is>
       </c>
       <c r="J1110" s="2" t="n">
-        <v>46088.05284924486</v>
+        <v>46088.05284924769</v>
       </c>
       <c r="K1110" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         </is>
       </c>
       <c r="J1111" s="2" t="n">
-        <v>46082.26118258166</v>
+        <v>46082.26118258102</v>
       </c>
       <c r="K1111" t="inlineStr">
         <is>
@@ -57142,7 +57142,7 @@
         </is>
       </c>
       <c r="J1112" s="2" t="n">
-        <v>46063.26118258501</v>
+        <v>46063.26118258102</v>
       </c>
       <c r="K1112" t="inlineStr">
         <is>
@@ -57193,7 +57193,7 @@
         </is>
       </c>
       <c r="J1113" s="2" t="n">
-        <v>46072.09451592155</v>
+        <v>46072.09451592593</v>
       </c>
       <c r="K1113" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         </is>
       </c>
       <c r="J1114" s="2" t="n">
-        <v>46066.05284925872</v>
+        <v>46066.05284925926</v>
       </c>
       <c r="K1114" t="inlineStr">
         <is>
@@ -57295,7 +57295,7 @@
         </is>
       </c>
       <c r="J1115" s="2" t="n">
-        <v>46084.38618259532</v>
+        <v>46084.38618259259</v>
       </c>
       <c r="K1115" t="inlineStr">
         <is>
@@ -57346,7 +57346,7 @@
         </is>
       </c>
       <c r="J1116" s="2" t="n">
-        <v>46066.09451593187</v>
+        <v>46066.0945159375</v>
       </c>
       <c r="K1116" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         </is>
       </c>
       <c r="J1117" s="2" t="n">
-        <v>46086.3861826019</v>
+        <v>46086.38618260417</v>
       </c>
       <c r="K1117" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         </is>
       </c>
       <c r="J1118" s="2" t="n">
-        <v>46072.34451593849</v>
+        <v>46072.3445159375</v>
       </c>
       <c r="K1118" t="inlineStr">
         <is>
@@ -57499,7 +57499,7 @@
         </is>
       </c>
       <c r="J1119" s="2" t="n">
-        <v>46077.05284927483</v>
+        <v>46077.05284927083</v>
       </c>
       <c r="K1119" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         </is>
       </c>
       <c r="J1120" s="2" t="n">
-        <v>46083.01118261142</v>
+        <v>46083.01118261574</v>
       </c>
       <c r="K1120" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         </is>
       </c>
       <c r="J1121" s="2" t="n">
-        <v>46078.30284928159</v>
+        <v>46078.30284928241</v>
       </c>
       <c r="K1121" t="inlineStr">
         <is>
@@ -57652,7 +57652,7 @@
         </is>
       </c>
       <c r="J1122" s="2" t="n">
-        <v>46073.13618261818</v>
+        <v>46073.13618261574</v>
       </c>
       <c r="K1122" t="inlineStr">
         <is>
@@ -57703,7 +57703,7 @@
         </is>
       </c>
       <c r="J1123" s="2" t="n">
-        <v>46070.01118262145</v>
+        <v>46070.01118261574</v>
       </c>
       <c r="K1123" t="inlineStr">
         <is>
@@ -57754,7 +57754,7 @@
         </is>
       </c>
       <c r="J1124" s="2" t="n">
-        <v>46084.05284929121</v>
+        <v>46084.05284929398</v>
       </c>
       <c r="K1124" t="inlineStr">
         <is>
@@ -57805,7 +57805,7 @@
         </is>
       </c>
       <c r="J1125" s="2" t="n">
-        <v>46081.3445159614</v>
+        <v>46081.34451596065</v>
       </c>
       <c r="K1125" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         </is>
       </c>
       <c r="J1126" s="2" t="n">
-        <v>46086.30284929779</v>
+        <v>46086.30284929398</v>
       </c>
       <c r="K1126" t="inlineStr">
         <is>
@@ -57907,7 +57907,7 @@
         </is>
       </c>
       <c r="J1127" s="2" t="n">
-        <v>46061.13618263436</v>
+        <v>46061.13618263889</v>
       </c>
       <c r="K1127" t="inlineStr">
         <is>
@@ -57958,7 +57958,7 @@
         </is>
       </c>
       <c r="J1128" s="2" t="n">
-        <v>46061.0528493048</v>
+        <v>46061.05284930555</v>
       </c>
       <c r="K1128" t="inlineStr">
         <is>
@@ -58009,7 +58009,7 @@
         </is>
       </c>
       <c r="J1129" s="2" t="n">
-        <v>46071.38618264139</v>
+        <v>46071.38618263889</v>
       </c>
       <c r="K1129" t="inlineStr">
         <is>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="J1130" s="2" t="n">
-        <v>46073.26118264463</v>
+        <v>46073.26118263889</v>
       </c>
       <c r="K1130" t="inlineStr">
         <is>
@@ -58111,7 +58111,7 @@
         </is>
       </c>
       <c r="J1131" s="2" t="n">
-        <v>46078.21951598113</v>
+        <v>46078.21951598379</v>
       </c>
       <c r="K1131" t="inlineStr">
         <is>
@@ -58162,7 +58162,7 @@
         </is>
       </c>
       <c r="J1132" s="2" t="n">
-        <v>46081.21951598463</v>
+        <v>46081.21951598379</v>
       </c>
       <c r="K1132" t="inlineStr">
         <is>
@@ -58213,7 +58213,7 @@
         </is>
       </c>
       <c r="J1133" s="2" t="n">
-        <v>46075.21951598772</v>
+        <v>46075.21951598379</v>
       </c>
       <c r="K1133" t="inlineStr">
         <is>
@@ -58264,7 +58264,7 @@
         </is>
       </c>
       <c r="J1134" s="2" t="n">
-        <v>46062.09451599094</v>
+        <v>46062.09451599537</v>
       </c>
       <c r="K1134" t="inlineStr">
         <is>
@@ -58315,7 +58315,7 @@
         </is>
       </c>
       <c r="J1135" s="2" t="n">
-        <v>46067.01118266105</v>
+        <v>46067.01118266203</v>
       </c>
       <c r="K1135" t="inlineStr">
         <is>
@@ -58366,7 +58366,7 @@
         </is>
       </c>
       <c r="J1136" s="2" t="n">
-        <v>46062.21951599737</v>
+        <v>46062.21951599537</v>
       </c>
       <c r="K1136" t="inlineStr">
         <is>
@@ -58417,7 +58417,7 @@
         </is>
       </c>
       <c r="J1137" s="2" t="n">
-        <v>46066.26118266714</v>
+        <v>46066.26118266203</v>
       </c>
       <c r="K1137" t="inlineStr">
         <is>
@@ -58468,7 +58468,7 @@
         </is>
       </c>
       <c r="J1138" s="2" t="n">
-        <v>46084.17784933686</v>
+        <v>46084.17784934027</v>
       </c>
       <c r="K1138" t="inlineStr">
         <is>
@@ -58519,7 +58519,7 @@
         </is>
       </c>
       <c r="J1139" s="2" t="n">
-        <v>46071.13618267373</v>
+        <v>46071.13618267361</v>
       </c>
       <c r="K1139" t="inlineStr">
         <is>
@@ -58570,7 +58570,7 @@
         </is>
       </c>
       <c r="J1140" s="2" t="n">
-        <v>46065.3028493436</v>
+        <v>46065.30284934027</v>
       </c>
       <c r="K1140" t="inlineStr">
         <is>
@@ -58621,7 +58621,7 @@
         </is>
       </c>
       <c r="J1141" s="2" t="n">
-        <v>46065.34451601349</v>
+        <v>46065.34451601852</v>
       </c>
       <c r="K1141" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         </is>
       </c>
       <c r="J1142" s="2" t="n">
-        <v>46063.09451601723</v>
+        <v>46063.09451601852</v>
       </c>
       <c r="K1142" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         </is>
       </c>
       <c r="J1143" s="2" t="n">
-        <v>46073.38618268719</v>
+        <v>46073.38618268519</v>
       </c>
       <c r="K1143" t="inlineStr">
         <is>
@@ -58774,7 +58774,7 @@
         </is>
       </c>
       <c r="J1144" s="2" t="n">
-        <v>46083.30284935699</v>
+        <v>46083.30284935185</v>
       </c>
       <c r="K1144" t="inlineStr">
         <is>
@@ -58825,7 +58825,7 @@
         </is>
       </c>
       <c r="J1145" s="2" t="n">
-        <v>46067.09451602664</v>
+        <v>46067.09451603009</v>
       </c>
       <c r="K1145" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         </is>
       </c>
       <c r="J1146" s="2" t="n">
-        <v>46060.26118269685</v>
+        <v>46060.26118269676</v>
       </c>
       <c r="K1146" t="inlineStr">
         <is>
@@ -58927,7 +58927,7 @@
         </is>
       </c>
       <c r="J1147" s="2" t="n">
-        <v>46071.30284936668</v>
+        <v>46071.30284936343</v>
       </c>
       <c r="K1147" t="inlineStr">
         <is>
@@ -58978,7 +58978,7 @@
         </is>
       </c>
       <c r="J1148" s="2" t="n">
-        <v>46068.05284936976</v>
+        <v>46068.052849375</v>
       </c>
       <c r="K1148" t="inlineStr">
         <is>
@@ -59029,7 +59029,7 @@
         </is>
       </c>
       <c r="J1149" s="2" t="n">
-        <v>46067.01118270647</v>
+        <v>46067.01118270833</v>
       </c>
       <c r="K1149" t="inlineStr">
         <is>
@@ -59080,7 +59080,7 @@
         </is>
       </c>
       <c r="J1150" s="2" t="n">
-        <v>46084.34451604296</v>
+        <v>46084.34451604167</v>
       </c>
       <c r="K1150" t="inlineStr">
         <is>
@@ -59131,9 +59131,2559 @@
         </is>
       </c>
       <c r="J1151" s="2" t="n">
-        <v>46066.05284937933</v>
+        <v>46066.052849375</v>
       </c>
       <c r="K1151" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>837289bd-48f8-4c39-a638-e8da5b054ab2</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>bdf4b332-0b8b-4345-8efc-5da99cba448f</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1152" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>OP-956</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1152" s="2" t="n">
+        <v>46060.13900370518</v>
+      </c>
+      <c r="K1152" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>0abbc0ff-6b77-4c78-99b6-acbf818514b8</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>19c89a45-aa5b-42a7-a4c4-f37c45aabfa6</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1153" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>OP-430</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1153" s="2" t="n">
+        <v>46082.43067037634</v>
+      </c>
+      <c r="K1153" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>d609c24b-7293-454f-b974-b919b148d679</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>c836f447-2e61-4e2d-93e6-40c39cb154f4</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1154" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>OP-267</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1154" s="2" t="n">
+        <v>46069.30567037963</v>
+      </c>
+      <c r="K1154" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>49151ad8-ad5c-4641-b40c-5c99a85920fd</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>62f560a5-91f1-4f66-b3cb-9d58b6eab438</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1155" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>OP-627</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1155" s="2" t="n">
+        <v>46082.43067038291</v>
+      </c>
+      <c r="K1155" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>93c80424-8831-4934-bdde-bd55cb7c565b</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>bb4bd56d-5a84-4a0c-a431-099e02ae72d8</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1156" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>OP-980</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1156" s="2" t="n">
+        <v>46061.09733705282</v>
+      </c>
+      <c r="K1156" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>b53a746b-6829-4469-93f0-1382cffd2b36</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>44faa6cf-9b22-4d69-b9a2-4345a45d3352</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1157" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>OP-941</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1157" s="2" t="n">
+        <v>46068.13900372252</v>
+      </c>
+      <c r="K1157" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>00972849-845b-4ed6-974c-ef389a66940b</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>b49d50bb-b452-432a-b4d6-91832883d3bc</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1158" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>OP-792</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1158" s="2" t="n">
+        <v>46073.43067039228</v>
+      </c>
+      <c r="K1158" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>c6689148-0468-4379-9804-bea45ac1ba43</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>71f378d4-e4cd-43fc-a31f-bef166595fa4</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1159" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>OP-708</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1159" s="2" t="n">
+        <v>46079.347337062</v>
+      </c>
+      <c r="K1159" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>091a0d00-5f18-42b6-aab9-72728af328c8</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>fcae4882-87eb-4fab-9351-03c7d2848d20</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1160" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>OP-286</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1160" s="2" t="n">
+        <v>46082.13900373227</v>
+      </c>
+      <c r="K1160" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>dddf9843-096e-49a7-ac5c-b239e1a33737</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>e9168ebc-7ecf-4cbe-8a98-f938355e9523</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1161" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>OP-441</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1161" s="2" t="n">
+        <v>46063.13900373533</v>
+      </c>
+      <c r="K1161" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>a271da11-35cd-4bb9-b17c-d16114a4ee83</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>6b39cd39-e27a-4b64-aeca-4e007d2af4e1</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1162" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>OP-382</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1162" s="2" t="n">
+        <v>46080.26400373855</v>
+      </c>
+      <c r="K1162" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>7d8150c1-0500-4b89-bf65-d9a3113199fd</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>61a1cfe8-947b-48ce-9efd-5de0790e0464</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1163" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>OP-610</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1163" s="2" t="n">
+        <v>46077.38900374183</v>
+      </c>
+      <c r="K1163" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>8a5b35ca-1692-484a-8c2d-2d1f0edc3acc</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>781ed867-0298-4e17-b8b2-acff8967a7bf</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1164" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>OP-247</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1164" s="2" t="n">
+        <v>46073.38900374485</v>
+      </c>
+      <c r="K1164" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2d00435c-0498-42fa-856f-177a03e58671</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>63ddbf74-1643-45a2-9ec6-d121cb1b59a1</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1165" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>OP-345</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1165" s="2" t="n">
+        <v>46082.43067041459</v>
+      </c>
+      <c r="K1165" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>16b58a7b-3289-4f07-a362-aa62c5534f67</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>b4477b36-8d6b-4bfa-8342-f947487f970d</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1166" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>OP-861</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1166" s="2" t="n">
+        <v>46088.13900375108</v>
+      </c>
+      <c r="K1166" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>615f84cd-2b5f-472d-9393-9270965fdab5</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>4a9cb2bb-1014-48da-9937-60401e10b680</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1167" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>OP-335</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1167" s="2" t="n">
+        <v>46068.1806704211</v>
+      </c>
+      <c r="K1167" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>ac033626-0768-45fc-820f-a1a0ba764992</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>726735f7-3ea1-47ab-8022-fd30fa0f6c7f</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1168" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>OP-322</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1168" s="2" t="n">
+        <v>46075.1806704245</v>
+      </c>
+      <c r="K1168" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>cd336aab-d65a-410c-aa1d-fb3fa6a0b920</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>2fe930f4-2ee6-4474-a7b3-a7eff48c5025</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1169" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>OP-791</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1169" s="2" t="n">
+        <v>46081.18067042749</v>
+      </c>
+      <c r="K1169" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>90b867bd-5ffc-4124-bf03-1af66090f232</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>e8d5f8dc-538a-47b8-aa19-c6efbbb15162</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1170" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>OP-245</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1170" s="2" t="n">
+        <v>46066.22233709736</v>
+      </c>
+      <c r="K1170" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>45928179-f482-4bcc-a447-92df70a1e054</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>0d6bfacf-0d3c-4e53-8b7d-c70341d3949a</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1171" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>OP-276</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1171" s="2" t="n">
+        <v>46089.34733710044</v>
+      </c>
+      <c r="K1171" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>dbc090dc-82ca-4aaa-86b7-8ac0f7cf0976</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>6298f79d-8fc6-4201-b04c-9e078adfbca5</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1172" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>OP-559</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1172" s="2" t="n">
+        <v>46076.09733710357</v>
+      </c>
+      <c r="K1172" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>dea1570f-f018-4062-b245-6bf5fefd18b1</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>771e2c3f-e781-4e76-af89-0c99cd1ff86c</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1173" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>OP-306</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1173" s="2" t="n">
+        <v>46078.2640037733</v>
+      </c>
+      <c r="K1173" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>67209e8a-1c0e-420f-929a-a1dd7919bab6</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>6c399d03-88ad-4a26-9e67-715a2d62bf92</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1174" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>OP-700</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1174" s="2" t="n">
+        <v>46069.22233711019</v>
+      </c>
+      <c r="K1174" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>e25ab4ed-caa8-4361-9058-d7f24c0e55c1</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>046b44a0-97a7-4dff-adbd-96108301e013</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1175" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>OP-563</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1175" s="2" t="n">
+        <v>46070.34733711321</v>
+      </c>
+      <c r="K1175" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>be95e730-88c9-4493-aec6-69458409b982</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>62e0c69d-24d8-460c-a781-bb7ffe39cb94</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1176" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>OP-541</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1176" s="2" t="n">
+        <v>46066.1390037829</v>
+      </c>
+      <c r="K1176" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>176fc72b-2724-48f9-9d04-18c36a987064</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>f06f517b-cbfb-4184-a8ef-2a5dcb5b7a5d</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1177" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>OP-552</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1177" s="2" t="n">
+        <v>46061.26400378596</v>
+      </c>
+      <c r="K1177" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>39d50eb6-15d1-4220-936d-5bdeab7e0217</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>c5ace0d9-ce34-4d25-94c8-c819aef3c171</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1178" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>OP-542</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1178" s="2" t="n">
+        <v>46064.30567045596</v>
+      </c>
+      <c r="K1178" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>837c378c-9c77-46be-ad87-1525fc1d725d</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>288d828c-0f2f-407f-abb4-2c8a67d328bd</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1179" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>OP-418</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1179" s="2" t="n">
+        <v>46078.47233712584</v>
+      </c>
+      <c r="K1179" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>762a1956-f190-4d6b-889a-ff2fc964643b</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>c0568aea-d541-4170-ba5b-38da5ce5ae4f</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1180" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>OP-872</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1180" s="2" t="n">
+        <v>46069.38900379551</v>
+      </c>
+      <c r="K1180" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>5c24f50a-861b-4b49-ba64-24035da183c8</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>3f1b1d8a-1e2c-4b9d-8dd8-936c29080361</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1181" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>OP-925</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1181" s="2" t="n">
+        <v>46070.26400379881</v>
+      </c>
+      <c r="K1181" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2d9c5504-a93d-4d2f-9b20-d68bfeea7b2c</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>b8c0a864-7562-46c7-894c-47370b646b8c</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1182" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>OP-325</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1182" s="2" t="n">
+        <v>46074.2640038021</v>
+      </c>
+      <c r="K1182" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>0bcef0d2-faa0-44bb-853b-75c00c0c9e6b</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>7f883c33-d214-4625-b546-6d594d62c7ac</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1183" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>OP-733</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1183" s="2" t="n">
+        <v>46063.30567047193</v>
+      </c>
+      <c r="K1183" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>6fccc0c8-b448-44b8-928f-a0f2dd52670e</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>1e0f76eb-e3fa-4a67-b771-555dcb1987a0</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1184" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>OP-147</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1184" s="2" t="n">
+        <v>46088.13900380846</v>
+      </c>
+      <c r="K1184" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>679042cd-ace0-444d-9879-2091ae5807f1</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>5cae1cf4-f2db-4493-aa63-af54df75d896</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1185" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>OP-156</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1185" s="2" t="n">
+        <v>46070.26400381183</v>
+      </c>
+      <c r="K1185" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>28e6e270-085f-450d-a630-6980e8629aca</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>0bb142ac-6ba7-4e2e-acae-c5ac023342df</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1186" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>OP-461</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1186" s="2" t="n">
+        <v>46083.38900381498</v>
+      </c>
+      <c r="K1186" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>1890d5f6-4f04-40bc-a190-b70a648c9cfe</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>e3e4474e-6e98-48c2-9344-3af5ba3909e5</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1187" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>OP-173</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1187" s="2" t="n">
+        <v>46086.47233715146</v>
+      </c>
+      <c r="K1187" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>65b2bdb0-5c4c-419d-a1ff-53b19de2bc74</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>f712fc12-f343-4248-8ce4-8649ce06a500</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1188" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>OP-943</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1188" s="2" t="n">
+        <v>46078.38900382112</v>
+      </c>
+      <c r="K1188" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>41b69df9-709c-43aa-927c-fa4d0fa16999</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>26b04a3b-76b1-4ffa-ba1a-982a51f09914</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1189" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>OP-737</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1189" s="2" t="n">
+        <v>46065.26400382446</v>
+      </c>
+      <c r="K1189" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>1a93c491-b6c5-4615-9288-4ba590128d51</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>ed5dc14e-dbda-4b9a-8919-cda379a62979</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1190" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>OP-846</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1190" s="2" t="n">
+        <v>46082.18067049429</v>
+      </c>
+      <c r="K1190" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>b3a925be-9e70-46bd-8099-a48d5606fee1</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>ed88fb44-c86b-4715-a767-834c2848c74e</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1191" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>OP-881</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1191" s="2" t="n">
+        <v>46089.38900383063</v>
+      </c>
+      <c r="K1191" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>bef71a3c-4866-4b33-a4d4-b65a136cb363</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>3f17a970-39db-4117-85be-a95d593c2536</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1192" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>OP-239</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1192" s="2" t="n">
+        <v>46075.09733716727</v>
+      </c>
+      <c r="K1192" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>9a3c3aa7-be86-404e-983b-9536fae5faa9</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>8acd125c-97ca-40ee-a7fe-fb2143675c19</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1193" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>OP-154</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1193" s="2" t="n">
+        <v>46082.4723371704</v>
+      </c>
+      <c r="K1193" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>0caa9d21-82cd-4e4d-ad2a-08924b55bf16</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>e7728085-bf72-47c0-a8cf-b4110c3548aa</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1194" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>OP-164</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1194" s="2" t="n">
+        <v>46064.38900384012</v>
+      </c>
+      <c r="K1194" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>0433af19-c8d8-4eab-8823-1e5d50220026</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>843a114b-443f-4556-b73b-2876fcff2f82</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1195" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>OP-527</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1195" s="2" t="n">
+        <v>46061.13900384307</v>
+      </c>
+      <c r="K1195" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>205a9c39-eee6-451a-8477-51ea919bc0b0</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>b5b095cb-ccec-4024-95c6-af22afb6b6f5</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1196" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>OP-701</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1196" s="2" t="n">
+        <v>46063.47233717977</v>
+      </c>
+      <c r="K1196" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>593760c6-03ac-4114-b566-65e34ffb8ab2</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>e55383eb-f12d-4688-ad53-c70b1cbcae49</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1197" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>OP-734</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1197" s="2" t="n">
+        <v>46068.34733718279</v>
+      </c>
+      <c r="K1197" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>551f86af-4362-4a8b-95af-6578e12a1a26</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>57c46f50-a180-4588-9da7-adac5f8b862e</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1198" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>OP-185</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1198" s="2" t="n">
+        <v>46069.09733718588</v>
+      </c>
+      <c r="K1198" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>06d12145-385e-49fa-9666-d446102631d6</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>a54b3498-017c-4e06-977a-b50cc555b9b6</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1199" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>OP-821</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1199" s="2" t="n">
+        <v>46079.22233718942</v>
+      </c>
+      <c r="K1199" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>12dbbdad-2264-4698-82d9-68b11ae2b687</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>9c6e2f28-7db4-4bd1-8fce-f4b1fb405422</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1200" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>OP-473</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1200" s="2" t="n">
+        <v>46075.22233719264</v>
+      </c>
+      <c r="K1200" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>eee830c1-3f86-4f2b-9480-1748ad2a1bcd</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>c86a7f02-5792-4c0d-8afb-4325fd0b98fe</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1201" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>OP-403</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1201" s="2" t="n">
+        <v>46062.18067052915</v>
+      </c>
+      <c r="K1201" t="inlineStr">
         <is>
           <t>good</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1201"/>
+  <dimension ref="A1:K1251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59182,7 +59182,7 @@
         </is>
       </c>
       <c r="J1152" s="2" t="n">
-        <v>46060.13900370518</v>
+        <v>46060.13900370371</v>
       </c>
       <c r="K1152" t="inlineStr">
         <is>
@@ -59233,7 +59233,7 @@
         </is>
       </c>
       <c r="J1153" s="2" t="n">
-        <v>46082.43067037634</v>
+        <v>46082.43067038195</v>
       </c>
       <c r="K1153" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         </is>
       </c>
       <c r="J1154" s="2" t="n">
-        <v>46069.30567037963</v>
+        <v>46069.30567038195</v>
       </c>
       <c r="K1154" t="inlineStr">
         <is>
@@ -59335,7 +59335,7 @@
         </is>
       </c>
       <c r="J1155" s="2" t="n">
-        <v>46082.43067038291</v>
+        <v>46082.43067038195</v>
       </c>
       <c r="K1155" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         </is>
       </c>
       <c r="J1156" s="2" t="n">
-        <v>46061.09733705282</v>
+        <v>46061.09733704861</v>
       </c>
       <c r="K1156" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         </is>
       </c>
       <c r="J1157" s="2" t="n">
-        <v>46068.13900372252</v>
+        <v>46068.13900372685</v>
       </c>
       <c r="K1157" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         </is>
       </c>
       <c r="J1158" s="2" t="n">
-        <v>46073.43067039228</v>
+        <v>46073.43067039352</v>
       </c>
       <c r="K1158" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         </is>
       </c>
       <c r="J1159" s="2" t="n">
-        <v>46079.347337062</v>
+        <v>46079.34733706019</v>
       </c>
       <c r="K1159" t="inlineStr">
         <is>
@@ -59590,7 +59590,7 @@
         </is>
       </c>
       <c r="J1160" s="2" t="n">
-        <v>46082.13900373227</v>
+        <v>46082.13900372685</v>
       </c>
       <c r="K1160" t="inlineStr">
         <is>
@@ -59641,7 +59641,7 @@
         </is>
       </c>
       <c r="J1161" s="2" t="n">
-        <v>46063.13900373533</v>
+        <v>46063.13900373843</v>
       </c>
       <c r="K1161" t="inlineStr">
         <is>
@@ -59692,7 +59692,7 @@
         </is>
       </c>
       <c r="J1162" s="2" t="n">
-        <v>46080.26400373855</v>
+        <v>46080.26400373843</v>
       </c>
       <c r="K1162" t="inlineStr">
         <is>
@@ -59743,7 +59743,7 @@
         </is>
       </c>
       <c r="J1163" s="2" t="n">
-        <v>46077.38900374183</v>
+        <v>46077.38900373843</v>
       </c>
       <c r="K1163" t="inlineStr">
         <is>
@@ -59794,7 +59794,7 @@
         </is>
       </c>
       <c r="J1164" s="2" t="n">
-        <v>46073.38900374485</v>
+        <v>46073.38900375</v>
       </c>
       <c r="K1164" t="inlineStr">
         <is>
@@ -59845,7 +59845,7 @@
         </is>
       </c>
       <c r="J1165" s="2" t="n">
-        <v>46082.43067041459</v>
+        <v>46082.43067041667</v>
       </c>
       <c r="K1165" t="inlineStr">
         <is>
@@ -59896,7 +59896,7 @@
         </is>
       </c>
       <c r="J1166" s="2" t="n">
-        <v>46088.13900375108</v>
+        <v>46088.13900375</v>
       </c>
       <c r="K1166" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         </is>
       </c>
       <c r="J1167" s="2" t="n">
-        <v>46068.1806704211</v>
+        <v>46068.18067041667</v>
       </c>
       <c r="K1167" t="inlineStr">
         <is>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="J1168" s="2" t="n">
-        <v>46075.1806704245</v>
+        <v>46075.18067042824</v>
       </c>
       <c r="K1168" t="inlineStr">
         <is>
@@ -60049,7 +60049,7 @@
         </is>
       </c>
       <c r="J1169" s="2" t="n">
-        <v>46081.18067042749</v>
+        <v>46081.18067042824</v>
       </c>
       <c r="K1169" t="inlineStr">
         <is>
@@ -60100,7 +60100,7 @@
         </is>
       </c>
       <c r="J1170" s="2" t="n">
-        <v>46066.22233709736</v>
+        <v>46066.22233709491</v>
       </c>
       <c r="K1170" t="inlineStr">
         <is>
@@ -60151,7 +60151,7 @@
         </is>
       </c>
       <c r="J1171" s="2" t="n">
-        <v>46089.34733710044</v>
+        <v>46089.34733709491</v>
       </c>
       <c r="K1171" t="inlineStr">
         <is>
@@ -60202,7 +60202,7 @@
         </is>
       </c>
       <c r="J1172" s="2" t="n">
-        <v>46076.09733710357</v>
+        <v>46076.09733710648</v>
       </c>
       <c r="K1172" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         </is>
       </c>
       <c r="J1173" s="2" t="n">
-        <v>46078.2640037733</v>
+        <v>46078.26400377315</v>
       </c>
       <c r="K1173" t="inlineStr">
         <is>
@@ -60304,7 +60304,7 @@
         </is>
       </c>
       <c r="J1174" s="2" t="n">
-        <v>46069.22233711019</v>
+        <v>46069.22233710648</v>
       </c>
       <c r="K1174" t="inlineStr">
         <is>
@@ -60355,7 +60355,7 @@
         </is>
       </c>
       <c r="J1175" s="2" t="n">
-        <v>46070.34733711321</v>
+        <v>46070.34733711806</v>
       </c>
       <c r="K1175" t="inlineStr">
         <is>
@@ -60406,7 +60406,7 @@
         </is>
       </c>
       <c r="J1176" s="2" t="n">
-        <v>46066.1390037829</v>
+        <v>46066.13900378472</v>
       </c>
       <c r="K1176" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         </is>
       </c>
       <c r="J1177" s="2" t="n">
-        <v>46061.26400378596</v>
+        <v>46061.26400378472</v>
       </c>
       <c r="K1177" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         </is>
       </c>
       <c r="J1178" s="2" t="n">
-        <v>46064.30567045596</v>
+        <v>46064.30567045139</v>
       </c>
       <c r="K1178" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         </is>
       </c>
       <c r="J1179" s="2" t="n">
-        <v>46078.47233712584</v>
+        <v>46078.47233712963</v>
       </c>
       <c r="K1179" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         </is>
       </c>
       <c r="J1180" s="2" t="n">
-        <v>46069.38900379551</v>
+        <v>46069.3890037963</v>
       </c>
       <c r="K1180" t="inlineStr">
         <is>
@@ -60661,7 +60661,7 @@
         </is>
       </c>
       <c r="J1181" s="2" t="n">
-        <v>46070.26400379881</v>
+        <v>46070.2640037963</v>
       </c>
       <c r="K1181" t="inlineStr">
         <is>
@@ -60712,7 +60712,7 @@
         </is>
       </c>
       <c r="J1182" s="2" t="n">
-        <v>46074.2640038021</v>
+        <v>46074.26400380787</v>
       </c>
       <c r="K1182" t="inlineStr">
         <is>
@@ -60763,7 +60763,7 @@
         </is>
       </c>
       <c r="J1183" s="2" t="n">
-        <v>46063.30567047193</v>
+        <v>46063.30567047454</v>
       </c>
       <c r="K1183" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         </is>
       </c>
       <c r="J1184" s="2" t="n">
-        <v>46088.13900380846</v>
+        <v>46088.13900380787</v>
       </c>
       <c r="K1184" t="inlineStr">
         <is>
@@ -60865,7 +60865,7 @@
         </is>
       </c>
       <c r="J1185" s="2" t="n">
-        <v>46070.26400381183</v>
+        <v>46070.26400380787</v>
       </c>
       <c r="K1185" t="inlineStr">
         <is>
@@ -60916,7 +60916,7 @@
         </is>
       </c>
       <c r="J1186" s="2" t="n">
-        <v>46083.38900381498</v>
+        <v>46083.38900381944</v>
       </c>
       <c r="K1186" t="inlineStr">
         <is>
@@ -60967,7 +60967,7 @@
         </is>
       </c>
       <c r="J1187" s="2" t="n">
-        <v>46086.47233715146</v>
+        <v>46086.47233715278</v>
       </c>
       <c r="K1187" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         </is>
       </c>
       <c r="J1188" s="2" t="n">
-        <v>46078.38900382112</v>
+        <v>46078.38900381944</v>
       </c>
       <c r="K1188" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         </is>
       </c>
       <c r="J1189" s="2" t="n">
-        <v>46065.26400382446</v>
+        <v>46065.26400381944</v>
       </c>
       <c r="K1189" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         </is>
       </c>
       <c r="J1190" s="2" t="n">
-        <v>46082.18067049429</v>
+        <v>46082.18067049768</v>
       </c>
       <c r="K1190" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         </is>
       </c>
       <c r="J1191" s="2" t="n">
-        <v>46089.38900383063</v>
+        <v>46089.38900383102</v>
       </c>
       <c r="K1191" t="inlineStr">
         <is>
@@ -61222,7 +61222,7 @@
         </is>
       </c>
       <c r="J1192" s="2" t="n">
-        <v>46075.09733716727</v>
+        <v>46075.09733716435</v>
       </c>
       <c r="K1192" t="inlineStr">
         <is>
@@ -61273,7 +61273,7 @@
         </is>
       </c>
       <c r="J1193" s="2" t="n">
-        <v>46082.4723371704</v>
+        <v>46082.47233717592</v>
       </c>
       <c r="K1193" t="inlineStr">
         <is>
@@ -61324,7 +61324,7 @@
         </is>
       </c>
       <c r="J1194" s="2" t="n">
-        <v>46064.38900384012</v>
+        <v>46064.3890038426</v>
       </c>
       <c r="K1194" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         </is>
       </c>
       <c r="J1195" s="2" t="n">
-        <v>46061.13900384307</v>
+        <v>46061.1390038426</v>
       </c>
       <c r="K1195" t="inlineStr">
         <is>
@@ -61426,7 +61426,7 @@
         </is>
       </c>
       <c r="J1196" s="2" t="n">
-        <v>46063.47233717977</v>
+        <v>46063.47233717592</v>
       </c>
       <c r="K1196" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         </is>
       </c>
       <c r="J1197" s="2" t="n">
-        <v>46068.34733718279</v>
+        <v>46068.3473371875</v>
       </c>
       <c r="K1197" t="inlineStr">
         <is>
@@ -61528,7 +61528,7 @@
         </is>
       </c>
       <c r="J1198" s="2" t="n">
-        <v>46069.09733718588</v>
+        <v>46069.0973371875</v>
       </c>
       <c r="K1198" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         </is>
       </c>
       <c r="J1199" s="2" t="n">
-        <v>46079.22233718942</v>
+        <v>46079.2223371875</v>
       </c>
       <c r="K1199" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         </is>
       </c>
       <c r="J1200" s="2" t="n">
-        <v>46075.22233719264</v>
+        <v>46075.2223371875</v>
       </c>
       <c r="K1200" t="inlineStr">
         <is>
@@ -61681,9 +61681,2559 @@
         </is>
       </c>
       <c r="J1201" s="2" t="n">
-        <v>46062.18067052915</v>
+        <v>46062.18067053241</v>
       </c>
       <c r="K1201" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>c32a89a5-5098-4934-a7be-fe9dcb905c73</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>9a8ff805-6da3-4da3-b1ef-f58c00603732</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1202" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>OP-108</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1202" s="2" t="n">
+        <v>46071.25649777852</v>
+      </c>
+      <c r="K1202" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>4335174e-52c5-43f6-b389-3c98d18246f8</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>6eb81ee1-6e66-41bc-9aed-38095788779f</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1203" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>OP-456</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1203" s="2" t="n">
+        <v>46060.58983111622</v>
+      </c>
+      <c r="K1203" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>218f934b-cb74-47be-9d08-2a419540a4a3</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>7cfc8e0c-02a5-4518-9d5a-7113557c184e</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1204" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>OP-608</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1204" s="2" t="n">
+        <v>46070.46483111942</v>
+      </c>
+      <c r="K1204" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>099f1668-6622-4875-a4d6-59a5ebf107c9</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>596693ff-c197-470c-83c5-ff193f42a5ed</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1205" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>OP-207</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1205" s="2" t="n">
+        <v>46084.50649778925</v>
+      </c>
+      <c r="K1205" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>30f0f981-e923-490f-a441-eba7f222ba9d</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>2dde8c4e-2466-4cf3-accf-9d2acd738fbb</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1206" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>OP-420</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1206" s="2" t="n">
+        <v>46080.29816445887</v>
+      </c>
+      <c r="K1206" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>33295795-43b6-437d-80f8-b1cb43474e11</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>f021a564-f38d-4a0a-b157-17e169e61a38</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1207" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>OP-948</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1207" s="2" t="n">
+        <v>46060.29816446183</v>
+      </c>
+      <c r="K1207" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>40ae3740-94f3-4f9f-a405-fbb05a6b79fc</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>3a1d1b14-3923-45b1-b286-e485dd10740c</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1208" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>OP-653</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1208" s="2" t="n">
+        <v>46068.38149779812</v>
+      </c>
+      <c r="K1208" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>7cc3cf55-867d-4f4a-b455-f5ade04b85b7</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>2071a1ba-aae1-400f-aad6-a03e2c96d338</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1209" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>OP-692</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1209" s="2" t="n">
+        <v>46067.25649780095</v>
+      </c>
+      <c r="K1209" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>746e0d2d-ef44-474f-bfd1-9cdc7e882319</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>9ad3e4dc-e4d4-45a3-bd81-430fdbcf5f65</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1210" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>OP-151</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1210" s="2" t="n">
+        <v>46089.2564978038</v>
+      </c>
+      <c r="K1210" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>7cef5bdb-643b-4a24-b62e-a6aecef3c7d7</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>e58e06c0-083a-4911-88db-58130f90716c</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1211" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>OP-594</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1211" s="2" t="n">
+        <v>46079.33983114008</v>
+      </c>
+      <c r="K1211" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>6d100e51-9bc5-4b1e-af83-f0f2909e8a20</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>ac1cc16c-c20a-4c98-827a-b36c83d66644</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1212" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>OP-797</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1212" s="2" t="n">
+        <v>46087.38149780969</v>
+      </c>
+      <c r="K1212" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>ce9519a8-a729-43b0-8f7f-6ca253809916</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>61ef864d-5038-4613-983f-45fc3d206e2b</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1213" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>OP-150</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1213" s="2" t="n">
+        <v>46084.38149781265</v>
+      </c>
+      <c r="K1213" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>eb18a12d-2764-42ac-9420-a8c7261dcaa0</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>dfeb839d-8703-433f-8bdd-56112e282277</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1214" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>OP-528</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1214" s="2" t="n">
+        <v>46067.46483114878</v>
+      </c>
+      <c r="K1214" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>01b27b0b-0727-48b2-9861-966b0a878891</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>91b0138d-aecb-43cc-b23d-5d29a1db951f</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1215" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>OP-233</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1215" s="2" t="n">
+        <v>46073.58983115174</v>
+      </c>
+      <c r="K1215" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>ab214090-fe45-4bbf-9161-9befeaf69db4</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>9c8e2496-1f1e-405e-9fa0-985b00fda461</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1216" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>OP-842</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1216" s="2" t="n">
+        <v>46064.54816448804</v>
+      </c>
+      <c r="K1216" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>7409435c-7bfe-41c8-ab13-2710f4fabf3c</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>55a1d6a0-fffd-4488-b317-a266765d87a0</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1217" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>OP-188</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1217" s="2" t="n">
+        <v>46077.54816449086</v>
+      </c>
+      <c r="K1217" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>e4964e18-101e-4455-9964-0e08121d722d</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>177bf079-0211-4389-8503-686b1f1a1a6d</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1218" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>OP-960</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1218" s="2" t="n">
+        <v>46076.58983116035</v>
+      </c>
+      <c r="K1218" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>c8c69098-e06a-41bb-be24-d1716bf3dfe8</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>9e93126b-69c6-4ad5-86c8-2bd587aa43ed</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1219" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>OP-428</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1219" s="2" t="n">
+        <v>46072.42316449668</v>
+      </c>
+      <c r="K1219" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2a26e766-dd30-44b5-935c-c9436083a3e1</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>c30dcdeb-1eb3-4e45-bd5c-88e93fb3840e</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1220" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>OP-284</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1220" s="2" t="n">
+        <v>46073.54816449956</v>
+      </c>
+      <c r="K1220" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>fa70c38d-d78b-4e21-be85-8d65babde155</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>be96c13b-a08f-47f8-9b98-91042f4d0095</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1221" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>OP-749</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1221" s="2" t="n">
+        <v>46075.21483116906</v>
+      </c>
+      <c r="K1221" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>ec274b0f-6427-47d8-95d9-92476c3a6975</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>e9cc9899-a89d-4165-9b89-8dcdbb2e5949</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1222" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>OP-148</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1222" s="2" t="n">
+        <v>46076.4648311719</v>
+      </c>
+      <c r="K1222" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>8e7e30cc-4751-4d05-ae75-66b761ccc2d5</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>bfc165f5-879e-485f-a379-7a153e0cb1f7</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1223" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>OP-326</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1223" s="2" t="n">
+        <v>46080.58983117482</v>
+      </c>
+      <c r="K1223" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>7c5ec03d-1251-4d23-a08f-730caf558b2d</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>c49fa654-d4bc-423d-9713-72190c1a1eb5</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1224" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>OP-578</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1224" s="2" t="n">
+        <v>46066.42316451106</v>
+      </c>
+      <c r="K1224" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>7c52a042-3cb0-42c3-a370-75feebba17f1</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>0c3b1af1-6e10-4338-b047-6ad57d99f9e2</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1225" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>OP-269</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1225" s="2" t="n">
+        <v>46062.50649784736</v>
+      </c>
+      <c r="K1225" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>1d399460-65fe-4b1d-8b94-ea469c1f2d0c</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>d17e70c4-6cfb-4fcb-ab96-cf70cb5d3c51</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1226" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>OP-208</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1226" s="2" t="n">
+        <v>46080.58983118348</v>
+      </c>
+      <c r="K1226" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2655e4ae-dc6f-48c6-80a6-011aa290f13a</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>a05239ce-9766-4939-8328-c688ce099f98</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1227" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>OP-823</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1227" s="2" t="n">
+        <v>46074.38149785316</v>
+      </c>
+      <c r="K1227" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2ef6c65b-b444-4914-a190-ad417f677d9d</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>fb91054a-0ddc-449f-9813-17f721d8ed71</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1228" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>OP-310</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1228" s="2" t="n">
+        <v>46080.50649785598</v>
+      </c>
+      <c r="K1228" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>5dde649a-3384-4fd2-9539-378869987755</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>438e6c33-561f-40e8-8db1-dfdca7b3e896</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1229" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>OP-141</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1229" s="2" t="n">
+        <v>46061.54816452546</v>
+      </c>
+      <c r="K1229" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>cfbfb741-407b-4673-9038-16fd1128dc28</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>eb675ef2-a6e8-408c-aaae-53eafb439578</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1230" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>OP-742</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1230" s="2" t="n">
+        <v>46080.58983119501</v>
+      </c>
+      <c r="K1230" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>17a24d62-5133-43b3-a14d-efbf882df920</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>9a31b5aa-4f68-4fbe-873a-0448c3f59d19</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1231" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>OP-358</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1231" s="2" t="n">
+        <v>46061.21483119796</v>
+      </c>
+      <c r="K1231" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>0afcacfc-a4e1-4380-a369-66e4541d087b</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>08ef3b3a-3584-40e2-ae2d-db4b7260616c</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1232" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>OP-522</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1232" s="2" t="n">
+        <v>46079.3398312008</v>
+      </c>
+      <c r="K1232" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>5e98553f-87d0-4289-bfff-3eebaf966139</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>87536869-7fa6-422f-825f-36f07177e404</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1233" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>OP-242</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1233" s="2" t="n">
+        <v>46080.33983120374</v>
+      </c>
+      <c r="K1233" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>a8af9e02-b7c4-4a60-ae44-3cc042eed99a</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>7e5f2b36-466e-48ab-912b-15351ead53c6</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1234" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>OP-945</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1234" s="2" t="n">
+        <v>46087.58983120666</v>
+      </c>
+      <c r="K1234" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>6741a73a-784b-4b80-9bb9-fe93337fdfa0</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>a0a624e9-5a4e-4e4e-8f0e-f5c33e9065b1</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1235" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>OP-354</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1235" s="2" t="n">
+        <v>46072.21483120972</v>
+      </c>
+      <c r="K1235" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>54250bd9-8d5b-4572-8dda-0d432faf52cc</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>7da06451-7637-4e8e-a945-bbd0f9c4c823</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1236" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>OP-478</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1236" s="2" t="n">
+        <v>46069.54816454583</v>
+      </c>
+      <c r="K1236" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>9b279951-87e7-4489-8b6c-ce3e9a82f745</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>70e017c0-d36d-4bb3-80dd-50cef40c261c</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1237" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>OP-837</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1237" s="2" t="n">
+        <v>46083.5064978821</v>
+      </c>
+      <c r="K1237" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>76e05e7b-8f00-4419-bf72-01d67faeecfa</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>6748ac31-4d13-4f4f-a60e-1fdff1edf4dd</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1238" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>OP-454</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1238" s="2" t="n">
+        <v>46061.5898312182</v>
+      </c>
+      <c r="K1238" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>78abd322-3a5a-498b-8d95-ba611daec162</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>32ae9cc1-19eb-44e4-8424-4ff932fc20ce</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1239" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>OP-313</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1239" s="2" t="n">
+        <v>46088.42316455442</v>
+      </c>
+      <c r="K1239" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>7b472e10-20ae-45c5-9fac-3f5f0a37acf6</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>3e2da127-51fa-4e4b-a534-c680530aac0f</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1240" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>OP-212</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1240" s="2" t="n">
+        <v>46063.38149789056</v>
+      </c>
+      <c r="K1240" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>4d98fda4-4cac-44c3-b492-4b34b80f6f90</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>03edb0d7-86ad-4298-85bb-d8383182d0e5</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1241" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F1241" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>OP-453</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1241" s="2" t="n">
+        <v>46069.29816456001</v>
+      </c>
+      <c r="K1241" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>c95d3884-d21b-47e8-a515-17c1b4a6760a</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>4c573721-54ef-44ec-b407-144c237e2596</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1242" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1242" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>OP-686</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1242" s="2" t="n">
+        <v>46061.29816456295</v>
+      </c>
+      <c r="K1242" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>7226576f-f767-4f78-b388-9fa4db8d16a8</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>02f6b388-0396-44af-af45-818bf41cecee</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1243" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>OP-506</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1243" s="2" t="n">
+        <v>46068.54816456592</v>
+      </c>
+      <c r="K1243" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>44f0b660-2b4d-4c17-af7e-1e2e03319efd</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>e5566647-dbd8-4d00-9f9f-bf4e8f44350f</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1244" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F1244" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>OP-434</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1244" s="2" t="n">
+        <v>46071.33983123542</v>
+      </c>
+      <c r="K1244" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>8c74b0c8-3942-42f0-86c9-3db10c9fc5d8</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>53d03aa6-8b91-4402-afc5-18e0a2422c7d</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1245" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>OP-497</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1245" s="2" t="n">
+        <v>46069.33983123826</v>
+      </c>
+      <c r="K1245" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>7ebca057-7ec5-45ef-91f4-fbfccc7aa652</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>b3525334-3cb2-461b-855b-ba39faa00e6e</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1246" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>OP-404</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1246" s="2" t="n">
+        <v>46067.25649790786</v>
+      </c>
+      <c r="K1246" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>ecae2784-6c5e-4228-8ad0-8a28ce271fc4</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>be6fbd69-e5c9-47ac-94c5-a6eddb3ee14c</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1247" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F1247" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>OP-244</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1247" s="2" t="n">
+        <v>46082.21483124405</v>
+      </c>
+      <c r="K1247" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>f4f17845-2525-408e-9858-980212b8ae53</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>0bdb2e56-1f52-4ed9-a45a-a0069354e994</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1248" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>OP-823</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1248" s="2" t="n">
+        <v>46066.21483124694</v>
+      </c>
+      <c r="K1248" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>f648e759-fb59-4a9e-92f2-2f9870791d01</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>18b55cba-6b9c-4e06-9977-e93909a1f08e</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1249" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>OP-721</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1249" s="2" t="n">
+        <v>46061.29816458326</v>
+      </c>
+      <c r="K1249" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>da5ffc8f-e0f5-421d-afc8-41d66d14c88a</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>c559c979-3a78-4837-9383-c508d34515c8</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1250" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>OP-675</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1250" s="2" t="n">
+        <v>46063.38149791938</v>
+      </c>
+      <c r="K1250" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>4f51390c-fa0a-465f-80d9-430df7f426c2</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>db3046ee-b42d-4d8f-86d3-2f3c746bcd21</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1251" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>OP-803</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1251" s="2" t="n">
+        <v>46072.21483125574</v>
+      </c>
+      <c r="K1251" t="inlineStr">
         <is>
           <t>good</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1251"/>
+  <dimension ref="A1:K1301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61732,7 +61732,7 @@
         </is>
       </c>
       <c r="J1202" s="2" t="n">
-        <v>46071.25649777852</v>
+        <v>46071.25649777778</v>
       </c>
       <c r="K1202" t="inlineStr">
         <is>
@@ -61783,7 +61783,7 @@
         </is>
       </c>
       <c r="J1203" s="2" t="n">
-        <v>46060.58983111622</v>
+        <v>46060.58983111111</v>
       </c>
       <c r="K1203" t="inlineStr">
         <is>
@@ -61834,7 +61834,7 @@
         </is>
       </c>
       <c r="J1204" s="2" t="n">
-        <v>46070.46483111942</v>
+        <v>46070.46483112268</v>
       </c>
       <c r="K1204" t="inlineStr">
         <is>
@@ -61885,7 +61885,7 @@
         </is>
       </c>
       <c r="J1205" s="2" t="n">
-        <v>46084.50649778925</v>
+        <v>46084.50649778935</v>
       </c>
       <c r="K1205" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="J1206" s="2" t="n">
-        <v>46080.29816445887</v>
+        <v>46080.29816445602</v>
       </c>
       <c r="K1206" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         </is>
       </c>
       <c r="J1207" s="2" t="n">
-        <v>46060.29816446183</v>
+        <v>46060.29816446759</v>
       </c>
       <c r="K1207" t="inlineStr">
         <is>
@@ -62038,7 +62038,7 @@
         </is>
       </c>
       <c r="J1208" s="2" t="n">
-        <v>46068.38149779812</v>
+        <v>46068.38149780092</v>
       </c>
       <c r="K1208" t="inlineStr">
         <is>
@@ -62089,7 +62089,7 @@
         </is>
       </c>
       <c r="J1209" s="2" t="n">
-        <v>46067.25649780095</v>
+        <v>46067.25649780092</v>
       </c>
       <c r="K1209" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         </is>
       </c>
       <c r="J1210" s="2" t="n">
-        <v>46089.2564978038</v>
+        <v>46089.25649780092</v>
       </c>
       <c r="K1210" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         </is>
       </c>
       <c r="J1211" s="2" t="n">
-        <v>46079.33983114008</v>
+        <v>46079.33983114584</v>
       </c>
       <c r="K1211" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         </is>
       </c>
       <c r="J1212" s="2" t="n">
-        <v>46087.38149780969</v>
+        <v>46087.3814978125</v>
       </c>
       <c r="K1212" t="inlineStr">
         <is>
@@ -62293,7 +62293,7 @@
         </is>
       </c>
       <c r="J1213" s="2" t="n">
-        <v>46084.38149781265</v>
+        <v>46084.3814978125</v>
       </c>
       <c r="K1213" t="inlineStr">
         <is>
@@ -62344,7 +62344,7 @@
         </is>
       </c>
       <c r="J1214" s="2" t="n">
-        <v>46067.46483114878</v>
+        <v>46067.46483114584</v>
       </c>
       <c r="K1214" t="inlineStr">
         <is>
@@ -62395,7 +62395,7 @@
         </is>
       </c>
       <c r="J1215" s="2" t="n">
-        <v>46073.58983115174</v>
+        <v>46073.58983115741</v>
       </c>
       <c r="K1215" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         </is>
       </c>
       <c r="J1216" s="2" t="n">
-        <v>46064.54816448804</v>
+        <v>46064.54816449074</v>
       </c>
       <c r="K1216" t="inlineStr">
         <is>
@@ -62497,7 +62497,7 @@
         </is>
       </c>
       <c r="J1217" s="2" t="n">
-        <v>46077.54816449086</v>
+        <v>46077.54816449074</v>
       </c>
       <c r="K1217" t="inlineStr">
         <is>
@@ -62548,7 +62548,7 @@
         </is>
       </c>
       <c r="J1218" s="2" t="n">
-        <v>46076.58983116035</v>
+        <v>46076.58983115741</v>
       </c>
       <c r="K1218" t="inlineStr">
         <is>
@@ -62599,7 +62599,7 @@
         </is>
       </c>
       <c r="J1219" s="2" t="n">
-        <v>46072.42316449668</v>
+        <v>46072.42316450232</v>
       </c>
       <c r="K1219" t="inlineStr">
         <is>
@@ -62650,7 +62650,7 @@
         </is>
       </c>
       <c r="J1220" s="2" t="n">
-        <v>46073.54816449956</v>
+        <v>46073.54816450232</v>
       </c>
       <c r="K1220" t="inlineStr">
         <is>
@@ -62701,7 +62701,7 @@
         </is>
       </c>
       <c r="J1221" s="2" t="n">
-        <v>46075.21483116906</v>
+        <v>46075.21483116898</v>
       </c>
       <c r="K1221" t="inlineStr">
         <is>
@@ -62752,7 +62752,7 @@
         </is>
       </c>
       <c r="J1222" s="2" t="n">
-        <v>46076.4648311719</v>
+        <v>46076.46483116898</v>
       </c>
       <c r="K1222" t="inlineStr">
         <is>
@@ -62803,7 +62803,7 @@
         </is>
       </c>
       <c r="J1223" s="2" t="n">
-        <v>46080.58983117482</v>
+        <v>46080.58983118056</v>
       </c>
       <c r="K1223" t="inlineStr">
         <is>
@@ -62854,7 +62854,7 @@
         </is>
       </c>
       <c r="J1224" s="2" t="n">
-        <v>46066.42316451106</v>
+        <v>46066.42316451389</v>
       </c>
       <c r="K1224" t="inlineStr">
         <is>
@@ -62905,7 +62905,7 @@
         </is>
       </c>
       <c r="J1225" s="2" t="n">
-        <v>46062.50649784736</v>
+        <v>46062.50649784722</v>
       </c>
       <c r="K1225" t="inlineStr">
         <is>
@@ -62956,7 +62956,7 @@
         </is>
       </c>
       <c r="J1226" s="2" t="n">
-        <v>46080.58983118348</v>
+        <v>46080.58983118056</v>
       </c>
       <c r="K1226" t="inlineStr">
         <is>
@@ -63007,7 +63007,7 @@
         </is>
       </c>
       <c r="J1227" s="2" t="n">
-        <v>46074.38149785316</v>
+        <v>46074.3814978588</v>
       </c>
       <c r="K1227" t="inlineStr">
         <is>
@@ -63058,7 +63058,7 @@
         </is>
       </c>
       <c r="J1228" s="2" t="n">
-        <v>46080.50649785598</v>
+        <v>46080.5064978588</v>
       </c>
       <c r="K1228" t="inlineStr">
         <is>
@@ -63160,7 +63160,7 @@
         </is>
       </c>
       <c r="J1230" s="2" t="n">
-        <v>46080.58983119501</v>
+        <v>46080.58983119213</v>
       </c>
       <c r="K1230" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         </is>
       </c>
       <c r="J1231" s="2" t="n">
-        <v>46061.21483119796</v>
+        <v>46061.2148312037</v>
       </c>
       <c r="K1231" t="inlineStr">
         <is>
@@ -63262,7 +63262,7 @@
         </is>
       </c>
       <c r="J1232" s="2" t="n">
-        <v>46079.3398312008</v>
+        <v>46079.3398312037</v>
       </c>
       <c r="K1232" t="inlineStr">
         <is>
@@ -63313,7 +63313,7 @@
         </is>
       </c>
       <c r="J1233" s="2" t="n">
-        <v>46080.33983120374</v>
+        <v>46080.3398312037</v>
       </c>
       <c r="K1233" t="inlineStr">
         <is>
@@ -63364,7 +63364,7 @@
         </is>
       </c>
       <c r="J1234" s="2" t="n">
-        <v>46087.58983120666</v>
+        <v>46087.5898312037</v>
       </c>
       <c r="K1234" t="inlineStr">
         <is>
@@ -63415,7 +63415,7 @@
         </is>
       </c>
       <c r="J1235" s="2" t="n">
-        <v>46072.21483120972</v>
+        <v>46072.21483121528</v>
       </c>
       <c r="K1235" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         </is>
       </c>
       <c r="J1236" s="2" t="n">
-        <v>46069.54816454583</v>
+        <v>46069.54816454861</v>
       </c>
       <c r="K1236" t="inlineStr">
         <is>
@@ -63517,7 +63517,7 @@
         </is>
       </c>
       <c r="J1237" s="2" t="n">
-        <v>46083.5064978821</v>
+        <v>46083.50649788194</v>
       </c>
       <c r="K1237" t="inlineStr">
         <is>
@@ -63568,7 +63568,7 @@
         </is>
       </c>
       <c r="J1238" s="2" t="n">
-        <v>46061.5898312182</v>
+        <v>46061.58983121528</v>
       </c>
       <c r="K1238" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         </is>
       </c>
       <c r="J1239" s="2" t="n">
-        <v>46088.42316455442</v>
+        <v>46088.42316456018</v>
       </c>
       <c r="K1239" t="inlineStr">
         <is>
@@ -63670,7 +63670,7 @@
         </is>
       </c>
       <c r="J1240" s="2" t="n">
-        <v>46063.38149789056</v>
+        <v>46063.38149789352</v>
       </c>
       <c r="K1240" t="inlineStr">
         <is>
@@ -63721,7 +63721,7 @@
         </is>
       </c>
       <c r="J1241" s="2" t="n">
-        <v>46069.29816456001</v>
+        <v>46069.29816456018</v>
       </c>
       <c r="K1241" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         </is>
       </c>
       <c r="J1242" s="2" t="n">
-        <v>46061.29816456295</v>
+        <v>46061.29816456018</v>
       </c>
       <c r="K1242" t="inlineStr">
         <is>
@@ -63823,7 +63823,7 @@
         </is>
       </c>
       <c r="J1243" s="2" t="n">
-        <v>46068.54816456592</v>
+        <v>46068.54816456018</v>
       </c>
       <c r="K1243" t="inlineStr">
         <is>
@@ -63874,7 +63874,7 @@
         </is>
       </c>
       <c r="J1244" s="2" t="n">
-        <v>46071.33983123542</v>
+        <v>46071.33983123842</v>
       </c>
       <c r="K1244" t="inlineStr">
         <is>
@@ -63925,7 +63925,7 @@
         </is>
       </c>
       <c r="J1245" s="2" t="n">
-        <v>46069.33983123826</v>
+        <v>46069.33983123842</v>
       </c>
       <c r="K1245" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         </is>
       </c>
       <c r="J1246" s="2" t="n">
-        <v>46067.25649790786</v>
+        <v>46067.25649790509</v>
       </c>
       <c r="K1246" t="inlineStr">
         <is>
@@ -64027,7 +64027,7 @@
         </is>
       </c>
       <c r="J1247" s="2" t="n">
-        <v>46082.21483124405</v>
+        <v>46082.21483123842</v>
       </c>
       <c r="K1247" t="inlineStr">
         <is>
@@ -64078,7 +64078,7 @@
         </is>
       </c>
       <c r="J1248" s="2" t="n">
-        <v>46066.21483124694</v>
+        <v>46066.21483125</v>
       </c>
       <c r="K1248" t="inlineStr">
         <is>
@@ -64129,7 +64129,7 @@
         </is>
       </c>
       <c r="J1249" s="2" t="n">
-        <v>46061.29816458326</v>
+        <v>46061.29816458334</v>
       </c>
       <c r="K1249" t="inlineStr">
         <is>
@@ -64180,7 +64180,7 @@
         </is>
       </c>
       <c r="J1250" s="2" t="n">
-        <v>46063.38149791938</v>
+        <v>46063.38149791666</v>
       </c>
       <c r="K1250" t="inlineStr">
         <is>
@@ -64231,11 +64231,2561 @@
         </is>
       </c>
       <c r="J1251" s="2" t="n">
-        <v>46072.21483125574</v>
+        <v>46072.21483125</v>
       </c>
       <c r="K1251" t="inlineStr">
         <is>
           <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>4a22c247-1ebe-486e-bc6d-b2fe6a889bfd</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>c1afc87a-643f-4914-a4a9-ffc8466f3eb3</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1252" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>OP-906</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1252" s="2" t="n">
+        <v>46085.61982821159</v>
+      </c>
+      <c r="K1252" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>736f98c7-47d6-4d90-84af-4f9e1ad85d00</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>c6ea2614-3a4d-4eaa-9873-dbcbbfdb9431</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1253" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>OP-766</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1253" s="2" t="n">
+        <v>46065.57816154934</v>
+      </c>
+      <c r="K1253" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>94424292-b395-41d4-948f-373826ad0a41</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>e82fe2e6-0b60-4807-bd8a-793a9b2f49fe</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1254" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>OP-597</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1254" s="2" t="n">
+        <v>46076.28649488607</v>
+      </c>
+      <c r="K1254" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>ace1a32d-1bee-4f2f-8001-e1fbb214dd50</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>13273bba-d933-4a91-938a-a7f7b28e8890</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1255" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>OP-563</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1255" s="2" t="n">
+        <v>46081.57816155596</v>
+      </c>
+      <c r="K1255" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>3d183174-bf13-4c85-a2b0-e5a45ed40548</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>234d1e42-9650-4cdf-8589-89c7e325b347</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1256" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>OP-287</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1256" s="2" t="n">
+        <v>46076.28649489286</v>
+      </c>
+      <c r="K1256" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>a4ef57be-92a9-482f-af9b-58c967a2bcb8</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>36ac80a6-9ebf-4acf-962f-0b280dabc221</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1257" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>OP-734</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1257" s="2" t="n">
+        <v>46079.4948282293</v>
+      </c>
+      <c r="K1257" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>97f66c80-c3db-4aa4-af0d-741fba39a77b</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>d335773b-eda9-4318-9c55-8638aa61138c</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1258" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>OP-989</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1258" s="2" t="n">
+        <v>46081.32816156574</v>
+      </c>
+      <c r="K1258" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>d3f27662-18c9-4971-9b1d-ab55852d0770</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>09a0a469-10fd-41c9-b065-4effe35e04bb</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1259" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>OP-804</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1259" s="2" t="n">
+        <v>46084.45316156915</v>
+      </c>
+      <c r="K1259" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>0c26a190-67d1-4fe1-894a-1454967ee6e6</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>41781fb9-cd8a-47b8-9969-51c7327ca9b0</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1260" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>OP-860</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1260" s="2" t="n">
+        <v>46070.28649490578</v>
+      </c>
+      <c r="K1260" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>6cc8863d-c1d6-477b-93e3-6c5c0725c657</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>2e77154a-a2df-42fc-bd9b-331b1db91f45</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1261" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>OP-831</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1261" s="2" t="n">
+        <v>46083.45316157572</v>
+      </c>
+      <c r="K1261" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>e6b28a6a-bb30-4537-b27d-d1f1d8f911c7</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>8508e6e9-6400-4104-bda2-c827580f5781</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1262" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1262" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>OP-701</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1262" s="2" t="n">
+        <v>46072.32816157916</v>
+      </c>
+      <c r="K1262" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>01ad5824-d2be-4362-bbf4-e61aaf091150</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>cbde95c0-da37-4281-9c1a-418c872be54f</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1263" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1263" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>OP-465</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1263" s="2" t="n">
+        <v>46073.66149491597</v>
+      </c>
+      <c r="K1263" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>86f20129-cf87-48b7-875e-1a1cc835584d</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>329535c1-3bfe-4010-8fb3-a463cc2c53c8</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1264" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F1264" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>OP-786</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1264" s="2" t="n">
+        <v>46063.41149491908</v>
+      </c>
+      <c r="K1264" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>fbbcd4a8-03fe-4b46-9792-f29620c2eb9b</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>a1c8ebe8-e479-481d-9f8d-bab0fbefd54e</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1265" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1265" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>OP-136</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1265" s="2" t="n">
+        <v>46080.53649492214</v>
+      </c>
+      <c r="K1265" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>6a1dddd2-6b2e-45ea-ab58-80f935032dc6</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>db49429e-66c0-4409-bca7-8b57d328aaf4</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1266" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1266" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>OP-856</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1266" s="2" t="n">
+        <v>46075.28649492549</v>
+      </c>
+      <c r="K1266" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>4756dfc7-7bc3-48f6-b960-81882ac04ca0</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>7f543c70-cc08-4b4c-a892-e33637504543</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1267" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1267" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>OP-440</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1267" s="2" t="n">
+        <v>46063.53649492861</v>
+      </c>
+      <c r="K1267" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>abab25ab-c877-42d2-bc82-06a7235bc01c</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>3e3e5545-d4d8-4bfa-bbfd-cd13ac788188</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1268" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1268" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>OP-442</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1268" s="2" t="n">
+        <v>46085.45316159836</v>
+      </c>
+      <c r="K1268" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>5b44e2be-f386-4a1d-b253-ff1348999065</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>045557d5-41d0-419b-ac29-8031371c7565</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1269" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1269" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>OP-726</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1269" s="2" t="n">
+        <v>46068.66149493483</v>
+      </c>
+      <c r="K1269" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>11578d23-e3de-486a-972a-2c6c8ea71910</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>da24ee09-852a-43f6-bee2-dc6fa932d14a</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1270" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F1270" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>OP-566</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1270" s="2" t="n">
+        <v>46085.61982827157</v>
+      </c>
+      <c r="K1270" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>49cb5d06-ebd0-4383-a7da-1397c459e50b</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>10924f7b-09ee-4478-bc3b-610693f8af29</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1271" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F1271" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>OP-385</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1271" s="2" t="n">
+        <v>46060.41149494136</v>
+      </c>
+      <c r="K1271" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>9bcb6f1e-9c92-49b3-b704-4806cacf421e</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>817f4449-3843-4f1f-9e20-196f05093068</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1272" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1272" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>OP-468</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1272" s="2" t="n">
+        <v>46085.45316161124</v>
+      </c>
+      <c r="K1272" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>b944c79e-3027-4031-bca7-853aa290a397</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>e02efd50-472d-423a-9220-99fcc0ff11e3</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1273" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F1273" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>OP-898</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1273" s="2" t="n">
+        <v>46079.36982828128</v>
+      </c>
+      <c r="K1273" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>d85f2373-76a2-4bbc-af3f-8dba08765314</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>bf19db49-3742-4d79-b413-c77141a69904</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1274" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1274" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>OP-609</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1274" s="2" t="n">
+        <v>46088.66149495118</v>
+      </c>
+      <c r="K1274" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>25ea66cd-929f-4e04-a1c3-818104188b24</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>8245ad66-a0ae-432a-b17a-b8ef166c9c1b</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1275" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1275" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>OP-857</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1275" s="2" t="n">
+        <v>46088.28649495429</v>
+      </c>
+      <c r="K1275" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>fbc2b8c6-6e20-415c-92a9-9e0bd978fbb2</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>eeeb64f8-db7b-4d17-a698-800ecee7442e</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1276" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F1276" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>OP-289</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1276" s="2" t="n">
+        <v>46065.41149495731</v>
+      </c>
+      <c r="K1276" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>a9125429-559e-47bc-aef9-5a66fea2f0dd</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>4a9d71b7-ec13-4219-bfef-da5f684e346d</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1277" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1277" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>OP-631</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1277" s="2" t="n">
+        <v>46076.45316162728</v>
+      </c>
+      <c r="K1277" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>9a69bcd4-66f9-4424-a071-9030cef1954d</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>7363adaa-9a64-4f4b-912e-34a85500526c</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1278" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1278" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>OP-691</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1278" s="2" t="n">
+        <v>46078.41149496372</v>
+      </c>
+      <c r="K1278" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>16120d9a-6d5d-40f3-98c1-e423bea00e58</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>245c0e15-5690-4550-9892-abbd6587468f</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1279" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1279" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>OP-554</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1279" s="2" t="n">
+        <v>46067.41149496689</v>
+      </c>
+      <c r="K1279" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>39adcfa1-0ffb-49d9-939b-1dbb408081b4</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>ef291911-db07-4742-9d82-5e60fd3904de</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1280" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1280" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>OP-358</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1280" s="2" t="n">
+        <v>46087.28649496995</v>
+      </c>
+      <c r="K1280" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>fb43d553-f657-4cd0-9927-e20af8c5ca4b</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>d8244b87-6537-433a-955c-1acb09861283</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1281" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1281" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>OP-188</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1281" s="2" t="n">
+        <v>46062.36982830654</v>
+      </c>
+      <c r="K1281" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>1052b6d4-cee6-48e3-957d-0a1e75634ec4</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>570f9ac6-f58d-4d2f-8e67-ef269695365e</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1282" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F1282" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>OP-710</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1282" s="2" t="n">
+        <v>46067.5781616433</v>
+      </c>
+      <c r="K1282" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>16caa07a-2c9e-4e7e-9ffb-f61ccf6eff3c</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>e4b8ea04-4e72-4fcf-9a43-a9fba34f0fa8</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1283" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F1283" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>OP-231</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1283" s="2" t="n">
+        <v>46086.66149497985</v>
+      </c>
+      <c r="K1283" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>1e83e064-aa02-4fc8-889f-9bb7cf4e6953</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>f76d1f94-d08f-4521-a9ea-ced64a27e7ac</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1284" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F1284" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>OP-624</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1284" s="2" t="n">
+        <v>46068.49482831665</v>
+      </c>
+      <c r="K1284" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>5b3842f3-6495-4fa3-af57-6dc9f081810e</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>2b26ed8c-4969-4498-8154-2f577b42efb8</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1285" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1285" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>OP-589</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1285" s="2" t="n">
+        <v>46078.28649498662</v>
+      </c>
+      <c r="K1285" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>88743f52-57f2-4ab8-8d8e-f88ed8440b66</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>13fdc35e-5136-46d5-adac-c7cb4199e051</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1286" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1286" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>OP-457</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1286" s="2" t="n">
+        <v>46085.41149498964</v>
+      </c>
+      <c r="K1286" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>11bbdef2-bfba-437d-8c65-af81f14fad6e</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>298736fc-77fe-447f-8feb-d01ab1a656bd</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1287" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F1287" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>OP-285</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1287" s="2" t="n">
+        <v>46068.45316165939</v>
+      </c>
+      <c r="K1287" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>d72666e3-b822-4743-96cd-49d0cf6738c2</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>c3cfbebe-94a1-4102-9d49-ccc86f61d85a</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1288" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1288" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>OP-803</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1288" s="2" t="n">
+        <v>46063.61982832933</v>
+      </c>
+      <c r="K1288" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>22e5cd77-5579-44b9-8797-88c6678765f6</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>7ebc5a2d-c96b-47bb-8e15-ebe133d899da</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1289" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1289" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>OP-483</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1289" s="2" t="n">
+        <v>46083.32816166578</v>
+      </c>
+      <c r="K1289" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>cdcd6ab5-683c-4cad-be9a-2e0ca8aaef22</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>69a36108-4301-40fb-89af-82d0fd82c575</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1290" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1290" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>OP-456</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1290" s="2" t="n">
+        <v>46073.53649500227</v>
+      </c>
+      <c r="K1290" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>8f8c75e7-9145-4b53-b231-80d1a092b07f</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>73d3ee13-8936-43d6-bee6-e28a6201e3ab</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1291" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1291" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>OP-900</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1291" s="2" t="n">
+        <v>46074.4531616722</v>
+      </c>
+      <c r="K1291" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>44d59eb7-cf8d-4f53-9794-ed7c11d87fd8</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>6d8619e4-69a3-4338-9b21-791a88a2b35c</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1292" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1292" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>OP-467</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1292" s="2" t="n">
+        <v>46069.28649500881</v>
+      </c>
+      <c r="K1292" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>1220ca30-7dab-4dcc-adac-4a5bdc0669c5</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>7bbfdca7-3ad4-46b4-9297-7f13ac39e5c8</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1293" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F1293" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>OP-682</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1293" s="2" t="n">
+        <v>46067.66149501244</v>
+      </c>
+      <c r="K1293" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>b71ee8b0-e6b6-4353-8118-54f273b56387</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>f8b4359f-457f-4743-9450-3f697c0915f0</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1294" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1294" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>OP-119</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1294" s="2" t="n">
+        <v>46080.61982834889</v>
+      </c>
+      <c r="K1294" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>4b8cc007-ec1a-4713-82b1-fe26748bfeb4</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>eb01cbf2-e9f5-459c-b243-8768aa44172f</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1295" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1295" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>OP-488</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1295" s="2" t="n">
+        <v>46064.61982835206</v>
+      </c>
+      <c r="K1295" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>c4aea900-5eb8-48cf-be8d-029daef330f7</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>45f7d833-ad78-4bd0-aa46-0722228363ae</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1296" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F1296" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>OP-281</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1296" s="2" t="n">
+        <v>46086.57816168849</v>
+      </c>
+      <c r="K1296" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>f95b3f0d-b89b-42a1-a359-e32cfbeb2ed3</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>ef79e2a1-f6c9-476b-952f-969c4cb4b643</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1297" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1297" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>OP-786</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1297" s="2" t="n">
+        <v>46072.66149502491</v>
+      </c>
+      <c r="K1297" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>ce27f0fb-e2ac-4e3e-a35c-cebdee598cca</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>2f568f3c-79b6-4786-a007-6b430fe5b2bd</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1298" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F1298" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>OP-902</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1298" s="2" t="n">
+        <v>46081.66149502806</v>
+      </c>
+      <c r="K1298" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>a73de0ea-afb6-4c38-95c8-6f4674580c3e</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>4f6598ee-d976-4fb2-a81d-9da12b17b329</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1299" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1299" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>OP-282</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1299" s="2" t="n">
+        <v>46060.66149503145</v>
+      </c>
+      <c r="K1299" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>255676d6-67aa-4630-8dd6-fb723c037d2a</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>a5a0bc4a-ab0e-46d3-8297-2e0a6058aee8</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1300" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F1300" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>OP-678</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1300" s="2" t="n">
+        <v>46080.53649503446</v>
+      </c>
+      <c r="K1300" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>9b531509-56e5-4330-bae4-2bb08c367fe6</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>6d2125d6-4fa7-4dfb-ad1a-6f00ed30bbfe</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1301" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>OP-376</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1301" s="2" t="n">
+        <v>46074.53649503752</v>
+      </c>
+      <c r="K1301" t="inlineStr">
+        <is>
+          <t>poor</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1301"/>
+  <dimension ref="A1:K1351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64282,7 +64282,7 @@
         </is>
       </c>
       <c r="J1252" s="2" t="n">
-        <v>46085.61982821159</v>
+        <v>46085.61982820602</v>
       </c>
       <c r="K1252" t="inlineStr">
         <is>
@@ -64333,7 +64333,7 @@
         </is>
       </c>
       <c r="J1253" s="2" t="n">
-        <v>46065.57816154934</v>
+        <v>46065.57816155093</v>
       </c>
       <c r="K1253" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         </is>
       </c>
       <c r="J1254" s="2" t="n">
-        <v>46076.28649488607</v>
+        <v>46076.28649488426</v>
       </c>
       <c r="K1254" t="inlineStr">
         <is>
@@ -64435,7 +64435,7 @@
         </is>
       </c>
       <c r="J1255" s="2" t="n">
-        <v>46081.57816155596</v>
+        <v>46081.57816155093</v>
       </c>
       <c r="K1255" t="inlineStr">
         <is>
@@ -64486,7 +64486,7 @@
         </is>
       </c>
       <c r="J1256" s="2" t="n">
-        <v>46076.28649489286</v>
+        <v>46076.28649489583</v>
       </c>
       <c r="K1256" t="inlineStr">
         <is>
@@ -64537,7 +64537,7 @@
         </is>
       </c>
       <c r="J1257" s="2" t="n">
-        <v>46079.4948282293</v>
+        <v>46079.49482822917</v>
       </c>
       <c r="K1257" t="inlineStr">
         <is>
@@ -64588,7 +64588,7 @@
         </is>
       </c>
       <c r="J1258" s="2" t="n">
-        <v>46081.32816156574</v>
+        <v>46081.3281615625</v>
       </c>
       <c r="K1258" t="inlineStr">
         <is>
@@ -64639,7 +64639,7 @@
         </is>
       </c>
       <c r="J1259" s="2" t="n">
-        <v>46084.45316156915</v>
+        <v>46084.45316157407</v>
       </c>
       <c r="K1259" t="inlineStr">
         <is>
@@ -64690,7 +64690,7 @@
         </is>
       </c>
       <c r="J1260" s="2" t="n">
-        <v>46070.28649490578</v>
+        <v>46070.28649490741</v>
       </c>
       <c r="K1260" t="inlineStr">
         <is>
@@ -64741,7 +64741,7 @@
         </is>
       </c>
       <c r="J1261" s="2" t="n">
-        <v>46083.45316157572</v>
+        <v>46083.45316157407</v>
       </c>
       <c r="K1261" t="inlineStr">
         <is>
@@ -64792,7 +64792,7 @@
         </is>
       </c>
       <c r="J1262" s="2" t="n">
-        <v>46072.32816157916</v>
+        <v>46072.32816157407</v>
       </c>
       <c r="K1262" t="inlineStr">
         <is>
@@ -64843,7 +64843,7 @@
         </is>
       </c>
       <c r="J1263" s="2" t="n">
-        <v>46073.66149491597</v>
+        <v>46073.66149491898</v>
       </c>
       <c r="K1263" t="inlineStr">
         <is>
@@ -64894,7 +64894,7 @@
         </is>
       </c>
       <c r="J1264" s="2" t="n">
-        <v>46063.41149491908</v>
+        <v>46063.41149491898</v>
       </c>
       <c r="K1264" t="inlineStr">
         <is>
@@ -64945,7 +64945,7 @@
         </is>
       </c>
       <c r="J1265" s="2" t="n">
-        <v>46080.53649492214</v>
+        <v>46080.53649491898</v>
       </c>
       <c r="K1265" t="inlineStr">
         <is>
@@ -64996,7 +64996,7 @@
         </is>
       </c>
       <c r="J1266" s="2" t="n">
-        <v>46075.28649492549</v>
+        <v>46075.28649493056</v>
       </c>
       <c r="K1266" t="inlineStr">
         <is>
@@ -65047,7 +65047,7 @@
         </is>
       </c>
       <c r="J1267" s="2" t="n">
-        <v>46063.53649492861</v>
+        <v>46063.53649493056</v>
       </c>
       <c r="K1267" t="inlineStr">
         <is>
@@ -65098,7 +65098,7 @@
         </is>
       </c>
       <c r="J1268" s="2" t="n">
-        <v>46085.45316159836</v>
+        <v>46085.45316159722</v>
       </c>
       <c r="K1268" t="inlineStr">
         <is>
@@ -65149,7 +65149,7 @@
         </is>
       </c>
       <c r="J1269" s="2" t="n">
-        <v>46068.66149493483</v>
+        <v>46068.66149493056</v>
       </c>
       <c r="K1269" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         </is>
       </c>
       <c r="J1270" s="2" t="n">
-        <v>46085.61982827157</v>
+        <v>46085.61982827546</v>
       </c>
       <c r="K1270" t="inlineStr">
         <is>
@@ -65251,7 +65251,7 @@
         </is>
       </c>
       <c r="J1271" s="2" t="n">
-        <v>46060.41149494136</v>
+        <v>46060.41149494213</v>
       </c>
       <c r="K1271" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         </is>
       </c>
       <c r="J1272" s="2" t="n">
-        <v>46085.45316161124</v>
+        <v>46085.4531616088</v>
       </c>
       <c r="K1272" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         </is>
       </c>
       <c r="J1273" s="2" t="n">
-        <v>46079.36982828128</v>
+        <v>46079.36982828704</v>
       </c>
       <c r="K1273" t="inlineStr">
         <is>
@@ -65404,7 +65404,7 @@
         </is>
       </c>
       <c r="J1274" s="2" t="n">
-        <v>46088.66149495118</v>
+        <v>46088.6614949537</v>
       </c>
       <c r="K1274" t="inlineStr">
         <is>
@@ -65455,7 +65455,7 @@
         </is>
       </c>
       <c r="J1275" s="2" t="n">
-        <v>46088.28649495429</v>
+        <v>46088.2864949537</v>
       </c>
       <c r="K1275" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         </is>
       </c>
       <c r="J1276" s="2" t="n">
-        <v>46065.41149495731</v>
+        <v>46065.4114949537</v>
       </c>
       <c r="K1276" t="inlineStr">
         <is>
@@ -65557,7 +65557,7 @@
         </is>
       </c>
       <c r="J1277" s="2" t="n">
-        <v>46076.45316162728</v>
+        <v>46076.45316163194</v>
       </c>
       <c r="K1277" t="inlineStr">
         <is>
@@ -65608,7 +65608,7 @@
         </is>
       </c>
       <c r="J1278" s="2" t="n">
-        <v>46078.41149496372</v>
+        <v>46078.41149496528</v>
       </c>
       <c r="K1278" t="inlineStr">
         <is>
@@ -65659,7 +65659,7 @@
         </is>
       </c>
       <c r="J1279" s="2" t="n">
-        <v>46067.41149496689</v>
+        <v>46067.41149496528</v>
       </c>
       <c r="K1279" t="inlineStr">
         <is>
@@ -65710,7 +65710,7 @@
         </is>
       </c>
       <c r="J1280" s="2" t="n">
-        <v>46087.28649496995</v>
+        <v>46087.28649496528</v>
       </c>
       <c r="K1280" t="inlineStr">
         <is>
@@ -65761,7 +65761,7 @@
         </is>
       </c>
       <c r="J1281" s="2" t="n">
-        <v>46062.36982830654</v>
+        <v>46062.36982831018</v>
       </c>
       <c r="K1281" t="inlineStr">
         <is>
@@ -65812,7 +65812,7 @@
         </is>
       </c>
       <c r="J1282" s="2" t="n">
-        <v>46067.5781616433</v>
+        <v>46067.57816164352</v>
       </c>
       <c r="K1282" t="inlineStr">
         <is>
@@ -65863,7 +65863,7 @@
         </is>
       </c>
       <c r="J1283" s="2" t="n">
-        <v>46086.66149497985</v>
+        <v>46086.66149497686</v>
       </c>
       <c r="K1283" t="inlineStr">
         <is>
@@ -65914,7 +65914,7 @@
         </is>
       </c>
       <c r="J1284" s="2" t="n">
-        <v>46068.49482831665</v>
+        <v>46068.49482832176</v>
       </c>
       <c r="K1284" t="inlineStr">
         <is>
@@ -65965,7 +65965,7 @@
         </is>
       </c>
       <c r="J1285" s="2" t="n">
-        <v>46078.28649498662</v>
+        <v>46078.28649498842</v>
       </c>
       <c r="K1285" t="inlineStr">
         <is>
@@ -66016,7 +66016,7 @@
         </is>
       </c>
       <c r="J1286" s="2" t="n">
-        <v>46085.41149498964</v>
+        <v>46085.41149498842</v>
       </c>
       <c r="K1286" t="inlineStr">
         <is>
@@ -66067,7 +66067,7 @@
         </is>
       </c>
       <c r="J1287" s="2" t="n">
-        <v>46068.45316165939</v>
+        <v>46068.4531616551</v>
       </c>
       <c r="K1287" t="inlineStr">
         <is>
@@ -66118,7 +66118,7 @@
         </is>
       </c>
       <c r="J1288" s="2" t="n">
-        <v>46063.61982832933</v>
+        <v>46063.61982833334</v>
       </c>
       <c r="K1288" t="inlineStr">
         <is>
@@ -66169,7 +66169,7 @@
         </is>
       </c>
       <c r="J1289" s="2" t="n">
-        <v>46083.32816166578</v>
+        <v>46083.32816166666</v>
       </c>
       <c r="K1289" t="inlineStr">
         <is>
@@ -66220,7 +66220,7 @@
         </is>
       </c>
       <c r="J1290" s="2" t="n">
-        <v>46073.53649500227</v>
+        <v>46073.536495</v>
       </c>
       <c r="K1290" t="inlineStr">
         <is>
@@ -66271,7 +66271,7 @@
         </is>
       </c>
       <c r="J1291" s="2" t="n">
-        <v>46074.4531616722</v>
+        <v>46074.45316166666</v>
       </c>
       <c r="K1291" t="inlineStr">
         <is>
@@ -66322,7 +66322,7 @@
         </is>
       </c>
       <c r="J1292" s="2" t="n">
-        <v>46069.28649500881</v>
+        <v>46069.28649501158</v>
       </c>
       <c r="K1292" t="inlineStr">
         <is>
@@ -66373,7 +66373,7 @@
         </is>
       </c>
       <c r="J1293" s="2" t="n">
-        <v>46067.66149501244</v>
+        <v>46067.66149501158</v>
       </c>
       <c r="K1293" t="inlineStr">
         <is>
@@ -66424,7 +66424,7 @@
         </is>
       </c>
       <c r="J1294" s="2" t="n">
-        <v>46080.61982834889</v>
+        <v>46080.6198283449</v>
       </c>
       <c r="K1294" t="inlineStr">
         <is>
@@ -66475,7 +66475,7 @@
         </is>
       </c>
       <c r="J1295" s="2" t="n">
-        <v>46064.61982835206</v>
+        <v>46064.61982835648</v>
       </c>
       <c r="K1295" t="inlineStr">
         <is>
@@ -66526,7 +66526,7 @@
         </is>
       </c>
       <c r="J1296" s="2" t="n">
-        <v>46086.57816168849</v>
+        <v>46086.57816168982</v>
       </c>
       <c r="K1296" t="inlineStr">
         <is>
@@ -66577,7 +66577,7 @@
         </is>
       </c>
       <c r="J1297" s="2" t="n">
-        <v>46072.66149502491</v>
+        <v>46072.66149502315</v>
       </c>
       <c r="K1297" t="inlineStr">
         <is>
@@ -66628,7 +66628,7 @@
         </is>
       </c>
       <c r="J1298" s="2" t="n">
-        <v>46081.66149502806</v>
+        <v>46081.66149502315</v>
       </c>
       <c r="K1298" t="inlineStr">
         <is>
@@ -66679,7 +66679,7 @@
         </is>
       </c>
       <c r="J1299" s="2" t="n">
-        <v>46060.66149503145</v>
+        <v>46060.66149503472</v>
       </c>
       <c r="K1299" t="inlineStr">
         <is>
@@ -66730,7 +66730,7 @@
         </is>
       </c>
       <c r="J1300" s="2" t="n">
-        <v>46080.53649503446</v>
+        <v>46080.53649503472</v>
       </c>
       <c r="K1300" t="inlineStr">
         <is>
@@ -66781,11 +66781,2561 @@
         </is>
       </c>
       <c r="J1301" s="2" t="n">
-        <v>46074.53649503752</v>
+        <v>46074.53649503472</v>
       </c>
       <c r="K1301" t="inlineStr">
         <is>
           <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>1489ba9a-cd30-4406-8af0-2f6fc3ece3af</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>803c794c-abad-44c9-af7c-ca5cc9e6da48</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1302" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>OP-656</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1302" s="2" t="n">
+        <v>46060.66141161769</v>
+      </c>
+      <c r="K1302" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>9c156dfc-b874-436c-97f7-d792f6d2ab35</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>9b2fe321-2c99-4766-bf76-030845ae0a1d</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1303" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>OP-650</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1303" s="2" t="n">
+        <v>46062.45307828911</v>
+      </c>
+      <c r="K1303" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>650022fc-e5c5-434d-9252-b687c4f96093</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>19acb1fc-9efc-4a37-a12c-049ffbbea276</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1304" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>OP-107</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1304" s="2" t="n">
+        <v>46079.70307829274</v>
+      </c>
+      <c r="K1304" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>be5bea17-cb28-49ac-bbcb-58312270c75a</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>1fc39a69-26aa-4602-a7d0-3a2763eaa2b9</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1305" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>OP-382</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1305" s="2" t="n">
+        <v>46070.70307829587</v>
+      </c>
+      <c r="K1305" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>09e3e4c9-eaa3-4b1c-af4a-ea40895ad34f</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>9d84f1d3-9ade-4269-b2ae-7c452cf014fd</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1306" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>OP-839</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1306" s="2" t="n">
+        <v>46089.36974496576</v>
+      </c>
+      <c r="K1306" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>bd6fd975-8eb6-48a7-a5f8-d03f4c5658ee</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>7c4e7a82-1f01-46ad-96d0-56f9ef7ae577</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1307" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>OP-269</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1307" s="2" t="n">
+        <v>46062.6197449691</v>
+      </c>
+      <c r="K1307" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>181f0bfa-13a9-405d-8080-e13e5a301350</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>3f4421ff-1261-427e-944e-2671b034212e</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1308" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>OP-624</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1308" s="2" t="n">
+        <v>46071.45307830565</v>
+      </c>
+      <c r="K1308" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>dcc6699c-f310-4b73-858a-49964420098c</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>4af20b6a-3945-44ce-903a-613eca25acdb</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1309" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1309" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>OP-720</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1309" s="2" t="n">
+        <v>46070.70307830923</v>
+      </c>
+      <c r="K1309" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>974da5c0-7208-4941-803f-fd4bd4da9863</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>b0dac955-6769-4d1f-b623-491b7e33dcb0</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1310" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1310" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>OP-290</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1310" s="2" t="n">
+        <v>46060.66141164579</v>
+      </c>
+      <c r="K1310" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>e9295ac5-c417-49cf-9f01-140884a00b96</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>014902fb-6dee-40fe-87c8-882e3172cf74</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1311" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1311" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>OP-233</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1311" s="2" t="n">
+        <v>46081.61974498229</v>
+      </c>
+      <c r="K1311" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>440a2ed2-8ef0-475a-887d-ff43bb959db6</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>dc4e4b8b-f4f6-4d98-bd2e-3b5c404b0764</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1312" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F1312" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>OP-663</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1312" s="2" t="n">
+        <v>46074.41141165234</v>
+      </c>
+      <c r="K1312" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>03d344e0-23da-49d1-af29-740cd9fa2b99</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>20b2a01d-fbea-4e99-b06f-9f0225766fc9</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1313" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1313" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>OP-567</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1313" s="2" t="n">
+        <v>46074.41141165568</v>
+      </c>
+      <c r="K1313" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>08410a99-135a-42c7-a16f-f5caaf2a0491</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>14af815e-0b83-4a49-8a3b-497794c1e6ed</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1314" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1314" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>OP-969</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1314" s="2" t="n">
+        <v>46071.41141165879</v>
+      </c>
+      <c r="K1314" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>820962f6-7385-4190-a283-aa2edb1b17a5</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>0458c646-6470-4be2-b304-40de35f43fdb</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1315" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1315" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>OP-578</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1315" s="2" t="n">
+        <v>46077.57807832849</v>
+      </c>
+      <c r="K1315" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>84737af7-a379-4bed-ae19-374539b14c31</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>86418913-14b6-44cb-a8af-87109b9e0d46</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1316" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1316" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>OP-413</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1316" s="2" t="n">
+        <v>46089.53641166523</v>
+      </c>
+      <c r="K1316" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>faeac5f3-8b4b-4bed-8e4d-a22690e5a30e</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>9311be89-f97f-4b07-86e3-ca6f88abf3c1</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1317" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F1317" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>OP-922</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1317" s="2" t="n">
+        <v>46066.49474500177</v>
+      </c>
+      <c r="K1317" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>4f763387-3004-46e3-8993-4bf88ad63f88</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>ab708a6c-697e-4ca9-b36f-95faf07403a8</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1318" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1318" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>OP-362</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1318" s="2" t="n">
+        <v>46089.41141167151</v>
+      </c>
+      <c r="K1318" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>a0ee25f8-51dd-46c6-8337-fe5d08a2b966</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>91302732-2aa5-486d-bb0e-69526d06c573</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1319" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F1319" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>OP-505</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1319" s="2" t="n">
+        <v>46085.61974500802</v>
+      </c>
+      <c r="K1319" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>19cb2914-e762-4db0-8508-d73d26a4b602</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>32761a91-cda4-4b00-87f6-2607f212de2e</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1320" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1320" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>OP-285</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1320" s="2" t="n">
+        <v>46071.49474501122</v>
+      </c>
+      <c r="K1320" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>8a62b806-726d-43ce-af5d-860f06ecbfd8</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>5d569967-0717-4da5-a164-dd10978bcd76</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1321" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1321" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>OP-524</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1321" s="2" t="n">
+        <v>46074.32807834771</v>
+      </c>
+      <c r="K1321" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>daa3bf63-06eb-434b-a5df-ae52eb032e32</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>ea9c5664-f75b-4a88-bd7e-2f74275746ba</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1322" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F1322" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>OP-626</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1322" s="2" t="n">
+        <v>46063.57807835082</v>
+      </c>
+      <c r="K1322" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>bf7f5657-c8da-494c-b1bb-ea82a7280241</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>b2bb4ac7-06a7-42db-b132-a871e334a877</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1323" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1323" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>OP-916</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1323" s="2" t="n">
+        <v>46067.53641168836</v>
+      </c>
+      <c r="K1323" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>3cab0ca8-2cd2-4234-a44e-522d369d20ad</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>ae2124e8-b55d-4db4-bdf5-8a53283b062b</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1324" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F1324" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>OP-539</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1324" s="2" t="n">
+        <v>46085.49474502495</v>
+      </c>
+      <c r="K1324" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>24519c97-282a-4a56-adf8-3cb58d8b7a46</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>c6e0c488-1d90-4d67-aa47-6af90217e633</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1325" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1325" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>OP-325</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1325" s="2" t="n">
+        <v>46080.41141169467</v>
+      </c>
+      <c r="K1325" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>5b12fab7-7795-4491-88de-097473678081</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>6c69b523-65b3-46c3-a792-c6ac665b3114</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1326" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F1326" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>OP-966</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1326" s="2" t="n">
+        <v>46073.7030783644</v>
+      </c>
+      <c r="K1326" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>e3d70f9a-b701-440d-ae3f-efe7c6b14a85</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>49f28af4-1cb9-47b6-9c10-b4ac3cc1fece</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1327" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1327" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>OP-185</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1327" s="2" t="n">
+        <v>46087.49474503446</v>
+      </c>
+      <c r="K1327" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>69894532-76d0-4732-abd7-ab835ab88e67</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>00dfaaad-0ab4-4d0a-93f1-61ce2b4b0f84</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1328" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F1328" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>OP-488</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1328" s="2" t="n">
+        <v>46069.32807837099</v>
+      </c>
+      <c r="K1328" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>ffa7e32e-eb14-41a9-a268-8928020e2d7c</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>3e30eee4-0eaa-4b65-a121-1ba9d2501417</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1329" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F1329" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>OP-780</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1329" s="2" t="n">
+        <v>46063.61974504074</v>
+      </c>
+      <c r="K1329" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>a1c869d1-bdab-4621-8b0e-e1ecb289cdf7</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>0682c165-3967-4c80-854d-3d7e4e158fbe</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1330" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F1330" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>OP-874</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1330" s="2" t="n">
+        <v>46061.61974504391</v>
+      </c>
+      <c r="K1330" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>e41ed728-9419-45d5-913e-a92c4267d36d</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>15f2ec6e-3f14-41f8-9570-7155c28f11e1</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1331" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1331" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>OP-146</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1331" s="2" t="n">
+        <v>46080.66141171393</v>
+      </c>
+      <c r="K1331" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>fd64a200-677b-4ba9-adad-36d03c0cda2d</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>472cded4-4ab1-46fe-a32d-dff5d0472b1b</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1332" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F1332" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>OP-558</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1332" s="2" t="n">
+        <v>46083.57807838394</v>
+      </c>
+      <c r="K1332" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>c8d843a0-811c-4f5a-8763-e59ecb005bc4</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>1bd9a9d6-6554-4986-ba99-c3c3f1e77fbf</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1333" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F1333" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>OP-549</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1333" s="2" t="n">
+        <v>46074.32807838697</v>
+      </c>
+      <c r="K1333" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>508ed286-3257-40ad-b68a-580b1f6ec651</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>eecb0e7d-3672-4af6-9b8a-836dfc7b4222</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1334" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1334" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>OP-982</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1334" s="2" t="n">
+        <v>46065.61974505691</v>
+      </c>
+      <c r="K1334" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>fca6265b-594d-4a1d-b753-e9a79226058d</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>159082a5-2306-483a-b4e9-74f021151a87</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1335" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1335" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>OP-824</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1335" s="2" t="n">
+        <v>46085.45307839325</v>
+      </c>
+      <c r="K1335" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>a759c734-f8e7-49c3-b87c-8507afd9e4c2</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>cc9693d7-3843-4f40-b387-625ace8642ec</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1336" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1336" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>OP-698</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1336" s="2" t="n">
+        <v>46074.36974506292</v>
+      </c>
+      <c r="K1336" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>58ce19d5-e5d2-4e0d-9c1c-6adf606a6115</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>f75fa40f-8655-45c6-b5b8-c5357845776b</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1337" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1337" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>OP-840</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1337" s="2" t="n">
+        <v>46069.5364117327</v>
+      </c>
+      <c r="K1337" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>ab8d6560-9e7d-4e2b-9f01-c01fc17fe92a</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>4ee705b5-1b9e-4056-8963-991087f303a8</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1338" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1338" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>OP-933</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1338" s="2" t="n">
+        <v>46064.53641173617</v>
+      </c>
+      <c r="K1338" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2830d65d-aa99-401d-a8d4-146feb30c4eb</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>46b96833-2ac3-4f5b-9f92-afbf42061e0d</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1339" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1339" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>OP-661</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1339" s="2" t="n">
+        <v>46084.36974507258</v>
+      </c>
+      <c r="K1339" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>cd432ea0-d63d-4198-a475-b3d5022c78e7</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>ebe49ddf-36a6-40d6-9d18-5fe71107e8f2</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1340" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1340" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>OP-889</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1340" s="2" t="n">
+        <v>46070.32807840892</v>
+      </c>
+      <c r="K1340" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>b7ae54b6-298e-48e9-88f7-2ce4fcaca6f4</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>e2daa030-a550-4b12-aadb-ddc1a4c36032</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1341" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F1341" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>OP-266</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1341" s="2" t="n">
+        <v>46068.57807841194</v>
+      </c>
+      <c r="K1341" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>3d1a7f44-dbff-4764-8424-6a26724b7b2c</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>8239e330-26a6-4cfe-b592-0f782f98a731</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1342" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1342" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>OP-802</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1342" s="2" t="n">
+        <v>46066.4530784153</v>
+      </c>
+      <c r="K1342" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>30eba982-1906-4d38-ac15-e730ab2f3de1</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>bcd812ef-db00-4a21-b1af-76d28a7cf8cf</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1343" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1343" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>OP-505</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1343" s="2" t="n">
+        <v>46084.4947450852</v>
+      </c>
+      <c r="K1343" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>ffa52743-289e-46a2-b10a-a2e7ec141cb2</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>e9f4f7bb-f29c-479c-8729-dd71ab1729b7</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1344" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1344" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>OP-135</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1344" s="2" t="n">
+        <v>46084.66141175497</v>
+      </c>
+      <c r="K1344" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>fc3e5298-4bad-4cc9-bf57-384300041033</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>1987d7dd-e960-4872-babc-c54f3e81ba88</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1345" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1345" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>OP-984</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1345" s="2" t="n">
+        <v>46067.49474509164</v>
+      </c>
+      <c r="K1345" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>3d6fb26c-8ef6-406f-b8da-a168167eb28c</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>2a840d95-cabe-49f5-ab28-4c51ea88fdcc</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1346" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1346" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>OP-924</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1346" s="2" t="n">
+        <v>46074.49474509484</v>
+      </c>
+      <c r="K1346" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>a72e1810-466e-402f-b4bf-62946aab3754</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>b8b8a080-ebee-4b4e-987c-611dfb3353a1</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1347" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1347" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>OP-927</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1347" s="2" t="n">
+        <v>46087.53641176457</v>
+      </c>
+      <c r="K1347" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>48e2c416-5062-42fe-aff2-dbe91d33dbe6</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>c36cf6ac-c8e5-4282-b820-2757f763f03c</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1348" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F1348" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>OP-605</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1348" s="2" t="n">
+        <v>46089.45307843439</v>
+      </c>
+      <c r="K1348" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>9335542c-8575-4009-b5fd-b53f09f05cbf</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>ab43e0bd-22ed-4136-a721-ea7d489fccbe</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1349" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F1349" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>OP-705</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1349" s="2" t="n">
+        <v>46081.32807843768</v>
+      </c>
+      <c r="K1349" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>aea91e0c-9ba4-4f62-abd7-0a180104f4b9</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>c59a1917-59f1-4042-b2ea-18e6965a90fa</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1350" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1350" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>OP-713</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1350" s="2" t="n">
+        <v>46061.45307844078</v>
+      </c>
+      <c r="K1350" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>69b23be8-b037-4348-94a1-868410772585</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>0f5dca8e-067c-425d-b7bc-42ae7a8e4374</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1351" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1351" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>OP-379</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1351" s="2" t="n">
+        <v>46082.53641177717</v>
+      </c>
+      <c r="K1351" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1351"/>
+  <dimension ref="A1:K1401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66832,7 +66832,7 @@
         </is>
       </c>
       <c r="J1302" s="2" t="n">
-        <v>46060.66141161769</v>
+        <v>46060.66141162037</v>
       </c>
       <c r="K1302" t="inlineStr">
         <is>
@@ -66883,7 +66883,7 @@
         </is>
       </c>
       <c r="J1303" s="2" t="n">
-        <v>46062.45307828911</v>
+        <v>46062.45307828704</v>
       </c>
       <c r="K1303" t="inlineStr">
         <is>
@@ -66934,7 +66934,7 @@
         </is>
       </c>
       <c r="J1304" s="2" t="n">
-        <v>46079.70307829274</v>
+        <v>46079.70307828704</v>
       </c>
       <c r="K1304" t="inlineStr">
         <is>
@@ -66985,7 +66985,7 @@
         </is>
       </c>
       <c r="J1305" s="2" t="n">
-        <v>46070.70307829587</v>
+        <v>46070.70307829861</v>
       </c>
       <c r="K1305" t="inlineStr">
         <is>
@@ -67036,7 +67036,7 @@
         </is>
       </c>
       <c r="J1306" s="2" t="n">
-        <v>46089.36974496576</v>
+        <v>46089.36974496528</v>
       </c>
       <c r="K1306" t="inlineStr">
         <is>
@@ -67087,7 +67087,7 @@
         </is>
       </c>
       <c r="J1307" s="2" t="n">
-        <v>46062.6197449691</v>
+        <v>46062.61974496528</v>
       </c>
       <c r="K1307" t="inlineStr">
         <is>
@@ -67138,7 +67138,7 @@
         </is>
       </c>
       <c r="J1308" s="2" t="n">
-        <v>46071.45307830565</v>
+        <v>46071.45307831019</v>
       </c>
       <c r="K1308" t="inlineStr">
         <is>
@@ -67189,7 +67189,7 @@
         </is>
       </c>
       <c r="J1309" s="2" t="n">
-        <v>46070.70307830923</v>
+        <v>46070.70307831019</v>
       </c>
       <c r="K1309" t="inlineStr">
         <is>
@@ -67240,7 +67240,7 @@
         </is>
       </c>
       <c r="J1310" s="2" t="n">
-        <v>46060.66141164579</v>
+        <v>46060.66141164352</v>
       </c>
       <c r="K1310" t="inlineStr">
         <is>
@@ -67291,7 +67291,7 @@
         </is>
       </c>
       <c r="J1311" s="2" t="n">
-        <v>46081.61974498229</v>
+        <v>46081.61974497685</v>
       </c>
       <c r="K1311" t="inlineStr">
         <is>
@@ -67342,7 +67342,7 @@
         </is>
       </c>
       <c r="J1312" s="2" t="n">
-        <v>46074.41141165234</v>
+        <v>46074.41141165509</v>
       </c>
       <c r="K1312" t="inlineStr">
         <is>
@@ -67393,7 +67393,7 @@
         </is>
       </c>
       <c r="J1313" s="2" t="n">
-        <v>46074.41141165568</v>
+        <v>46074.41141165509</v>
       </c>
       <c r="K1313" t="inlineStr">
         <is>
@@ -67444,7 +67444,7 @@
         </is>
       </c>
       <c r="J1314" s="2" t="n">
-        <v>46071.41141165879</v>
+        <v>46071.41141165509</v>
       </c>
       <c r="K1314" t="inlineStr">
         <is>
@@ -67495,7 +67495,7 @@
         </is>
       </c>
       <c r="J1315" s="2" t="n">
-        <v>46077.57807832849</v>
+        <v>46077.57807833333</v>
       </c>
       <c r="K1315" t="inlineStr">
         <is>
@@ -67546,7 +67546,7 @@
         </is>
       </c>
       <c r="J1316" s="2" t="n">
-        <v>46089.53641166523</v>
+        <v>46089.53641166667</v>
       </c>
       <c r="K1316" t="inlineStr">
         <is>
@@ -67597,7 +67597,7 @@
         </is>
       </c>
       <c r="J1317" s="2" t="n">
-        <v>46066.49474500177</v>
+        <v>46066.494745</v>
       </c>
       <c r="K1317" t="inlineStr">
         <is>
@@ -67648,7 +67648,7 @@
         </is>
       </c>
       <c r="J1318" s="2" t="n">
-        <v>46089.41141167151</v>
+        <v>46089.41141166667</v>
       </c>
       <c r="K1318" t="inlineStr">
         <is>
@@ -67699,7 +67699,7 @@
         </is>
       </c>
       <c r="J1319" s="2" t="n">
-        <v>46085.61974500802</v>
+        <v>46085.61974501157</v>
       </c>
       <c r="K1319" t="inlineStr">
         <is>
@@ -67750,7 +67750,7 @@
         </is>
       </c>
       <c r="J1320" s="2" t="n">
-        <v>46071.49474501122</v>
+        <v>46071.49474501157</v>
       </c>
       <c r="K1320" t="inlineStr">
         <is>
@@ -67801,7 +67801,7 @@
         </is>
       </c>
       <c r="J1321" s="2" t="n">
-        <v>46074.32807834771</v>
+        <v>46074.32807834491</v>
       </c>
       <c r="K1321" t="inlineStr">
         <is>
@@ -67852,7 +67852,7 @@
         </is>
       </c>
       <c r="J1322" s="2" t="n">
-        <v>46063.57807835082</v>
+        <v>46063.57807835648</v>
       </c>
       <c r="K1322" t="inlineStr">
         <is>
@@ -67903,7 +67903,7 @@
         </is>
       </c>
       <c r="J1323" s="2" t="n">
-        <v>46067.53641168836</v>
+        <v>46067.53641168981</v>
       </c>
       <c r="K1323" t="inlineStr">
         <is>
@@ -67954,7 +67954,7 @@
         </is>
       </c>
       <c r="J1324" s="2" t="n">
-        <v>46085.49474502495</v>
+        <v>46085.49474502315</v>
       </c>
       <c r="K1324" t="inlineStr">
         <is>
@@ -68005,7 +68005,7 @@
         </is>
       </c>
       <c r="J1325" s="2" t="n">
-        <v>46080.41141169467</v>
+        <v>46080.41141168981</v>
       </c>
       <c r="K1325" t="inlineStr">
         <is>
@@ -68056,7 +68056,7 @@
         </is>
       </c>
       <c r="J1326" s="2" t="n">
-        <v>46073.7030783644</v>
+        <v>46073.70307836805</v>
       </c>
       <c r="K1326" t="inlineStr">
         <is>
@@ -68107,7 +68107,7 @@
         </is>
       </c>
       <c r="J1327" s="2" t="n">
-        <v>46087.49474503446</v>
+        <v>46087.49474503472</v>
       </c>
       <c r="K1327" t="inlineStr">
         <is>
@@ -68158,7 +68158,7 @@
         </is>
       </c>
       <c r="J1328" s="2" t="n">
-        <v>46069.32807837099</v>
+        <v>46069.32807836805</v>
       </c>
       <c r="K1328" t="inlineStr">
         <is>
@@ -68209,7 +68209,7 @@
         </is>
       </c>
       <c r="J1329" s="2" t="n">
-        <v>46063.61974504074</v>
+        <v>46063.61974504629</v>
       </c>
       <c r="K1329" t="inlineStr">
         <is>
@@ -68260,7 +68260,7 @@
         </is>
       </c>
       <c r="J1330" s="2" t="n">
-        <v>46061.61974504391</v>
+        <v>46061.61974504629</v>
       </c>
       <c r="K1330" t="inlineStr">
         <is>
@@ -68311,7 +68311,7 @@
         </is>
       </c>
       <c r="J1331" s="2" t="n">
-        <v>46080.66141171393</v>
+        <v>46080.66141171296</v>
       </c>
       <c r="K1331" t="inlineStr">
         <is>
@@ -68362,7 +68362,7 @@
         </is>
       </c>
       <c r="J1332" s="2" t="n">
-        <v>46083.57807838394</v>
+        <v>46083.57807837963</v>
       </c>
       <c r="K1332" t="inlineStr">
         <is>
@@ -68413,7 +68413,7 @@
         </is>
       </c>
       <c r="J1333" s="2" t="n">
-        <v>46074.32807838697</v>
+        <v>46074.32807839121</v>
       </c>
       <c r="K1333" t="inlineStr">
         <is>
@@ -68464,7 +68464,7 @@
         </is>
       </c>
       <c r="J1334" s="2" t="n">
-        <v>46065.61974505691</v>
+        <v>46065.61974505787</v>
       </c>
       <c r="K1334" t="inlineStr">
         <is>
@@ -68515,7 +68515,7 @@
         </is>
       </c>
       <c r="J1335" s="2" t="n">
-        <v>46085.45307839325</v>
+        <v>46085.45307839121</v>
       </c>
       <c r="K1335" t="inlineStr">
         <is>
@@ -68566,7 +68566,7 @@
         </is>
       </c>
       <c r="J1336" s="2" t="n">
-        <v>46074.36974506292</v>
+        <v>46074.36974505787</v>
       </c>
       <c r="K1336" t="inlineStr">
         <is>
@@ -68617,7 +68617,7 @@
         </is>
       </c>
       <c r="J1337" s="2" t="n">
-        <v>46069.5364117327</v>
+        <v>46069.53641173611</v>
       </c>
       <c r="K1337" t="inlineStr">
         <is>
@@ -68668,7 +68668,7 @@
         </is>
       </c>
       <c r="J1338" s="2" t="n">
-        <v>46064.53641173617</v>
+        <v>46064.53641173611</v>
       </c>
       <c r="K1338" t="inlineStr">
         <is>
@@ -68719,7 +68719,7 @@
         </is>
       </c>
       <c r="J1339" s="2" t="n">
-        <v>46084.36974507258</v>
+        <v>46084.36974506945</v>
       </c>
       <c r="K1339" t="inlineStr">
         <is>
@@ -68770,7 +68770,7 @@
         </is>
       </c>
       <c r="J1340" s="2" t="n">
-        <v>46070.32807840892</v>
+        <v>46070.32807841435</v>
       </c>
       <c r="K1340" t="inlineStr">
         <is>
@@ -68821,7 +68821,7 @@
         </is>
       </c>
       <c r="J1341" s="2" t="n">
-        <v>46068.57807841194</v>
+        <v>46068.57807841435</v>
       </c>
       <c r="K1341" t="inlineStr">
         <is>
@@ -68872,7 +68872,7 @@
         </is>
       </c>
       <c r="J1342" s="2" t="n">
-        <v>46066.4530784153</v>
+        <v>46066.45307841435</v>
       </c>
       <c r="K1342" t="inlineStr">
         <is>
@@ -68923,7 +68923,7 @@
         </is>
       </c>
       <c r="J1343" s="2" t="n">
-        <v>46084.4947450852</v>
+        <v>46084.49474508102</v>
       </c>
       <c r="K1343" t="inlineStr">
         <is>
@@ -68974,7 +68974,7 @@
         </is>
       </c>
       <c r="J1344" s="2" t="n">
-        <v>46084.66141175497</v>
+        <v>46084.66141175926</v>
       </c>
       <c r="K1344" t="inlineStr">
         <is>
@@ -69025,7 +69025,7 @@
         </is>
       </c>
       <c r="J1345" s="2" t="n">
-        <v>46067.49474509164</v>
+        <v>46067.49474509259</v>
       </c>
       <c r="K1345" t="inlineStr">
         <is>
@@ -69076,7 +69076,7 @@
         </is>
       </c>
       <c r="J1346" s="2" t="n">
-        <v>46074.49474509484</v>
+        <v>46074.49474509259</v>
       </c>
       <c r="K1346" t="inlineStr">
         <is>
@@ -69127,7 +69127,7 @@
         </is>
       </c>
       <c r="J1347" s="2" t="n">
-        <v>46087.53641176457</v>
+        <v>46087.53641175926</v>
       </c>
       <c r="K1347" t="inlineStr">
         <is>
@@ -69178,7 +69178,7 @@
         </is>
       </c>
       <c r="J1348" s="2" t="n">
-        <v>46089.45307843439</v>
+        <v>46089.4530784375</v>
       </c>
       <c r="K1348" t="inlineStr">
         <is>
@@ -69229,7 +69229,7 @@
         </is>
       </c>
       <c r="J1349" s="2" t="n">
-        <v>46081.32807843768</v>
+        <v>46081.3280784375</v>
       </c>
       <c r="K1349" t="inlineStr">
         <is>
@@ -69280,7 +69280,7 @@
         </is>
       </c>
       <c r="J1350" s="2" t="n">
-        <v>46061.45307844078</v>
+        <v>46061.4530784375</v>
       </c>
       <c r="K1350" t="inlineStr">
         <is>
@@ -69331,11 +69331,2561 @@
         </is>
       </c>
       <c r="J1351" s="2" t="n">
-        <v>46082.53641177717</v>
+        <v>46082.53641178241</v>
       </c>
       <c r="K1351" t="inlineStr">
         <is>
           <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>7da89a03-f0df-4cf8-8b70-5789333845f7</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>042c0172-287c-41a9-aa2b-35d24bed17cb</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1352" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1352" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>OP-588</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1352" s="2" t="n">
+        <v>46078.44785992507</v>
+      </c>
+      <c r="K1352" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>d3b54be2-d46c-4302-a078-8a53c3053dc6</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>d89801b1-f7ce-452a-9967-c9e0646f5f20</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1353" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1353" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>OP-227</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1353" s="2" t="n">
+        <v>46060.65619326274</v>
+      </c>
+      <c r="K1353" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>9f300350-fc65-4eee-bf09-b04852ba38c0</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>07f0b4c3-3055-4059-bfc8-e5982f74dd40</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1354" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1354" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>OP-468</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1354" s="2" t="n">
+        <v>46077.53119326616</v>
+      </c>
+      <c r="K1354" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>ca7802a2-e483-4ab7-b51b-510015145cf3</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>6226717f-afae-405c-b543-aaaca372a881</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1355" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1355" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>OP-801</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1355" s="2" t="n">
+        <v>46080.4895266032</v>
+      </c>
+      <c r="K1355" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>a12e693d-b3cb-4baf-8918-b73e4f84cdcf</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>2bd5f778-63a7-41fe-b7ed-e7c08ef1a386</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1356" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F1356" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>OP-310</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1356" s="2" t="n">
+        <v>46077.61452660627</v>
+      </c>
+      <c r="K1356" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>e87dd4f8-c458-4a61-a0d8-0c3f2e00d9ab</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>bcaa84f3-497f-494a-87bc-ab1188aae3fc</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1357" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F1357" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>OP-823</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1357" s="2" t="n">
+        <v>46073.57285994302</v>
+      </c>
+      <c r="K1357" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>295d9f57-f11c-4719-a7a2-029a9b788fc2</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>61e49900-8e22-41cd-81d6-a8881bf76446</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1358" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1358" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>OP-433</t>
+        </is>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1358" s="2" t="n">
+        <v>46085.73952661296</v>
+      </c>
+      <c r="K1358" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>430cdb5d-f001-45bd-84ea-d310682dc82a</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>61189384-2783-44be-8198-bc01b2ee5878</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1359" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1359" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>OP-928</t>
+        </is>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1359" s="2" t="n">
+        <v>46075.69785994949</v>
+      </c>
+      <c r="K1359" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>f800e2ba-3909-4b8c-abcf-5cd0123f014d</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>53ffd795-6564-453d-b63b-0a499fbb0ad1</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1360" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1360" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>OP-322</t>
+        </is>
+      </c>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1360" s="2" t="n">
+        <v>46086.5728599526</v>
+      </c>
+      <c r="K1360" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>302b5d48-76a4-401b-81f7-e49feed0f30e</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>9681db5e-f4df-44ee-8c27-d53df6f5df80</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1361" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1361" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>OP-854</t>
+        </is>
+      </c>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1361" s="2" t="n">
+        <v>46072.6145266225</v>
+      </c>
+      <c r="K1361" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>34d800a7-0ea5-4d5a-a8bd-4eeb1f3810e8</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>eeba8993-98e2-4388-b4b6-e59f9469684b</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1362" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1362" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>OP-107</t>
+        </is>
+      </c>
+      <c r="I1362" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1362" s="2" t="n">
+        <v>46089.61452662585</v>
+      </c>
+      <c r="K1362" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>c4f68584-773d-4cfe-ac10-e9c42166f2fe</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>d413c626-7ec8-4ad4-9674-c399a597c62c</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1363" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1363" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>OP-504</t>
+        </is>
+      </c>
+      <c r="I1363" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1363" s="2" t="n">
+        <v>46080.53119329573</v>
+      </c>
+      <c r="K1363" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>b35bea31-b05c-40f8-afb0-7edc1aae7d84</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>86cc4417-25d9-4744-9627-df6a177b79ac</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1364" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1364" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>OP-173</t>
+        </is>
+      </c>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1364" s="2" t="n">
+        <v>46075.36452663234</v>
+      </c>
+      <c r="K1364" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>bef3741f-4a01-4eb2-a505-464a57b0480d</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>6ccfe209-ab8a-4ce9-987f-9783fe5e957c</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1365" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F1365" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>OP-536</t>
+        </is>
+      </c>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1365" s="2" t="n">
+        <v>46065.4895266364</v>
+      </c>
+      <c r="K1365" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>f1c6176b-3fda-421c-b8dd-d03421df737f</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>7cf7806f-dce3-429d-97a8-e0b9bd41b8ed</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1366" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1366" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>OP-921</t>
+        </is>
+      </c>
+      <c r="I1366" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1366" s="2" t="n">
+        <v>46062.44785997286</v>
+      </c>
+      <c r="K1366" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>c1082418-52ea-45f2-b2f6-dc4c4132eb2f</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>87e9a731-54a2-4375-a2e9-1e437e5c7b11</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1367" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1367" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>OP-649</t>
+        </is>
+      </c>
+      <c r="I1367" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1367" s="2" t="n">
+        <v>46067.48952664281</v>
+      </c>
+      <c r="K1367" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>f36ef4be-7238-4b51-90b8-0790c7cea03d</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>f1264bd0-b226-4918-b8cd-33df7c1d66c6</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1368" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F1368" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>OP-493</t>
+        </is>
+      </c>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1368" s="2" t="n">
+        <v>46065.57285997931</v>
+      </c>
+      <c r="K1368" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>b0ead2a0-4940-4723-912d-f91a6ea8a238</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>a9c1bb20-6bb7-4b54-9b8e-2c47eb726682</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1369" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1369" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>OP-189</t>
+        </is>
+      </c>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1369" s="2" t="n">
+        <v>46085.65619331602</v>
+      </c>
+      <c r="K1369" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>83e3f9a0-83e7-4e7a-8481-043586443b41</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>b659833e-9aaf-46f8-9a4a-8f61f6e12efa</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1370" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1370" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>OP-696</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1370" s="2" t="n">
+        <v>46081.69785998595</v>
+      </c>
+      <c r="K1370" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>4fda7248-5951-4e76-8b91-113429751605</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>e7923e10-72de-4366-acae-0293dac6674e</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1371" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1371" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>OP-140</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1371" s="2" t="n">
+        <v>46060.48952665571</v>
+      </c>
+      <c r="K1371" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>83c3798b-617e-47c5-a809-8efb5aae80f2</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>371953eb-61c5-415a-ba30-92c60efc9059</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1372" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F1372" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>OP-998</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1372" s="2" t="n">
+        <v>46082.48952665917</v>
+      </c>
+      <c r="K1372" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2059cecf-aea3-402f-a85e-05d8afdffd82</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>96a1a977-9b51-417f-99ed-aae66d9a89d9</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1373" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1373" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>OP-676</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1373" s="2" t="n">
+        <v>46069.53119332893</v>
+      </c>
+      <c r="K1373" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>cbd1e32c-0814-4682-b973-f2cd629cf0da</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>799033ac-761f-48e0-8324-c5f6b3d92ec5</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1374" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F1374" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>OP-505</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1374" s="2" t="n">
+        <v>46066.4895266655</v>
+      </c>
+      <c r="K1374" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>3c80d706-bdf1-482e-bcb6-c12cc3dbb3e8</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>09c88e58-ca09-454c-8de9-9820434f10e1</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1375" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F1375" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>OP-671</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1375" s="2" t="n">
+        <v>46060.73952666851</v>
+      </c>
+      <c r="K1375" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>b2912007-aa96-4030-86be-6be3ea5c4ee3</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>b2b466d4-7975-4ff3-99ce-87742466c525</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1376" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1376" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>OP-392</t>
+        </is>
+      </c>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1376" s="2" t="n">
+        <v>46072.36452667192</v>
+      </c>
+      <c r="K1376" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>bb0bbe03-df3d-466f-825e-a77500989319</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>531462a2-3085-4d1f-9780-eaebcdaaf18b</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1377" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F1377" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>OP-172</t>
+        </is>
+      </c>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1377" s="2" t="n">
+        <v>46077.61452667529</v>
+      </c>
+      <c r="K1377" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>b8bf1e6d-558d-4b5c-b34e-64669ad534be</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>2b4799c4-3670-4808-8778-eae82aeb1763</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1378" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1378" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>OP-791</t>
+        </is>
+      </c>
+      <c r="I1378" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1378" s="2" t="n">
+        <v>46064.53119334519</v>
+      </c>
+      <c r="K1378" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>e952ce2d-e0cb-473e-a28c-294e9fcd21f5</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>b6779d9f-5466-47a5-a68d-ad3a1ad73103</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1379" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1379" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>OP-194</t>
+        </is>
+      </c>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1379" s="2" t="n">
+        <v>46080.36452668263</v>
+      </c>
+      <c r="K1379" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2d1a2da5-7a8c-406e-ba60-6a613ae7de9e</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>5dc3c061-fc4c-478e-b42e-7fc97d9c1057</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1380" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F1380" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>OP-854</t>
+        </is>
+      </c>
+      <c r="I1380" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1380" s="2" t="n">
+        <v>46060.65619335238</v>
+      </c>
+      <c r="K1380" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>29e6ee9e-8b48-41ec-904e-e2ad51b652c3</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>11057573-f394-479c-a800-c397fa82254b</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1381" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1381" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>OP-105</t>
+        </is>
+      </c>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1381" s="2" t="n">
+        <v>46085.48952668892</v>
+      </c>
+      <c r="K1381" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>c7a2c9dc-8b85-4e49-b689-22edf74577fe</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>e33248c9-dd6a-4a57-adfb-42e950332c81</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1382" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F1382" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>OP-831</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1382" s="2" t="n">
+        <v>46072.44786002535</v>
+      </c>
+      <c r="K1382" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>23ec8288-88f0-4452-a3b9-68d6889cf9c5</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>b202a867-d31d-487b-8ec5-5ca805a2f47b</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1383" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F1383" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>OP-551</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1383" s="2" t="n">
+        <v>46087.44786002857</v>
+      </c>
+      <c r="K1383" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>22788e52-6865-4a2d-8ed3-999490b28872</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>a9ca00f1-bf17-46b7-8242-b5544f40e24e</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1384" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F1384" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>OP-288</t>
+        </is>
+      </c>
+      <c r="I1384" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1384" s="2" t="n">
+        <v>46089.6978600318</v>
+      </c>
+      <c r="K1384" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>0c16c6f4-0c4f-47cb-aa61-bd73a790582a</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>a14edb41-93ce-4614-a48e-79d6f7af4eb2</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1385" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1385" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>OP-340</t>
+        </is>
+      </c>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1385" s="2" t="n">
+        <v>46079.44786003488</v>
+      </c>
+      <c r="K1385" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2ab9833b-a0d8-42fb-8a9d-e3ebfbed6a6f</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>f5f9551a-34e9-4e7e-aac2-e00976b9d675</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1386" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1386" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>OP-449</t>
+        </is>
+      </c>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1386" s="2" t="n">
+        <v>46086.65619337198</v>
+      </c>
+      <c r="K1386" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>5ac2d995-16cf-47a6-a9e4-25c89c793cde</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>09129bc0-e031-451a-ba2c-557552e4613a</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1387" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1387" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>OP-917</t>
+        </is>
+      </c>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1387" s="2" t="n">
+        <v>46078.48952670841</v>
+      </c>
+      <c r="K1387" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>99a0087a-6867-4891-9f9f-580950a2fb70</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>d55e95ca-f146-4db6-bd4a-cd8a295f0757</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1388" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1388" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>OP-322</t>
+        </is>
+      </c>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1388" s="2" t="n">
+        <v>46078.73952671159</v>
+      </c>
+      <c r="K1388" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>a67e596d-3a93-44ce-bfd3-5e16e935959c</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>dbebf4b9-63ac-4758-b20c-73da260347ee</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1389" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1389" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>OP-477</t>
+        </is>
+      </c>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1389" s="2" t="n">
+        <v>46075.57286004804</v>
+      </c>
+      <c r="K1389" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>c964a373-7c26-481e-ba75-37f5fdd7eeaa</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>f97556a6-39e3-4c1c-99f9-89869070319b</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1390" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1390" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>OP-537</t>
+        </is>
+      </c>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1390" s="2" t="n">
+        <v>46076.57286005131</v>
+      </c>
+      <c r="K1390" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>ac689ae7-56f6-47aa-9577-1e4ed739cf87</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>79e97a7c-b334-4834-b507-a7fffdc05c30</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1391" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1391" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>OP-957</t>
+        </is>
+      </c>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1391" s="2" t="n">
+        <v>46077.44786005449</v>
+      </c>
+      <c r="K1391" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>372af3b5-9744-4aba-96d8-fb7215b04596</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>f8516c87-be83-4455-8d74-15fbca730b80</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1392" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1392" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>OP-456</t>
+        </is>
+      </c>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1392" s="2" t="n">
+        <v>46088.53119339088</v>
+      </c>
+      <c r="K1392" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>39841c20-c731-4a54-acff-2f968fdcbc96</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>ea5c9ae0-192e-4bad-8096-51f2b9a8ebc3</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1393" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1393" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>OP-731</t>
+        </is>
+      </c>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1393" s="2" t="n">
+        <v>46070.5728600606</v>
+      </c>
+      <c r="K1393" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2303165f-e451-40cc-90f1-b9e07bd1b5a0</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>784fa69c-0ef3-4ef4-977b-2be19f7ba08d</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1394" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1394" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>OP-526</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1394" s="2" t="n">
+        <v>46063.69786006435</v>
+      </c>
+      <c r="K1394" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>932c0fd9-2761-4f0b-8feb-7cef311582cf</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>6195dead-f130-41dd-a558-02f38456b2cc</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1395" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1395" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>OP-957</t>
+        </is>
+      </c>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1395" s="2" t="n">
+        <v>46069.57286006756</v>
+      </c>
+      <c r="K1395" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>e216c242-3d8e-4779-8d0b-674f2c01c78c</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>95cf1499-f773-433f-aa0f-c1e1d7a809af</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1396" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1396" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>OP-339</t>
+        </is>
+      </c>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1396" s="2" t="n">
+        <v>46079.40619340419</v>
+      </c>
+      <c r="K1396" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>dbb0e84e-eadc-4e4b-8a44-79e21678bc8c</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>9c6e90b1-dff2-4b78-ae67-cf32817d5df4</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1397" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1397" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>OP-895</t>
+        </is>
+      </c>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1397" s="2" t="n">
+        <v>46073.53119340763</v>
+      </c>
+      <c r="K1397" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>ea4b37f7-0b33-4287-905e-8080cd5cbf56</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>6c608919-9b21-4924-8ffa-05693147aed7</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1398" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1398" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>OP-295</t>
+        </is>
+      </c>
+      <c r="I1398" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1398" s="2" t="n">
+        <v>46087.57286007755</v>
+      </c>
+      <c r="K1398" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>7361d914-b294-4ea5-a6f6-d6e491e2537d</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>45ac5b49-4ae9-40ba-816a-20f768a2d408</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1399" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1399" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>OP-652</t>
+        </is>
+      </c>
+      <c r="I1399" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1399" s="2" t="n">
+        <v>46089.73952674748</v>
+      </c>
+      <c r="K1399" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>c5867c00-19ae-481d-9e49-88b6e980ef34</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>d66a44be-271b-4e19-b4fa-fb2b86a67062</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1400" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F1400" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>OP-226</t>
+        </is>
+      </c>
+      <c r="I1400" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1400" s="2" t="n">
+        <v>46068.57286008428</v>
+      </c>
+      <c r="K1400" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>019424ce-44dc-42f3-92e7-bb8f2dfec6b7</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>3e97200b-aff4-476f-9ae6-ad2ce4d611a1</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1401" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>OP-825</t>
+        </is>
+      </c>
+      <c r="I1401" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1401" s="2" t="n">
+        <v>46064.69786008786</v>
+      </c>
+      <c r="K1401" t="inlineStr">
+        <is>
+          <t>poor</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1401"/>
+  <dimension ref="A1:K1451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69382,7 +69382,7 @@
         </is>
       </c>
       <c r="J1352" s="2" t="n">
-        <v>46078.44785992507</v>
+        <v>46078.44785993056</v>
       </c>
       <c r="K1352" t="inlineStr">
         <is>
@@ -69433,7 +69433,7 @@
         </is>
       </c>
       <c r="J1353" s="2" t="n">
-        <v>46060.65619326274</v>
+        <v>46060.65619326389</v>
       </c>
       <c r="K1353" t="inlineStr">
         <is>
@@ -69484,7 +69484,7 @@
         </is>
       </c>
       <c r="J1354" s="2" t="n">
-        <v>46077.53119326616</v>
+        <v>46077.53119326389</v>
       </c>
       <c r="K1354" t="inlineStr">
         <is>
@@ -69535,7 +69535,7 @@
         </is>
       </c>
       <c r="J1355" s="2" t="n">
-        <v>46080.4895266032</v>
+        <v>46080.4895266088</v>
       </c>
       <c r="K1355" t="inlineStr">
         <is>
@@ -69586,7 +69586,7 @@
         </is>
       </c>
       <c r="J1356" s="2" t="n">
-        <v>46077.61452660627</v>
+        <v>46077.6145266088</v>
       </c>
       <c r="K1356" t="inlineStr">
         <is>
@@ -69637,7 +69637,7 @@
         </is>
       </c>
       <c r="J1357" s="2" t="n">
-        <v>46073.57285994302</v>
+        <v>46073.57285994213</v>
       </c>
       <c r="K1357" t="inlineStr">
         <is>
@@ -69688,7 +69688,7 @@
         </is>
       </c>
       <c r="J1358" s="2" t="n">
-        <v>46085.73952661296</v>
+        <v>46085.7395266088</v>
       </c>
       <c r="K1358" t="inlineStr">
         <is>
@@ -69739,7 +69739,7 @@
         </is>
       </c>
       <c r="J1359" s="2" t="n">
-        <v>46075.69785994949</v>
+        <v>46075.6978599537</v>
       </c>
       <c r="K1359" t="inlineStr">
         <is>
@@ -69790,7 +69790,7 @@
         </is>
       </c>
       <c r="J1360" s="2" t="n">
-        <v>46086.5728599526</v>
+        <v>46086.5728599537</v>
       </c>
       <c r="K1360" t="inlineStr">
         <is>
@@ -69841,7 +69841,7 @@
         </is>
       </c>
       <c r="J1361" s="2" t="n">
-        <v>46072.6145266225</v>
+        <v>46072.61452662037</v>
       </c>
       <c r="K1361" t="inlineStr">
         <is>
@@ -69892,7 +69892,7 @@
         </is>
       </c>
       <c r="J1362" s="2" t="n">
-        <v>46089.61452662585</v>
+        <v>46089.61452662037</v>
       </c>
       <c r="K1362" t="inlineStr">
         <is>
@@ -69943,7 +69943,7 @@
         </is>
       </c>
       <c r="J1363" s="2" t="n">
-        <v>46080.53119329573</v>
+        <v>46080.53119329861</v>
       </c>
       <c r="K1363" t="inlineStr">
         <is>
@@ -69994,7 +69994,7 @@
         </is>
       </c>
       <c r="J1364" s="2" t="n">
-        <v>46075.36452663234</v>
+        <v>46075.36452663194</v>
       </c>
       <c r="K1364" t="inlineStr">
         <is>
@@ -70045,7 +70045,7 @@
         </is>
       </c>
       <c r="J1365" s="2" t="n">
-        <v>46065.4895266364</v>
+        <v>46065.48952663194</v>
       </c>
       <c r="K1365" t="inlineStr">
         <is>
@@ -70096,7 +70096,7 @@
         </is>
       </c>
       <c r="J1366" s="2" t="n">
-        <v>46062.44785997286</v>
+        <v>46062.44785997686</v>
       </c>
       <c r="K1366" t="inlineStr">
         <is>
@@ -70147,7 +70147,7 @@
         </is>
       </c>
       <c r="J1367" s="2" t="n">
-        <v>46067.48952664281</v>
+        <v>46067.48952664352</v>
       </c>
       <c r="K1367" t="inlineStr">
         <is>
@@ -70198,7 +70198,7 @@
         </is>
       </c>
       <c r="J1368" s="2" t="n">
-        <v>46065.57285997931</v>
+        <v>46065.57285997686</v>
       </c>
       <c r="K1368" t="inlineStr">
         <is>
@@ -70249,7 +70249,7 @@
         </is>
       </c>
       <c r="J1369" s="2" t="n">
-        <v>46085.65619331602</v>
+        <v>46085.65619332176</v>
       </c>
       <c r="K1369" t="inlineStr">
         <is>
@@ -70300,7 +70300,7 @@
         </is>
       </c>
       <c r="J1370" s="2" t="n">
-        <v>46081.69785998595</v>
+        <v>46081.69785998842</v>
       </c>
       <c r="K1370" t="inlineStr">
         <is>
@@ -70351,7 +70351,7 @@
         </is>
       </c>
       <c r="J1371" s="2" t="n">
-        <v>46060.48952665571</v>
+        <v>46060.4895266551</v>
       </c>
       <c r="K1371" t="inlineStr">
         <is>
@@ -70402,7 +70402,7 @@
         </is>
       </c>
       <c r="J1372" s="2" t="n">
-        <v>46082.48952665917</v>
+        <v>46082.4895266551</v>
       </c>
       <c r="K1372" t="inlineStr">
         <is>
@@ -70453,7 +70453,7 @@
         </is>
       </c>
       <c r="J1373" s="2" t="n">
-        <v>46069.53119332893</v>
+        <v>46069.53119333334</v>
       </c>
       <c r="K1373" t="inlineStr">
         <is>
@@ -70504,7 +70504,7 @@
         </is>
       </c>
       <c r="J1374" s="2" t="n">
-        <v>46066.4895266655</v>
+        <v>46066.48952666666</v>
       </c>
       <c r="K1374" t="inlineStr">
         <is>
@@ -70555,7 +70555,7 @@
         </is>
       </c>
       <c r="J1375" s="2" t="n">
-        <v>46060.73952666851</v>
+        <v>46060.73952666666</v>
       </c>
       <c r="K1375" t="inlineStr">
         <is>
@@ -70606,7 +70606,7 @@
         </is>
       </c>
       <c r="J1376" s="2" t="n">
-        <v>46072.36452667192</v>
+        <v>46072.36452666666</v>
       </c>
       <c r="K1376" t="inlineStr">
         <is>
@@ -70657,7 +70657,7 @@
         </is>
       </c>
       <c r="J1377" s="2" t="n">
-        <v>46077.61452667529</v>
+        <v>46077.61452667824</v>
       </c>
       <c r="K1377" t="inlineStr">
         <is>
@@ -70708,7 +70708,7 @@
         </is>
       </c>
       <c r="J1378" s="2" t="n">
-        <v>46064.53119334519</v>
+        <v>46064.5311933449</v>
       </c>
       <c r="K1378" t="inlineStr">
         <is>
@@ -70759,7 +70759,7 @@
         </is>
       </c>
       <c r="J1379" s="2" t="n">
-        <v>46080.36452668263</v>
+        <v>46080.36452667824</v>
       </c>
       <c r="K1379" t="inlineStr">
         <is>
@@ -70810,7 +70810,7 @@
         </is>
       </c>
       <c r="J1380" s="2" t="n">
-        <v>46060.65619335238</v>
+        <v>46060.65619335648</v>
       </c>
       <c r="K1380" t="inlineStr">
         <is>
@@ -70861,7 +70861,7 @@
         </is>
       </c>
       <c r="J1381" s="2" t="n">
-        <v>46085.48952668892</v>
+        <v>46085.48952668982</v>
       </c>
       <c r="K1381" t="inlineStr">
         <is>
@@ -70912,7 +70912,7 @@
         </is>
       </c>
       <c r="J1382" s="2" t="n">
-        <v>46072.44786002535</v>
+        <v>46072.44786002315</v>
       </c>
       <c r="K1382" t="inlineStr">
         <is>
@@ -70963,7 +70963,7 @@
         </is>
       </c>
       <c r="J1383" s="2" t="n">
-        <v>46087.44786002857</v>
+        <v>46087.44786002315</v>
       </c>
       <c r="K1383" t="inlineStr">
         <is>
@@ -71014,7 +71014,7 @@
         </is>
       </c>
       <c r="J1384" s="2" t="n">
-        <v>46089.6978600318</v>
+        <v>46089.69786003472</v>
       </c>
       <c r="K1384" t="inlineStr">
         <is>
@@ -71065,7 +71065,7 @@
         </is>
       </c>
       <c r="J1385" s="2" t="n">
-        <v>46079.44786003488</v>
+        <v>46079.44786003472</v>
       </c>
       <c r="K1385" t="inlineStr">
         <is>
@@ -71116,7 +71116,7 @@
         </is>
       </c>
       <c r="J1386" s="2" t="n">
-        <v>46086.65619337198</v>
+        <v>46086.65619336806</v>
       </c>
       <c r="K1386" t="inlineStr">
         <is>
@@ -71167,7 +71167,7 @@
         </is>
       </c>
       <c r="J1387" s="2" t="n">
-        <v>46078.48952670841</v>
+        <v>46078.48952671296</v>
       </c>
       <c r="K1387" t="inlineStr">
         <is>
@@ -71218,7 +71218,7 @@
         </is>
       </c>
       <c r="J1388" s="2" t="n">
-        <v>46078.73952671159</v>
+        <v>46078.73952671296</v>
       </c>
       <c r="K1388" t="inlineStr">
         <is>
@@ -71269,7 +71269,7 @@
         </is>
       </c>
       <c r="J1389" s="2" t="n">
-        <v>46075.57286004804</v>
+        <v>46075.5728600463</v>
       </c>
       <c r="K1389" t="inlineStr">
         <is>
@@ -71320,7 +71320,7 @@
         </is>
       </c>
       <c r="J1390" s="2" t="n">
-        <v>46076.57286005131</v>
+        <v>46076.5728600463</v>
       </c>
       <c r="K1390" t="inlineStr">
         <is>
@@ -71371,7 +71371,7 @@
         </is>
       </c>
       <c r="J1391" s="2" t="n">
-        <v>46077.44786005449</v>
+        <v>46077.44786005787</v>
       </c>
       <c r="K1391" t="inlineStr">
         <is>
@@ -71422,7 +71422,7 @@
         </is>
       </c>
       <c r="J1392" s="2" t="n">
-        <v>46088.53119339088</v>
+        <v>46088.5311933912</v>
       </c>
       <c r="K1392" t="inlineStr">
         <is>
@@ -71473,7 +71473,7 @@
         </is>
       </c>
       <c r="J1393" s="2" t="n">
-        <v>46070.5728600606</v>
+        <v>46070.57286005787</v>
       </c>
       <c r="K1393" t="inlineStr">
         <is>
@@ -71524,7 +71524,7 @@
         </is>
       </c>
       <c r="J1394" s="2" t="n">
-        <v>46063.69786006435</v>
+        <v>46063.69786006944</v>
       </c>
       <c r="K1394" t="inlineStr">
         <is>
@@ -71575,7 +71575,7 @@
         </is>
       </c>
       <c r="J1395" s="2" t="n">
-        <v>46069.57286006756</v>
+        <v>46069.57286006944</v>
       </c>
       <c r="K1395" t="inlineStr">
         <is>
@@ -71626,7 +71626,7 @@
         </is>
       </c>
       <c r="J1396" s="2" t="n">
-        <v>46079.40619340419</v>
+        <v>46079.40619340278</v>
       </c>
       <c r="K1396" t="inlineStr">
         <is>
@@ -71677,7 +71677,7 @@
         </is>
       </c>
       <c r="J1397" s="2" t="n">
-        <v>46073.53119340763</v>
+        <v>46073.53119340278</v>
       </c>
       <c r="K1397" t="inlineStr">
         <is>
@@ -71728,7 +71728,7 @@
         </is>
       </c>
       <c r="J1398" s="2" t="n">
-        <v>46087.57286007755</v>
+        <v>46087.57286008102</v>
       </c>
       <c r="K1398" t="inlineStr">
         <is>
@@ -71779,7 +71779,7 @@
         </is>
       </c>
       <c r="J1399" s="2" t="n">
-        <v>46089.73952674748</v>
+        <v>46089.73952674768</v>
       </c>
       <c r="K1399" t="inlineStr">
         <is>
@@ -71830,7 +71830,7 @@
         </is>
       </c>
       <c r="J1400" s="2" t="n">
-        <v>46068.57286008428</v>
+        <v>46068.57286008102</v>
       </c>
       <c r="K1400" t="inlineStr">
         <is>
@@ -71881,9 +71881,2559 @@
         </is>
       </c>
       <c r="J1401" s="2" t="n">
-        <v>46064.69786008786</v>
+        <v>46064.69786009259</v>
       </c>
       <c r="K1401" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>4fb9b3aa-3558-44a7-bfd1-db28dbdb82ee</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>315233ab-de09-4dae-98c5-60b6571801ec</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1402" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1402" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>OP-818</t>
+        </is>
+      </c>
+      <c r="I1402" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1402" s="2" t="n">
+        <v>46076.44120367298</v>
+      </c>
+      <c r="K1402" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>a3683129-7283-4e2f-badd-e112e4e3bee0</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>eab062a8-1ce4-4835-8e45-830bbc1b4f20</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1403" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1403" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>OP-374</t>
+        </is>
+      </c>
+      <c r="I1403" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1403" s="2" t="n">
+        <v>46073.56620367727</v>
+      </c>
+      <c r="K1403" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>462578a0-c2a5-4907-b505-f5e96f363a7a</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>c8cddf37-cf9c-4eb8-938d-5a84537c9fb2</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1404" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F1404" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>OP-731</t>
+        </is>
+      </c>
+      <c r="I1404" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1404" s="2" t="n">
+        <v>46086.73287034714</v>
+      </c>
+      <c r="K1404" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>32e3b619-5802-4cd1-b7a2-107e3bfa2f6e</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>9fe9a17c-a3b0-4753-9222-2375b34f844d</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1405" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1405" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>OP-706</t>
+        </is>
+      </c>
+      <c r="I1405" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1405" s="2" t="n">
+        <v>46086.52453701737</v>
+      </c>
+      <c r="K1405" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>bbabe213-83ef-4767-bed3-500a6db66633</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>bc5b5ab3-fd7b-4b80-b7dd-26a1b1b369f5</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1406" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F1406" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>OP-854</t>
+        </is>
+      </c>
+      <c r="I1406" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1406" s="2" t="n">
+        <v>46073.44120368717</v>
+      </c>
+      <c r="K1406" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>4f721db0-51f8-47a7-a39a-2dad34574a15</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>380dc11e-72e7-4f87-a035-6fc7e73fcf74</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1407" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1407" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>OP-450</t>
+        </is>
+      </c>
+      <c r="I1407" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1407" s="2" t="n">
+        <v>46089.64953702364</v>
+      </c>
+      <c r="K1407" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>59d7e756-7d72-4141-b000-ae1674d8b910</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>7d49ce68-5ef4-4986-a6af-96d91692b951</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1408" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F1408" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>OP-175</t>
+        </is>
+      </c>
+      <c r="I1408" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1408" s="2" t="n">
+        <v>46088.69120369371</v>
+      </c>
+      <c r="K1408" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>d089a02b-3b1d-40ec-9bb7-50f1385f8acf</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>c15ff324-436b-4f2d-8f6b-5f3f9986a0e7</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1409" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1409" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>OP-641</t>
+        </is>
+      </c>
+      <c r="I1409" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1409" s="2" t="n">
+        <v>46073.48287036354</v>
+      </c>
+      <c r="K1409" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>aa6cddd2-e9c4-4a1a-b37a-7420c66e2ca7</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>f49e7147-f99e-41ec-b4fb-f831915d9808</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1410" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1410" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>OP-449</t>
+        </is>
+      </c>
+      <c r="I1410" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1410" s="2" t="n">
+        <v>46073.48287036682</v>
+      </c>
+      <c r="K1410" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>89140e8e-8777-4835-9de6-91cc62ffdfb0</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>92ca576c-ffe6-4381-b759-c6121480811f</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1411" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1411" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>OP-975</t>
+        </is>
+      </c>
+      <c r="I1411" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1411" s="2" t="n">
+        <v>46087.3995370366</v>
+      </c>
+      <c r="K1411" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>05a31adb-c752-469e-8082-5b6148961c5b</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>1fd0156d-2bea-4bbc-808c-1182cb60a55a</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1412" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1412" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>OP-860</t>
+        </is>
+      </c>
+      <c r="I1412" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1412" s="2" t="n">
+        <v>46075.5662037069</v>
+      </c>
+      <c r="K1412" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>4e022555-9b15-4e5d-9309-7ba2cd5800a9</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>c632a8d6-3b22-4dce-b0b5-7306627f5148</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1413" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1413" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>OP-913</t>
+        </is>
+      </c>
+      <c r="I1413" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1413" s="2" t="n">
+        <v>46083.44120371003</v>
+      </c>
+      <c r="K1413" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>23f04c09-049c-4bca-8235-53e22fe8ddfa</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>c0dd2dfd-3ea2-4b9a-9783-bf0889f8bff1</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1414" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1414" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>OP-258</t>
+        </is>
+      </c>
+      <c r="I1414" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1414" s="2" t="n">
+        <v>46073.73287037977</v>
+      </c>
+      <c r="K1414" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>a52ae35a-5084-4a47-a254-0d8052b26e21</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>b03112af-9a3b-459f-b875-2ecc7d9fba8c</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1415" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1415" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>OP-422</t>
+        </is>
+      </c>
+      <c r="I1415" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1415" s="2" t="n">
+        <v>46085.60787038316</v>
+      </c>
+      <c r="K1415" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>7032843c-4c22-4948-9614-8a4855791c2b</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>8dcd002e-a0e7-4018-b0de-e4c4fd212841</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1416" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F1416" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>OP-515</t>
+        </is>
+      </c>
+      <c r="I1416" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1416" s="2" t="n">
+        <v>46074.44120371975</v>
+      </c>
+      <c r="K1416" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>dd602eec-e604-40e7-8cd2-c79eac4cf8df</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>bffd4a96-12ad-4f6b-8b6a-0ca105fed16a</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1417" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1417" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>OP-794</t>
+        </is>
+      </c>
+      <c r="I1417" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1417" s="2" t="n">
+        <v>46068.39953705644</v>
+      </c>
+      <c r="K1417" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>7bc9a675-7284-44f7-bb8a-197862b18e2c</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>3af35cbb-553a-4847-b55a-cd2904c63077</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1418" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1418" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>OP-843</t>
+        </is>
+      </c>
+      <c r="I1418" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1418" s="2" t="n">
+        <v>46083.6495370595</v>
+      </c>
+      <c r="K1418" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>87ea85df-70ee-423c-ab03-827ccc745b9d</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>15022968-461a-44bb-b54b-c299deaf6bfc</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1419" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1419" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>OP-164</t>
+        </is>
+      </c>
+      <c r="I1419" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1419" s="2" t="n">
+        <v>46060.77453706272</v>
+      </c>
+      <c r="K1419" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>d9cb563c-8842-4099-9736-88b80e2c5680</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>09bedb2b-2ea0-4eb3-af78-bbc3c28ade61</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1420" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F1420" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>OP-822</t>
+        </is>
+      </c>
+      <c r="I1420" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1420" s="2" t="n">
+        <v>46067.64953706586</v>
+      </c>
+      <c r="K1420" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>d9e30c94-0639-4da1-98c2-f1f130cad66d</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>11dffe95-811d-4e2e-9fd8-be9946cb68f8</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1421" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1421" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>OP-816</t>
+        </is>
+      </c>
+      <c r="I1421" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1421" s="2" t="n">
+        <v>46063.60787040242</v>
+      </c>
+      <c r="K1421" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>860554e3-a2d0-4fe6-b5a5-d61b93e4a49c</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>234b7614-2114-4453-9ace-dbc32b4cb825</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1422" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F1422" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>OP-828</t>
+        </is>
+      </c>
+      <c r="I1422" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1422" s="2" t="n">
+        <v>46071.56620373875</v>
+      </c>
+      <c r="K1422" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>f0dea8b5-b5f4-406c-a47f-8831e46d86c5</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>fdb0626c-e24c-4cf5-bdc1-a8d380425e08</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1423" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1423" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>OP-233</t>
+        </is>
+      </c>
+      <c r="I1423" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1423" s="2" t="n">
+        <v>46073.73287040873</v>
+      </c>
+      <c r="K1423" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>df070e85-4cf9-4452-b3c4-c381df111cbc</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>f2ed00f5-36cb-478f-99be-63cead244709</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1424" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1424" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>OP-372</t>
+        </is>
+      </c>
+      <c r="I1424" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1424" s="2" t="n">
+        <v>46063.73287041192</v>
+      </c>
+      <c r="K1424" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>bf87b56f-49e5-49d6-972f-3611d5b8434e</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>d78dba12-9afe-48e4-9c3f-55269b2dc908</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1425" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1425" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>OP-997</t>
+        </is>
+      </c>
+      <c r="I1425" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1425" s="2" t="n">
+        <v>46073.39953708181</v>
+      </c>
+      <c r="K1425" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>91d7bbdc-a225-41ae-8836-ac68c348f322</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>edc89045-64eb-47e4-b5e3-41dbe705b88d</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1426" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F1426" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>OP-934</t>
+        </is>
+      </c>
+      <c r="I1426" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1426" s="2" t="n">
+        <v>46080.48287041856</v>
+      </c>
+      <c r="K1426" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>7d4de103-e2c8-4f01-a53a-380d5e690c1a</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>13614c8b-a55f-44db-9bdb-f1ff61e76013</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1427" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1427" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>OP-417</t>
+        </is>
+      </c>
+      <c r="I1427" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1427" s="2" t="n">
+        <v>46079.39953708846</v>
+      </c>
+      <c r="K1427" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>bcbd02ee-f11f-4e69-b814-04df2f4a9165</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>b882e698-7840-4ca0-b55d-395ac2b45bf6</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1428" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1428" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>OP-752</t>
+        </is>
+      </c>
+      <c r="I1428" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1428" s="2" t="n">
+        <v>46074.73287042485</v>
+      </c>
+      <c r="K1428" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>e4c6c136-af45-41cc-986d-1f2148cce279</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>7d9c9c31-fd3c-479d-8024-cc236370d0e0</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1429" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1429" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>OP-554</t>
+        </is>
+      </c>
+      <c r="I1429" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1429" s="2" t="n">
+        <v>46084.44120376134</v>
+      </c>
+      <c r="K1429" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>d75003a0-69bd-45a3-82ab-a090608fff4c</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>e8e78f87-cb95-4c3e-bab2-72eee3f5b485</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1430" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F1430" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>OP-158</t>
+        </is>
+      </c>
+      <c r="I1430" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1430" s="2" t="n">
+        <v>46072.77453709795</v>
+      </c>
+      <c r="K1430" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>57a7bd90-e4dc-43ee-a10d-cc02cea01ae1</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>0e415e56-3c59-4ba8-8785-cdedc6768dd6</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1431" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>OP-642</t>
+        </is>
+      </c>
+      <c r="I1431" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1431" s="2" t="n">
+        <v>46076.60787043439</v>
+      </c>
+      <c r="K1431" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>a36d41ad-2cbc-4ded-9608-8687d12c64e7</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>51882319-ae87-45eb-8db4-e713ebbee69d</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1432" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>OP-548</t>
+        </is>
+      </c>
+      <c r="I1432" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1432" s="2" t="n">
+        <v>46083.7328704375</v>
+      </c>
+      <c r="K1432" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>428516ec-ec81-4d7b-b3c5-a5c6f81fa79a</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>a227ebea-f21b-4d04-a2b7-4ab954d1d161</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1433" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>OP-603</t>
+        </is>
+      </c>
+      <c r="I1433" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1433" s="2" t="n">
+        <v>46062.73287044065</v>
+      </c>
+      <c r="K1433" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>7e770080-f67a-4e8c-b8bf-685f71ecf512</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>2ea7a0ee-0b88-45b1-8f6e-10bf837d4d01</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1434" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>OP-619</t>
+        </is>
+      </c>
+      <c r="I1434" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1434" s="2" t="n">
+        <v>46073.48287044399</v>
+      </c>
+      <c r="K1434" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>7427581e-a733-4da0-b33e-301e9b0edf8a</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>47dacfa0-4728-457b-990a-d2ef6b408eff</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1435" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>OP-789</t>
+        </is>
+      </c>
+      <c r="I1435" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1435" s="2" t="n">
+        <v>46085.77453711396</v>
+      </c>
+      <c r="K1435" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>07fe8118-1e03-471f-b470-e11555c8a459</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>f53b4355-9e88-4cfb-a4ab-73c5cfadee2a</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1436" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>OP-469</t>
+        </is>
+      </c>
+      <c r="I1436" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1436" s="2" t="n">
+        <v>46082.77453711702</v>
+      </c>
+      <c r="K1436" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>643e1712-df05-475b-b860-c13871764ad1</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>cfcc4d79-0855-42f9-a818-e9e9b139df07</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1437" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>OP-155</t>
+        </is>
+      </c>
+      <c r="I1437" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1437" s="2" t="n">
+        <v>46061.56620378693</v>
+      </c>
+      <c r="K1437" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>0f830727-8538-4d6a-a956-f4be65af5c46</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>83c896ed-1bc6-43fc-953b-c2ed8653c403</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1438" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>OP-513</t>
+        </is>
+      </c>
+      <c r="I1438" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1438" s="2" t="n">
+        <v>46082.44120378997</v>
+      </c>
+      <c r="K1438" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>5917c216-22aa-40ef-b590-c7635b1a3cb5</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>fe6eaa60-4df6-4912-8deb-c8d13c6186d7</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1439" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>OP-549</t>
+        </is>
+      </c>
+      <c r="I1439" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1439" s="2" t="n">
+        <v>46074.44120379307</v>
+      </c>
+      <c r="K1439" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>69233621-8438-4718-9c2d-900a81c23174</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>99751164-e488-40f3-9872-54ccdf062bef</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1440" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1440" t="inlineStr">
+        <is>
+          <t>OP-606</t>
+        </is>
+      </c>
+      <c r="I1440" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1440" s="2" t="n">
+        <v>46068.64953712944</v>
+      </c>
+      <c r="K1440" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>a06c2afd-f396-46d4-8f18-7a1d751e0df2</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>a9103f53-c513-45e3-a226-ab4e3265da6d</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1441" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>OP-779</t>
+        </is>
+      </c>
+      <c r="I1441" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1441" s="2" t="n">
+        <v>46082.64953713272</v>
+      </c>
+      <c r="K1441" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>952708b6-a7c5-4abe-b3b4-5db30ea3f1c7</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>41fab8da-6513-4c74-8f8b-d27c5ef456d5</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1442" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>OP-628</t>
+        </is>
+      </c>
+      <c r="I1442" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1442" s="2" t="n">
+        <v>46068.39953713587</v>
+      </c>
+      <c r="K1442" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>6e93b842-b274-48de-a07a-262622fd8433</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>de57da4b-992c-4fb2-a357-ba21928762a4</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1443" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1443" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>OP-968</t>
+        </is>
+      </c>
+      <c r="I1443" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1443" s="2" t="n">
+        <v>46078.52453713908</v>
+      </c>
+      <c r="K1443" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>1b236e8e-f08c-4a20-9d16-f45ac372c077</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>cdf7124e-bcf9-4481-818e-c51d0ee94887</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1444" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1444" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>OP-497</t>
+        </is>
+      </c>
+      <c r="I1444" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1444" s="2" t="n">
+        <v>46080.69120380878</v>
+      </c>
+      <c r="K1444" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>952cbf13-99a2-4e28-8cf3-e1aaf998b00b</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>ffa5af68-410a-4ab4-8502-d401c1df3fee</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1445" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1445" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>OP-949</t>
+        </is>
+      </c>
+      <c r="I1445" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1445" s="2" t="n">
+        <v>46081.39953714551</v>
+      </c>
+      <c r="K1445" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>54d5f284-19ff-4ccd-8509-fe7666622cde</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>30f111ce-8dff-4556-b7b9-13a8769da80b</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1446" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F1446" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>OP-658</t>
+        </is>
+      </c>
+      <c r="I1446" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1446" s="2" t="n">
+        <v>46062.60787048196</v>
+      </c>
+      <c r="K1446" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>8bb56c0d-9d85-4a0e-8c20-80caf8a08ff6</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>acb5eb49-7b5e-4cae-a741-c64cc062efb1</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1447" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>OP-192</t>
+        </is>
+      </c>
+      <c r="I1447" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1447" s="2" t="n">
+        <v>46086.77453715169</v>
+      </c>
+      <c r="K1447" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>b8f2b7dd-d648-4b58-b2c4-b8848853625d</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>e2d13110-c4bb-41fb-bcac-078759600775</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1448" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1448" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>OP-643</t>
+        </is>
+      </c>
+      <c r="I1448" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1448" s="2" t="n">
+        <v>46066.52453715487</v>
+      </c>
+      <c r="K1448" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>feeaa341-7c33-46d3-90e3-082d6970d1c9</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>0ce82719-aaeb-49e8-89b3-dc1e39078a56</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1449" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1449" t="inlineStr">
+        <is>
+          <t>OP-239</t>
+        </is>
+      </c>
+      <c r="I1449" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1449" s="2" t="n">
+        <v>46083.60787049133</v>
+      </c>
+      <c r="K1449" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>b4e6da8e-1ca9-41e1-a770-7bafa38061ba</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>1976c0dc-3963-4c80-9ae1-f1e0f5f188c8</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1450" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1450" t="inlineStr">
+        <is>
+          <t>OP-548</t>
+        </is>
+      </c>
+      <c r="I1450" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1450" s="2" t="n">
+        <v>46062.69120382769</v>
+      </c>
+      <c r="K1450" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>4ba720ef-0fb2-42ef-a1f8-0e4d634e2bfb</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>ba12dd4b-3f38-404f-9d51-6febaa1de92f</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1451" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1451" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1451" t="inlineStr">
+        <is>
+          <t>OP-897</t>
+        </is>
+      </c>
+      <c r="I1451" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1451" s="2" t="n">
+        <v>46068.52453716406</v>
+      </c>
+      <c r="K1451" t="inlineStr">
         <is>
           <t>poor</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1451"/>
+  <dimension ref="A1:K1501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71932,7 +71932,7 @@
         </is>
       </c>
       <c r="J1402" s="2" t="n">
-        <v>46076.44120367298</v>
+        <v>46076.44120366898</v>
       </c>
       <c r="K1402" t="inlineStr">
         <is>
@@ -71983,7 +71983,7 @@
         </is>
       </c>
       <c r="J1403" s="2" t="n">
-        <v>46073.56620367727</v>
+        <v>46073.56620368056</v>
       </c>
       <c r="K1403" t="inlineStr">
         <is>
@@ -72034,7 +72034,7 @@
         </is>
       </c>
       <c r="J1404" s="2" t="n">
-        <v>46086.73287034714</v>
+        <v>46086.73287034722</v>
       </c>
       <c r="K1404" t="inlineStr">
         <is>
@@ -72085,7 +72085,7 @@
         </is>
       </c>
       <c r="J1405" s="2" t="n">
-        <v>46086.52453701737</v>
+        <v>46086.52453701389</v>
       </c>
       <c r="K1405" t="inlineStr">
         <is>
@@ -72136,7 +72136,7 @@
         </is>
       </c>
       <c r="J1406" s="2" t="n">
-        <v>46073.44120368717</v>
+        <v>46073.44120369213</v>
       </c>
       <c r="K1406" t="inlineStr">
         <is>
@@ -72187,7 +72187,7 @@
         </is>
       </c>
       <c r="J1407" s="2" t="n">
-        <v>46089.64953702364</v>
+        <v>46089.64953702546</v>
       </c>
       <c r="K1407" t="inlineStr">
         <is>
@@ -72238,7 +72238,7 @@
         </is>
       </c>
       <c r="J1408" s="2" t="n">
-        <v>46088.69120369371</v>
+        <v>46088.69120369213</v>
       </c>
       <c r="K1408" t="inlineStr">
         <is>
@@ -72289,7 +72289,7 @@
         </is>
       </c>
       <c r="J1409" s="2" t="n">
-        <v>46073.48287036354</v>
+        <v>46073.4828703588</v>
       </c>
       <c r="K1409" t="inlineStr">
         <is>
@@ -72340,7 +72340,7 @@
         </is>
       </c>
       <c r="J1410" s="2" t="n">
-        <v>46073.48287036682</v>
+        <v>46073.48287037037</v>
       </c>
       <c r="K1410" t="inlineStr">
         <is>
@@ -72391,7 +72391,7 @@
         </is>
       </c>
       <c r="J1411" s="2" t="n">
-        <v>46087.3995370366</v>
+        <v>46087.39953703704</v>
       </c>
       <c r="K1411" t="inlineStr">
         <is>
@@ -72442,7 +72442,7 @@
         </is>
       </c>
       <c r="J1412" s="2" t="n">
-        <v>46075.5662037069</v>
+        <v>46075.5662037037</v>
       </c>
       <c r="K1412" t="inlineStr">
         <is>
@@ -72493,7 +72493,7 @@
         </is>
       </c>
       <c r="J1413" s="2" t="n">
-        <v>46083.44120371003</v>
+        <v>46083.44120371528</v>
       </c>
       <c r="K1413" t="inlineStr">
         <is>
@@ -72544,7 +72544,7 @@
         </is>
       </c>
       <c r="J1414" s="2" t="n">
-        <v>46073.73287037977</v>
+        <v>46073.73287038194</v>
       </c>
       <c r="K1414" t="inlineStr">
         <is>
@@ -72595,7 +72595,7 @@
         </is>
       </c>
       <c r="J1415" s="2" t="n">
-        <v>46085.60787038316</v>
+        <v>46085.60787038194</v>
       </c>
       <c r="K1415" t="inlineStr">
         <is>
@@ -72646,7 +72646,7 @@
         </is>
       </c>
       <c r="J1416" s="2" t="n">
-        <v>46074.44120371975</v>
+        <v>46074.44120371528</v>
       </c>
       <c r="K1416" t="inlineStr">
         <is>
@@ -72697,7 +72697,7 @@
         </is>
       </c>
       <c r="J1417" s="2" t="n">
-        <v>46068.39953705644</v>
+        <v>46068.39953706018</v>
       </c>
       <c r="K1417" t="inlineStr">
         <is>
@@ -72748,7 +72748,7 @@
         </is>
       </c>
       <c r="J1418" s="2" t="n">
-        <v>46083.6495370595</v>
+        <v>46083.64953706018</v>
       </c>
       <c r="K1418" t="inlineStr">
         <is>
@@ -72799,7 +72799,7 @@
         </is>
       </c>
       <c r="J1419" s="2" t="n">
-        <v>46060.77453706272</v>
+        <v>46060.77453706018</v>
       </c>
       <c r="K1419" t="inlineStr">
         <is>
@@ -72850,7 +72850,7 @@
         </is>
       </c>
       <c r="J1420" s="2" t="n">
-        <v>46067.64953706586</v>
+        <v>46067.64953706018</v>
       </c>
       <c r="K1420" t="inlineStr">
         <is>
@@ -72901,7 +72901,7 @@
         </is>
       </c>
       <c r="J1421" s="2" t="n">
-        <v>46063.60787040242</v>
+        <v>46063.6078704051</v>
       </c>
       <c r="K1421" t="inlineStr">
         <is>
@@ -72952,7 +72952,7 @@
         </is>
       </c>
       <c r="J1422" s="2" t="n">
-        <v>46071.56620373875</v>
+        <v>46071.56620373842</v>
       </c>
       <c r="K1422" t="inlineStr">
         <is>
@@ -73003,7 +73003,7 @@
         </is>
       </c>
       <c r="J1423" s="2" t="n">
-        <v>46073.73287040873</v>
+        <v>46073.7328704051</v>
       </c>
       <c r="K1423" t="inlineStr">
         <is>
@@ -73054,7 +73054,7 @@
         </is>
       </c>
       <c r="J1424" s="2" t="n">
-        <v>46063.73287041192</v>
+        <v>46063.73287041666</v>
       </c>
       <c r="K1424" t="inlineStr">
         <is>
@@ -73105,7 +73105,7 @@
         </is>
       </c>
       <c r="J1425" s="2" t="n">
-        <v>46073.39953708181</v>
+        <v>46073.39953708334</v>
       </c>
       <c r="K1425" t="inlineStr">
         <is>
@@ -73156,7 +73156,7 @@
         </is>
       </c>
       <c r="J1426" s="2" t="n">
-        <v>46080.48287041856</v>
+        <v>46080.48287041666</v>
       </c>
       <c r="K1426" t="inlineStr">
         <is>
@@ -73207,7 +73207,7 @@
         </is>
       </c>
       <c r="J1427" s="2" t="n">
-        <v>46079.39953708846</v>
+        <v>46079.39953708334</v>
       </c>
       <c r="K1427" t="inlineStr">
         <is>
@@ -73258,7 +73258,7 @@
         </is>
       </c>
       <c r="J1428" s="2" t="n">
-        <v>46074.73287042485</v>
+        <v>46074.73287042824</v>
       </c>
       <c r="K1428" t="inlineStr">
         <is>
@@ -73309,7 +73309,7 @@
         </is>
       </c>
       <c r="J1429" s="2" t="n">
-        <v>46084.44120376134</v>
+        <v>46084.44120376158</v>
       </c>
       <c r="K1429" t="inlineStr">
         <is>
@@ -73360,7 +73360,7 @@
         </is>
       </c>
       <c r="J1430" s="2" t="n">
-        <v>46072.77453709795</v>
+        <v>46072.77453709491</v>
       </c>
       <c r="K1430" t="inlineStr">
         <is>
@@ -73411,7 +73411,7 @@
         </is>
       </c>
       <c r="J1431" s="2" t="n">
-        <v>46076.60787043439</v>
+        <v>46076.60787043982</v>
       </c>
       <c r="K1431" t="inlineStr">
         <is>
@@ -73462,7 +73462,7 @@
         </is>
       </c>
       <c r="J1432" s="2" t="n">
-        <v>46083.7328704375</v>
+        <v>46083.73287043982</v>
       </c>
       <c r="K1432" t="inlineStr">
         <is>
@@ -73513,7 +73513,7 @@
         </is>
       </c>
       <c r="J1433" s="2" t="n">
-        <v>46062.73287044065</v>
+        <v>46062.73287043982</v>
       </c>
       <c r="K1433" t="inlineStr">
         <is>
@@ -73564,7 +73564,7 @@
         </is>
       </c>
       <c r="J1434" s="2" t="n">
-        <v>46073.48287044399</v>
+        <v>46073.48287043982</v>
       </c>
       <c r="K1434" t="inlineStr">
         <is>
@@ -73615,7 +73615,7 @@
         </is>
       </c>
       <c r="J1435" s="2" t="n">
-        <v>46085.77453711396</v>
+        <v>46085.77453711806</v>
       </c>
       <c r="K1435" t="inlineStr">
         <is>
@@ -73666,7 +73666,7 @@
         </is>
       </c>
       <c r="J1436" s="2" t="n">
-        <v>46082.77453711702</v>
+        <v>46082.77453711806</v>
       </c>
       <c r="K1436" t="inlineStr">
         <is>
@@ -73717,7 +73717,7 @@
         </is>
       </c>
       <c r="J1437" s="2" t="n">
-        <v>46061.56620378693</v>
+        <v>46061.56620378472</v>
       </c>
       <c r="K1437" t="inlineStr">
         <is>
@@ -73768,7 +73768,7 @@
         </is>
       </c>
       <c r="J1438" s="2" t="n">
-        <v>46082.44120378997</v>
+        <v>46082.44120378472</v>
       </c>
       <c r="K1438" t="inlineStr">
         <is>
@@ -73819,7 +73819,7 @@
         </is>
       </c>
       <c r="J1439" s="2" t="n">
-        <v>46074.44120379307</v>
+        <v>46074.4412037963</v>
       </c>
       <c r="K1439" t="inlineStr">
         <is>
@@ -73870,7 +73870,7 @@
         </is>
       </c>
       <c r="J1440" s="2" t="n">
-        <v>46068.64953712944</v>
+        <v>46068.64953712963</v>
       </c>
       <c r="K1440" t="inlineStr">
         <is>
@@ -73921,7 +73921,7 @@
         </is>
       </c>
       <c r="J1441" s="2" t="n">
-        <v>46082.64953713272</v>
+        <v>46082.64953712963</v>
       </c>
       <c r="K1441" t="inlineStr">
         <is>
@@ -73972,7 +73972,7 @@
         </is>
       </c>
       <c r="J1442" s="2" t="n">
-        <v>46068.39953713587</v>
+        <v>46068.3995371412</v>
       </c>
       <c r="K1442" t="inlineStr">
         <is>
@@ -74023,7 +74023,7 @@
         </is>
       </c>
       <c r="J1443" s="2" t="n">
-        <v>46078.52453713908</v>
+        <v>46078.5245371412</v>
       </c>
       <c r="K1443" t="inlineStr">
         <is>
@@ -74074,7 +74074,7 @@
         </is>
       </c>
       <c r="J1444" s="2" t="n">
-        <v>46080.69120380878</v>
+        <v>46080.69120380787</v>
       </c>
       <c r="K1444" t="inlineStr">
         <is>
@@ -74125,7 +74125,7 @@
         </is>
       </c>
       <c r="J1445" s="2" t="n">
-        <v>46081.39953714551</v>
+        <v>46081.3995371412</v>
       </c>
       <c r="K1445" t="inlineStr">
         <is>
@@ -74176,7 +74176,7 @@
         </is>
       </c>
       <c r="J1446" s="2" t="n">
-        <v>46062.60787048196</v>
+        <v>46062.60787048611</v>
       </c>
       <c r="K1446" t="inlineStr">
         <is>
@@ -74227,7 +74227,7 @@
         </is>
       </c>
       <c r="J1447" s="2" t="n">
-        <v>46086.77453715169</v>
+        <v>46086.77453715278</v>
       </c>
       <c r="K1447" t="inlineStr">
         <is>
@@ -74278,7 +74278,7 @@
         </is>
       </c>
       <c r="J1448" s="2" t="n">
-        <v>46066.52453715487</v>
+        <v>46066.52453715278</v>
       </c>
       <c r="K1448" t="inlineStr">
         <is>
@@ -74329,7 +74329,7 @@
         </is>
       </c>
       <c r="J1449" s="2" t="n">
-        <v>46083.60787049133</v>
+        <v>46083.60787048611</v>
       </c>
       <c r="K1449" t="inlineStr">
         <is>
@@ -74380,7 +74380,7 @@
         </is>
       </c>
       <c r="J1450" s="2" t="n">
-        <v>46062.69120382769</v>
+        <v>46062.69120383102</v>
       </c>
       <c r="K1450" t="inlineStr">
         <is>
@@ -74431,9 +74431,2559 @@
         </is>
       </c>
       <c r="J1451" s="2" t="n">
-        <v>46068.52453716406</v>
+        <v>46068.52453716435</v>
       </c>
       <c r="K1451" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>6c5945d6-461b-43e8-80f0-036e58603a6e</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>93a7dd36-c161-4c0b-899e-925c6aa3978d</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1452" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F1452" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1452" t="inlineStr">
+        <is>
+          <t>OP-535</t>
+        </is>
+      </c>
+      <c r="I1452" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1452" s="2" t="n">
+        <v>46079.73665133717</v>
+      </c>
+      <c r="K1452" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>f8ae6da3-a4fb-422d-a1f4-c069a751a228</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>6cef5e0a-eebb-4fc2-8f07-8993e3eaf566</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1453" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>OP-976</t>
+        </is>
+      </c>
+      <c r="I1453" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1453" s="2" t="n">
+        <v>46089.6116513415</v>
+      </c>
+      <c r="K1453" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>5e826f18-e725-4cf7-aed8-0ca140f55563</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>d0c08cf7-ce3d-4c80-ae6d-6e53d1efd26f</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1454" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1454" t="inlineStr">
+        <is>
+          <t>OP-567</t>
+        </is>
+      </c>
+      <c r="I1454" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1454" s="2" t="n">
+        <v>46082.81998467846</v>
+      </c>
+      <c r="K1454" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>d7049fa3-04c9-4f25-86ff-f95923bac30f</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>b7c770b6-07e3-4d03-8d78-48942e9e9f7a</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1455" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>OP-456</t>
+        </is>
+      </c>
+      <c r="I1455" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1455" s="2" t="n">
+        <v>46072.8199846816</v>
+      </c>
+      <c r="K1455" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>9abe9265-483a-4080-a803-86cc19e3a400</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>14e8f1c9-2069-4a38-970e-9d19d34d0c4e</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1456" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1456" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>OP-390</t>
+        </is>
+      </c>
+      <c r="I1456" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1456" s="2" t="n">
+        <v>46085.61165135141</v>
+      </c>
+      <c r="K1456" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>c9771ee1-14d7-4992-8802-4b59acc1bb9a</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>1d99a719-8e52-4c22-a377-cd029face776</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1457" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>OP-337</t>
+        </is>
+      </c>
+      <c r="I1457" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1457" s="2" t="n">
+        <v>46086.48665135512</v>
+      </c>
+      <c r="K1457" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>f8810bce-7a4b-4123-a25a-d64a538a4de3</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>51777f26-2035-4552-8cb1-630a4c2c0abc</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1458" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>OP-865</t>
+        </is>
+      </c>
+      <c r="I1458" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1458" s="2" t="n">
+        <v>46081.81998469165</v>
+      </c>
+      <c r="K1458" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>cbc2466a-d2f9-4b5d-8008-b1b8e4f3cc7f</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>707d7704-d0a9-44c7-9be2-ded67341a1fb</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1459" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>OP-308</t>
+        </is>
+      </c>
+      <c r="I1459" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1459" s="2" t="n">
+        <v>46070.77831802811</v>
+      </c>
+      <c r="K1459" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>6e41368c-c571-4b17-a14d-cf819fe9f7af</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>b5722f70-9126-4a23-8dea-e47e792fc988</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1460" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>OP-767</t>
+        </is>
+      </c>
+      <c r="I1460" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1460" s="2" t="n">
+        <v>46082.52831803136</v>
+      </c>
+      <c r="K1460" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>bd47a809-ecfb-41c1-9b93-825f9ef595a8</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>8e81bcf0-c5a6-4abf-b964-dd993289e4f2</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1461" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>OP-487</t>
+        </is>
+      </c>
+      <c r="I1461" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1461" s="2" t="n">
+        <v>46068.52831803489</v>
+      </c>
+      <c r="K1461" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>c040a478-860d-426a-91e2-d8ffc26ef7c1</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>b9721a7d-4ea7-4c5c-9064-41104bc17d22</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1462" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>OP-830</t>
+        </is>
+      </c>
+      <c r="I1462" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1462" s="2" t="n">
+        <v>46069.52831803829</v>
+      </c>
+      <c r="K1462" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>d7495fbf-c170-485d-89ca-b973198fe9ab</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>4a84da00-71f7-46a1-9351-d2352b101a51</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1463" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>OP-856</t>
+        </is>
+      </c>
+      <c r="I1463" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1463" s="2" t="n">
+        <v>46066.65331804139</v>
+      </c>
+      <c r="K1463" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>4977dd0a-3597-43c0-bd73-e9b8e362ab38</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>06e26132-7517-437f-bbbf-d5ea907afb83</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1464" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>OP-385</t>
+        </is>
+      </c>
+      <c r="I1464" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1464" s="2" t="n">
+        <v>46072.44498471131</v>
+      </c>
+      <c r="K1464" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>247267cf-0054-4dfa-8c66-6e700a853df0</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>25abd816-b2a4-40a1-b8ae-c93b921d1530</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1465" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>OP-640</t>
+        </is>
+      </c>
+      <c r="I1465" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1465" s="2" t="n">
+        <v>46074.48665138102</v>
+      </c>
+      <c r="K1465" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>8cb0567a-4e4e-4833-a59f-637298f5d7c8</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>2c0cb1c6-f81a-4ab9-9e5d-e51688ca0855</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1466" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1466" t="inlineStr">
+        <is>
+          <t>OP-372</t>
+        </is>
+      </c>
+      <c r="I1466" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1466" s="2" t="n">
+        <v>46075.6116513841</v>
+      </c>
+      <c r="K1466" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>92faec9b-f987-4db9-8dfe-9f82db6e769e</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>a04b9c4f-2345-48ba-8ef9-e301a6e4c5d4</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1467" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>OP-290</t>
+        </is>
+      </c>
+      <c r="I1467" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1467" s="2" t="n">
+        <v>46073.52831805387</v>
+      </c>
+      <c r="K1467" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>88c3f6bf-8493-4683-a986-41e12641e1d2</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>35c28588-998e-470a-b667-a3b5d40b79bc</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1468" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1468" t="inlineStr">
+        <is>
+          <t>OP-532</t>
+        </is>
+      </c>
+      <c r="I1468" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1468" s="2" t="n">
+        <v>46074.77831805713</v>
+      </c>
+      <c r="K1468" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2167e9c4-f000-4273-b942-4405c6fef85b</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>7bc7f9f4-dd81-49da-8f21-edafc1e67248</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1469" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1469" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1469" t="inlineStr">
+        <is>
+          <t>OP-217</t>
+        </is>
+      </c>
+      <c r="I1469" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1469" s="2" t="n">
+        <v>46086.8199847268</v>
+      </c>
+      <c r="K1469" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>9e33e597-9ea2-44c8-815f-8c98ccd29fbe</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>3bcb3e2b-3fcf-475e-b9a3-7abe86678f59</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1470" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1470" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1470" t="inlineStr">
+        <is>
+          <t>OP-133</t>
+        </is>
+      </c>
+      <c r="I1470" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1470" s="2" t="n">
+        <v>46060.6116513965</v>
+      </c>
+      <c r="K1470" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>3b775618-4b2c-4877-ab5f-7788bf80b2eb</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>eeff5a70-0003-4a71-8fc1-ddeee2675712</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1471" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1471" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1471" t="inlineStr">
+        <is>
+          <t>OP-472</t>
+        </is>
+      </c>
+      <c r="I1471" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1471" s="2" t="n">
+        <v>46082.69498473309</v>
+      </c>
+      <c r="K1471" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>f911042f-3c32-4469-9267-590de39d2d22</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>e2f063a2-b65d-4b41-b0c7-fc6f17fce8d5</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1472" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1472" t="inlineStr">
+        <is>
+          <t>OP-477</t>
+        </is>
+      </c>
+      <c r="I1472" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1472" s="2" t="n">
+        <v>46062.5699847363</v>
+      </c>
+      <c r="K1472" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>973d782e-250f-4772-a9a8-84e125351065</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>64563d3d-0a1d-4eb5-8a3e-36f31c8da6cb</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1473" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1473" t="inlineStr">
+        <is>
+          <t>OP-908</t>
+        </is>
+      </c>
+      <c r="I1473" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1473" s="2" t="n">
+        <v>46075.48665140612</v>
+      </c>
+      <c r="K1473" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>97af2079-6554-4a41-8c40-c2cbae113d85</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>870d4b67-fe2d-45d5-8b63-450adbeb9182</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1474" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1474" t="inlineStr">
+        <is>
+          <t>OP-588</t>
+        </is>
+      </c>
+      <c r="I1474" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1474" s="2" t="n">
+        <v>46077.56998474265</v>
+      </c>
+      <c r="K1474" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>a49383ce-401d-4bcb-94ce-0d5f2cebdf7d</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>bbd79780-2130-4f69-8370-2f02731f8084</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1475" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1475" t="inlineStr">
+        <is>
+          <t>OP-896</t>
+        </is>
+      </c>
+      <c r="I1475" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1475" s="2" t="n">
+        <v>46080.73665141374</v>
+      </c>
+      <c r="K1475" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>5a1504a8-f819-426f-8e82-5b51dca796a0</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>b0f04673-935e-4e30-99ec-1b107bc70620</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1476" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1476" t="inlineStr">
+        <is>
+          <t>OP-959</t>
+        </is>
+      </c>
+      <c r="I1476" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1476" s="2" t="n">
+        <v>46086.65331808354</v>
+      </c>
+      <c r="K1476" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>eeb071ca-ae51-472d-8935-f88d04c657c4</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>ec14a453-5157-4578-9df0-17e1bbc0429b</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1477" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F1477" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1477" t="inlineStr">
+        <is>
+          <t>OP-662</t>
+        </is>
+      </c>
+      <c r="I1477" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1477" s="2" t="n">
+        <v>46075.81998475341</v>
+      </c>
+      <c r="K1477" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>707af956-7ffe-48da-99f2-b81e5c9a16f4</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>c0b1ec6d-0ec7-481f-930d-b337447f3943</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1478" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1478" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1478" t="inlineStr">
+        <is>
+          <t>OP-937</t>
+        </is>
+      </c>
+      <c r="I1478" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1478" s="2" t="n">
+        <v>46066.81998475661</v>
+      </c>
+      <c r="K1478" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>83b625b6-a177-4f13-ad58-a46b00149545</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>ef74ad1b-a9ef-4bb5-8aea-3aa573751659</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1479" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1479" t="inlineStr">
+        <is>
+          <t>OP-116</t>
+        </is>
+      </c>
+      <c r="I1479" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1479" s="2" t="n">
+        <v>46066.52831809341</v>
+      </c>
+      <c r="K1479" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>5112658e-47b6-4d42-921b-b26a760f97cc</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>561d427b-61e5-4002-9905-ffb75c1988b9</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1480" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1480" t="inlineStr">
+        <is>
+          <t>OP-442</t>
+        </is>
+      </c>
+      <c r="I1480" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1480" s="2" t="n">
+        <v>46061.56998476313</v>
+      </c>
+      <c r="K1480" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>aa04ca12-cc42-40ae-a11f-02140b93536c</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>bac436f0-1e04-4674-a401-1935af996487</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1481" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1481" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1481" t="inlineStr">
+        <is>
+          <t>OP-544</t>
+        </is>
+      </c>
+      <c r="I1481" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1481" s="2" t="n">
+        <v>46072.69498476624</v>
+      </c>
+      <c r="K1481" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>f1ae980d-19a6-4427-ac40-aa0851d452c5</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>b7574b04-197e-4a71-9339-47ba35108319</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1482" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1482" t="inlineStr">
+        <is>
+          <t>OP-525</t>
+        </is>
+      </c>
+      <c r="I1482" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1482" s="2" t="n">
+        <v>46062.44498476941</v>
+      </c>
+      <c r="K1482" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>3be7c4f6-8975-4146-bfb7-b75cdea741d9</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>f44ed429-f41f-4e20-b349-351fad8f9293</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1483" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F1483" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1483" t="inlineStr">
+        <is>
+          <t>OP-267</t>
+        </is>
+      </c>
+      <c r="I1483" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1483" s="2" t="n">
+        <v>46078.44498477274</v>
+      </c>
+      <c r="K1483" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>6d06a0cc-c2df-48af-a164-3a97cbfa743e</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>73b57c8d-e51b-413f-881c-71a7dffb4179</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1484" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1484" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1484" t="inlineStr">
+        <is>
+          <t>OP-408</t>
+        </is>
+      </c>
+      <c r="I1484" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1484" s="2" t="n">
+        <v>46071.69498477592</v>
+      </c>
+      <c r="K1484" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>dc86c062-1cb3-4b6d-8ce6-25107eb98801</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>3c99ba9e-f5a7-4ad8-b7c2-b317cdb9dd5f</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1485" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1485" t="inlineStr">
+        <is>
+          <t>OP-546</t>
+        </is>
+      </c>
+      <c r="I1485" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1485" s="2" t="n">
+        <v>46072.73665144596</v>
+      </c>
+      <c r="K1485" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>7cd2cada-0abc-4266-94cf-57d7666bb5b8</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>05f239c7-29e5-41b4-9e85-192ea8b904d2</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1486" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1486" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1486" t="inlineStr">
+        <is>
+          <t>OP-802</t>
+        </is>
+      </c>
+      <c r="I1486" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1486" s="2" t="n">
+        <v>46079.56998478251</v>
+      </c>
+      <c r="K1486" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>59e08f34-474c-46f6-a0f7-4823e403c8fc</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>29df2464-ee11-4264-a02a-add31b6b7684</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1487" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1487" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1487" t="inlineStr">
+        <is>
+          <t>OP-923</t>
+        </is>
+      </c>
+      <c r="I1487" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1487" s="2" t="n">
+        <v>46069.528318119</v>
+      </c>
+      <c r="K1487" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>1f6fbf1c-87ec-4e7b-8e61-49429187afec</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>cde54da0-c63c-4291-a137-0de6b67688c5</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1488" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F1488" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1488" t="inlineStr">
+        <is>
+          <t>OP-183</t>
+        </is>
+      </c>
+      <c r="I1488" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1488" s="2" t="n">
+        <v>46066.44498478885</v>
+      </c>
+      <c r="K1488" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>f1cafe24-e29c-4cf8-90d9-ad1704d6bf8d</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>5d71e634-193c-47be-b8b6-1c7e03146d0b</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1489" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1489" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1489" t="inlineStr">
+        <is>
+          <t>OP-487</t>
+        </is>
+      </c>
+      <c r="I1489" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1489" s="2" t="n">
+        <v>46086.52831812551</v>
+      </c>
+      <c r="K1489" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>fcb0e2db-300a-4913-95f3-82b85e327eca</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>e7463096-b291-459a-bfa4-d8cea719ea12</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1490" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1490" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1490" t="inlineStr">
+        <is>
+          <t>OP-249</t>
+        </is>
+      </c>
+      <c r="I1490" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1490" s="2" t="n">
+        <v>46074.81998479523</v>
+      </c>
+      <c r="K1490" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>35dad39f-5378-4be7-9c8e-c932bb3ae813</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>30a4ff7d-c883-42fe-bb8d-5b5e5da4cff2</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1491" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1491" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1491" t="inlineStr">
+        <is>
+          <t>OP-641</t>
+        </is>
+      </c>
+      <c r="I1491" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1491" s="2" t="n">
+        <v>46076.61165146495</v>
+      </c>
+      <c r="K1491" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>33d20374-35b0-42df-8e71-5cd95d16d8c0</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>7ac6eeca-058f-46a6-b1ec-40ef22dc16de</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1492" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1492" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1492" t="inlineStr">
+        <is>
+          <t>OP-216</t>
+        </is>
+      </c>
+      <c r="I1492" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1492" s="2" t="n">
+        <v>46069.44498480145</v>
+      </c>
+      <c r="K1492" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>29b4faab-36a8-43c8-babc-8e454be0f9bf</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>c10197a7-2631-4208-ad01-fa12f8608570</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1493" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1493" t="inlineStr">
+        <is>
+          <t>OP-460</t>
+        </is>
+      </c>
+      <c r="I1493" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1493" s="2" t="n">
+        <v>46076.52831813797</v>
+      </c>
+      <c r="K1493" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>09f4643c-c63b-4383-afe9-fb3eec81593d</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>1d646589-8be6-4f5e-b24b-34b5f60ae183</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1494" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1494" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1494" t="inlineStr">
+        <is>
+          <t>OP-960</t>
+        </is>
+      </c>
+      <c r="I1494" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1494" s="2" t="n">
+        <v>46072.61165147444</v>
+      </c>
+      <c r="K1494" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>747d482f-ad71-46e9-8f96-5feed96bd00f</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>1c8d9e5b-ab8a-4920-9338-cbc14d94ff67</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1495" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1495" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1495" t="inlineStr">
+        <is>
+          <t>OP-911</t>
+        </is>
+      </c>
+      <c r="I1495" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1495" s="2" t="n">
+        <v>46071.4449848108</v>
+      </c>
+      <c r="K1495" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>20672f3f-e9fe-46a9-9c53-11f6d7f45602</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>7ae4f17e-f70a-498d-b970-245323816177</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1496" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1496" t="inlineStr">
+        <is>
+          <t>OP-375</t>
+        </is>
+      </c>
+      <c r="I1496" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1496" s="2" t="n">
+        <v>46076.52831814719</v>
+      </c>
+      <c r="K1496" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>0584b901-41de-42d3-ba77-a399aeb68640</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>88001572-2e2d-46e2-a534-c64b08db74b8</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1497" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1497" t="inlineStr">
+        <is>
+          <t>OP-865</t>
+        </is>
+      </c>
+      <c r="I1497" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1497" s="2" t="n">
+        <v>46070.77831815042</v>
+      </c>
+      <c r="K1497" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>bfc4a3b9-821d-47fa-89a4-8ce7ae8a68ff</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>b24f18ce-35bb-43b9-85ba-a05efcb082c3</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1498" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1498" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1498" t="inlineStr">
+        <is>
+          <t>OP-983</t>
+        </is>
+      </c>
+      <c r="I1498" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1498" s="2" t="n">
+        <v>46068.48665148678</v>
+      </c>
+      <c r="K1498" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>10b5db54-033b-49b0-b667-3b7506793b55</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>e0b1e092-25dc-4f82-aae2-20c94e21a487</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1499" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>OP-903</t>
+        </is>
+      </c>
+      <c r="I1499" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1499" s="2" t="n">
+        <v>46082.61165148987</v>
+      </c>
+      <c r="K1499" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>8c1e8071-6e2b-453e-baf0-1b99d8f56f03</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>41541b51-5d3a-441e-80c4-7bc5f6f2c5fc</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1500" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1500" t="inlineStr">
+        <is>
+          <t>OP-375</t>
+        </is>
+      </c>
+      <c r="I1500" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1500" s="2" t="n">
+        <v>46078.81998482619</v>
+      </c>
+      <c r="K1500" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>829eec77-2c81-4de3-a7c1-a0b9680ed212</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>f7db0db1-6ccb-4f9e-a82a-35354c6aac21</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1501" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>OP-926</t>
+        </is>
+      </c>
+      <c r="I1501" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1501" s="2" t="n">
+        <v>46069.81998482951</v>
+      </c>
+      <c r="K1501" t="inlineStr">
         <is>
           <t>poor</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1501"/>
+  <dimension ref="A1:K1551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74482,7 +74482,7 @@
         </is>
       </c>
       <c r="J1452" s="2" t="n">
-        <v>46079.73665133717</v>
+        <v>46079.73665134259</v>
       </c>
       <c r="K1452" t="inlineStr">
         <is>
@@ -74533,7 +74533,7 @@
         </is>
       </c>
       <c r="J1453" s="2" t="n">
-        <v>46089.6116513415</v>
+        <v>46089.61165134259</v>
       </c>
       <c r="K1453" t="inlineStr">
         <is>
@@ -74584,7 +74584,7 @@
         </is>
       </c>
       <c r="J1454" s="2" t="n">
-        <v>46082.81998467846</v>
+        <v>46082.81998467592</v>
       </c>
       <c r="K1454" t="inlineStr">
         <is>
@@ -74635,7 +74635,7 @@
         </is>
       </c>
       <c r="J1455" s="2" t="n">
-        <v>46072.8199846816</v>
+        <v>46072.81998467592</v>
       </c>
       <c r="K1455" t="inlineStr">
         <is>
@@ -74686,7 +74686,7 @@
         </is>
       </c>
       <c r="J1456" s="2" t="n">
-        <v>46085.61165135141</v>
+        <v>46085.61165135416</v>
       </c>
       <c r="K1456" t="inlineStr">
         <is>
@@ -74737,7 +74737,7 @@
         </is>
       </c>
       <c r="J1457" s="2" t="n">
-        <v>46086.48665135512</v>
+        <v>46086.48665135416</v>
       </c>
       <c r="K1457" t="inlineStr">
         <is>
@@ -74788,7 +74788,7 @@
         </is>
       </c>
       <c r="J1458" s="2" t="n">
-        <v>46081.81998469165</v>
+        <v>46081.8199846875</v>
       </c>
       <c r="K1458" t="inlineStr">
         <is>
@@ -74839,7 +74839,7 @@
         </is>
       </c>
       <c r="J1459" s="2" t="n">
-        <v>46070.77831802811</v>
+        <v>46070.7783180324</v>
       </c>
       <c r="K1459" t="inlineStr">
         <is>
@@ -74890,7 +74890,7 @@
         </is>
       </c>
       <c r="J1460" s="2" t="n">
-        <v>46082.52831803136</v>
+        <v>46082.5283180324</v>
       </c>
       <c r="K1460" t="inlineStr">
         <is>
@@ -74941,7 +74941,7 @@
         </is>
       </c>
       <c r="J1461" s="2" t="n">
-        <v>46068.52831803489</v>
+        <v>46068.5283180324</v>
       </c>
       <c r="K1461" t="inlineStr">
         <is>
@@ -74992,7 +74992,7 @@
         </is>
       </c>
       <c r="J1462" s="2" t="n">
-        <v>46069.52831803829</v>
+        <v>46069.52831804398</v>
       </c>
       <c r="K1462" t="inlineStr">
         <is>
@@ -75043,7 +75043,7 @@
         </is>
       </c>
       <c r="J1463" s="2" t="n">
-        <v>46066.65331804139</v>
+        <v>46066.65331804398</v>
       </c>
       <c r="K1463" t="inlineStr">
         <is>
@@ -75094,7 +75094,7 @@
         </is>
       </c>
       <c r="J1464" s="2" t="n">
-        <v>46072.44498471131</v>
+        <v>46072.44498471065</v>
       </c>
       <c r="K1464" t="inlineStr">
         <is>
@@ -75145,7 +75145,7 @@
         </is>
       </c>
       <c r="J1465" s="2" t="n">
-        <v>46074.48665138102</v>
+        <v>46074.48665137732</v>
       </c>
       <c r="K1465" t="inlineStr">
         <is>
@@ -75196,7 +75196,7 @@
         </is>
       </c>
       <c r="J1466" s="2" t="n">
-        <v>46075.6116513841</v>
+        <v>46075.61165138889</v>
       </c>
       <c r="K1466" t="inlineStr">
         <is>
@@ -75247,7 +75247,7 @@
         </is>
       </c>
       <c r="J1467" s="2" t="n">
-        <v>46073.52831805387</v>
+        <v>46073.52831805556</v>
       </c>
       <c r="K1467" t="inlineStr">
         <is>
@@ -75298,7 +75298,7 @@
         </is>
       </c>
       <c r="J1468" s="2" t="n">
-        <v>46074.77831805713</v>
+        <v>46074.77831805556</v>
       </c>
       <c r="K1468" t="inlineStr">
         <is>
@@ -75349,7 +75349,7 @@
         </is>
       </c>
       <c r="J1469" s="2" t="n">
-        <v>46086.8199847268</v>
+        <v>46086.81998472222</v>
       </c>
       <c r="K1469" t="inlineStr">
         <is>
@@ -75400,7 +75400,7 @@
         </is>
       </c>
       <c r="J1470" s="2" t="n">
-        <v>46060.6116513965</v>
+        <v>46060.61165140046</v>
       </c>
       <c r="K1470" t="inlineStr">
         <is>
@@ -75451,7 +75451,7 @@
         </is>
       </c>
       <c r="J1471" s="2" t="n">
-        <v>46082.69498473309</v>
+        <v>46082.6949847338</v>
       </c>
       <c r="K1471" t="inlineStr">
         <is>
@@ -75502,7 +75502,7 @@
         </is>
       </c>
       <c r="J1472" s="2" t="n">
-        <v>46062.5699847363</v>
+        <v>46062.5699847338</v>
       </c>
       <c r="K1472" t="inlineStr">
         <is>
@@ -75553,7 +75553,7 @@
         </is>
       </c>
       <c r="J1473" s="2" t="n">
-        <v>46075.48665140612</v>
+        <v>46075.48665140046</v>
       </c>
       <c r="K1473" t="inlineStr">
         <is>
@@ -75604,7 +75604,7 @@
         </is>
       </c>
       <c r="J1474" s="2" t="n">
-        <v>46077.56998474265</v>
+        <v>46077.56998474537</v>
       </c>
       <c r="K1474" t="inlineStr">
         <is>
@@ -75655,7 +75655,7 @@
         </is>
       </c>
       <c r="J1475" s="2" t="n">
-        <v>46080.73665141374</v>
+        <v>46080.73665141204</v>
       </c>
       <c r="K1475" t="inlineStr">
         <is>
@@ -75706,7 +75706,7 @@
         </is>
       </c>
       <c r="J1476" s="2" t="n">
-        <v>46086.65331808354</v>
+        <v>46086.6533180787</v>
       </c>
       <c r="K1476" t="inlineStr">
         <is>
@@ -75757,7 +75757,7 @@
         </is>
       </c>
       <c r="J1477" s="2" t="n">
-        <v>46075.81998475341</v>
+        <v>46075.81998475694</v>
       </c>
       <c r="K1477" t="inlineStr">
         <is>
@@ -75808,7 +75808,7 @@
         </is>
       </c>
       <c r="J1478" s="2" t="n">
-        <v>46066.81998475661</v>
+        <v>46066.81998475694</v>
       </c>
       <c r="K1478" t="inlineStr">
         <is>
@@ -75859,7 +75859,7 @@
         </is>
       </c>
       <c r="J1479" s="2" t="n">
-        <v>46066.52831809341</v>
+        <v>46066.52831809028</v>
       </c>
       <c r="K1479" t="inlineStr">
         <is>
@@ -75910,7 +75910,7 @@
         </is>
       </c>
       <c r="J1480" s="2" t="n">
-        <v>46061.56998476313</v>
+        <v>46061.56998476852</v>
       </c>
       <c r="K1480" t="inlineStr">
         <is>
@@ -75961,7 +75961,7 @@
         </is>
       </c>
       <c r="J1481" s="2" t="n">
-        <v>46072.69498476624</v>
+        <v>46072.69498476852</v>
       </c>
       <c r="K1481" t="inlineStr">
         <is>
@@ -76012,7 +76012,7 @@
         </is>
       </c>
       <c r="J1482" s="2" t="n">
-        <v>46062.44498476941</v>
+        <v>46062.44498476852</v>
       </c>
       <c r="K1482" t="inlineStr">
         <is>
@@ -76063,7 +76063,7 @@
         </is>
       </c>
       <c r="J1483" s="2" t="n">
-        <v>46078.44498477274</v>
+        <v>46078.44498476852</v>
       </c>
       <c r="K1483" t="inlineStr">
         <is>
@@ -76114,7 +76114,7 @@
         </is>
       </c>
       <c r="J1484" s="2" t="n">
-        <v>46071.69498477592</v>
+        <v>46071.69498478009</v>
       </c>
       <c r="K1484" t="inlineStr">
         <is>
@@ -76165,7 +76165,7 @@
         </is>
       </c>
       <c r="J1485" s="2" t="n">
-        <v>46072.73665144596</v>
+        <v>46072.73665144676</v>
       </c>
       <c r="K1485" t="inlineStr">
         <is>
@@ -76216,7 +76216,7 @@
         </is>
       </c>
       <c r="J1486" s="2" t="n">
-        <v>46079.56998478251</v>
+        <v>46079.56998478009</v>
       </c>
       <c r="K1486" t="inlineStr">
         <is>
@@ -76267,7 +76267,7 @@
         </is>
       </c>
       <c r="J1487" s="2" t="n">
-        <v>46069.528318119</v>
+        <v>46069.52831811343</v>
       </c>
       <c r="K1487" t="inlineStr">
         <is>
@@ -76318,7 +76318,7 @@
         </is>
       </c>
       <c r="J1488" s="2" t="n">
-        <v>46066.44498478885</v>
+        <v>46066.44498479167</v>
       </c>
       <c r="K1488" t="inlineStr">
         <is>
@@ -76369,7 +76369,7 @@
         </is>
       </c>
       <c r="J1489" s="2" t="n">
-        <v>46086.52831812551</v>
+        <v>46086.528318125</v>
       </c>
       <c r="K1489" t="inlineStr">
         <is>
@@ -76420,7 +76420,7 @@
         </is>
       </c>
       <c r="J1490" s="2" t="n">
-        <v>46074.81998479523</v>
+        <v>46074.81998479167</v>
       </c>
       <c r="K1490" t="inlineStr">
         <is>
@@ -76471,7 +76471,7 @@
         </is>
       </c>
       <c r="J1491" s="2" t="n">
-        <v>46076.61165146495</v>
+        <v>46076.61165146991</v>
       </c>
       <c r="K1491" t="inlineStr">
         <is>
@@ -76522,7 +76522,7 @@
         </is>
       </c>
       <c r="J1492" s="2" t="n">
-        <v>46069.44498480145</v>
+        <v>46069.44498480324</v>
       </c>
       <c r="K1492" t="inlineStr">
         <is>
@@ -76573,7 +76573,7 @@
         </is>
       </c>
       <c r="J1493" s="2" t="n">
-        <v>46076.52831813797</v>
+        <v>46076.52831813657</v>
       </c>
       <c r="K1493" t="inlineStr">
         <is>
@@ -76624,7 +76624,7 @@
         </is>
       </c>
       <c r="J1494" s="2" t="n">
-        <v>46072.61165147444</v>
+        <v>46072.61165146991</v>
       </c>
       <c r="K1494" t="inlineStr">
         <is>
@@ -76675,7 +76675,7 @@
         </is>
       </c>
       <c r="J1495" s="2" t="n">
-        <v>46071.4449848108</v>
+        <v>46071.44498481481</v>
       </c>
       <c r="K1495" t="inlineStr">
         <is>
@@ -76726,7 +76726,7 @@
         </is>
       </c>
       <c r="J1496" s="2" t="n">
-        <v>46076.52831814719</v>
+        <v>46076.52831814815</v>
       </c>
       <c r="K1496" t="inlineStr">
         <is>
@@ -76777,7 +76777,7 @@
         </is>
       </c>
       <c r="J1497" s="2" t="n">
-        <v>46070.77831815042</v>
+        <v>46070.77831814815</v>
       </c>
       <c r="K1497" t="inlineStr">
         <is>
@@ -76828,7 +76828,7 @@
         </is>
       </c>
       <c r="J1498" s="2" t="n">
-        <v>46068.48665148678</v>
+        <v>46068.48665148148</v>
       </c>
       <c r="K1498" t="inlineStr">
         <is>
@@ -76879,7 +76879,7 @@
         </is>
       </c>
       <c r="J1499" s="2" t="n">
-        <v>46082.61165148987</v>
+        <v>46082.61165149305</v>
       </c>
       <c r="K1499" t="inlineStr">
         <is>
@@ -76930,7 +76930,7 @@
         </is>
       </c>
       <c r="J1500" s="2" t="n">
-        <v>46078.81998482619</v>
+        <v>46078.81998482639</v>
       </c>
       <c r="K1500" t="inlineStr">
         <is>
@@ -76981,9 +76981,2559 @@
         </is>
       </c>
       <c r="J1501" s="2" t="n">
-        <v>46069.81998482951</v>
+        <v>46069.81998482639</v>
       </c>
       <c r="K1501" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>7fd045ef-7589-41b2-97e5-6011b3b5fd69</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>43ead498-870f-416c-b396-890889c57ea0</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1502" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>OP-440</t>
+        </is>
+      </c>
+      <c r="I1502" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1502" s="2" t="n">
+        <v>46071.73479247833</v>
+      </c>
+      <c r="K1502" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>76ca4314-0fb2-4994-ae5b-637a5fd4738f</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>7c5ebdec-d583-4838-8213-68859d666c6c</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1503" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1503" t="inlineStr">
+        <is>
+          <t>OP-864</t>
+        </is>
+      </c>
+      <c r="I1503" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1503" s="2" t="n">
+        <v>46089.52645914917</v>
+      </c>
+      <c r="K1503" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>0534b157-46db-4eea-b5d4-23f6a3418834</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>ac67a1e0-8f9d-4da3-ac13-3938417523d7</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1504" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1504" t="inlineStr">
+        <is>
+          <t>OP-125</t>
+        </is>
+      </c>
+      <c r="I1504" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1504" s="2" t="n">
+        <v>46077.85979248568</v>
+      </c>
+      <c r="K1504" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>e894eb62-50e5-4701-9b7a-88a3131ebf56</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>e97d69e4-2c88-46e7-8cde-8199f582f5b9</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1505" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1505" t="inlineStr">
+        <is>
+          <t>OP-444</t>
+        </is>
+      </c>
+      <c r="I1505" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1505" s="2" t="n">
+        <v>46084.48479248924</v>
+      </c>
+      <c r="K1505" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>14620950-2492-43a1-bd85-42d28870b240</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>460ae794-5de5-43a2-9fb7-a5ddadf804a0</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1506" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1506" t="inlineStr">
+        <is>
+          <t>OP-198</t>
+        </is>
+      </c>
+      <c r="I1506" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1506" s="2" t="n">
+        <v>46071.6097924923</v>
+      </c>
+      <c r="K1506" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>5a2fe505-03db-4e7f-ae92-8492994084d0</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>0d577491-be37-4c49-9002-72d0fefc6b2d</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1507" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1507" t="inlineStr">
+        <is>
+          <t>OP-815</t>
+        </is>
+      </c>
+      <c r="I1507" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1507" s="2" t="n">
+        <v>46064.65145916228</v>
+      </c>
+      <c r="K1507" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>c1064779-6e9b-4a7b-ae32-24a31d51693e</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>1b17354c-f320-46b2-923c-5a3e7a807718</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1508" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F1508" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>OP-638</t>
+        </is>
+      </c>
+      <c r="I1508" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1508" s="2" t="n">
+        <v>46076.52645916554</v>
+      </c>
+      <c r="K1508" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>9e1cc35c-9e7c-4c29-be58-3ec979227fef</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>404f2c56-b24b-4538-86d7-660edac1076e</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1509" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1509" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1509" t="inlineStr">
+        <is>
+          <t>OP-548</t>
+        </is>
+      </c>
+      <c r="I1509" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1509" s="2" t="n">
+        <v>46082.6931258353</v>
+      </c>
+      <c r="K1509" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>0474c895-2937-4589-87d8-e34fbb9fb4ee</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>fbca9172-dda7-4fe7-a1e9-f0da0239e89c</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1510" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1510" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>OP-758</t>
+        </is>
+      </c>
+      <c r="I1510" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1510" s="2" t="n">
+        <v>46073.85979250519</v>
+      </c>
+      <c r="K1510" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>8b62f952-0267-43f1-8c8d-510d8010ab2b</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>d4379e26-250b-46f3-918b-e3e66820d055</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1511" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1511" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1511" t="inlineStr">
+        <is>
+          <t>OP-682</t>
+        </is>
+      </c>
+      <c r="I1511" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1511" s="2" t="n">
+        <v>46073.81812584171</v>
+      </c>
+      <c r="K1511" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>89dbcce3-001a-46d3-b42b-9702f7ea89a1</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>af909e78-6d84-4e73-95c6-7816f8f19772</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1512" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1512" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1512" t="inlineStr">
+        <is>
+          <t>OP-962</t>
+        </is>
+      </c>
+      <c r="I1512" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1512" s="2" t="n">
+        <v>46078.52645917836</v>
+      </c>
+      <c r="K1512" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>f167f870-ea29-4c0a-8b85-cc9b3ab40cdb</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>f81f159b-951d-4ade-bc7d-817395085946</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1513" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1513" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1513" t="inlineStr">
+        <is>
+          <t>OP-786</t>
+        </is>
+      </c>
+      <c r="I1513" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1513" s="2" t="n">
+        <v>46065.73479251489</v>
+      </c>
+      <c r="K1513" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>5616eb8f-83f1-4387-887c-8c33bb45893e</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>fa8dd032-10c7-420f-bc7e-cad5db014adb</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1514" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1514" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1514" t="inlineStr">
+        <is>
+          <t>OP-476</t>
+        </is>
+      </c>
+      <c r="I1514" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1514" s="2" t="n">
+        <v>46080.48479251795</v>
+      </c>
+      <c r="K1514" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>045e5f54-92e7-4f6f-adfc-f036d54e0f98</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>be79ec6f-f616-41ae-9692-49ebc3f17f3d</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1515" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1515" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1515" t="inlineStr">
+        <is>
+          <t>OP-129</t>
+        </is>
+      </c>
+      <c r="I1515" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1515" s="2" t="n">
+        <v>46060.69312585449</v>
+      </c>
+      <c r="K1515" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>eedf8b31-c0a6-461c-9e4a-64a91551a1e2</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>fe69e734-7888-4b9e-9932-8190010df45e</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1516" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F1516" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1516" t="inlineStr">
+        <is>
+          <t>OP-634</t>
+        </is>
+      </c>
+      <c r="I1516" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1516" s="2" t="n">
+        <v>46088.60979252449</v>
+      </c>
+      <c r="K1516" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>d03d5937-6740-4b77-943f-37ed5a20c42f</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>c22d9f4b-48e5-4569-9e5e-15f419b34d78</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1517" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1517" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1517" t="inlineStr">
+        <is>
+          <t>OP-118</t>
+        </is>
+      </c>
+      <c r="I1517" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1517" s="2" t="n">
+        <v>46064.69312586108</v>
+      </c>
+      <c r="K1517" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>a670e598-81dd-4f4b-8ae7-4af7f7a46fa3</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>b2b53b75-d7e6-44bb-9c62-02c3b74eb452</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1518" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1518" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1518" t="inlineStr">
+        <is>
+          <t>OP-664</t>
+        </is>
+      </c>
+      <c r="I1518" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1518" s="2" t="n">
+        <v>46067.73479253083</v>
+      </c>
+      <c r="K1518" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>e9e8808e-12ed-4eaf-ac63-fe843da15cda</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>967cd44a-5048-4e88-9d54-8ef465483dcb</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1519" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1519" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1519" t="inlineStr">
+        <is>
+          <t>OP-873</t>
+        </is>
+      </c>
+      <c r="I1519" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1519" s="2" t="n">
+        <v>46067.69312586734</v>
+      </c>
+      <c r="K1519" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>71b209b0-d921-4254-80f1-5a8131ffb867</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>6530f826-58e2-490e-95fe-e9a2fb8b4d5a</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1520" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1520" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr">
+        <is>
+          <t>OP-603</t>
+        </is>
+      </c>
+      <c r="I1520" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1520" s="2" t="n">
+        <v>46064.73479253714</v>
+      </c>
+      <c r="K1520" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>93490a30-a8c0-48c4-9953-ab62f7e3328f</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>69a3f584-36f2-43b2-89e0-4bf3e2c00ba9</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1521" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1521" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1521" t="inlineStr">
+        <is>
+          <t>OP-452</t>
+        </is>
+      </c>
+      <c r="I1521" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1521" s="2" t="n">
+        <v>46066.69312587352</v>
+      </c>
+      <c r="K1521" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>1f42f5a5-d223-4482-885f-9c1bb92953f7</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>1836e4ae-19a2-40ff-a833-e4ae189b10b7</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1522" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1522" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>OP-799</t>
+        </is>
+      </c>
+      <c r="I1522" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1522" s="2" t="n">
+        <v>46089.73479254323</v>
+      </c>
+      <c r="K1522" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>d2a4d75a-f3c3-4f85-97ba-2d56ac526a3e</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>2a60688e-379f-4b5c-915a-54da616893c8</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1523" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F1523" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1523" t="inlineStr">
+        <is>
+          <t>OP-962</t>
+        </is>
+      </c>
+      <c r="I1523" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1523" s="2" t="n">
+        <v>46076.73479254648</v>
+      </c>
+      <c r="K1523" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>8922a092-948a-462c-bccb-44f7b26dd82d</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>65c4a910-295a-4f61-9265-7d4137adabdf</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1524" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1524" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1524" t="inlineStr">
+        <is>
+          <t>OP-261</t>
+        </is>
+      </c>
+      <c r="I1524" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1524" s="2" t="n">
+        <v>46071.56812588294</v>
+      </c>
+      <c r="K1524" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>15a1dbab-3eba-4fb0-b342-7a71bf03a413</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>f95a8bcf-3bf1-4449-bcef-894d85f72918</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1525" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="F1525" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>OP-569</t>
+        </is>
+      </c>
+      <c r="I1525" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1525" s="2" t="n">
+        <v>46068.81812588588</v>
+      </c>
+      <c r="K1525" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>e2f57606-7450-49a3-afc9-5504319d454e</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>903e0975-c5bb-4cbc-bd34-5958da4c5476</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1526" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1526" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1526" t="inlineStr">
+        <is>
+          <t>OP-468</t>
+        </is>
+      </c>
+      <c r="I1526" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1526" s="2" t="n">
+        <v>46072.48479255572</v>
+      </c>
+      <c r="K1526" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>3b668e50-336a-4545-9a83-5896afb89816</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>ad80ecb9-1bf4-4c82-8ed6-b1f9e101e211</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1527" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1527" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1527" t="inlineStr">
+        <is>
+          <t>OP-198</t>
+        </is>
+      </c>
+      <c r="I1527" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1527" s="2" t="n">
+        <v>46061.73479255912</v>
+      </c>
+      <c r="K1527" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>41a09aec-a796-4378-9f37-7e1105081381</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>f0239146-558d-4c14-9514-6d11280b4e2a</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1528" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F1528" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1528" t="inlineStr">
+        <is>
+          <t>OP-695</t>
+        </is>
+      </c>
+      <c r="I1528" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1528" s="2" t="n">
+        <v>46079.48479256217</v>
+      </c>
+      <c r="K1528" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>26fca6c2-c4f9-489c-b279-36114e12a41a</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>2ad03e7e-04c9-486c-9845-fe18c3002cf8</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1529" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1529" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1529" t="inlineStr">
+        <is>
+          <t>OP-798</t>
+        </is>
+      </c>
+      <c r="I1529" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1529" s="2" t="n">
+        <v>46086.7764592319</v>
+      </c>
+      <c r="K1529" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>433c196a-a3ab-4279-84bd-850a7bd1dd22</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>64e76db7-cbdb-4080-9529-edd682f22665</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1530" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1530" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1530" t="inlineStr">
+        <is>
+          <t>OP-199</t>
+        </is>
+      </c>
+      <c r="I1530" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1530" s="2" t="n">
+        <v>46061.81812590175</v>
+      </c>
+      <c r="K1530" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>a43a04b9-fa8e-4966-a76d-64480a963b65</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>5cbec4d9-11b0-49c3-85bd-78c356084d53</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1531" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1531" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1531" t="inlineStr">
+        <is>
+          <t>OP-492</t>
+        </is>
+      </c>
+      <c r="I1531" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1531" s="2" t="n">
+        <v>46080.81812590487</v>
+      </c>
+      <c r="K1531" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>92e40181-cd72-4758-86d4-6e51207729bb</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>075238b2-a36b-474f-9705-e6766faac0d5</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1532" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1532" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1532" t="inlineStr">
+        <is>
+          <t>OP-877</t>
+        </is>
+      </c>
+      <c r="I1532" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1532" s="2" t="n">
+        <v>46081.77645924145</v>
+      </c>
+      <c r="K1532" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>72fba5a4-e4d2-4aaf-8d3a-2ba2dcee7621</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>a9ea206b-caea-48a4-a271-b220636b24cb</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1533" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1533" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>OP-751</t>
+        </is>
+      </c>
+      <c r="I1533" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1533" s="2" t="n">
+        <v>46065.56812591136</v>
+      </c>
+      <c r="K1533" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>4b83cd91-2923-4356-acf9-5a707bdaf4aa</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>4805c05d-46f5-458b-b23a-e6b6f52ecf89</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1534" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F1534" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1534" t="inlineStr">
+        <is>
+          <t>OP-339</t>
+        </is>
+      </c>
+      <c r="I1534" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1534" s="2" t="n">
+        <v>46082.73479258129</v>
+      </c>
+      <c r="K1534" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>94c4a8e0-ef20-4cbc-9018-a12bd4b8253b</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>9ea13220-e54c-4951-8e76-d130654c4c37</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1535" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1535" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1535" t="inlineStr">
+        <is>
+          <t>OP-158</t>
+        </is>
+      </c>
+      <c r="I1535" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1535" s="2" t="n">
+        <v>46082.60979258436</v>
+      </c>
+      <c r="K1535" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>a991da17-16e8-46d1-aa21-0bf315718d1d</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>c1886a20-3adb-4dcd-b1cd-11a253aefda1</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1536" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1536" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>OP-382</t>
+        </is>
+      </c>
+      <c r="I1536" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1536" s="2" t="n">
+        <v>46072.8597925875</v>
+      </c>
+      <c r="K1536" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>ebce5291-a427-4ce9-a927-9ef2611a28fa</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>def9ea47-d57e-4c3f-b8f9-38acb7611352</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1537" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1537" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1537" t="inlineStr">
+        <is>
+          <t>OP-186</t>
+        </is>
+      </c>
+      <c r="I1537" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1537" s="2" t="n">
+        <v>46069.60979259075</v>
+      </c>
+      <c r="K1537" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>728875f3-96fe-4217-b753-51af2eb5f4a0</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>f6751b24-dd46-4249-bae6-abcf2526741a</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1538" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1538" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1538" t="inlineStr">
+        <is>
+          <t>OP-204</t>
+        </is>
+      </c>
+      <c r="I1538" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1538" s="2" t="n">
+        <v>46082.60979259395</v>
+      </c>
+      <c r="K1538" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>c4e42b13-0086-4938-8aae-63947c93b86f</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>d24bc756-3716-44b0-aa85-b07557b579c5</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1539" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F1539" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1539" t="inlineStr">
+        <is>
+          <t>OP-313</t>
+        </is>
+      </c>
+      <c r="I1539" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1539" s="2" t="n">
+        <v>46088.77645926388</v>
+      </c>
+      <c r="K1539" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>8f45edac-1a76-4d72-b28d-ac3894a06ae4</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>28612b0a-bc11-4198-aec4-ad60e16c15cd</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1540" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F1540" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1540" t="inlineStr">
+        <is>
+          <t>OP-586</t>
+        </is>
+      </c>
+      <c r="I1540" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1540" s="2" t="n">
+        <v>46071.69312593353</v>
+      </c>
+      <c r="K1540" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>0d90ceca-ff65-4f74-b1fa-e759b1e3430d</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>1d8d0756-c8d6-4287-82e8-ff4bb3ed804b</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1541" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1541" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1541" t="inlineStr">
+        <is>
+          <t>OP-407</t>
+        </is>
+      </c>
+      <c r="I1541" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1541" s="2" t="n">
+        <v>46087.7347926036</v>
+      </c>
+      <c r="K1541" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>f27afc3c-4948-4c07-bcae-dbae452223dd</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>388562b1-f2ec-45d3-9a5c-4d989d6a1681</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1542" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1542" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1542" t="inlineStr">
+        <is>
+          <t>OP-401</t>
+        </is>
+      </c>
+      <c r="I1542" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1542" s="2" t="n">
+        <v>46071.52645927331</v>
+      </c>
+      <c r="K1542" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>bca2d9f3-da5e-4457-afdb-99caee6745fb</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>cb529afb-515f-4ace-b3de-bb143aed65c5</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1543" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1543" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1543" t="inlineStr">
+        <is>
+          <t>OP-114</t>
+        </is>
+      </c>
+      <c r="I1543" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1543" s="2" t="n">
+        <v>46080.69312594321</v>
+      </c>
+      <c r="K1543" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>12a5ebcd-b1c5-4d7b-9907-e3089ff5abcc</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>6708345b-4eaf-4bc0-852d-27808640263e</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1544" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1544" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1544" t="inlineStr">
+        <is>
+          <t>OP-400</t>
+        </is>
+      </c>
+      <c r="I1544" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1544" s="2" t="n">
+        <v>46065.85979261299</v>
+      </c>
+      <c r="K1544" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>dc090665-ebde-459b-812e-4eb86b55ca86</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>a4a799ab-ceab-44ed-88f2-61159292cede</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1545" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1545" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1545" t="inlineStr">
+        <is>
+          <t>OP-600</t>
+        </is>
+      </c>
+      <c r="I1545" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1545" s="2" t="n">
+        <v>46070.52645928298</v>
+      </c>
+      <c r="K1545" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>aca633ee-4763-4780-912d-be52cda24f39</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>789a2e54-11f1-40ab-88d9-5de9af64a414</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1546" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1546" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1546" t="inlineStr">
+        <is>
+          <t>OP-820</t>
+        </is>
+      </c>
+      <c r="I1546" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1546" s="2" t="n">
+        <v>46076.6514592861</v>
+      </c>
+      <c r="K1546" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>361e18eb-3509-41b7-a501-db494f925531</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>0ad01bbe-0572-45f3-8f5e-9bc5640777b7</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1547" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1547" t="inlineStr">
+        <is>
+          <t>OP-868</t>
+        </is>
+      </c>
+      <c r="I1547" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1547" s="2" t="n">
+        <v>46067.81812595594</v>
+      </c>
+      <c r="K1547" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>fc72dcee-bfad-40d1-8f0f-cb6cfda70c06</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>8c3dd099-3828-4305-96c3-3bbc3f06b2c0</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1548" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1548" t="inlineStr">
+        <is>
+          <t>OP-942</t>
+        </is>
+      </c>
+      <c r="I1548" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1548" s="2" t="n">
+        <v>46089.6097926258</v>
+      </c>
+      <c r="K1548" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>83079ecc-3223-4f8f-94db-19db3464f35a</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>e21b025c-9608-45b0-8548-3fd14ae75f2a</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1549" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1549" t="inlineStr">
+        <is>
+          <t>OP-715</t>
+        </is>
+      </c>
+      <c r="I1549" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1549" s="2" t="n">
+        <v>46074.609792629</v>
+      </c>
+      <c r="K1549" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>c5641cef-acc9-4e12-ada2-c3af2e5a4daa</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>043e59f6-65ab-4ca4-bf1a-cfa6f53d27e5</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1550" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1550" t="inlineStr">
+        <is>
+          <t>OP-423</t>
+        </is>
+      </c>
+      <c r="I1550" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1550" s="2" t="n">
+        <v>46086.6097926322</v>
+      </c>
+      <c r="K1550" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>17102359-cec0-40e3-995d-8b64cf1741d9</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>3522ebf8-6440-454d-85cc-59c762d79052</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1551" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1551" t="inlineStr">
+        <is>
+          <t>OP-887</t>
+        </is>
+      </c>
+      <c r="I1551" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1551" s="2" t="n">
+        <v>46076.7347926353</v>
+      </c>
+      <c r="K1551" t="inlineStr">
         <is>
           <t>poor</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1551"/>
+  <dimension ref="A1:K1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77032,7 +77032,7 @@
         </is>
       </c>
       <c r="J1502" s="2" t="n">
-        <v>46071.73479247833</v>
+        <v>46071.73479247685</v>
       </c>
       <c r="K1502" t="inlineStr">
         <is>
@@ -77083,7 +77083,7 @@
         </is>
       </c>
       <c r="J1503" s="2" t="n">
-        <v>46089.52645914917</v>
+        <v>46089.52645914352</v>
       </c>
       <c r="K1503" t="inlineStr">
         <is>
@@ -77134,7 +77134,7 @@
         </is>
       </c>
       <c r="J1504" s="2" t="n">
-        <v>46077.85979248568</v>
+        <v>46077.85979248842</v>
       </c>
       <c r="K1504" t="inlineStr">
         <is>
@@ -77185,7 +77185,7 @@
         </is>
       </c>
       <c r="J1505" s="2" t="n">
-        <v>46084.48479248924</v>
+        <v>46084.48479248842</v>
       </c>
       <c r="K1505" t="inlineStr">
         <is>
@@ -77236,7 +77236,7 @@
         </is>
       </c>
       <c r="J1506" s="2" t="n">
-        <v>46071.6097924923</v>
+        <v>46071.60979248842</v>
       </c>
       <c r="K1506" t="inlineStr">
         <is>
@@ -77287,7 +77287,7 @@
         </is>
       </c>
       <c r="J1507" s="2" t="n">
-        <v>46064.65145916228</v>
+        <v>46064.65145916666</v>
       </c>
       <c r="K1507" t="inlineStr">
         <is>
@@ -77338,7 +77338,7 @@
         </is>
       </c>
       <c r="J1508" s="2" t="n">
-        <v>46076.52645916554</v>
+        <v>46076.52645916666</v>
       </c>
       <c r="K1508" t="inlineStr">
         <is>
@@ -77389,7 +77389,7 @@
         </is>
       </c>
       <c r="J1509" s="2" t="n">
-        <v>46082.6931258353</v>
+        <v>46082.69312583334</v>
       </c>
       <c r="K1509" t="inlineStr">
         <is>
@@ -77440,7 +77440,7 @@
         </is>
       </c>
       <c r="J1510" s="2" t="n">
-        <v>46073.85979250519</v>
+        <v>46073.8597925</v>
       </c>
       <c r="K1510" t="inlineStr">
         <is>
@@ -77491,7 +77491,7 @@
         </is>
       </c>
       <c r="J1511" s="2" t="n">
-        <v>46073.81812584171</v>
+        <v>46073.8181258449</v>
       </c>
       <c r="K1511" t="inlineStr">
         <is>
@@ -77542,7 +77542,7 @@
         </is>
       </c>
       <c r="J1512" s="2" t="n">
-        <v>46078.52645917836</v>
+        <v>46078.52645917824</v>
       </c>
       <c r="K1512" t="inlineStr">
         <is>
@@ -77593,7 +77593,7 @@
         </is>
       </c>
       <c r="J1513" s="2" t="n">
-        <v>46065.73479251489</v>
+        <v>46065.73479251158</v>
       </c>
       <c r="K1513" t="inlineStr">
         <is>
@@ -77644,7 +77644,7 @@
         </is>
       </c>
       <c r="J1514" s="2" t="n">
-        <v>46080.48479251795</v>
+        <v>46080.48479252315</v>
       </c>
       <c r="K1514" t="inlineStr">
         <is>
@@ -77695,7 +77695,7 @@
         </is>
       </c>
       <c r="J1515" s="2" t="n">
-        <v>46060.69312585449</v>
+        <v>46060.69312585648</v>
       </c>
       <c r="K1515" t="inlineStr">
         <is>
@@ -77746,7 +77746,7 @@
         </is>
       </c>
       <c r="J1516" s="2" t="n">
-        <v>46088.60979252449</v>
+        <v>46088.60979252315</v>
       </c>
       <c r="K1516" t="inlineStr">
         <is>
@@ -77797,7 +77797,7 @@
         </is>
       </c>
       <c r="J1517" s="2" t="n">
-        <v>46064.69312586108</v>
+        <v>46064.69312585648</v>
       </c>
       <c r="K1517" t="inlineStr">
         <is>
@@ -77848,7 +77848,7 @@
         </is>
       </c>
       <c r="J1518" s="2" t="n">
-        <v>46067.73479253083</v>
+        <v>46067.73479253472</v>
       </c>
       <c r="K1518" t="inlineStr">
         <is>
@@ -77899,7 +77899,7 @@
         </is>
       </c>
       <c r="J1519" s="2" t="n">
-        <v>46067.69312586734</v>
+        <v>46067.69312586806</v>
       </c>
       <c r="K1519" t="inlineStr">
         <is>
@@ -77950,7 +77950,7 @@
         </is>
       </c>
       <c r="J1520" s="2" t="n">
-        <v>46064.73479253714</v>
+        <v>46064.73479253472</v>
       </c>
       <c r="K1520" t="inlineStr">
         <is>
@@ -78001,7 +78001,7 @@
         </is>
       </c>
       <c r="J1521" s="2" t="n">
-        <v>46066.69312587352</v>
+        <v>46066.69312586806</v>
       </c>
       <c r="K1521" t="inlineStr">
         <is>
@@ -78052,7 +78052,7 @@
         </is>
       </c>
       <c r="J1522" s="2" t="n">
-        <v>46089.73479254323</v>
+        <v>46089.7347925463</v>
       </c>
       <c r="K1522" t="inlineStr">
         <is>
@@ -78103,7 +78103,7 @@
         </is>
       </c>
       <c r="J1523" s="2" t="n">
-        <v>46076.73479254648</v>
+        <v>46076.7347925463</v>
       </c>
       <c r="K1523" t="inlineStr">
         <is>
@@ -78154,7 +78154,7 @@
         </is>
       </c>
       <c r="J1524" s="2" t="n">
-        <v>46071.56812588294</v>
+        <v>46071.56812587963</v>
       </c>
       <c r="K1524" t="inlineStr">
         <is>
@@ -78205,7 +78205,7 @@
         </is>
       </c>
       <c r="J1525" s="2" t="n">
-        <v>46068.81812588588</v>
+        <v>46068.8181258912</v>
       </c>
       <c r="K1525" t="inlineStr">
         <is>
@@ -78256,7 +78256,7 @@
         </is>
       </c>
       <c r="J1526" s="2" t="n">
-        <v>46072.48479255572</v>
+        <v>46072.48479255787</v>
       </c>
       <c r="K1526" t="inlineStr">
         <is>
@@ -78307,7 +78307,7 @@
         </is>
       </c>
       <c r="J1527" s="2" t="n">
-        <v>46061.73479255912</v>
+        <v>46061.73479255787</v>
       </c>
       <c r="K1527" t="inlineStr">
         <is>
@@ -78358,7 +78358,7 @@
         </is>
       </c>
       <c r="J1528" s="2" t="n">
-        <v>46079.48479256217</v>
+        <v>46079.48479255787</v>
       </c>
       <c r="K1528" t="inlineStr">
         <is>
@@ -78409,7 +78409,7 @@
         </is>
       </c>
       <c r="J1529" s="2" t="n">
-        <v>46086.7764592319</v>
+        <v>46086.77645923611</v>
       </c>
       <c r="K1529" t="inlineStr">
         <is>
@@ -78460,7 +78460,7 @@
         </is>
       </c>
       <c r="J1530" s="2" t="n">
-        <v>46061.81812590175</v>
+        <v>46061.81812590278</v>
       </c>
       <c r="K1530" t="inlineStr">
         <is>
@@ -78511,7 +78511,7 @@
         </is>
       </c>
       <c r="J1531" s="2" t="n">
-        <v>46080.81812590487</v>
+        <v>46080.81812590278</v>
       </c>
       <c r="K1531" t="inlineStr">
         <is>
@@ -78562,7 +78562,7 @@
         </is>
       </c>
       <c r="J1532" s="2" t="n">
-        <v>46081.77645924145</v>
+        <v>46081.77645923611</v>
       </c>
       <c r="K1532" t="inlineStr">
         <is>
@@ -78613,7 +78613,7 @@
         </is>
       </c>
       <c r="J1533" s="2" t="n">
-        <v>46065.56812591136</v>
+        <v>46065.56812591435</v>
       </c>
       <c r="K1533" t="inlineStr">
         <is>
@@ -78664,7 +78664,7 @@
         </is>
       </c>
       <c r="J1534" s="2" t="n">
-        <v>46082.73479258129</v>
+        <v>46082.73479258102</v>
       </c>
       <c r="K1534" t="inlineStr">
         <is>
@@ -78715,7 +78715,7 @@
         </is>
       </c>
       <c r="J1535" s="2" t="n">
-        <v>46082.60979258436</v>
+        <v>46082.60979258102</v>
       </c>
       <c r="K1535" t="inlineStr">
         <is>
@@ -78766,7 +78766,7 @@
         </is>
       </c>
       <c r="J1536" s="2" t="n">
-        <v>46072.8597925875</v>
+        <v>46072.85979259259</v>
       </c>
       <c r="K1536" t="inlineStr">
         <is>
@@ -78817,7 +78817,7 @@
         </is>
       </c>
       <c r="J1537" s="2" t="n">
-        <v>46069.60979259075</v>
+        <v>46069.60979259259</v>
       </c>
       <c r="K1537" t="inlineStr">
         <is>
@@ -78868,7 +78868,7 @@
         </is>
       </c>
       <c r="J1538" s="2" t="n">
-        <v>46082.60979259395</v>
+        <v>46082.60979259259</v>
       </c>
       <c r="K1538" t="inlineStr">
         <is>
@@ -78919,7 +78919,7 @@
         </is>
       </c>
       <c r="J1539" s="2" t="n">
-        <v>46088.77645926388</v>
+        <v>46088.77645925926</v>
       </c>
       <c r="K1539" t="inlineStr">
         <is>
@@ -78970,7 +78970,7 @@
         </is>
       </c>
       <c r="J1540" s="2" t="n">
-        <v>46071.69312593353</v>
+        <v>46071.6931259375</v>
       </c>
       <c r="K1540" t="inlineStr">
         <is>
@@ -79021,7 +79021,7 @@
         </is>
       </c>
       <c r="J1541" s="2" t="n">
-        <v>46087.7347926036</v>
+        <v>46087.73479260417</v>
       </c>
       <c r="K1541" t="inlineStr">
         <is>
@@ -79072,7 +79072,7 @@
         </is>
       </c>
       <c r="J1542" s="2" t="n">
-        <v>46071.52645927331</v>
+        <v>46071.52645927083</v>
       </c>
       <c r="K1542" t="inlineStr">
         <is>
@@ -79123,7 +79123,7 @@
         </is>
       </c>
       <c r="J1543" s="2" t="n">
-        <v>46080.69312594321</v>
+        <v>46080.6931259375</v>
       </c>
       <c r="K1543" t="inlineStr">
         <is>
@@ -79174,7 +79174,7 @@
         </is>
       </c>
       <c r="J1544" s="2" t="n">
-        <v>46065.85979261299</v>
+        <v>46065.85979261574</v>
       </c>
       <c r="K1544" t="inlineStr">
         <is>
@@ -79225,7 +79225,7 @@
         </is>
       </c>
       <c r="J1545" s="2" t="n">
-        <v>46070.52645928298</v>
+        <v>46070.52645928241</v>
       </c>
       <c r="K1545" t="inlineStr">
         <is>
@@ -79276,7 +79276,7 @@
         </is>
       </c>
       <c r="J1546" s="2" t="n">
-        <v>46076.6514592861</v>
+        <v>46076.65145928241</v>
       </c>
       <c r="K1546" t="inlineStr">
         <is>
@@ -79327,7 +79327,7 @@
         </is>
       </c>
       <c r="J1547" s="2" t="n">
-        <v>46067.81812595594</v>
+        <v>46067.81812596065</v>
       </c>
       <c r="K1547" t="inlineStr">
         <is>
@@ -79378,7 +79378,7 @@
         </is>
       </c>
       <c r="J1548" s="2" t="n">
-        <v>46089.6097926258</v>
+        <v>46089.60979262731</v>
       </c>
       <c r="K1548" t="inlineStr">
         <is>
@@ -79429,7 +79429,7 @@
         </is>
       </c>
       <c r="J1549" s="2" t="n">
-        <v>46074.609792629</v>
+        <v>46074.60979262731</v>
       </c>
       <c r="K1549" t="inlineStr">
         <is>
@@ -79480,7 +79480,7 @@
         </is>
       </c>
       <c r="J1550" s="2" t="n">
-        <v>46086.6097926322</v>
+        <v>46086.60979262731</v>
       </c>
       <c r="K1550" t="inlineStr">
         <is>
@@ -79531,11 +79531,2561 @@
         </is>
       </c>
       <c r="J1551" s="2" t="n">
-        <v>46076.7347926353</v>
+        <v>46076.73479263889</v>
       </c>
       <c r="K1551" t="inlineStr">
         <is>
           <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>52277492-7343-4806-8b6f-ae0a523acac8</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>82a04c67-3eb9-4673-88bf-14fe0b9482d0</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1552" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1552" t="inlineStr">
+        <is>
+          <t>OP-651</t>
+        </is>
+      </c>
+      <c r="I1552" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1552" s="2" t="n">
+        <v>46063.77064938827</v>
+      </c>
+      <c r="K1552" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>d13a24e3-7114-44f7-9d07-b96269c289b9</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>bc321edc-229c-4a48-8a7a-7ccdfa5dae42</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1553" t="inlineStr">
+        <is>
+          <t>OP-138</t>
+        </is>
+      </c>
+      <c r="I1553" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1553" s="2" t="n">
+        <v>46072.60398272613</v>
+      </c>
+      <c r="K1553" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>00757a26-b05f-4463-9b59-e9647d754958</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>74242ec0-3458-4f01-b43e-6361481a7820</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1554" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1554" t="inlineStr">
+        <is>
+          <t>OP-115</t>
+        </is>
+      </c>
+      <c r="I1554" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1554" s="2" t="n">
+        <v>46072.56231606295</v>
+      </c>
+      <c r="K1554" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>a8cbdcb8-f7c0-4064-ac3f-cacf1a19be60</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>6a15ed7f-1488-43dc-9bcd-f89dc4094bb7</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1555" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1555" t="inlineStr">
+        <is>
+          <t>OP-747</t>
+        </is>
+      </c>
+      <c r="I1555" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1555" s="2" t="n">
+        <v>46077.89564939943</v>
+      </c>
+      <c r="K1555" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>7e02a8be-4671-49f3-9943-37845bac2a11</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>dd7074f7-f55f-499a-9a38-baebcd56a308</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1556" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1556" t="inlineStr">
+        <is>
+          <t>OP-116</t>
+        </is>
+      </c>
+      <c r="I1556" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1556" s="2" t="n">
+        <v>46082.81231606951</v>
+      </c>
+      <c r="K1556" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>3df26bd7-7997-465d-b59e-75e90f378c65</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>719684b9-50eb-4921-8d7d-df59fbf67eb1</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1557" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1557" t="inlineStr">
+        <is>
+          <t>OP-829</t>
+        </is>
+      </c>
+      <c r="I1557" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1557" s="2" t="n">
+        <v>46069.64564940595</v>
+      </c>
+      <c r="K1557" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>c6ba1236-447a-44e6-8e1f-7eb7968d5044</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>61bc4fe3-444b-4de9-8927-f46d060dd889</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1558" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1558" t="inlineStr">
+        <is>
+          <t>OP-851</t>
+        </is>
+      </c>
+      <c r="I1558" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1558" s="2" t="n">
+        <v>46089.64564940913</v>
+      </c>
+      <c r="K1558" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>05a6e876-1693-466f-bebe-c351dbf127f9</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>2edebf3a-a0bc-471d-a3d7-6cc9e69b978a</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1559" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1559" t="inlineStr">
+        <is>
+          <t>OP-204</t>
+        </is>
+      </c>
+      <c r="I1559" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1559" s="2" t="n">
+        <v>46081.81231607906</v>
+      </c>
+      <c r="K1559" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>697e02f0-4f19-411a-b1af-59ec445137e0</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>fcf166d5-2662-4fa3-afee-125d1ccc8631</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1560" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1560" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1560" t="inlineStr">
+        <is>
+          <t>OP-345</t>
+        </is>
+      </c>
+      <c r="I1560" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1560" s="2" t="n">
+        <v>46063.81231608216</v>
+      </c>
+      <c r="K1560" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>24142ede-4891-4870-98af-595ed4d0f8c4</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>e86d0ec7-ac06-486c-82e6-690e23bef1ea</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1561" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1561" t="inlineStr">
+        <is>
+          <t>OP-777</t>
+        </is>
+      </c>
+      <c r="I1561" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1561" s="2" t="n">
+        <v>46075.85398275188</v>
+      </c>
+      <c r="K1561" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>4f81b5f1-ff5a-4fa9-a514-2bb01be641bb</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>0764d7a0-740e-4595-b8f4-a312b615c481</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1562" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1562" t="inlineStr">
+        <is>
+          <t>OP-864</t>
+        </is>
+      </c>
+      <c r="I1562" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1562" s="2" t="n">
+        <v>46069.52064942173</v>
+      </c>
+      <c r="K1562" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>fb1e03fb-73ff-44b7-a18f-cfa073b81888</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>cf4be5de-aebb-446f-8587-59dd8f0af58f</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1563" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1563" t="inlineStr">
+        <is>
+          <t>OP-110</t>
+        </is>
+      </c>
+      <c r="I1563" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1563" s="2" t="n">
+        <v>46078.81231609193</v>
+      </c>
+      <c r="K1563" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>7ba80c18-ada9-4beb-b01a-f9df40e07ddb</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>3947e43a-1719-4984-8e3b-590345bee770</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1564" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1564" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1564" t="inlineStr">
+        <is>
+          <t>OP-580</t>
+        </is>
+      </c>
+      <c r="I1564" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1564" s="2" t="n">
+        <v>46078.68731609503</v>
+      </c>
+      <c r="K1564" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>0bfad8c2-a45f-4f72-9da4-84fe28bf4000</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>a31213b1-2755-4cf7-941b-a941ea08f7eb</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1565" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1565" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1565" t="inlineStr">
+        <is>
+          <t>OP-450</t>
+        </is>
+      </c>
+      <c r="I1565" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1565" s="2" t="n">
+        <v>46069.56231609808</v>
+      </c>
+      <c r="K1565" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>72c75ac2-0bc4-481b-875d-b551b47029d8</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>193650e0-91a8-4f3c-be49-a665fdab8769</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1566" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1566" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1566" t="inlineStr">
+        <is>
+          <t>OP-564</t>
+        </is>
+      </c>
+      <c r="I1566" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1566" s="2" t="n">
+        <v>46062.52064943448</v>
+      </c>
+      <c r="K1566" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>68fa7cfc-537e-42b5-8e93-c7edbe9ac1c2</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>720bc1c3-dad2-4482-9965-ca1e6c36cea1</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1567" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1567" t="inlineStr">
+        <is>
+          <t>OP-659</t>
+        </is>
+      </c>
+      <c r="I1567" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1567" s="2" t="n">
+        <v>46074.52064943776</v>
+      </c>
+      <c r="K1567" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>b7e30e79-c287-473c-9587-f70504e93fa3</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>4d458f3a-1eb5-4cd7-9a97-e5c9c55b53b3</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1568" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1568" t="inlineStr">
+        <is>
+          <t>OP-771</t>
+        </is>
+      </c>
+      <c r="I1568" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1568" s="2" t="n">
+        <v>46071.8123161075</v>
+      </c>
+      <c r="K1568" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>9b4caafc-fd95-4ba3-a631-e4b937e1372c</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>082aafa9-f9b3-4446-ab72-679767d04d66</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1569" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1569" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1569" t="inlineStr">
+        <is>
+          <t>OP-633</t>
+        </is>
+      </c>
+      <c r="I1569" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1569" s="2" t="n">
+        <v>46082.72898277719</v>
+      </c>
+      <c r="K1569" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>77924066-147b-4510-893e-cf246d7385ad</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>1c7f08a8-3072-425e-b5bf-5ff9fd546ad6</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1570" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1570" t="inlineStr">
+        <is>
+          <t>OP-605</t>
+        </is>
+      </c>
+      <c r="I1570" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1570" s="2" t="n">
+        <v>46065.56231611404</v>
+      </c>
+      <c r="K1570" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>ea0e7a72-f51b-4b01-87ff-a0ad1bff0a7e</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>7d5d970d-04cd-46e0-9ff8-4d554d8dd0ad</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1571" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1571" t="inlineStr">
+        <is>
+          <t>OP-599</t>
+        </is>
+      </c>
+      <c r="I1571" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1571" s="2" t="n">
+        <v>46068.72898278375</v>
+      </c>
+      <c r="K1571" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2a0696b5-f0af-4e06-af20-5eb407209d09</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>f93b9637-5fe6-44bd-b6a6-6e35bb967566</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1572" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1572" t="inlineStr">
+        <is>
+          <t>OP-866</t>
+        </is>
+      </c>
+      <c r="I1572" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1572" s="2" t="n">
+        <v>46066.64564945344</v>
+      </c>
+      <c r="K1572" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>024d6d82-8caa-4a30-8c76-65a5197d3abe</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>2283e264-2c0c-4706-84bf-a0f47e6d5822</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1573" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1573" t="inlineStr">
+        <is>
+          <t>OP-733</t>
+        </is>
+      </c>
+      <c r="I1573" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1573" s="2" t="n">
+        <v>46068.72898278983</v>
+      </c>
+      <c r="K1573" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>da3de8ae-c926-4522-92bc-8000adafb51d</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>16d47716-e177-4925-85d6-3e3b3b47f9e5</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1574" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1574" t="inlineStr">
+        <is>
+          <t>OP-149</t>
+        </is>
+      </c>
+      <c r="I1574" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1574" s="2" t="n">
+        <v>46077.68731612641</v>
+      </c>
+      <c r="K1574" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>25c157b9-93f2-46cf-8d1b-c293196792e6</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>502664f9-7266-48cd-90d2-f3367666cbc8</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1575" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1575" t="inlineStr">
+        <is>
+          <t>OP-130</t>
+        </is>
+      </c>
+      <c r="I1575" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1575" s="2" t="n">
+        <v>46072.72898279614</v>
+      </c>
+      <c r="K1575" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>185d2ab1-a646-44c2-8581-8443ef8a1b64</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>8332fc06-6930-41a0-8cd7-e905465ad935</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1576" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1576" t="inlineStr">
+        <is>
+          <t>OP-326</t>
+        </is>
+      </c>
+      <c r="I1576" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1576" s="2" t="n">
+        <v>46069.81231613263</v>
+      </c>
+      <c r="K1576" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>774a9a7b-f22c-4d97-a1be-3b4f7fd0e1ee</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>3d27dd1a-a56c-44c2-93ed-e25c132aba62</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1577" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>OP-296</t>
+        </is>
+      </c>
+      <c r="I1577" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1577" s="2" t="n">
+        <v>46082.81231613571</v>
+      </c>
+      <c r="K1577" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>c74de2e7-9852-44c9-b4a8-1447a4538de1</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>eeb6d8a2-aca3-457c-b5a4-c9dc228e6bcb</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1578" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1578" t="inlineStr">
+        <is>
+          <t>OP-837</t>
+        </is>
+      </c>
+      <c r="I1578" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1578" s="2" t="n">
+        <v>46070.64564947234</v>
+      </c>
+      <c r="K1578" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>6150ef61-763d-4e24-9ba9-f2e300fc7fd1</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>e9d3dd75-88ee-4c15-98bf-2aa2dfcdd8a9</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1579" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1579" t="inlineStr">
+        <is>
+          <t>OP-381</t>
+        </is>
+      </c>
+      <c r="I1579" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1579" s="2" t="n">
+        <v>46089.72898280869</v>
+      </c>
+      <c r="K1579" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>260f6921-5977-4081-be53-2d1c45b3a5ed</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>738cf86d-19ef-474a-81f0-90e94185d453</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1580" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1580" t="inlineStr">
+        <is>
+          <t>OP-753</t>
+        </is>
+      </c>
+      <c r="I1580" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1580" s="2" t="n">
+        <v>46089.81231614517</v>
+      </c>
+      <c r="K1580" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>147a2415-3261-407f-90e6-797440fca82d</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>5290939c-4ef1-4dec-b2fd-79ecd4a0c8f4</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1581" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1581" t="inlineStr">
+        <is>
+          <t>OP-839</t>
+        </is>
+      </c>
+      <c r="I1581" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1581" s="2" t="n">
+        <v>46066.77064948171</v>
+      </c>
+      <c r="K1581" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>b29fcd59-b942-4d57-9d6d-7e2d3cae8780</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>84793907-d425-4b5f-84e1-58f5fec4d756</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1582" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1582" t="inlineStr">
+        <is>
+          <t>OP-376</t>
+        </is>
+      </c>
+      <c r="I1582" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1582" s="2" t="n">
+        <v>46075.72898281834</v>
+      </c>
+      <c r="K1582" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>ba0f3148-7657-4353-b358-d29b30ce5785</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>c9e2e540-1006-48f0-936a-c96df820744d</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1583" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1583" t="inlineStr">
+        <is>
+          <t>OP-695</t>
+        </is>
+      </c>
+      <c r="I1583" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1583" s="2" t="n">
+        <v>46080.68731615464</v>
+      </c>
+      <c r="K1583" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>8940feeb-2c62-429f-b822-d9e0b5f402f3</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>b91551f5-2bd3-4247-9bfc-33cd1149855d</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1584" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1584" t="inlineStr">
+        <is>
+          <t>OP-429</t>
+        </is>
+      </c>
+      <c r="I1584" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1584" s="2" t="n">
+        <v>46070.64564949115</v>
+      </c>
+      <c r="K1584" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>9e926289-3893-47b4-8cb5-54910ccd4afa</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>8b635b57-5a39-4409-85a4-930bcbe379bc</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1585" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1585" t="inlineStr">
+        <is>
+          <t>OP-573</t>
+        </is>
+      </c>
+      <c r="I1585" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1585" s="2" t="n">
+        <v>46080.56231616112</v>
+      </c>
+      <c r="K1585" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>b021837f-d769-4011-ac3f-ed5571b146ee</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>96139e9b-077f-40a8-85ae-3e5a5b8a6d9e</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1586" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>OP-936</t>
+        </is>
+      </c>
+      <c r="I1586" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1586" s="2" t="n">
+        <v>46082.64564949764</v>
+      </c>
+      <c r="K1586" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>40560178-d7d7-44b9-8dd1-eb260d1a864b</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>28baa84b-0ac2-4aea-aa21-2e15271c2448</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1587" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1587" t="inlineStr">
+        <is>
+          <t>OP-919</t>
+        </is>
+      </c>
+      <c r="I1587" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1587" s="2" t="n">
+        <v>46067.56231616739</v>
+      </c>
+      <c r="K1587" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>4aabeb69-808c-4cde-8ea3-04f1c445061c</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>b32bc3c0-6835-47dd-aaac-ba5a8e64d1b6</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1588" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1588" t="inlineStr">
+        <is>
+          <t>OP-887</t>
+        </is>
+      </c>
+      <c r="I1588" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1588" s="2" t="n">
+        <v>46082.72898283718</v>
+      </c>
+      <c r="K1588" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>457b6ccc-f1eb-4388-9b4b-beb66d0afb9e</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>ec72b444-4f6f-4213-ba14-fae0813369f7</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1589" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1589" t="inlineStr">
+        <is>
+          <t>OP-599</t>
+        </is>
+      </c>
+      <c r="I1589" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1589" s="2" t="n">
+        <v>46064.5206495071</v>
+      </c>
+      <c r="K1589" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>1168dda8-1ead-4a67-82ef-5910ae610831</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>a96c54e6-05b1-41e9-b2a2-af1197dfb230</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1590" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1590" t="inlineStr">
+        <is>
+          <t>OP-882</t>
+        </is>
+      </c>
+      <c r="I1590" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1590" s="2" t="n">
+        <v>46070.77064951023</v>
+      </c>
+      <c r="K1590" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>34cf438d-44d7-4975-bf29-7710565c2558</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>0891ead1-2926-4a13-b395-b43c4eb0f483</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1591" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1591" t="inlineStr">
+        <is>
+          <t>OP-285</t>
+        </is>
+      </c>
+      <c r="I1591" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1591" s="2" t="n">
+        <v>46071.68731618</v>
+      </c>
+      <c r="K1591" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>b580acea-d36f-4ae2-816d-8048dee0ffe4</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>95a0cdad-0d8e-455e-aba0-20fb0e569294</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1592" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1592" t="inlineStr">
+        <is>
+          <t>OP-799</t>
+        </is>
+      </c>
+      <c r="I1592" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1592" s="2" t="n">
+        <v>46075.77064951656</v>
+      </c>
+      <c r="K1592" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>d24e0f46-2993-4eab-8f95-0597c8af961e</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>87009d6e-a488-4d92-8aec-f096f0c3402c</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1593" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1593" t="inlineStr">
+        <is>
+          <t>OP-501</t>
+        </is>
+      </c>
+      <c r="I1593" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1593" s="2" t="n">
+        <v>46080.56231618626</v>
+      </c>
+      <c r="K1593" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>1e379c25-d307-42da-8850-a3f886ea5075</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>8dff7b50-f382-49bc-8f61-18e5bb86a257</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1594" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1594" t="inlineStr">
+        <is>
+          <t>OP-990</t>
+        </is>
+      </c>
+      <c r="I1594" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1594" s="2" t="n">
+        <v>46067.89564952277</v>
+      </c>
+      <c r="K1594" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>a74dc66e-7e6d-40b5-8096-48d315560404</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>1797cd90-3237-4bf7-9f2d-930a28ce0af5</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1595" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1595" t="inlineStr">
+        <is>
+          <t>OP-670</t>
+        </is>
+      </c>
+      <c r="I1595" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1595" s="2" t="n">
+        <v>46086.72898285909</v>
+      </c>
+      <c r="K1595" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>3662a14a-18df-41c0-bf38-9fd9e3abf61e</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>53c97ff1-4f0f-4243-aee9-b8db6686cbc9</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1596" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1596" t="inlineStr">
+        <is>
+          <t>OP-642</t>
+        </is>
+      </c>
+      <c r="I1596" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1596" s="2" t="n">
+        <v>46076.56231619621</v>
+      </c>
+      <c r="K1596" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>0a759255-bbe1-44f2-9594-aec20f2a8d54</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>13f88061-a8b6-4caf-b9e3-fe48dc8e0eeb</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1597" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1597" t="inlineStr">
+        <is>
+          <t>OP-542</t>
+        </is>
+      </c>
+      <c r="I1597" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1597" s="2" t="n">
+        <v>46078.68731619942</v>
+      </c>
+      <c r="K1597" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>b9862900-5607-4b9c-a2e1-43b989d49fa4</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>7fde1eef-84f6-412e-8763-a6e019dc7398</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1598" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F1598" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>OP-927</t>
+        </is>
+      </c>
+      <c r="I1598" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1598" s="2" t="n">
+        <v>46088.68731620242</v>
+      </c>
+      <c r="K1598" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>567d1392-7f70-4ec4-bed0-94c744c6179f</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>b022749b-faf7-43aa-ac2d-48ecdd214338</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1599" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1599" t="inlineStr">
+        <is>
+          <t>OP-790</t>
+        </is>
+      </c>
+      <c r="I1599" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1599" s="2" t="n">
+        <v>46076.89564953899</v>
+      </c>
+      <c r="K1599" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>7980b7ab-4de6-4f39-855e-b4f0e23ad811</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>009aab46-bbae-408d-898f-aff157ab4e90</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1600" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1600" t="inlineStr">
+        <is>
+          <t>OP-520</t>
+        </is>
+      </c>
+      <c r="I1600" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1600" s="2" t="n">
+        <v>46075.52064954201</v>
+      </c>
+      <c r="K1600" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>8696dffe-bf0d-48a3-b1fa-1e170a798c8f</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>ac3cb701-ca53-445f-8bb9-7f7ceb1d846d</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1601" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1601" t="inlineStr">
+        <is>
+          <t>OP-287</t>
+        </is>
+      </c>
+      <c r="I1601" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1601" s="2" t="n">
+        <v>46083.68731621286</v>
+      </c>
+      <c r="K1601" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1601"/>
+  <dimension ref="A1:K1651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79582,7 +79582,7 @@
         </is>
       </c>
       <c r="J1552" s="2" t="n">
-        <v>46063.77064938827</v>
+        <v>46063.77064938658</v>
       </c>
       <c r="K1552" t="inlineStr">
         <is>
@@ -79633,7 +79633,7 @@
         </is>
       </c>
       <c r="J1553" s="2" t="n">
-        <v>46072.60398272613</v>
+        <v>46072.60398273148</v>
       </c>
       <c r="K1553" t="inlineStr">
         <is>
@@ -79684,7 +79684,7 @@
         </is>
       </c>
       <c r="J1554" s="2" t="n">
-        <v>46072.56231606295</v>
+        <v>46072.56231606482</v>
       </c>
       <c r="K1554" t="inlineStr">
         <is>
@@ -79735,7 +79735,7 @@
         </is>
       </c>
       <c r="J1555" s="2" t="n">
-        <v>46077.89564939943</v>
+        <v>46077.89564939815</v>
       </c>
       <c r="K1555" t="inlineStr">
         <is>
@@ -79786,7 +79786,7 @@
         </is>
       </c>
       <c r="J1556" s="2" t="n">
-        <v>46082.81231606951</v>
+        <v>46082.81231606482</v>
       </c>
       <c r="K1556" t="inlineStr">
         <is>
@@ -79837,7 +79837,7 @@
         </is>
       </c>
       <c r="J1557" s="2" t="n">
-        <v>46069.64564940595</v>
+        <v>46069.64564940972</v>
       </c>
       <c r="K1557" t="inlineStr">
         <is>
@@ -79888,7 +79888,7 @@
         </is>
       </c>
       <c r="J1558" s="2" t="n">
-        <v>46089.64564940913</v>
+        <v>46089.64564940972</v>
       </c>
       <c r="K1558" t="inlineStr">
         <is>
@@ -79939,7 +79939,7 @@
         </is>
       </c>
       <c r="J1559" s="2" t="n">
-        <v>46081.81231607906</v>
+        <v>46081.81231607639</v>
       </c>
       <c r="K1559" t="inlineStr">
         <is>
@@ -79990,7 +79990,7 @@
         </is>
       </c>
       <c r="J1560" s="2" t="n">
-        <v>46063.81231608216</v>
+        <v>46063.81231607639</v>
       </c>
       <c r="K1560" t="inlineStr">
         <is>
@@ -80041,7 +80041,7 @@
         </is>
       </c>
       <c r="J1561" s="2" t="n">
-        <v>46075.85398275188</v>
+        <v>46075.85398275463</v>
       </c>
       <c r="K1561" t="inlineStr">
         <is>
@@ -80092,7 +80092,7 @@
         </is>
       </c>
       <c r="J1562" s="2" t="n">
-        <v>46069.52064942173</v>
+        <v>46069.5206494213</v>
       </c>
       <c r="K1562" t="inlineStr">
         <is>
@@ -80143,7 +80143,7 @@
         </is>
       </c>
       <c r="J1563" s="2" t="n">
-        <v>46078.81231609193</v>
+        <v>46078.81231608796</v>
       </c>
       <c r="K1563" t="inlineStr">
         <is>
@@ -80194,7 +80194,7 @@
         </is>
       </c>
       <c r="J1564" s="2" t="n">
-        <v>46078.68731609503</v>
+        <v>46078.68731609954</v>
       </c>
       <c r="K1564" t="inlineStr">
         <is>
@@ -80245,7 +80245,7 @@
         </is>
       </c>
       <c r="J1565" s="2" t="n">
-        <v>46069.56231609808</v>
+        <v>46069.56231609954</v>
       </c>
       <c r="K1565" t="inlineStr">
         <is>
@@ -80296,7 +80296,7 @@
         </is>
       </c>
       <c r="J1566" s="2" t="n">
-        <v>46062.52064943448</v>
+        <v>46062.52064943287</v>
       </c>
       <c r="K1566" t="inlineStr">
         <is>
@@ -80347,7 +80347,7 @@
         </is>
       </c>
       <c r="J1567" s="2" t="n">
-        <v>46074.52064943776</v>
+        <v>46074.52064943287</v>
       </c>
       <c r="K1567" t="inlineStr">
         <is>
@@ -80398,7 +80398,7 @@
         </is>
       </c>
       <c r="J1568" s="2" t="n">
-        <v>46071.8123161075</v>
+        <v>46071.81231611111</v>
       </c>
       <c r="K1568" t="inlineStr">
         <is>
@@ -80449,7 +80449,7 @@
         </is>
       </c>
       <c r="J1569" s="2" t="n">
-        <v>46082.72898277719</v>
+        <v>46082.72898277778</v>
       </c>
       <c r="K1569" t="inlineStr">
         <is>
@@ -80500,7 +80500,7 @@
         </is>
       </c>
       <c r="J1570" s="2" t="n">
-        <v>46065.56231611404</v>
+        <v>46065.56231611111</v>
       </c>
       <c r="K1570" t="inlineStr">
         <is>
@@ -80551,7 +80551,7 @@
         </is>
       </c>
       <c r="J1571" s="2" t="n">
-        <v>46068.72898278375</v>
+        <v>46068.72898278935</v>
       </c>
       <c r="K1571" t="inlineStr">
         <is>
@@ -80602,7 +80602,7 @@
         </is>
       </c>
       <c r="J1572" s="2" t="n">
-        <v>46066.64564945344</v>
+        <v>46066.64564945602</v>
       </c>
       <c r="K1572" t="inlineStr">
         <is>
@@ -80653,7 +80653,7 @@
         </is>
       </c>
       <c r="J1573" s="2" t="n">
-        <v>46068.72898278983</v>
+        <v>46068.72898278935</v>
       </c>
       <c r="K1573" t="inlineStr">
         <is>
@@ -80704,7 +80704,7 @@
         </is>
       </c>
       <c r="J1574" s="2" t="n">
-        <v>46077.68731612641</v>
+        <v>46077.68731612268</v>
       </c>
       <c r="K1574" t="inlineStr">
         <is>
@@ -80755,7 +80755,7 @@
         </is>
       </c>
       <c r="J1575" s="2" t="n">
-        <v>46072.72898279614</v>
+        <v>46072.72898280092</v>
       </c>
       <c r="K1575" t="inlineStr">
         <is>
@@ -80806,7 +80806,7 @@
         </is>
       </c>
       <c r="J1576" s="2" t="n">
-        <v>46069.81231613263</v>
+        <v>46069.81231613426</v>
       </c>
       <c r="K1576" t="inlineStr">
         <is>
@@ -80857,7 +80857,7 @@
         </is>
       </c>
       <c r="J1577" s="2" t="n">
-        <v>46082.81231613571</v>
+        <v>46082.81231613426</v>
       </c>
       <c r="K1577" t="inlineStr">
         <is>
@@ -80908,7 +80908,7 @@
         </is>
       </c>
       <c r="J1578" s="2" t="n">
-        <v>46070.64564947234</v>
+        <v>46070.64564946759</v>
       </c>
       <c r="K1578" t="inlineStr">
         <is>
@@ -80959,7 +80959,7 @@
         </is>
       </c>
       <c r="J1579" s="2" t="n">
-        <v>46089.72898280869</v>
+        <v>46089.7289828125</v>
       </c>
       <c r="K1579" t="inlineStr">
         <is>
@@ -81010,7 +81010,7 @@
         </is>
       </c>
       <c r="J1580" s="2" t="n">
-        <v>46089.81231614517</v>
+        <v>46089.81231614584</v>
       </c>
       <c r="K1580" t="inlineStr">
         <is>
@@ -81061,7 +81061,7 @@
         </is>
       </c>
       <c r="J1581" s="2" t="n">
-        <v>46066.77064948171</v>
+        <v>46066.77064947916</v>
       </c>
       <c r="K1581" t="inlineStr">
         <is>
@@ -81112,7 +81112,7 @@
         </is>
       </c>
       <c r="J1582" s="2" t="n">
-        <v>46075.72898281834</v>
+        <v>46075.72898282408</v>
       </c>
       <c r="K1582" t="inlineStr">
         <is>
@@ -81163,7 +81163,7 @@
         </is>
       </c>
       <c r="J1583" s="2" t="n">
-        <v>46080.68731615464</v>
+        <v>46080.6873161574</v>
       </c>
       <c r="K1583" t="inlineStr">
         <is>
@@ -81214,7 +81214,7 @@
         </is>
       </c>
       <c r="J1584" s="2" t="n">
-        <v>46070.64564949115</v>
+        <v>46070.64564949074</v>
       </c>
       <c r="K1584" t="inlineStr">
         <is>
@@ -81265,7 +81265,7 @@
         </is>
       </c>
       <c r="J1585" s="2" t="n">
-        <v>46080.56231616112</v>
+        <v>46080.5623161574</v>
       </c>
       <c r="K1585" t="inlineStr">
         <is>
@@ -81316,7 +81316,7 @@
         </is>
       </c>
       <c r="J1586" s="2" t="n">
-        <v>46082.64564949764</v>
+        <v>46082.64564950232</v>
       </c>
       <c r="K1586" t="inlineStr">
         <is>
@@ -81367,7 +81367,7 @@
         </is>
       </c>
       <c r="J1587" s="2" t="n">
-        <v>46067.56231616739</v>
+        <v>46067.56231616898</v>
       </c>
       <c r="K1587" t="inlineStr">
         <is>
@@ -81418,7 +81418,7 @@
         </is>
       </c>
       <c r="J1588" s="2" t="n">
-        <v>46082.72898283718</v>
+        <v>46082.72898283565</v>
       </c>
       <c r="K1588" t="inlineStr">
         <is>
@@ -81469,7 +81469,7 @@
         </is>
       </c>
       <c r="J1589" s="2" t="n">
-        <v>46064.5206495071</v>
+        <v>46064.52064950232</v>
       </c>
       <c r="K1589" t="inlineStr">
         <is>
@@ -81520,7 +81520,7 @@
         </is>
       </c>
       <c r="J1590" s="2" t="n">
-        <v>46070.77064951023</v>
+        <v>46070.77064951389</v>
       </c>
       <c r="K1590" t="inlineStr">
         <is>
@@ -81571,7 +81571,7 @@
         </is>
       </c>
       <c r="J1591" s="2" t="n">
-        <v>46071.68731618</v>
+        <v>46071.68731618056</v>
       </c>
       <c r="K1591" t="inlineStr">
         <is>
@@ -81622,7 +81622,7 @@
         </is>
       </c>
       <c r="J1592" s="2" t="n">
-        <v>46075.77064951656</v>
+        <v>46075.77064951389</v>
       </c>
       <c r="K1592" t="inlineStr">
         <is>
@@ -81673,7 +81673,7 @@
         </is>
       </c>
       <c r="J1593" s="2" t="n">
-        <v>46080.56231618626</v>
+        <v>46080.56231618056</v>
       </c>
       <c r="K1593" t="inlineStr">
         <is>
@@ -81724,7 +81724,7 @@
         </is>
       </c>
       <c r="J1594" s="2" t="n">
-        <v>46067.89564952277</v>
+        <v>46067.89564952546</v>
       </c>
       <c r="K1594" t="inlineStr">
         <is>
@@ -81775,7 +81775,7 @@
         </is>
       </c>
       <c r="J1595" s="2" t="n">
-        <v>46086.72898285909</v>
+        <v>46086.7289828588</v>
       </c>
       <c r="K1595" t="inlineStr">
         <is>
@@ -81826,7 +81826,7 @@
         </is>
       </c>
       <c r="J1596" s="2" t="n">
-        <v>46076.56231619621</v>
+        <v>46076.56231619213</v>
       </c>
       <c r="K1596" t="inlineStr">
         <is>
@@ -81877,7 +81877,7 @@
         </is>
       </c>
       <c r="J1597" s="2" t="n">
-        <v>46078.68731619942</v>
+        <v>46078.6873162037</v>
       </c>
       <c r="K1597" t="inlineStr">
         <is>
@@ -81928,7 +81928,7 @@
         </is>
       </c>
       <c r="J1598" s="2" t="n">
-        <v>46088.68731620242</v>
+        <v>46088.6873162037</v>
       </c>
       <c r="K1598" t="inlineStr">
         <is>
@@ -81979,7 +81979,7 @@
         </is>
       </c>
       <c r="J1599" s="2" t="n">
-        <v>46076.89564953899</v>
+        <v>46076.89564953704</v>
       </c>
       <c r="K1599" t="inlineStr">
         <is>
@@ -82030,7 +82030,7 @@
         </is>
       </c>
       <c r="J1600" s="2" t="n">
-        <v>46075.52064954201</v>
+        <v>46075.52064953704</v>
       </c>
       <c r="K1600" t="inlineStr">
         <is>
@@ -82081,11 +82081,2561 @@
         </is>
       </c>
       <c r="J1601" s="2" t="n">
-        <v>46083.68731621286</v>
+        <v>46083.68731621528</v>
       </c>
       <c r="K1601" t="inlineStr">
         <is>
           <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>ebab1215-bfd4-4acf-be2b-e71eca0261a5</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>ea1ade11-e0de-457b-bd14-dba10e5b8df1</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1602" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1602" t="inlineStr">
+        <is>
+          <t>OP-772</t>
+        </is>
+      </c>
+      <c r="I1602" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1602" s="2" t="n">
+        <v>46061.570378092</v>
+      </c>
+      <c r="K1602" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>08eb5342-a0e2-4937-ac76-9f3cec44a912</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>2f64b978-cdb5-4011-805c-affa8505dcc3</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1603" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1603" t="inlineStr">
+        <is>
+          <t>OP-758</t>
+        </is>
+      </c>
+      <c r="I1603" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1603" s="2" t="n">
+        <v>46088.86204476283</v>
+      </c>
+      <c r="K1603" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>8922702d-a02a-40f7-9bee-dc9dac64a31c</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>f8ebd807-a83d-48ef-922f-350303dc643c</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1604" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1604" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1604" t="inlineStr">
+        <is>
+          <t>OP-534</t>
+        </is>
+      </c>
+      <c r="I1604" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1604" s="2" t="n">
+        <v>46081.73704476601</v>
+      </c>
+      <c r="K1604" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>4c566872-0d42-4d8d-9d0f-74a4836932c9</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>d2644b10-1e36-4b4c-baea-73611e153056</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1605" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1605" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1605" t="inlineStr">
+        <is>
+          <t>OP-595</t>
+        </is>
+      </c>
+      <c r="I1605" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1605" s="2" t="n">
+        <v>46082.65371143596</v>
+      </c>
+      <c r="K1605" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2335a8f0-f5e7-40e9-a246-b5dcaa1055a8</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>165c2050-dd0b-4d08-bac7-cd9b837c7876</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1606" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F1606" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>OP-738</t>
+        </is>
+      </c>
+      <c r="I1606" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1606" s="2" t="n">
+        <v>46068.94537810552</v>
+      </c>
+      <c r="K1606" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>6cfa323d-4bd6-4b94-b16b-e9c4b052855a</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>2397a646-3569-4429-9221-ca160cf56935</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1607" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1607" t="inlineStr">
+        <is>
+          <t>OP-476</t>
+        </is>
+      </c>
+      <c r="I1607" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1607" s="2" t="n">
+        <v>46073.69537810851</v>
+      </c>
+      <c r="K1607" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>7664df7a-de18-456c-99f7-3bff2be1dc4e</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>4ccf7ba1-aab8-4a4f-8072-14e2df78904b</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1608" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1608" t="inlineStr">
+        <is>
+          <t>OP-704</t>
+        </is>
+      </c>
+      <c r="I1608" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1608" s="2" t="n">
+        <v>46086.69537811175</v>
+      </c>
+      <c r="K1608" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>92e45831-684d-491e-9631-bd7a766e7658</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>aac7b5b9-d2a6-44af-a9ce-62e197ef6ba1</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1609" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1609" t="inlineStr">
+        <is>
+          <t>OP-505</t>
+        </is>
+      </c>
+      <c r="I1609" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1609" s="2" t="n">
+        <v>46084.77871144808</v>
+      </c>
+      <c r="K1609" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>069950e8-83dc-4515-a81b-a94b80b5134b</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>4a8b5bcc-e2e2-4ae4-b750-f12a8a0403e3</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1610" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1610" t="inlineStr">
+        <is>
+          <t>OP-374</t>
+        </is>
+      </c>
+      <c r="I1610" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1610" s="2" t="n">
+        <v>46079.77871145105</v>
+      </c>
+      <c r="K1610" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>de12916e-015b-4a5b-a934-eff1c9d14671</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>4f444683-952d-4d16-9cbf-471e4f5ea548</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1611" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1611" t="inlineStr">
+        <is>
+          <t>OP-500</t>
+        </is>
+      </c>
+      <c r="I1611" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1611" s="2" t="n">
+        <v>46081.73704478729</v>
+      </c>
+      <c r="K1611" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>9a4a17e8-b2dc-46d6-ba3b-821eb5778b4b</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>c6ef6f80-7d7a-4c78-82ad-cdb3b898be49</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1612" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1612" t="inlineStr">
+        <is>
+          <t>OP-212</t>
+        </is>
+      </c>
+      <c r="I1612" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1612" s="2" t="n">
+        <v>46083.73704479045</v>
+      </c>
+      <c r="K1612" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>8ea94bcd-3e3b-464e-99fa-1132cc56b6f9</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>324a63d0-6a77-4c68-b7fc-b0ed62bdf894</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1613" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1613" t="inlineStr">
+        <is>
+          <t>OP-624</t>
+        </is>
+      </c>
+      <c r="I1613" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1613" s="2" t="n">
+        <v>46081.61204479326</v>
+      </c>
+      <c r="K1613" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>66b57d19-2535-40f7-9067-4f2388603821</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>b231d7f9-304a-49b2-aa3f-26c8dc5ca713</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1614" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1614" t="inlineStr">
+        <is>
+          <t>OP-547</t>
+        </is>
+      </c>
+      <c r="I1614" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1614" s="2" t="n">
+        <v>46068.69537812958</v>
+      </c>
+      <c r="K1614" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>cfd99f52-1f53-410b-98c5-73e55d3b2b58</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>51b23182-54fe-408e-b79d-d8a6767491c5</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1615" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1615" t="inlineStr">
+        <is>
+          <t>OP-224</t>
+        </is>
+      </c>
+      <c r="I1615" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1615" s="2" t="n">
+        <v>46082.73704479905</v>
+      </c>
+      <c r="K1615" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>67750f6d-a11a-4295-9fe1-f311c0dbf8a7</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>68d2577e-a351-4963-9504-73eed23780b8</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1616" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1616" t="inlineStr">
+        <is>
+          <t>OP-517</t>
+        </is>
+      </c>
+      <c r="I1616" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1616" s="2" t="n">
+        <v>46072.6537114687</v>
+      </c>
+      <c r="K1616" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>69a4245a-4432-49d3-adb2-d64725df580f</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>5397d209-ec33-4d75-9188-edb617d2a6bd</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1617" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1617" t="inlineStr">
+        <is>
+          <t>OP-822</t>
+        </is>
+      </c>
+      <c r="I1617" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1617" s="2" t="n">
+        <v>46068.8620448049</v>
+      </c>
+      <c r="K1617" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>53a4c2dd-f3e9-4d65-9347-aef81c040d50</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>00a450c1-b452-49f8-8ffd-44980fbab741</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1618" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1618" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1618" t="inlineStr">
+        <is>
+          <t>OP-227</t>
+        </is>
+      </c>
+      <c r="I1618" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1618" s="2" t="n">
+        <v>46073.73704480778</v>
+      </c>
+      <c r="K1618" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>043add4e-b0ce-4b0f-976a-35e5693f9d40</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>e5953e7c-def1-4859-9914-497d9e45a546</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1619" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1619" t="inlineStr">
+        <is>
+          <t>OP-444</t>
+        </is>
+      </c>
+      <c r="I1619" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1619" s="2" t="n">
+        <v>46064.73704481064</v>
+      </c>
+      <c r="K1619" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>af5044ea-79b9-468b-9c76-ee8dacd9a1cf</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>c8c49300-bf43-48b5-9dd4-c026dffbd8fa</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1620" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1620" t="inlineStr">
+        <is>
+          <t>OP-384</t>
+        </is>
+      </c>
+      <c r="I1620" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1620" s="2" t="n">
+        <v>46075.77871148023</v>
+      </c>
+      <c r="K1620" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>4eac3673-d018-4976-89c0-164730ca1e5f</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>8d48a831-a3b9-4c65-a364-03f34843c89b</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1621" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1621" t="inlineStr">
+        <is>
+          <t>OP-998</t>
+        </is>
+      </c>
+      <c r="I1621" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1621" s="2" t="n">
+        <v>46065.82037814968</v>
+      </c>
+      <c r="K1621" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>0eff7296-2071-43df-b8c6-7a641c9a8b7d</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>062773b1-56d2-49db-b88f-9f97350a2fee</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1622" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1622" t="inlineStr">
+        <is>
+          <t>OP-948</t>
+        </is>
+      </c>
+      <c r="I1622" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1622" s="2" t="n">
+        <v>46063.57037815246</v>
+      </c>
+      <c r="K1622" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>4fc8c5cf-3e75-4af0-ac0e-dee9732e0cc4</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>cbac912c-7bac-4388-b743-45016096e1ab</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1623" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F1623" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1623" t="inlineStr">
+        <is>
+          <t>OP-791</t>
+        </is>
+      </c>
+      <c r="I1623" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1623" s="2" t="n">
+        <v>46087.57037815528</v>
+      </c>
+      <c r="K1623" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>9fe9bde6-bd22-43b8-901f-b67e566fd6cf</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>d021f5b2-c8e6-46cc-b11f-b4a767296329</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1624" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1624" t="inlineStr">
+        <is>
+          <t>OP-816</t>
+        </is>
+      </c>
+      <c r="I1624" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1624" s="2" t="n">
+        <v>46066.65371149177</v>
+      </c>
+      <c r="K1624" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>0cdc3b51-fe84-4d5c-b60c-8c49c697a411</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>749840f1-b431-4b26-9350-71270d4e85be</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1625" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1625" t="inlineStr">
+        <is>
+          <t>OP-985</t>
+        </is>
+      </c>
+      <c r="I1625" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1625" s="2" t="n">
+        <v>46065.69537816125</v>
+      </c>
+      <c r="K1625" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>cd710f62-6785-4733-b8f3-46cce59def68</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>235b0eee-0e97-4f9a-8430-ff35d8f66e2a</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1626" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1626" t="inlineStr">
+        <is>
+          <t>OP-274</t>
+        </is>
+      </c>
+      <c r="I1626" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1626" s="2" t="n">
+        <v>46066.7787114974</v>
+      </c>
+      <c r="K1626" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>67ab538a-9154-424c-88e2-c2947b6f7bf3</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>1c55a946-2bc9-4634-8b87-664eb8bf4a22</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1627" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1627" t="inlineStr">
+        <is>
+          <t>OP-706</t>
+        </is>
+      </c>
+      <c r="I1627" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1627" s="2" t="n">
+        <v>46086.82037816704</v>
+      </c>
+      <c r="K1627" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>c0b421bf-ab75-4b03-8559-ec0b8b68305e</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>c4b2e4f1-5221-44c1-8fe7-fad95537e24c</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1628" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1628" t="inlineStr">
+        <is>
+          <t>OP-644</t>
+        </is>
+      </c>
+      <c r="I1628" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1628" s="2" t="n">
+        <v>46074.94537817016</v>
+      </c>
+      <c r="K1628" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>e785c03b-0af2-4320-9c59-02ffecedd230</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>15d3c483-b65b-46bd-9541-fcf711d1c507</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1629" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1629" t="inlineStr">
+        <is>
+          <t>OP-948</t>
+        </is>
+      </c>
+      <c r="I1629" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1629" s="2" t="n">
+        <v>46087.77871150631</v>
+      </c>
+      <c r="K1629" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>ce2c509f-fc40-4a4e-a7cb-3ffae8fa286f</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>bfaed988-53d0-48bb-8972-f6cd027f8079</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1630" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1630" t="inlineStr">
+        <is>
+          <t>OP-944</t>
+        </is>
+      </c>
+      <c r="I1630" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1630" s="2" t="n">
+        <v>46077.57037817586</v>
+      </c>
+      <c r="K1630" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>3c249272-9af9-41f4-a415-dde4e1741eb7</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>2938f337-2cc1-4b8b-9a68-34337776f600</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1631" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1631" t="inlineStr">
+        <is>
+          <t>OP-390</t>
+        </is>
+      </c>
+      <c r="I1631" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1631" s="2" t="n">
+        <v>46073.86204484557</v>
+      </c>
+      <c r="K1631" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>596a9155-1790-44f7-84df-27288cf85c3d</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>9ef9153b-2e51-40d7-b1d4-a64e45d92077</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1632" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1632" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1632" t="inlineStr">
+        <is>
+          <t>OP-373</t>
+        </is>
+      </c>
+      <c r="I1632" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1632" s="2" t="n">
+        <v>46073.73704484868</v>
+      </c>
+      <c r="K1632" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>11bd6e7c-9a15-46d1-bb58-8a1df97dbf6e</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>594bc6c5-c9d8-40cd-9c24-17d7a0085ab8</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1633" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1633" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1633" t="inlineStr">
+        <is>
+          <t>OP-857</t>
+        </is>
+      </c>
+      <c r="I1633" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1633" s="2" t="n">
+        <v>46088.69537818477</v>
+      </c>
+      <c r="K1633" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>bdd743f9-ee05-4008-ac08-9a46f3a933f3</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>7977ee2c-bae1-4870-8b16-eef3e094461e</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1634" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1634" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1634" t="inlineStr">
+        <is>
+          <t>OP-873</t>
+        </is>
+      </c>
+      <c r="I1634" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1634" s="2" t="n">
+        <v>46073.73704485437</v>
+      </c>
+      <c r="K1634" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>ba2c2a92-f176-495f-99bf-84d20bb17cdb</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>e2e2de27-e4b9-43d0-9ddd-802346c4d403</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1635" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1635" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1635" t="inlineStr">
+        <is>
+          <t>OP-195</t>
+        </is>
+      </c>
+      <c r="I1635" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1635" s="2" t="n">
+        <v>46069.77871152383</v>
+      </c>
+      <c r="K1635" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>b935d39c-d039-48bb-ae0a-db612da11c60</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>5e3e0231-2d14-411e-9b47-bca184c4aa5d</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1636" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1636" t="inlineStr">
+        <is>
+          <t>OP-756</t>
+        </is>
+      </c>
+      <c r="I1636" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1636" s="2" t="n">
+        <v>46080.82037819338</v>
+      </c>
+      <c r="K1636" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>c8d9f886-a986-4b2f-9fbb-769bb5cf0e1d</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>27d2ecc2-69db-4819-b606-b41d0bf486d8</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1637" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1637" t="inlineStr">
+        <is>
+          <t>OP-644</t>
+        </is>
+      </c>
+      <c r="I1637" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1637" s="2" t="n">
+        <v>46061.90371152961</v>
+      </c>
+      <c r="K1637" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>1701883e-6ed7-44a9-bf93-b36090dca8ad</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>91b3022c-da7f-4b4e-a964-ba8a9a2a95ef</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1638" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1638" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1638" t="inlineStr">
+        <is>
+          <t>OP-739</t>
+        </is>
+      </c>
+      <c r="I1638" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1638" s="2" t="n">
+        <v>46064.69537819903</v>
+      </c>
+      <c r="K1638" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>5c2b1ad0-6b2e-47be-9e07-f8077602fe7a</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>af96b77e-68de-48a0-82dc-fc97c9fe0e3b</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1639" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1639" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1639" t="inlineStr">
+        <is>
+          <t>OP-774</t>
+        </is>
+      </c>
+      <c r="I1639" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1639" s="2" t="n">
+        <v>46084.94537820183</v>
+      </c>
+      <c r="K1639" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>bc97ffb2-fbdf-4675-a04b-48e5579850d6</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>da937882-1298-4b84-b4fc-4964515d2ee7</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1640" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1640" t="inlineStr">
+        <is>
+          <t>OP-112</t>
+        </is>
+      </c>
+      <c r="I1640" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1640" s="2" t="n">
+        <v>46067.77871153837</v>
+      </c>
+      <c r="K1640" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>699620ec-b5e7-4330-8b93-5ea3c4220b89</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>ff95a6ca-c245-4299-af48-ed8c1e7d27b0</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1641" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1641" t="inlineStr">
+        <is>
+          <t>OP-985</t>
+        </is>
+      </c>
+      <c r="I1641" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1641" s="2" t="n">
+        <v>46073.82037820783</v>
+      </c>
+      <c r="K1641" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>4435e454-e2b6-49e4-81dc-3ed55b213a30</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>df7f5860-c639-4c07-aa2a-1ea062c086d4</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1642" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1642" t="inlineStr">
+        <is>
+          <t>OP-964</t>
+        </is>
+      </c>
+      <c r="I1642" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1642" s="2" t="n">
+        <v>46068.86204487725</v>
+      </c>
+      <c r="K1642" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>ec1ac942-652e-470a-bbff-de96794fd68c</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>9c88d087-aae5-4e0b-a32a-c2e7825f72ac</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1643" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1643" t="inlineStr">
+        <is>
+          <t>OP-461</t>
+        </is>
+      </c>
+      <c r="I1643" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1643" s="2" t="n">
+        <v>46065.77871154668</v>
+      </c>
+      <c r="K1643" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>a7271000-a6ba-4a4f-9ce8-7f452f630b1f</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>e985b288-8447-478e-9c29-dee339fc3912</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1644" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1644" t="inlineStr">
+        <is>
+          <t>OP-143</t>
+        </is>
+      </c>
+      <c r="I1644" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1644" s="2" t="n">
+        <v>46081.69537821649</v>
+      </c>
+      <c r="K1644" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>41a855fc-9170-48b3-ab3b-d9519cc12594</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>aec046df-5801-45ed-9d71-b6210c999eeb</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1645" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1645" t="inlineStr">
+        <is>
+          <t>OP-418</t>
+        </is>
+      </c>
+      <c r="I1645" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1645" s="2" t="n">
+        <v>46071.9453782194</v>
+      </c>
+      <c r="K1645" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>9032cda1-1b05-4c55-ac4b-dc0c645f833c</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>518bf301-5c1c-48a3-b60c-60db3add2b43</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1646" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1646" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1646" t="inlineStr">
+        <is>
+          <t>OP-772</t>
+        </is>
+      </c>
+      <c r="I1646" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1646" s="2" t="n">
+        <v>46069.82037822221</v>
+      </c>
+      <c r="K1646" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>b02810d5-684a-4afa-9c63-7ba3ff50a0dc</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>30f5a114-3f55-43c7-8c20-7b493195a827</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1647" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F1647" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1647" t="inlineStr">
+        <is>
+          <t>OP-699</t>
+        </is>
+      </c>
+      <c r="I1647" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1647" s="2" t="n">
+        <v>46065.94537822509</v>
+      </c>
+      <c r="K1647" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>b7c9d81b-ff65-4560-8323-a7378d5e4ccd</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>859f9a02-9e1c-40da-b029-149d2e1b2c24</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1648" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1648" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1648" t="inlineStr">
+        <is>
+          <t>OP-407</t>
+        </is>
+      </c>
+      <c r="I1648" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1648" s="2" t="n">
+        <v>46086.61204489461</v>
+      </c>
+      <c r="K1648" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>67605ecc-14dc-49f5-b927-4ef53a951451</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>8c7dcd58-00b9-44fe-b999-e3a10c1a0d40</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1649" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1649" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1649" t="inlineStr">
+        <is>
+          <t>OP-554</t>
+        </is>
+      </c>
+      <c r="I1649" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1649" s="2" t="n">
+        <v>46075.82037823083</v>
+      </c>
+      <c r="K1649" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>fc052671-aae6-4746-ab00-e3d068948282</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>6c1a0323-a6f9-4d7a-8282-fee59517b9fc</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1650" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1650" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1650" t="inlineStr">
+        <is>
+          <t>OP-760</t>
+        </is>
+      </c>
+      <c r="I1650" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1650" s="2" t="n">
+        <v>46083.90371156701</v>
+      </c>
+      <c r="K1650" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>4475aac7-bd98-4a06-ab28-1dd0fb8fef74</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>3db46911-742e-4c93-b385-83fa04a7b668</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1651" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1651" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1651" t="inlineStr">
+        <is>
+          <t>OP-345</t>
+        </is>
+      </c>
+      <c r="I1651" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1651" s="2" t="n">
+        <v>46061.82037823647</v>
+      </c>
+      <c r="K1651" t="inlineStr">
+        <is>
+          <t>poor</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1651"/>
+  <dimension ref="A1:K1701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82132,7 +82132,7 @@
         </is>
       </c>
       <c r="J1602" s="2" t="n">
-        <v>46061.570378092</v>
+        <v>46061.57037809028</v>
       </c>
       <c r="K1602" t="inlineStr">
         <is>
@@ -82183,7 +82183,7 @@
         </is>
       </c>
       <c r="J1603" s="2" t="n">
-        <v>46088.86204476283</v>
+        <v>46088.86204476852</v>
       </c>
       <c r="K1603" t="inlineStr">
         <is>
@@ -82234,7 +82234,7 @@
         </is>
       </c>
       <c r="J1604" s="2" t="n">
-        <v>46081.73704476601</v>
+        <v>46081.73704476852</v>
       </c>
       <c r="K1604" t="inlineStr">
         <is>
@@ -82285,7 +82285,7 @@
         </is>
       </c>
       <c r="J1605" s="2" t="n">
-        <v>46082.65371143596</v>
+        <v>46082.65371143519</v>
       </c>
       <c r="K1605" t="inlineStr">
         <is>
@@ -82336,7 +82336,7 @@
         </is>
       </c>
       <c r="J1606" s="2" t="n">
-        <v>46068.94537810552</v>
+        <v>46068.94537810185</v>
       </c>
       <c r="K1606" t="inlineStr">
         <is>
@@ -82387,7 +82387,7 @@
         </is>
       </c>
       <c r="J1607" s="2" t="n">
-        <v>46073.69537810851</v>
+        <v>46073.69537811343</v>
       </c>
       <c r="K1607" t="inlineStr">
         <is>
@@ -82438,7 +82438,7 @@
         </is>
       </c>
       <c r="J1608" s="2" t="n">
-        <v>46086.69537811175</v>
+        <v>46086.69537811343</v>
       </c>
       <c r="K1608" t="inlineStr">
         <is>
@@ -82489,7 +82489,7 @@
         </is>
       </c>
       <c r="J1609" s="2" t="n">
-        <v>46084.77871144808</v>
+        <v>46084.77871144676</v>
       </c>
       <c r="K1609" t="inlineStr">
         <is>
@@ -82540,7 +82540,7 @@
         </is>
       </c>
       <c r="J1610" s="2" t="n">
-        <v>46079.77871145105</v>
+        <v>46079.77871144676</v>
       </c>
       <c r="K1610" t="inlineStr">
         <is>
@@ -82591,7 +82591,7 @@
         </is>
       </c>
       <c r="J1611" s="2" t="n">
-        <v>46081.73704478729</v>
+        <v>46081.73704479167</v>
       </c>
       <c r="K1611" t="inlineStr">
         <is>
@@ -82642,7 +82642,7 @@
         </is>
       </c>
       <c r="J1612" s="2" t="n">
-        <v>46083.73704479045</v>
+        <v>46083.73704479167</v>
       </c>
       <c r="K1612" t="inlineStr">
         <is>
@@ -82693,7 +82693,7 @@
         </is>
       </c>
       <c r="J1613" s="2" t="n">
-        <v>46081.61204479326</v>
+        <v>46081.61204479167</v>
       </c>
       <c r="K1613" t="inlineStr">
         <is>
@@ -82744,7 +82744,7 @@
         </is>
       </c>
       <c r="J1614" s="2" t="n">
-        <v>46068.69537812958</v>
+        <v>46068.695378125</v>
       </c>
       <c r="K1614" t="inlineStr">
         <is>
@@ -82795,7 +82795,7 @@
         </is>
       </c>
       <c r="J1615" s="2" t="n">
-        <v>46082.73704479905</v>
+        <v>46082.73704480324</v>
       </c>
       <c r="K1615" t="inlineStr">
         <is>
@@ -82846,7 +82846,7 @@
         </is>
       </c>
       <c r="J1616" s="2" t="n">
-        <v>46072.6537114687</v>
+        <v>46072.65371146991</v>
       </c>
       <c r="K1616" t="inlineStr">
         <is>
@@ -82897,7 +82897,7 @@
         </is>
       </c>
       <c r="J1617" s="2" t="n">
-        <v>46068.8620448049</v>
+        <v>46068.86204480324</v>
       </c>
       <c r="K1617" t="inlineStr">
         <is>
@@ -82948,7 +82948,7 @@
         </is>
       </c>
       <c r="J1618" s="2" t="n">
-        <v>46073.73704480778</v>
+        <v>46073.73704480324</v>
       </c>
       <c r="K1618" t="inlineStr">
         <is>
@@ -82999,7 +82999,7 @@
         </is>
       </c>
       <c r="J1619" s="2" t="n">
-        <v>46064.73704481064</v>
+        <v>46064.73704481481</v>
       </c>
       <c r="K1619" t="inlineStr">
         <is>
@@ -83050,7 +83050,7 @@
         </is>
       </c>
       <c r="J1620" s="2" t="n">
-        <v>46075.77871148023</v>
+        <v>46075.77871148148</v>
       </c>
       <c r="K1620" t="inlineStr">
         <is>
@@ -83101,7 +83101,7 @@
         </is>
       </c>
       <c r="J1621" s="2" t="n">
-        <v>46065.82037814968</v>
+        <v>46065.82037814815</v>
       </c>
       <c r="K1621" t="inlineStr">
         <is>
@@ -83152,7 +83152,7 @@
         </is>
       </c>
       <c r="J1622" s="2" t="n">
-        <v>46063.57037815246</v>
+        <v>46063.57037814815</v>
       </c>
       <c r="K1622" t="inlineStr">
         <is>
@@ -83203,7 +83203,7 @@
         </is>
       </c>
       <c r="J1623" s="2" t="n">
-        <v>46087.57037815528</v>
+        <v>46087.57037815973</v>
       </c>
       <c r="K1623" t="inlineStr">
         <is>
@@ -83254,7 +83254,7 @@
         </is>
       </c>
       <c r="J1624" s="2" t="n">
-        <v>46066.65371149177</v>
+        <v>46066.65371149305</v>
       </c>
       <c r="K1624" t="inlineStr">
         <is>
@@ -83305,7 +83305,7 @@
         </is>
       </c>
       <c r="J1625" s="2" t="n">
-        <v>46065.69537816125</v>
+        <v>46065.69537815973</v>
       </c>
       <c r="K1625" t="inlineStr">
         <is>
@@ -83356,7 +83356,7 @@
         </is>
       </c>
       <c r="J1626" s="2" t="n">
-        <v>46066.7787114974</v>
+        <v>46066.77871149305</v>
       </c>
       <c r="K1626" t="inlineStr">
         <is>
@@ -83407,7 +83407,7 @@
         </is>
       </c>
       <c r="J1627" s="2" t="n">
-        <v>46086.82037816704</v>
+        <v>46086.82037817129</v>
       </c>
       <c r="K1627" t="inlineStr">
         <is>
@@ -83458,7 +83458,7 @@
         </is>
       </c>
       <c r="J1628" s="2" t="n">
-        <v>46074.94537817016</v>
+        <v>46074.94537817129</v>
       </c>
       <c r="K1628" t="inlineStr">
         <is>
@@ -83509,7 +83509,7 @@
         </is>
       </c>
       <c r="J1629" s="2" t="n">
-        <v>46087.77871150631</v>
+        <v>46087.77871150463</v>
       </c>
       <c r="K1629" t="inlineStr">
         <is>
@@ -83560,7 +83560,7 @@
         </is>
       </c>
       <c r="J1630" s="2" t="n">
-        <v>46077.57037817586</v>
+        <v>46077.57037817129</v>
       </c>
       <c r="K1630" t="inlineStr">
         <is>
@@ -83611,7 +83611,7 @@
         </is>
       </c>
       <c r="J1631" s="2" t="n">
-        <v>46073.86204484557</v>
+        <v>46073.86204484953</v>
       </c>
       <c r="K1631" t="inlineStr">
         <is>
@@ -83662,7 +83662,7 @@
         </is>
       </c>
       <c r="J1632" s="2" t="n">
-        <v>46073.73704484868</v>
+        <v>46073.73704484953</v>
       </c>
       <c r="K1632" t="inlineStr">
         <is>
@@ -83713,7 +83713,7 @@
         </is>
       </c>
       <c r="J1633" s="2" t="n">
-        <v>46088.69537818477</v>
+        <v>46088.69537818287</v>
       </c>
       <c r="K1633" t="inlineStr">
         <is>
@@ -83764,7 +83764,7 @@
         </is>
       </c>
       <c r="J1634" s="2" t="n">
-        <v>46073.73704485437</v>
+        <v>46073.73704484953</v>
       </c>
       <c r="K1634" t="inlineStr">
         <is>
@@ -83815,7 +83815,7 @@
         </is>
       </c>
       <c r="J1635" s="2" t="n">
-        <v>46069.77871152383</v>
+        <v>46069.77871152778</v>
       </c>
       <c r="K1635" t="inlineStr">
         <is>
@@ -83866,7 +83866,7 @@
         </is>
       </c>
       <c r="J1636" s="2" t="n">
-        <v>46080.82037819338</v>
+        <v>46080.82037819445</v>
       </c>
       <c r="K1636" t="inlineStr">
         <is>
@@ -83917,7 +83917,7 @@
         </is>
       </c>
       <c r="J1637" s="2" t="n">
-        <v>46061.90371152961</v>
+        <v>46061.90371152778</v>
       </c>
       <c r="K1637" t="inlineStr">
         <is>
@@ -83968,7 +83968,7 @@
         </is>
       </c>
       <c r="J1638" s="2" t="n">
-        <v>46064.69537819903</v>
+        <v>46064.69537819445</v>
       </c>
       <c r="K1638" t="inlineStr">
         <is>
@@ -84019,7 +84019,7 @@
         </is>
       </c>
       <c r="J1639" s="2" t="n">
-        <v>46084.94537820183</v>
+        <v>46084.94537820602</v>
       </c>
       <c r="K1639" t="inlineStr">
         <is>
@@ -84070,7 +84070,7 @@
         </is>
       </c>
       <c r="J1640" s="2" t="n">
-        <v>46067.77871153837</v>
+        <v>46067.77871153935</v>
       </c>
       <c r="K1640" t="inlineStr">
         <is>
@@ -84121,7 +84121,7 @@
         </is>
       </c>
       <c r="J1641" s="2" t="n">
-        <v>46073.82037820783</v>
+        <v>46073.82037820602</v>
       </c>
       <c r="K1641" t="inlineStr">
         <is>
@@ -84172,7 +84172,7 @@
         </is>
       </c>
       <c r="J1642" s="2" t="n">
-        <v>46068.86204487725</v>
+        <v>46068.86204487269</v>
       </c>
       <c r="K1642" t="inlineStr">
         <is>
@@ -84223,7 +84223,7 @@
         </is>
       </c>
       <c r="J1643" s="2" t="n">
-        <v>46065.77871154668</v>
+        <v>46065.77871155093</v>
       </c>
       <c r="K1643" t="inlineStr">
         <is>
@@ -84274,7 +84274,7 @@
         </is>
       </c>
       <c r="J1644" s="2" t="n">
-        <v>46081.69537821649</v>
+        <v>46081.69537821759</v>
       </c>
       <c r="K1644" t="inlineStr">
         <is>
@@ -84325,7 +84325,7 @@
         </is>
       </c>
       <c r="J1645" s="2" t="n">
-        <v>46071.9453782194</v>
+        <v>46071.94537821759</v>
       </c>
       <c r="K1645" t="inlineStr">
         <is>
@@ -84376,7 +84376,7 @@
         </is>
       </c>
       <c r="J1646" s="2" t="n">
-        <v>46069.82037822221</v>
+        <v>46069.82037821759</v>
       </c>
       <c r="K1646" t="inlineStr">
         <is>
@@ -84427,7 +84427,7 @@
         </is>
       </c>
       <c r="J1647" s="2" t="n">
-        <v>46065.94537822509</v>
+        <v>46065.94537822917</v>
       </c>
       <c r="K1647" t="inlineStr">
         <is>
@@ -84478,7 +84478,7 @@
         </is>
       </c>
       <c r="J1648" s="2" t="n">
-        <v>46086.61204489461</v>
+        <v>46086.61204489583</v>
       </c>
       <c r="K1648" t="inlineStr">
         <is>
@@ -84529,7 +84529,7 @@
         </is>
       </c>
       <c r="J1649" s="2" t="n">
-        <v>46075.82037823083</v>
+        <v>46075.82037822917</v>
       </c>
       <c r="K1649" t="inlineStr">
         <is>
@@ -84580,7 +84580,7 @@
         </is>
       </c>
       <c r="J1650" s="2" t="n">
-        <v>46083.90371156701</v>
+        <v>46083.9037115625</v>
       </c>
       <c r="K1650" t="inlineStr">
         <is>
@@ -84631,11 +84631,2561 @@
         </is>
       </c>
       <c r="J1651" s="2" t="n">
-        <v>46061.82037823647</v>
+        <v>46061.82037824074</v>
       </c>
       <c r="K1651" t="inlineStr">
         <is>
           <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>546d2eaa-c51d-4306-ac59-fa948c07ad09</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>57ab6d74-f2aa-4832-9eb1-6ff9d5bf8e3e</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1652" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F1652" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1652" t="inlineStr">
+        <is>
+          <t>OP-498</t>
+        </is>
+      </c>
+      <c r="I1652" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1652" s="2" t="n">
+        <v>46079.0535767574</v>
+      </c>
+      <c r="K1652" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>71c6fadf-ed87-475e-9ea7-0fa7a8186492</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>7923be07-ca5a-46e1-b54f-99074ef66e2c</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1653" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F1653" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1653" t="inlineStr">
+        <is>
+          <t>OP-402</t>
+        </is>
+      </c>
+      <c r="I1653" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1653" s="2" t="n">
+        <v>46074.09524342918</v>
+      </c>
+      <c r="K1653" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>96e81b4a-08b9-46c0-a613-7fb046f2147e</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>4d898aa9-1c65-4b1e-a54b-38b41cea9839</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1654" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1654" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1654" t="inlineStr">
+        <is>
+          <t>OP-973</t>
+        </is>
+      </c>
+      <c r="I1654" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1654" s="2" t="n">
+        <v>46082.01191009995</v>
+      </c>
+      <c r="K1654" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>fe7cb56f-d15a-4c2a-9f63-0a4801eb239c</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>06e330e3-42c6-473e-8b0c-5609d9c4fd34</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1655" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1655" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1655" t="inlineStr">
+        <is>
+          <t>OP-563</t>
+        </is>
+      </c>
+      <c r="I1655" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1655" s="2" t="n">
+        <v>46086.88691010346</v>
+      </c>
+      <c r="K1655" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>ab4facd4-47ff-4f42-a22f-8b8ba1d3e68f</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>5dc314db-1ec4-4fca-a591-3f46528f9e14</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1656" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1656" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1656" t="inlineStr">
+        <is>
+          <t>OP-716</t>
+        </is>
+      </c>
+      <c r="I1656" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1656" s="2" t="n">
+        <v>46071.01191010661</v>
+      </c>
+      <c r="K1656" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2c8483d4-9b1a-45b2-afc6-de2aa53c3606</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>12e7c0d0-038c-4ca1-9dd4-1a58f374423f</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1657" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F1657" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1657" t="inlineStr">
+        <is>
+          <t>OP-232</t>
+        </is>
+      </c>
+      <c r="I1657" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1657" s="2" t="n">
+        <v>46082.84524344344</v>
+      </c>
+      <c r="K1657" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>4994c1e9-fb2f-4c48-8394-edeeff8cc0be</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>3320910b-fe0c-40dc-a6fa-b2621760955a</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1658" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1658" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1658" t="inlineStr">
+        <is>
+          <t>OP-866</t>
+        </is>
+      </c>
+      <c r="I1658" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1658" s="2" t="n">
+        <v>46077.80357677994</v>
+      </c>
+      <c r="K1658" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2c967c5b-fa23-42e9-8cbb-27f3f80ce7ee</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>b85720b9-16f7-4d68-9800-f5099246c862</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1659" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1659" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1659" t="inlineStr">
+        <is>
+          <t>OP-401</t>
+        </is>
+      </c>
+      <c r="I1659" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1659" s="2" t="n">
+        <v>46088.09524344984</v>
+      </c>
+      <c r="K1659" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>b448308d-75c0-4389-a0e9-6e5fb320bc68</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>2562bd8c-c4ae-4098-af74-634b0c20a9bb</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1660" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F1660" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1660" t="inlineStr">
+        <is>
+          <t>OP-292</t>
+        </is>
+      </c>
+      <c r="I1660" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1660" s="2" t="n">
+        <v>46068.01191012007</v>
+      </c>
+      <c r="K1660" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>61b47140-5ad7-475c-a621-19e3a7b0161a</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>b2043ac9-51b6-4436-9009-2b9441ec57c6</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1661" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1661" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1661" t="inlineStr">
+        <is>
+          <t>OP-522</t>
+        </is>
+      </c>
+      <c r="I1661" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1661" s="2" t="n">
+        <v>46060.88691012332</v>
+      </c>
+      <c r="K1661" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>6bfe7e68-0fc6-47a9-9367-b1d351c897e0</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>b76145ac-2cca-45d8-8027-848e5228b265</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1662" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1662" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1662" t="inlineStr">
+        <is>
+          <t>OP-295</t>
+        </is>
+      </c>
+      <c r="I1662" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1662" s="2" t="n">
+        <v>46083.01191012653</v>
+      </c>
+      <c r="K1662" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>95d212aa-fb3b-4a35-b88b-df7ea0b7ede6</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>579b495e-6d4e-4dbb-83fa-211bcaafc3ed</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1663" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F1663" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1663" t="inlineStr">
+        <is>
+          <t>OP-703</t>
+        </is>
+      </c>
+      <c r="I1663" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1663" s="2" t="n">
+        <v>46060.84524346314</v>
+      </c>
+      <c r="K1663" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>68b492ec-9727-44ca-a5a6-944209ab7be6</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>12f1af42-93ef-485d-9778-a762bc02b4ae</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1664" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F1664" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1664" t="inlineStr">
+        <is>
+          <t>OP-184</t>
+        </is>
+      </c>
+      <c r="I1664" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1664" s="2" t="n">
+        <v>46079.09524346657</v>
+      </c>
+      <c r="K1664" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>c32167f7-75f7-4546-8249-a22c328e28dd</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>9b060e97-5aeb-4ba9-9b1a-a0e6e69da063</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1665" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F1665" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1665" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1665" t="inlineStr">
+        <is>
+          <t>OP-703</t>
+        </is>
+      </c>
+      <c r="I1665" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1665" s="2" t="n">
+        <v>46071.80357680303</v>
+      </c>
+      <c r="K1665" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>d6531bbf-77ab-4983-9655-5969c971ca62</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>dfe14294-5675-4662-af29-698700b69859</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1666" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F1666" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1666" t="inlineStr">
+        <is>
+          <t>OP-764</t>
+        </is>
+      </c>
+      <c r="I1666" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1666" s="2" t="n">
+        <v>46074.97024347279</v>
+      </c>
+      <c r="K1666" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>b2c52543-a012-4fb8-9002-f1fe8c526686</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>69e7348b-c265-405c-b2f6-2dc28a3eec80</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1667" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1667" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1667" t="inlineStr">
+        <is>
+          <t>OP-119</t>
+        </is>
+      </c>
+      <c r="I1667" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1667" s="2" t="n">
+        <v>46082.09524347637</v>
+      </c>
+      <c r="K1667" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>f4d2798c-52aa-4c42-8bb4-21c3cc706152</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>21084d39-cd0e-4b0a-8312-fe2471e2ad13</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1668" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F1668" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1668" t="inlineStr">
+        <is>
+          <t>OP-647</t>
+        </is>
+      </c>
+      <c r="I1668" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1668" s="2" t="n">
+        <v>46070.92857681295</v>
+      </c>
+      <c r="K1668" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>baa572d9-a7c2-4fed-8406-c34685213cdd</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>58878448-5c52-42eb-a195-866fa8bf7e52</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1669" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F1669" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1669" t="inlineStr">
+        <is>
+          <t>OP-839</t>
+        </is>
+      </c>
+      <c r="I1669" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1669" s="2" t="n">
+        <v>46062.80357681617</v>
+      </c>
+      <c r="K1669" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>c042ec70-b38f-4241-88dc-2dc706724c37</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>5c60f1ac-e406-4d09-8556-1b3ee905ebf8</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1670" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F1670" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1670" t="inlineStr">
+        <is>
+          <t>OP-955</t>
+        </is>
+      </c>
+      <c r="I1670" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1670" s="2" t="n">
+        <v>46071.01191015267</v>
+      </c>
+      <c r="K1670" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>73353992-9c86-475e-b241-723d2ec43935</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>ef6a45c5-4825-49f2-876f-92cb78724d7c</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1671" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1671" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1671" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1671" t="inlineStr">
+        <is>
+          <t>OP-162</t>
+        </is>
+      </c>
+      <c r="I1671" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1671" s="2" t="n">
+        <v>46081.80357682281</v>
+      </c>
+      <c r="K1671" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>1f0f6fe8-8f4c-4e1f-87b2-1c9aec54b27e</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>3ead2d53-4ccb-429b-a2a5-e7a68cee8e8a</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1672" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1672" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1672" t="inlineStr">
+        <is>
+          <t>OP-814</t>
+        </is>
+      </c>
+      <c r="I1672" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1672" s="2" t="n">
+        <v>46070.88691015931</v>
+      </c>
+      <c r="K1672" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>086d75fe-fa8a-4be4-855a-53728f30d4ef</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>0c5f752e-b73b-4645-bf37-c3bbfd9cb7d8</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1673" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1673" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1673" t="inlineStr">
+        <is>
+          <t>OP-582</t>
+        </is>
+      </c>
+      <c r="I1673" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1673" s="2" t="n">
+        <v>46065.88691016247</v>
+      </c>
+      <c r="K1673" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>3e63e9d2-cc0b-4dbf-9668-fdb653485ce1</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>2449b7e5-78fc-40d4-b51c-7a641035fd87</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1674" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1674" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1674" t="inlineStr">
+        <is>
+          <t>OP-626</t>
+        </is>
+      </c>
+      <c r="I1674" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1674" s="2" t="n">
+        <v>46089.01191016587</v>
+      </c>
+      <c r="K1674" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>be5952c2-844b-4fbd-b499-3634ac508ec9</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>8fd0e957-b0e0-48c7-b5cb-937a005f8741</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1675" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F1675" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1675" t="inlineStr">
+        <is>
+          <t>OP-141</t>
+        </is>
+      </c>
+      <c r="I1675" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1675" s="2" t="n">
+        <v>46071.97024350247</v>
+      </c>
+      <c r="K1675" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>b098279e-d550-4451-9b9e-2f860d18fb08</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>c08bef1a-097c-4d6d-97ce-ace3a2036c13</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1676" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1676" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1676" t="inlineStr">
+        <is>
+          <t>OP-111</t>
+        </is>
+      </c>
+      <c r="I1676" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1676" s="2" t="n">
+        <v>46060.80357683908</v>
+      </c>
+      <c r="K1676" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>6d3817b2-8790-4d42-a4eb-f32278452925</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>70dfe2fc-eeb1-43d9-929d-de1432f0debe</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1677" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1677" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1677" t="inlineStr">
+        <is>
+          <t>OP-426</t>
+        </is>
+      </c>
+      <c r="I1677" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1677" s="2" t="n">
+        <v>46061.7619101755</v>
+      </c>
+      <c r="K1677" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>83b80d39-2756-44b6-a26e-09fd0ed5800a</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>d8df92f9-4a92-476f-b577-7ed831caf15b</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1678" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1678" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1678" t="inlineStr">
+        <is>
+          <t>OP-274</t>
+        </is>
+      </c>
+      <c r="I1678" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1678" s="2" t="n">
+        <v>46077.8869101791</v>
+      </c>
+      <c r="K1678" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>b0c419c5-05d3-4ee3-a3eb-31a0f43454cb</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>5e4c6806-f63b-48b6-bcb1-715e65bc82fe</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1679" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F1679" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1679" t="inlineStr">
+        <is>
+          <t>OP-264</t>
+        </is>
+      </c>
+      <c r="I1679" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1679" s="2" t="n">
+        <v>46072.97024351553</v>
+      </c>
+      <c r="K1679" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>de7c8353-3e35-4fc3-86cc-c62fa22c86b4</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>6b6a2616-8905-478f-a523-6cc7cc7e9975</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1680" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1680" t="inlineStr">
+        <is>
+          <t>OP-349</t>
+        </is>
+      </c>
+      <c r="I1680" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1680" s="2" t="n">
+        <v>46080.05357685211</v>
+      </c>
+      <c r="K1680" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>d9f9c1e9-bcf8-4b6f-89c4-ab6ce39ebec7</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>92459525-16a6-4d67-805f-6fdf96fcf29d</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1681" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1681" t="inlineStr">
+        <is>
+          <t>OP-663</t>
+        </is>
+      </c>
+      <c r="I1681" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1681" s="2" t="n">
+        <v>46070.97024352251</v>
+      </c>
+      <c r="K1681" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>64659285-6500-4119-8a18-c70221189591</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>b063787e-7684-48c6-9c66-b68552a50c2a</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1682" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F1682" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1682" t="inlineStr">
+        <is>
+          <t>OP-103</t>
+        </is>
+      </c>
+      <c r="I1682" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1682" s="2" t="n">
+        <v>46077.05357685918</v>
+      </c>
+      <c r="K1682" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>cc077357-59de-463f-bf23-d707ea748e50</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>ef2bb356-22ba-4a69-b6bd-474dbcd2bfda</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1683" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1683" t="inlineStr">
+        <is>
+          <t>OP-308</t>
+        </is>
+      </c>
+      <c r="I1683" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1683" s="2" t="n">
+        <v>46079.8869101956</v>
+      </c>
+      <c r="K1683" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>40696172-742f-465b-b34b-5be777fbe725</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>c7dd6d71-5a7a-4f0d-a69b-881815587ddf</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1684" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1684" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1684" t="inlineStr">
+        <is>
+          <t>OP-647</t>
+        </is>
+      </c>
+      <c r="I1684" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1684" s="2" t="n">
+        <v>46083.01191019875</v>
+      </c>
+      <c r="K1684" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>c59082a4-040c-4397-bf31-49df5c01f9f5</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>1b9426e0-dc1d-49ec-bb71-5dc56c29d85d</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1685" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1685" t="inlineStr">
+        <is>
+          <t>OP-743</t>
+        </is>
+      </c>
+      <c r="I1685" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1685" s="2" t="n">
+        <v>46077.05357686911</v>
+      </c>
+      <c r="K1685" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>0a797b11-232d-4cbf-9a78-2f58ef5e08c9</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>260bc29a-d52a-43f3-ab31-c7a7ef019d16</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1686" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F1686" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1686" t="inlineStr">
+        <is>
+          <t>OP-321</t>
+        </is>
+      </c>
+      <c r="I1686" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1686" s="2" t="n">
+        <v>46087.88691020555</v>
+      </c>
+      <c r="K1686" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>8a8d0f88-92a3-4e63-8659-3a924eae8001</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>06bab144-a675-4a7d-bd87-79014aedc371</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1687" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1687" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1687" t="inlineStr">
+        <is>
+          <t>OP-461</t>
+        </is>
+      </c>
+      <c r="I1687" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1687" s="2" t="n">
+        <v>46078.97024354199</v>
+      </c>
+      <c r="K1687" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>b1bd0d3c-0df0-4ff9-9b22-7d3cf086d115</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>4a697c78-2548-4eec-be93-c019ec24998b</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1688" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1688" t="inlineStr">
+        <is>
+          <t>OP-219</t>
+        </is>
+      </c>
+      <c r="I1688" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1688" s="2" t="n">
+        <v>46069.88691021168</v>
+      </c>
+      <c r="K1688" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>77a11c19-c711-4cd3-b223-7991e748397c</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>794b3f5d-2b87-45f8-9f5d-540c3ccbb0c9</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1689" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F1689" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1689" t="inlineStr">
+        <is>
+          <t>OP-436</t>
+        </is>
+      </c>
+      <c r="I1689" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1689" s="2" t="n">
+        <v>46077.01191021502</v>
+      </c>
+      <c r="K1689" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>6a90a976-6c33-4007-a6be-7858a3b1c4b8</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>dd2423ec-5c50-4b40-8941-591a214a1726</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1690" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1690" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1690" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1690" t="inlineStr">
+        <is>
+          <t>OP-247</t>
+        </is>
+      </c>
+      <c r="I1690" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1690" s="2" t="n">
+        <v>46079.92857688489</v>
+      </c>
+      <c r="K1690" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>32b5bcb6-44e6-464f-9e77-ddfe056a97fc</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>99b9ea5f-acab-42d1-a108-88ca690492f9</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1691" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1691" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G1691" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1691" t="inlineStr">
+        <is>
+          <t>OP-451</t>
+        </is>
+      </c>
+      <c r="I1691" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1691" s="2" t="n">
+        <v>46080.80357688816</v>
+      </c>
+      <c r="K1691" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>c4c45376-a6c7-48d0-9668-c1638422e454</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>4a4bd5ff-b415-4f34-ac73-d84b8e657757</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1692" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1692" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1692" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1692" t="inlineStr">
+        <is>
+          <t>OP-825</t>
+        </is>
+      </c>
+      <c r="I1692" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1692" s="2" t="n">
+        <v>46088.88691022486</v>
+      </c>
+      <c r="K1692" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>46f17afc-4e0e-4134-9dbb-7f9f642978b2</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>0f9bc35e-a2cd-4f1d-8d76-3e1d23bf416b</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1693" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F1693" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1693" t="inlineStr">
+        <is>
+          <t>OP-651</t>
+        </is>
+      </c>
+      <c r="I1693" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1693" s="2" t="n">
+        <v>46071.05357689474</v>
+      </c>
+      <c r="K1693" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>20e49761-167a-472e-a477-cd5f0dc851f4</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>1d279b40-4d75-4083-8567-f2de1634e430</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1694" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F1694" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1694" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1694" t="inlineStr">
+        <is>
+          <t>OP-653</t>
+        </is>
+      </c>
+      <c r="I1694" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1694" s="2" t="n">
+        <v>46087.76191023138</v>
+      </c>
+      <c r="K1694" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>e5ad0a14-bf24-4ecc-9bc4-cf3efa91f408</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>2fb1608f-059c-42f9-8705-575d4c58a877</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1695" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1695" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1695" t="inlineStr">
+        <is>
+          <t>OP-358</t>
+        </is>
+      </c>
+      <c r="I1695" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1695" s="2" t="n">
+        <v>46075.92857690123</v>
+      </c>
+      <c r="K1695" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>e179c128-270c-4844-bf39-bf6b21ff53bd</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>c1eef5b2-75f6-43b0-b8e6-461d99ac512b</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1696" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1696" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G1696" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1696" t="inlineStr">
+        <is>
+          <t>OP-694</t>
+        </is>
+      </c>
+      <c r="I1696" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1696" s="2" t="n">
+        <v>46065.72024357169</v>
+      </c>
+      <c r="K1696" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>829680ec-83e1-4fcf-a391-3c4f4c2f741e</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>949ebc06-2a8a-4987-a932-6fd616a8aa81</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1697" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F1697" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1697" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1697" t="inlineStr">
+        <is>
+          <t>OP-668</t>
+        </is>
+      </c>
+      <c r="I1697" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1697" s="2" t="n">
+        <v>46067.72024357478</v>
+      </c>
+      <c r="K1697" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>fecee184-b926-4a60-a1a9-d9b08e7c0075</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>6a1a7d08-fada-4ce2-a11f-5245489f4c6f</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1698" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F1698" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1698" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1698" t="inlineStr">
+        <is>
+          <t>OP-260</t>
+        </is>
+      </c>
+      <c r="I1698" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1698" s="2" t="n">
+        <v>46083.72024357798</v>
+      </c>
+      <c r="K1698" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>913229aa-2a78-4e8b-9234-3e48295fac7e</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>944c66d7-f53a-4cd6-9511-159698cd4419</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1699" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1699" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1699" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1699" t="inlineStr">
+        <is>
+          <t>OP-804</t>
+        </is>
+      </c>
+      <c r="I1699" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1699" s="2" t="n">
+        <v>46088.01191024825</v>
+      </c>
+      <c r="K1699" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>4165c738-6227-4421-8514-88303264844b</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>41a4f48d-0e68-4c42-9660-515a903adaa2</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1700" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1700" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1700" t="inlineStr">
+        <is>
+          <t>OP-364</t>
+        </is>
+      </c>
+      <c r="I1700" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1700" s="2" t="n">
+        <v>46084.84524358477</v>
+      </c>
+      <c r="K1700" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>7ed3a925-cc98-4925-a2de-9d1d807a1203</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>973218a7-b805-4dfb-8a1b-df529cffde50</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1701" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1701" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1701" t="inlineStr">
+        <is>
+          <t>OP-811</t>
+        </is>
+      </c>
+      <c r="I1701" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1701" s="2" t="n">
+        <v>46081.01191025465</v>
+      </c>
+      <c r="K1701" t="inlineStr">
+        <is>
+          <t>good</t>
         </is>
       </c>
     </row>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1701"/>
+  <dimension ref="A1:K1751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84682,7 +84682,7 @@
         </is>
       </c>
       <c r="J1652" s="2" t="n">
-        <v>46079.0535767574</v>
+        <v>46079.05357675926</v>
       </c>
       <c r="K1652" t="inlineStr">
         <is>
@@ -84733,7 +84733,7 @@
         </is>
       </c>
       <c r="J1653" s="2" t="n">
-        <v>46074.09524342918</v>
+        <v>46074.09524342592</v>
       </c>
       <c r="K1653" t="inlineStr">
         <is>
@@ -84784,7 +84784,7 @@
         </is>
       </c>
       <c r="J1654" s="2" t="n">
-        <v>46082.01191009995</v>
+        <v>46082.01191010416</v>
       </c>
       <c r="K1654" t="inlineStr">
         <is>
@@ -84835,7 +84835,7 @@
         </is>
       </c>
       <c r="J1655" s="2" t="n">
-        <v>46086.88691010346</v>
+        <v>46086.88691010416</v>
       </c>
       <c r="K1655" t="inlineStr">
         <is>
@@ -84886,7 +84886,7 @@
         </is>
       </c>
       <c r="J1656" s="2" t="n">
-        <v>46071.01191010661</v>
+        <v>46071.01191010416</v>
       </c>
       <c r="K1656" t="inlineStr">
         <is>
@@ -84937,7 +84937,7 @@
         </is>
       </c>
       <c r="J1657" s="2" t="n">
-        <v>46082.84524344344</v>
+        <v>46082.84524344908</v>
       </c>
       <c r="K1657" t="inlineStr">
         <is>
@@ -84988,7 +84988,7 @@
         </is>
       </c>
       <c r="J1658" s="2" t="n">
-        <v>46077.80357677994</v>
+        <v>46077.8035767824</v>
       </c>
       <c r="K1658" t="inlineStr">
         <is>
@@ -85039,7 +85039,7 @@
         </is>
       </c>
       <c r="J1659" s="2" t="n">
-        <v>46088.09524344984</v>
+        <v>46088.09524344908</v>
       </c>
       <c r="K1659" t="inlineStr">
         <is>
@@ -85090,7 +85090,7 @@
         </is>
       </c>
       <c r="J1660" s="2" t="n">
-        <v>46068.01191012007</v>
+        <v>46068.01191011574</v>
       </c>
       <c r="K1660" t="inlineStr">
         <is>
@@ -85141,7 +85141,7 @@
         </is>
       </c>
       <c r="J1661" s="2" t="n">
-        <v>46060.88691012332</v>
+        <v>46060.88691012732</v>
       </c>
       <c r="K1661" t="inlineStr">
         <is>
@@ -85192,7 +85192,7 @@
         </is>
       </c>
       <c r="J1662" s="2" t="n">
-        <v>46083.01191012653</v>
+        <v>46083.01191012732</v>
       </c>
       <c r="K1662" t="inlineStr">
         <is>
@@ -85243,7 +85243,7 @@
         </is>
       </c>
       <c r="J1663" s="2" t="n">
-        <v>46060.84524346314</v>
+        <v>46060.84524346065</v>
       </c>
       <c r="K1663" t="inlineStr">
         <is>
@@ -85294,7 +85294,7 @@
         </is>
       </c>
       <c r="J1664" s="2" t="n">
-        <v>46079.09524346657</v>
+        <v>46079.09524347222</v>
       </c>
       <c r="K1664" t="inlineStr">
         <is>
@@ -85345,7 +85345,7 @@
         </is>
       </c>
       <c r="J1665" s="2" t="n">
-        <v>46071.80357680303</v>
+        <v>46071.80357680556</v>
       </c>
       <c r="K1665" t="inlineStr">
         <is>
@@ -85396,7 +85396,7 @@
         </is>
       </c>
       <c r="J1666" s="2" t="n">
-        <v>46074.97024347279</v>
+        <v>46074.97024347222</v>
       </c>
       <c r="K1666" t="inlineStr">
         <is>
@@ -85447,7 +85447,7 @@
         </is>
       </c>
       <c r="J1667" s="2" t="n">
-        <v>46082.09524347637</v>
+        <v>46082.09524347222</v>
       </c>
       <c r="K1667" t="inlineStr">
         <is>
@@ -85498,7 +85498,7 @@
         </is>
       </c>
       <c r="J1668" s="2" t="n">
-        <v>46070.92857681295</v>
+        <v>46070.92857681713</v>
       </c>
       <c r="K1668" t="inlineStr">
         <is>
@@ -85549,7 +85549,7 @@
         </is>
       </c>
       <c r="J1669" s="2" t="n">
-        <v>46062.80357681617</v>
+        <v>46062.80357681713</v>
       </c>
       <c r="K1669" t="inlineStr">
         <is>
@@ -85600,7 +85600,7 @@
         </is>
       </c>
       <c r="J1670" s="2" t="n">
-        <v>46071.01191015267</v>
+        <v>46071.01191015046</v>
       </c>
       <c r="K1670" t="inlineStr">
         <is>
@@ -85651,7 +85651,7 @@
         </is>
       </c>
       <c r="J1671" s="2" t="n">
-        <v>46081.80357682281</v>
+        <v>46081.80357681713</v>
       </c>
       <c r="K1671" t="inlineStr">
         <is>
@@ -85702,7 +85702,7 @@
         </is>
       </c>
       <c r="J1672" s="2" t="n">
-        <v>46070.88691015931</v>
+        <v>46070.88691016204</v>
       </c>
       <c r="K1672" t="inlineStr">
         <is>
@@ -85753,7 +85753,7 @@
         </is>
       </c>
       <c r="J1673" s="2" t="n">
-        <v>46065.88691016247</v>
+        <v>46065.88691016204</v>
       </c>
       <c r="K1673" t="inlineStr">
         <is>
@@ -85804,7 +85804,7 @@
         </is>
       </c>
       <c r="J1674" s="2" t="n">
-        <v>46089.01191016587</v>
+        <v>46089.01191016204</v>
       </c>
       <c r="K1674" t="inlineStr">
         <is>
@@ -85855,7 +85855,7 @@
         </is>
       </c>
       <c r="J1675" s="2" t="n">
-        <v>46071.97024350247</v>
+        <v>46071.97024350694</v>
       </c>
       <c r="K1675" t="inlineStr">
         <is>
@@ -85906,7 +85906,7 @@
         </is>
       </c>
       <c r="J1676" s="2" t="n">
-        <v>46060.80357683908</v>
+        <v>46060.80357684028</v>
       </c>
       <c r="K1676" t="inlineStr">
         <is>
@@ -85957,7 +85957,7 @@
         </is>
       </c>
       <c r="J1677" s="2" t="n">
-        <v>46061.7619101755</v>
+        <v>46061.76191017361</v>
       </c>
       <c r="K1677" t="inlineStr">
         <is>
@@ -86008,7 +86008,7 @@
         </is>
       </c>
       <c r="J1678" s="2" t="n">
-        <v>46077.8869101791</v>
+        <v>46077.88691017361</v>
       </c>
       <c r="K1678" t="inlineStr">
         <is>
@@ -86059,7 +86059,7 @@
         </is>
       </c>
       <c r="J1679" s="2" t="n">
-        <v>46072.97024351553</v>
+        <v>46072.97024351852</v>
       </c>
       <c r="K1679" t="inlineStr">
         <is>
@@ -86110,7 +86110,7 @@
         </is>
       </c>
       <c r="J1680" s="2" t="n">
-        <v>46080.05357685211</v>
+        <v>46080.05357685185</v>
       </c>
       <c r="K1680" t="inlineStr">
         <is>
@@ -86161,7 +86161,7 @@
         </is>
       </c>
       <c r="J1681" s="2" t="n">
-        <v>46070.97024352251</v>
+        <v>46070.97024351852</v>
       </c>
       <c r="K1681" t="inlineStr">
         <is>
@@ -86212,7 +86212,7 @@
         </is>
       </c>
       <c r="J1682" s="2" t="n">
-        <v>46077.05357685918</v>
+        <v>46077.05357686343</v>
       </c>
       <c r="K1682" t="inlineStr">
         <is>
@@ -86263,7 +86263,7 @@
         </is>
       </c>
       <c r="J1683" s="2" t="n">
-        <v>46079.8869101956</v>
+        <v>46079.88691019676</v>
       </c>
       <c r="K1683" t="inlineStr">
         <is>
@@ -86314,7 +86314,7 @@
         </is>
       </c>
       <c r="J1684" s="2" t="n">
-        <v>46083.01191019875</v>
+        <v>46083.01191019676</v>
       </c>
       <c r="K1684" t="inlineStr">
         <is>
@@ -86365,7 +86365,7 @@
         </is>
       </c>
       <c r="J1685" s="2" t="n">
-        <v>46077.05357686911</v>
+        <v>46077.05357686343</v>
       </c>
       <c r="K1685" t="inlineStr">
         <is>
@@ -86416,7 +86416,7 @@
         </is>
       </c>
       <c r="J1686" s="2" t="n">
-        <v>46087.88691020555</v>
+        <v>46087.88691020833</v>
       </c>
       <c r="K1686" t="inlineStr">
         <is>
@@ -86467,7 +86467,7 @@
         </is>
       </c>
       <c r="J1687" s="2" t="n">
-        <v>46078.97024354199</v>
+        <v>46078.97024354167</v>
       </c>
       <c r="K1687" t="inlineStr">
         <is>
@@ -86518,7 +86518,7 @@
         </is>
       </c>
       <c r="J1688" s="2" t="n">
-        <v>46069.88691021168</v>
+        <v>46069.88691020833</v>
       </c>
       <c r="K1688" t="inlineStr">
         <is>
@@ -86569,7 +86569,7 @@
         </is>
       </c>
       <c r="J1689" s="2" t="n">
-        <v>46077.01191021502</v>
+        <v>46077.01191021991</v>
       </c>
       <c r="K1689" t="inlineStr">
         <is>
@@ -86620,7 +86620,7 @@
         </is>
       </c>
       <c r="J1690" s="2" t="n">
-        <v>46079.92857688489</v>
+        <v>46079.92857688657</v>
       </c>
       <c r="K1690" t="inlineStr">
         <is>
@@ -86671,7 +86671,7 @@
         </is>
       </c>
       <c r="J1691" s="2" t="n">
-        <v>46080.80357688816</v>
+        <v>46080.80357688657</v>
       </c>
       <c r="K1691" t="inlineStr">
         <is>
@@ -86722,7 +86722,7 @@
         </is>
       </c>
       <c r="J1692" s="2" t="n">
-        <v>46088.88691022486</v>
+        <v>46088.88691021991</v>
       </c>
       <c r="K1692" t="inlineStr">
         <is>
@@ -86773,7 +86773,7 @@
         </is>
       </c>
       <c r="J1693" s="2" t="n">
-        <v>46071.05357689474</v>
+        <v>46071.05357689815</v>
       </c>
       <c r="K1693" t="inlineStr">
         <is>
@@ -86824,7 +86824,7 @@
         </is>
       </c>
       <c r="J1694" s="2" t="n">
-        <v>46087.76191023138</v>
+        <v>46087.76191023148</v>
       </c>
       <c r="K1694" t="inlineStr">
         <is>
@@ -86875,7 +86875,7 @@
         </is>
       </c>
       <c r="J1695" s="2" t="n">
-        <v>46075.92857690123</v>
+        <v>46075.92857689815</v>
       </c>
       <c r="K1695" t="inlineStr">
         <is>
@@ -86926,7 +86926,7 @@
         </is>
       </c>
       <c r="J1696" s="2" t="n">
-        <v>46065.72024357169</v>
+        <v>46065.72024357639</v>
       </c>
       <c r="K1696" t="inlineStr">
         <is>
@@ -86977,7 +86977,7 @@
         </is>
       </c>
       <c r="J1697" s="2" t="n">
-        <v>46067.72024357478</v>
+        <v>46067.72024357639</v>
       </c>
       <c r="K1697" t="inlineStr">
         <is>
@@ -87028,7 +87028,7 @@
         </is>
       </c>
       <c r="J1698" s="2" t="n">
-        <v>46083.72024357798</v>
+        <v>46083.72024357639</v>
       </c>
       <c r="K1698" t="inlineStr">
         <is>
@@ -87079,7 +87079,7 @@
         </is>
       </c>
       <c r="J1699" s="2" t="n">
-        <v>46088.01191024825</v>
+        <v>46088.01191024305</v>
       </c>
       <c r="K1699" t="inlineStr">
         <is>
@@ -87130,7 +87130,7 @@
         </is>
       </c>
       <c r="J1700" s="2" t="n">
-        <v>46084.84524358477</v>
+        <v>46084.84524358797</v>
       </c>
       <c r="K1700" t="inlineStr">
         <is>
@@ -87181,9 +87181,2559 @@
         </is>
       </c>
       <c r="J1701" s="2" t="n">
-        <v>46081.01191025465</v>
+        <v>46081.01191025463</v>
       </c>
       <c r="K1701" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>1995e74c-fa56-42b1-b8e3-96982d8e61b7</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>f4ddca0a-8d6e-44d0-9ee1-7a810dfa9b0e</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1702" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1702" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1702" t="inlineStr">
+        <is>
+          <t>OP-417</t>
+        </is>
+      </c>
+      <c r="I1702" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1702" s="2" t="n">
+        <v>46072.56022146757</v>
+      </c>
+      <c r="K1702" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>e3b5265f-79b5-4727-ba1c-8d043812934d</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>2c3bb197-67e5-435f-8433-3556cab58193</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1703" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1703" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1703" t="inlineStr">
+        <is>
+          <t>OP-829</t>
+        </is>
+      </c>
+      <c r="I1703" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1703" s="2" t="n">
+        <v>46065.31022147178</v>
+      </c>
+      <c r="K1703" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>1a9f5f6c-7c15-4120-b214-a0ffbeb4d91e</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>ff87bae6-6f31-494d-8205-180932ca4233</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1704" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="F1704" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1704" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1704" t="inlineStr">
+        <is>
+          <t>OP-608</t>
+        </is>
+      </c>
+      <c r="I1704" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1704" s="2" t="n">
+        <v>46064.31022147501</v>
+      </c>
+      <c r="K1704" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>a9bbb48d-afd4-482a-9d63-3e03b343a3e6</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>bf74494f-051e-4574-9a1a-aec3f3e9208d</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1705" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F1705" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1705" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1705" t="inlineStr">
+        <is>
+          <t>OP-720</t>
+        </is>
+      </c>
+      <c r="I1705" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1705" s="2" t="n">
+        <v>46075.476888145</v>
+      </c>
+      <c r="K1705" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>147ae135-c536-4cb1-98af-a99bf219febf</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>0c8c97e3-5295-47c9-8cb1-972dd8fff04b</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1706" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F1706" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1706" t="inlineStr">
+        <is>
+          <t>OP-446</t>
+        </is>
+      </c>
+      <c r="I1706" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1706" s="2" t="n">
+        <v>46074.35188814825</v>
+      </c>
+      <c r="K1706" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>c8b271b7-fa39-47b0-9ba5-9745435a22b5</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>b4ee5f9c-67a0-47e6-aa1c-a0b4bebecbbd</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1707" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1707" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1707" t="inlineStr">
+        <is>
+          <t>OP-183</t>
+        </is>
+      </c>
+      <c r="I1707" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1707" s="2" t="n">
+        <v>46065.60188815143</v>
+      </c>
+      <c r="K1707" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>11b46680-64d1-4d21-8e4e-117271b69240</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>c4453e34-7115-41a3-ac3d-cd5577a50d82</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1708" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F1708" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1708" t="inlineStr">
+        <is>
+          <t>OP-382</t>
+        </is>
+      </c>
+      <c r="I1708" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1708" s="2" t="n">
+        <v>46067.22688815483</v>
+      </c>
+      <c r="K1708" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>38bd66a2-b2ff-42a1-a784-e9c1376d2acc</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>b604085a-7388-40c9-ac7c-8740ca2c8fd0</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1709" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1709" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1709" t="inlineStr">
+        <is>
+          <t>OP-226</t>
+        </is>
+      </c>
+      <c r="I1709" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1709" s="2" t="n">
+        <v>46061.56022149131</v>
+      </c>
+      <c r="K1709" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>e76e8e31-bb24-4d05-ae80-e3c5eeea24e5</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>a1ed0d99-f814-4a34-b2aa-19694f92df1d</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1710" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1710" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1710" t="inlineStr">
+        <is>
+          <t>OP-706</t>
+        </is>
+      </c>
+      <c r="I1710" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1710" s="2" t="n">
+        <v>46087.60188816103</v>
+      </c>
+      <c r="K1710" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>4f1426f2-65e6-424f-b32c-2110733bc342</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>503b913b-7f84-4634-bbee-f0de199efaf1</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1711" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1711" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1711" t="inlineStr">
+        <is>
+          <t>OP-145</t>
+        </is>
+      </c>
+      <c r="I1711" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1711" s="2" t="n">
+        <v>46078.60188816462</v>
+      </c>
+      <c r="K1711" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>c7a59355-7541-4718-a0b6-03677e7854af</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>1f0c4806-5f83-4757-843b-3ce783d94ed1</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1712" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F1712" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1712" t="inlineStr">
+        <is>
+          <t>OP-191</t>
+        </is>
+      </c>
+      <c r="I1712" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1712" s="2" t="n">
+        <v>46087.51855483503</v>
+      </c>
+      <c r="K1712" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>56c682b1-473e-4bb2-bc43-4889f2784338</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>90931d55-9c18-42d6-b45f-545f8c04a3c5</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1713" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F1713" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1713" t="inlineStr">
+        <is>
+          <t>OP-333</t>
+        </is>
+      </c>
+      <c r="I1713" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1713" s="2" t="n">
+        <v>46075.56022150483</v>
+      </c>
+      <c r="K1713" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>e51d7b9a-a2a0-4d79-9606-5cd8a6777ff3</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>9171a899-96a3-4b86-8007-fdf3642d883c</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1714" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F1714" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1714" t="inlineStr">
+        <is>
+          <t>OP-921</t>
+        </is>
+      </c>
+      <c r="I1714" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1714" s="2" t="n">
+        <v>46080.5185548414</v>
+      </c>
+      <c r="K1714" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>8f536705-9838-4681-a963-c3a7d4ba45be</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>d39a7d81-f7e2-487f-80c8-05ceb05bf1b1</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1715" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1715" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1715" t="inlineStr">
+        <is>
+          <t>OP-887</t>
+        </is>
+      </c>
+      <c r="I1715" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1715" s="2" t="n">
+        <v>46085.39355484464</v>
+      </c>
+      <c r="K1715" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>657bd5f7-8bd2-4fdb-a535-a03e8b088fe7</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>3283ce6f-36b6-48cd-9e89-574e38696d87</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1716" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="F1716" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1716" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1716" t="inlineStr">
+        <is>
+          <t>OP-589</t>
+        </is>
+      </c>
+      <c r="I1716" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1716" s="2" t="n">
+        <v>46087.60188818105</v>
+      </c>
+      <c r="K1716" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>02d0a616-09fa-4332-a583-c744bd499a3b</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>3ce1a7c4-66ee-47ae-999e-98568c0308fd</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1717" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F1717" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1717" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1717" t="inlineStr">
+        <is>
+          <t>OP-288</t>
+        </is>
+      </c>
+      <c r="I1717" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1717" s="2" t="n">
+        <v>46079.56022151747</v>
+      </c>
+      <c r="K1717" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>cdc757f0-87b2-4df8-84c8-120958a5b79d</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>504a65b7-c3d6-4166-b758-bb902bd19b72</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1718" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F1718" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1718" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1718" t="inlineStr">
+        <is>
+          <t>OP-450</t>
+        </is>
+      </c>
+      <c r="I1718" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1718" s="2" t="n">
+        <v>46067.31022152056</v>
+      </c>
+      <c r="K1718" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>db4646a8-2afb-471f-89b6-feb61fbee241</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>d16cd225-39dc-4a14-9a3b-090e0b8e587c</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1719" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F1719" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1719" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1719" t="inlineStr">
+        <is>
+          <t>OP-823</t>
+        </is>
+      </c>
+      <c r="I1719" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1719" s="2" t="n">
+        <v>46077.43522152376</v>
+      </c>
+      <c r="K1719" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>7aa18259-277e-42cb-874e-4ce0572ec419</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>0d3e9a26-5073-422c-9963-0de08047c88e</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1720" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1720" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1720" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1720" t="inlineStr">
+        <is>
+          <t>OP-736</t>
+        </is>
+      </c>
+      <c r="I1720" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1720" s="2" t="n">
+        <v>46075.51855486031</v>
+      </c>
+      <c r="K1720" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>dcd4b59e-c5bf-41a9-bf4c-a180266c5957</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>d1459ffa-93b9-4965-96f5-46458a9e59ef</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1721" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F1721" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1721" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1721" t="inlineStr">
+        <is>
+          <t>OP-316</t>
+        </is>
+      </c>
+      <c r="I1721" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1721" s="2" t="n">
+        <v>46088.56022153005</v>
+      </c>
+      <c r="K1721" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2aa49ac1-8136-4ab1-a394-ff3e55b7a67f</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>e54b6ca7-1b45-4ac2-990d-37c8a27bdd17</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1722" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F1722" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1722" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1722" t="inlineStr">
+        <is>
+          <t>OP-632</t>
+        </is>
+      </c>
+      <c r="I1722" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1722" s="2" t="n">
+        <v>46072.47688819988</v>
+      </c>
+      <c r="K1722" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>e61021fd-00e0-489a-8ad6-0c47bd4135a0</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>6e126c78-b907-4ad5-b820-2dd132493ce1</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1723" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="F1723" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1723" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1723" t="inlineStr">
+        <is>
+          <t>OP-889</t>
+        </is>
+      </c>
+      <c r="I1723" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1723" s="2" t="n">
+        <v>46085.47688820327</v>
+      </c>
+      <c r="K1723" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>224577b5-b934-4c99-a140-8c00ec7c70b8</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>fa4b4209-549a-4b18-891c-a5d7517af47d</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1724" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F1724" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1724" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1724" t="inlineStr">
+        <is>
+          <t>OP-231</t>
+        </is>
+      </c>
+      <c r="I1724" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1724" s="2" t="n">
+        <v>46074.4352215397</v>
+      </c>
+      <c r="K1724" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>e12c57e4-6302-44e9-8292-a0cdbdfa1103</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>4c0de839-9120-4329-8d07-e4d34a2ceed2</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1725" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F1725" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1725" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1725" t="inlineStr">
+        <is>
+          <t>OP-664</t>
+        </is>
+      </c>
+      <c r="I1725" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1725" s="2" t="n">
+        <v>46078.39355487603</v>
+      </c>
+      <c r="K1725" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>71ea074b-bed1-458c-9441-921780411bcb</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>4f22234f-0d19-418f-898e-57f2e157b85b</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1726" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="F1726" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1726" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1726" t="inlineStr">
+        <is>
+          <t>OP-338</t>
+        </is>
+      </c>
+      <c r="I1726" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1726" s="2" t="n">
+        <v>46066.5602215459</v>
+      </c>
+      <c r="K1726" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>71c5b412-1130-4ec4-a1cb-72545970c521</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>8f46e708-fb90-4fb9-b75a-2331ddbd7ab4</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1727" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1727" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1727" t="inlineStr">
+        <is>
+          <t>OP-223</t>
+        </is>
+      </c>
+      <c r="I1727" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1727" s="2" t="n">
+        <v>46063.43522154899</v>
+      </c>
+      <c r="K1727" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>92374d3b-00a4-4e84-a54f-6a5eec2c2114</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>b86e336f-cf03-4875-90ac-bc8c94d1abb2</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1728" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1728" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1728" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1728" t="inlineStr">
+        <is>
+          <t>OP-891</t>
+        </is>
+      </c>
+      <c r="I1728" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1728" s="2" t="n">
+        <v>46061.47688821885</v>
+      </c>
+      <c r="K1728" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>68e81b32-6b01-4f4b-a870-d5db362b9642</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>f2784152-1332-4324-8269-cd162b8bba8c</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1729" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1729" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1729" t="inlineStr">
+        <is>
+          <t>OP-448</t>
+        </is>
+      </c>
+      <c r="I1729" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1729" s="2" t="n">
+        <v>46064.60188822207</v>
+      </c>
+      <c r="K1729" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>32c82b61-13e2-44d4-bf51-3cb328657547</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>796c11a2-9a25-43e0-8ff9-47fa9911a9e4</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1730" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1730" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1730" t="inlineStr">
+        <is>
+          <t>OP-249</t>
+        </is>
+      </c>
+      <c r="I1730" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1730" s="2" t="n">
+        <v>46075.35188822538</v>
+      </c>
+      <c r="K1730" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>dc9c8e4e-12fb-4619-bdaa-c4d8c0a543c2</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>8a4462d1-a0ce-4637-931e-963e3e2c0fdc</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1731" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G1731" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1731" t="inlineStr">
+        <is>
+          <t>OP-390</t>
+        </is>
+      </c>
+      <c r="I1731" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1731" s="2" t="n">
+        <v>46081.22688822845</v>
+      </c>
+      <c r="K1731" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>69c2cc7e-0bc4-4935-8959-23079b332644</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>c7a05a34-fb92-492e-8386-6542e879adc1</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1732" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G1732" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1732" t="inlineStr">
+        <is>
+          <t>OP-780</t>
+        </is>
+      </c>
+      <c r="I1732" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1732" s="2" t="n">
+        <v>46065.43522156496</v>
+      </c>
+      <c r="K1732" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>0cad678d-9c6a-48a5-ba63-1842e01c3bb6</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>154b43ad-64df-44ef-a48d-60762d0059ef</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1733" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1733" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1733" t="inlineStr">
+        <is>
+          <t>OP-561</t>
+        </is>
+      </c>
+      <c r="I1733" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1733" s="2" t="n">
+        <v>46064.60188823478</v>
+      </c>
+      <c r="K1733" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>8ac7cac7-d4b6-4ce4-9560-0b6ccff7af4e</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>717acdea-bcd0-45e9-ab95-b3ecd58e34b0</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1734" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1734" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1734" t="inlineStr">
+        <is>
+          <t>OP-970</t>
+        </is>
+      </c>
+      <c r="I1734" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1734" s="2" t="n">
+        <v>46089.35188823805</v>
+      </c>
+      <c r="K1734" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>cb6e1255-6a84-47bc-a9a5-a31ae905408c</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>25076df8-400f-4109-8e22-1bc52e8eccac</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1735" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1735" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1735" t="inlineStr">
+        <is>
+          <t>OP-849</t>
+        </is>
+      </c>
+      <c r="I1735" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1735" s="2" t="n">
+        <v>46068.56022157448</v>
+      </c>
+      <c r="K1735" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>82d41889-2480-4d43-a24c-c26b273143a9</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>f8dc4389-8a70-4a31-86b9-1910ce5e56d0</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1736" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F1736" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1736" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1736" t="inlineStr">
+        <is>
+          <t>OP-119</t>
+        </is>
+      </c>
+      <c r="I1736" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1736" s="2" t="n">
+        <v>46078.56022157765</v>
+      </c>
+      <c r="K1736" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>c31887db-1380-4f0f-a0b1-d1ac9cdcf81c</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>dd112ac8-d264-499c-a23d-e018926e1a43</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1737" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="G1737" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1737" t="inlineStr">
+        <is>
+          <t>OP-506</t>
+        </is>
+      </c>
+      <c r="I1737" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1737" s="2" t="n">
+        <v>46087.2268882475</v>
+      </c>
+      <c r="K1737" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>99db77da-ae52-4405-91c6-aeea23cb4fc7</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>fc16ce42-9e10-41b8-b0d4-7e990c8eff82</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1738" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1738" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1738" t="inlineStr">
+        <is>
+          <t>OP-362</t>
+        </is>
+      </c>
+      <c r="I1738" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1738" s="2" t="n">
+        <v>46076.39355491735</v>
+      </c>
+      <c r="K1738" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>e08c1097-0677-4bc7-a0fb-e5242884da84</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>1da8ac8a-e486-4869-9749-a9c6c9832700</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1739" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G1739" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1739" t="inlineStr">
+        <is>
+          <t>OP-821</t>
+        </is>
+      </c>
+      <c r="I1739" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1739" s="2" t="n">
+        <v>46078.47688825382</v>
+      </c>
+      <c r="K1739" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>feff95ed-41f5-4d3c-a906-2a839820857b</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>f357bd3e-4aa3-4c35-8fa1-900d8c277bf9</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1740" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1740" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1740" t="inlineStr">
+        <is>
+          <t>OP-783</t>
+        </is>
+      </c>
+      <c r="I1740" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1740" s="2" t="n">
+        <v>46075.47688825684</v>
+      </c>
+      <c r="K1740" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>385de0d6-6e2d-45c5-bfb8-e3e35e54bfdc</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>2a0e9d17-703d-4c3b-864c-4fc6327956e5</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1741" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1741" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1741" t="inlineStr">
+        <is>
+          <t>OP-621</t>
+        </is>
+      </c>
+      <c r="I1741" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1741" s="2" t="n">
+        <v>46086.22688826011</v>
+      </c>
+      <c r="K1741" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>049ac81c-5722-4419-9e0b-df299944c81b</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>edb13e45-57ef-4ea6-897b-b07e2be59ae8</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1742" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1742" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1742" t="inlineStr">
+        <is>
+          <t>OP-238</t>
+        </is>
+      </c>
+      <c r="I1742" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1742" s="2" t="n">
+        <v>46085.47688826314</v>
+      </c>
+      <c r="K1742" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>8eee307d-d3a9-4aaf-9380-8c20b00bab9d</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>dc90146d-128d-49b1-b4ca-57d26dce2bb3</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1743" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1743" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1743" t="inlineStr">
+        <is>
+          <t>OP-719</t>
+        </is>
+      </c>
+      <c r="I1743" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1743" s="2" t="n">
+        <v>46083.22688826622</v>
+      </c>
+      <c r="K1743" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2ed6bea0-583e-47ff-8167-65dcafdba20d</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>169ee050-8624-4623-93a3-395d634a3855</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1744" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1744" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1744" t="inlineStr">
+        <is>
+          <t>OP-602</t>
+        </is>
+      </c>
+      <c r="I1744" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1744" s="2" t="n">
+        <v>46070.60188826924</v>
+      </c>
+      <c r="K1744" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>63d0c74e-e5dd-4be0-868f-af33ef92fd19</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>a4c828a0-3afd-45ea-a4d2-c6e4a4cb86d8</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1745" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1745" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1745" t="inlineStr">
+        <is>
+          <t>OP-650</t>
+        </is>
+      </c>
+      <c r="I1745" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1745" s="2" t="n">
+        <v>46083.39355493927</v>
+      </c>
+      <c r="K1745" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>ce312452-e71d-4e61-8937-4f43f50bea92</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>7d00b664-fcfe-4efe-b6af-e8841b875413</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1746" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1746" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1746" t="inlineStr">
+        <is>
+          <t>OP-608</t>
+        </is>
+      </c>
+      <c r="I1746" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1746" s="2" t="n">
+        <v>46068.2268882757</v>
+      </c>
+      <c r="K1746" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>db479e34-e787-467f-9259-dbae656756ff</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>7a52e499-ed14-4bf4-b071-35aac2c3164f</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1747" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G1747" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1747" t="inlineStr">
+        <is>
+          <t>OP-581</t>
+        </is>
+      </c>
+      <c r="I1747" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1747" s="2" t="n">
+        <v>46077.3935549454</v>
+      </c>
+      <c r="K1747" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>f2395ac0-b1d6-44cb-a5b5-5dcc5d8ab7f8</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>b4cb8dd2-62be-478d-b2f2-24fda97dfd4d</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1748" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G1748" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1748" t="inlineStr">
+        <is>
+          <t>OP-475</t>
+        </is>
+      </c>
+      <c r="I1748" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1748" s="2" t="n">
+        <v>46061.60188828197</v>
+      </c>
+      <c r="K1748" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>bacd9c2c-0233-4b2d-91c1-7203d0a37172</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>d4e4d4e9-26c4-4407-9b5d-ebd2f6e8174c</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1749" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1749" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1749" t="inlineStr">
+        <is>
+          <t>OP-583</t>
+        </is>
+      </c>
+      <c r="I1749" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1749" s="2" t="n">
+        <v>46066.22688828521</v>
+      </c>
+      <c r="K1749" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>931627ae-bc71-429c-a451-19982b6c3fc8</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>6a86c908-e562-4056-b138-1eedc260241b</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1750" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1750" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1750" t="inlineStr">
+        <is>
+          <t>OP-298</t>
+        </is>
+      </c>
+      <c r="I1750" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1750" s="2" t="n">
+        <v>46066.43522162154</v>
+      </c>
+      <c r="K1750" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>caaafa58-cbb8-46b8-a487-b61388176c3d</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>0f4a82f0-8519-481c-9026-86692b20a125</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1751" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1751" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1751" t="inlineStr">
+        <is>
+          <t>OP-656</t>
+        </is>
+      </c>
+      <c r="I1751" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1751" s="2" t="n">
+        <v>46086.51855495793</v>
+      </c>
+      <c r="K1751" t="inlineStr">
         <is>
           <t>good</t>
         </is>

--- a/decision_log.xlsx
+++ b/decision_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1751"/>
+  <dimension ref="A1:K1801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87232,7 +87232,7 @@
         </is>
       </c>
       <c r="J1702" s="2" t="n">
-        <v>46072.56022146757</v>
+        <v>46072.56022146991</v>
       </c>
       <c r="K1702" t="inlineStr">
         <is>
@@ -87283,7 +87283,7 @@
         </is>
       </c>
       <c r="J1703" s="2" t="n">
-        <v>46065.31022147178</v>
+        <v>46065.31022146991</v>
       </c>
       <c r="K1703" t="inlineStr">
         <is>
@@ -87334,7 +87334,7 @@
         </is>
       </c>
       <c r="J1704" s="2" t="n">
-        <v>46064.31022147501</v>
+        <v>46064.31022146991</v>
       </c>
       <c r="K1704" t="inlineStr">
         <is>
@@ -87385,7 +87385,7 @@
         </is>
       </c>
       <c r="J1705" s="2" t="n">
-        <v>46075.476888145</v>
+        <v>46075.47688814815</v>
       </c>
       <c r="K1705" t="inlineStr">
         <is>
@@ -87436,7 +87436,7 @@
         </is>
       </c>
       <c r="J1706" s="2" t="n">
-        <v>46074.35188814825</v>
+        <v>46074.35188814815</v>
       </c>
       <c r="K1706" t="inlineStr">
         <is>
@@ -87487,7 +87487,7 @@
         </is>
       </c>
       <c r="J1707" s="2" t="n">
-        <v>46065.60188815143</v>
+        <v>46065.60188814815</v>
       </c>
       <c r="K1707" t="inlineStr">
         <is>
@@ -87538,7 +87538,7 @@
         </is>
       </c>
       <c r="J1708" s="2" t="n">
-        <v>46067.22688815483</v>
+        <v>46067.22688815972</v>
       </c>
       <c r="K1708" t="inlineStr">
         <is>
@@ -87589,7 +87589,7 @@
         </is>
       </c>
       <c r="J1709" s="2" t="n">
-        <v>46061.56022149131</v>
+        <v>46061.56022149305</v>
       </c>
       <c r="K1709" t="inlineStr">
         <is>
@@ -87640,7 +87640,7 @@
         </is>
       </c>
       <c r="J1710" s="2" t="n">
-        <v>46087.60188816103</v>
+        <v>46087.60188815972</v>
       </c>
       <c r="K1710" t="inlineStr">
         <is>
@@ -87691,7 +87691,7 @@
         </is>
       </c>
       <c r="J1711" s="2" t="n">
-        <v>46078.60188816462</v>
+        <v>46078.60188815972</v>
       </c>
       <c r="K1711" t="inlineStr">
         <is>
@@ -87742,7 +87742,7 @@
         </is>
       </c>
       <c r="J1712" s="2" t="n">
-        <v>46087.51855483503</v>
+        <v>46087.51855483796</v>
       </c>
       <c r="K1712" t="inlineStr">
         <is>
@@ -87793,7 +87793,7 @@
         </is>
       </c>
       <c r="J1713" s="2" t="n">
-        <v>46075.56022150483</v>
+        <v>46075.56022150463</v>
       </c>
       <c r="K1713" t="inlineStr">
         <is>
@@ -87844,7 +87844,7 @@
         </is>
       </c>
       <c r="J1714" s="2" t="n">
-        <v>46080.5185548414</v>
+        <v>46080.51855483796</v>
       </c>
       <c r="K1714" t="inlineStr">
         <is>
@@ -87895,7 +87895,7 @@
         </is>
       </c>
       <c r="J1715" s="2" t="n">
-        <v>46085.39355484464</v>
+        <v>46085.39355484954</v>
       </c>
       <c r="K1715" t="inlineStr">
         <is>
@@ -87946,7 +87946,7 @@
         </is>
       </c>
       <c r="J1716" s="2" t="n">
-        <v>46087.60188818105</v>
+        <v>46087.60188818287</v>
       </c>
       <c r="K1716" t="inlineStr">
         <is>
@@ -87997,7 +87997,7 @@
         </is>
       </c>
       <c r="J1717" s="2" t="n">
-        <v>46079.56022151747</v>
+        <v>46079.56022151621</v>
       </c>
       <c r="K1717" t="inlineStr">
         <is>
@@ -88048,7 +88048,7 @@
         </is>
       </c>
       <c r="J1718" s="2" t="n">
-        <v>46067.31022152056</v>
+        <v>46067.31022151621</v>
       </c>
       <c r="K1718" t="inlineStr">
         <is>
@@ -88099,7 +88099,7 @@
         </is>
       </c>
       <c r="J1719" s="2" t="n">
-        <v>46077.43522152376</v>
+        <v>46077.43522152778</v>
       </c>
       <c r="K1719" t="inlineStr">
         <is>
@@ -88150,7 +88150,7 @@
         </is>
       </c>
       <c r="J1720" s="2" t="n">
-        <v>46075.51855486031</v>
+        <v>46075.51855486111</v>
       </c>
       <c r="K1720" t="inlineStr">
         <is>
@@ -88201,7 +88201,7 @@
         </is>
       </c>
       <c r="J1721" s="2" t="n">
-        <v>46088.56022153005</v>
+        <v>46088.56022152778</v>
       </c>
       <c r="K1721" t="inlineStr">
         <is>
@@ -88252,7 +88252,7 @@
         </is>
       </c>
       <c r="J1722" s="2" t="n">
-        <v>46072.47688819988</v>
+        <v>46072.47688819445</v>
       </c>
       <c r="K1722" t="inlineStr">
         <is>
@@ -88303,7 +88303,7 @@
         </is>
       </c>
       <c r="J1723" s="2" t="n">
-        <v>46085.47688820327</v>
+        <v>46085.47688820602</v>
       </c>
       <c r="K1723" t="inlineStr">
         <is>
@@ -88354,7 +88354,7 @@
         </is>
       </c>
       <c r="J1724" s="2" t="n">
-        <v>46074.4352215397</v>
+        <v>46074.43522153935</v>
       </c>
       <c r="K1724" t="inlineStr">
         <is>
@@ -88405,7 +88405,7 @@
         </is>
       </c>
       <c r="J1725" s="2" t="n">
-        <v>46078.39355487603</v>
+        <v>46078.39355487269</v>
       </c>
       <c r="K1725" t="inlineStr">
         <is>
@@ -88456,7 +88456,7 @@
         </is>
       </c>
       <c r="J1726" s="2" t="n">
-        <v>46066.5602215459</v>
+        <v>46066.56022155093</v>
       </c>
       <c r="K1726" t="inlineStr">
         <is>
@@ -88507,7 +88507,7 @@
         </is>
       </c>
       <c r="J1727" s="2" t="n">
-        <v>46063.43522154899</v>
+        <v>46063.43522155093</v>
       </c>
       <c r="K1727" t="inlineStr">
         <is>
@@ -88558,7 +88558,7 @@
         </is>
       </c>
       <c r="J1728" s="2" t="n">
-        <v>46061.47688821885</v>
+        <v>46061.47688821759</v>
       </c>
       <c r="K1728" t="inlineStr">
         <is>
@@ -88609,7 +88609,7 @@
         </is>
       </c>
       <c r="J1729" s="2" t="n">
-        <v>46064.60188822207</v>
+        <v>46064.60188821759</v>
       </c>
       <c r="K1729" t="inlineStr">
         <is>
@@ -88660,7 +88660,7 @@
         </is>
       </c>
       <c r="J1730" s="2" t="n">
-        <v>46075.35188822538</v>
+        <v>46075.35188822917</v>
       </c>
       <c r="K1730" t="inlineStr">
         <is>
@@ -88711,7 +88711,7 @@
         </is>
       </c>
       <c r="J1731" s="2" t="n">
-        <v>46081.22688822845</v>
+        <v>46081.22688822917</v>
       </c>
       <c r="K1731" t="inlineStr">
         <is>
@@ -88762,7 +88762,7 @@
         </is>
       </c>
       <c r="J1732" s="2" t="n">
-        <v>46065.43522156496</v>
+        <v>46065.4352215625</v>
       </c>
       <c r="K1732" t="inlineStr">
         <is>
@@ -88813,7 +88813,7 @@
         </is>
       </c>
       <c r="J1733" s="2" t="n">
-        <v>46064.60188823478</v>
+        <v>46064.60188822917</v>
       </c>
       <c r="K1733" t="inlineStr">
         <is>
@@ -88864,7 +88864,7 @@
         </is>
       </c>
       <c r="J1734" s="2" t="n">
-        <v>46089.35188823805</v>
+        <v>46089.35188824074</v>
       </c>
       <c r="K1734" t="inlineStr">
         <is>
@@ -88915,7 +88915,7 @@
         </is>
       </c>
       <c r="J1735" s="2" t="n">
-        <v>46068.56022157448</v>
+        <v>46068.56022157407</v>
       </c>
       <c r="K1735" t="inlineStr">
         <is>
@@ -88966,7 +88966,7 @@
         </is>
       </c>
       <c r="J1736" s="2" t="n">
-        <v>46078.56022157765</v>
+        <v>46078.56022157407</v>
       </c>
       <c r="K1736" t="inlineStr">
         <is>
@@ -89017,7 +89017,7 @@
         </is>
       </c>
       <c r="J1737" s="2" t="n">
-        <v>46087.2268882475</v>
+        <v>46087.22688825231</v>
       </c>
       <c r="K1737" t="inlineStr">
         <is>
@@ -89068,7 +89068,7 @@
         </is>
       </c>
       <c r="J1738" s="2" t="n">
-        <v>46076.39355491735</v>
+        <v>46076.39355491898</v>
       </c>
       <c r="K1738" t="inlineStr">
         <is>
@@ -89119,7 +89119,7 @@
         </is>
       </c>
       <c r="J1739" s="2" t="n">
-        <v>46078.47688825382</v>
+        <v>46078.47688825231</v>
       </c>
       <c r="K1739" t="inlineStr">
         <is>
@@ -89170,7 +89170,7 @@
         </is>
       </c>
       <c r="J1740" s="2" t="n">
-        <v>46075.47688825684</v>
+        <v>46075.47688825231</v>
       </c>
       <c r="K1740" t="inlineStr">
         <is>
@@ -89221,7 +89221,7 @@
         </is>
       </c>
       <c r="J1741" s="2" t="n">
-        <v>46086.22688826011</v>
+        <v>46086.22688826389</v>
       </c>
       <c r="K1741" t="inlineStr">
         <is>
@@ -89272,7 +89272,7 @@
         </is>
       </c>
       <c r="J1742" s="2" t="n">
-        <v>46085.47688826314</v>
+        <v>46085.47688826389</v>
       </c>
       <c r="K1742" t="inlineStr">
         <is>
@@ -89323,7 +89323,7 @@
         </is>
       </c>
       <c r="J1743" s="2" t="n">
-        <v>46083.22688826622</v>
+        <v>46083.22688826389</v>
       </c>
       <c r="K1743" t="inlineStr">
         <is>
@@ -89374,7 +89374,7 @@
         </is>
       </c>
       <c r="J1744" s="2" t="n">
-        <v>46070.60188826924</v>
+        <v>46070.60188826389</v>
       </c>
       <c r="K1744" t="inlineStr">
         <is>
@@ -89425,7 +89425,7 @@
         </is>
       </c>
       <c r="J1745" s="2" t="n">
-        <v>46083.39355493927</v>
+        <v>46083.39355494213</v>
       </c>
       <c r="K1745" t="inlineStr">
         <is>
@@ -89476,7 +89476,7 @@
         </is>
       </c>
       <c r="J1746" s="2" t="n">
-        <v>46068.2268882757</v>
+        <v>46068.22688827547</v>
       </c>
       <c r="K1746" t="inlineStr">
         <is>
@@ -89527,7 +89527,7 @@
         </is>
       </c>
       <c r="J1747" s="2" t="n">
-        <v>46077.3935549454</v>
+        <v>46077.39355494213</v>
       </c>
       <c r="K1747" t="inlineStr">
         <is>
@@ -89578,7 +89578,7 @@
         </is>
       </c>
       <c r="J1748" s="2" t="n">
-        <v>46061.60188828197</v>
+        <v>46061.60188828703</v>
       </c>
       <c r="K1748" t="inlineStr">
         <is>
@@ -89629,7 +89629,7 @@
         </is>
       </c>
       <c r="J1749" s="2" t="n">
-        <v>46066.22688828521</v>
+        <v>46066.22688828703</v>
       </c>
       <c r="K1749" t="inlineStr">
         <is>
@@ -89680,7 +89680,7 @@
         </is>
       </c>
       <c r="J1750" s="2" t="n">
-        <v>46066.43522162154</v>
+        <v>46066.43522162037</v>
       </c>
       <c r="K1750" t="inlineStr">
         <is>
@@ -89731,11 +89731,2561 @@
         </is>
       </c>
       <c r="J1751" s="2" t="n">
-        <v>46086.51855495793</v>
+        <v>46086.51855495371</v>
       </c>
       <c r="K1751" t="inlineStr">
         <is>
           <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>5940f849-98b1-47c1-bfce-ebb57378348e</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>9170c1a3-49ac-4096-8f62-8b2343897fc3</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1752" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="G1752" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1752" t="inlineStr">
+        <is>
+          <t>OP-245</t>
+        </is>
+      </c>
+      <c r="I1752" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1752" s="2" t="n">
+        <v>46082.27730555884</v>
+      </c>
+      <c r="K1752" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>319f100d-6c54-4da4-a1f0-4069d08c8589</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>e296c0d2-7e2d-4794-acf1-d5e4421841d5</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1753" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1753" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1753" t="inlineStr">
+        <is>
+          <t>OP-221</t>
+        </is>
+      </c>
+      <c r="I1753" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1753" s="2" t="n">
+        <v>46084.44397222983</v>
+      </c>
+      <c r="K1753" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>deb23378-f7e7-43b8-a219-aa77b717f00c</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>74afb41f-0b93-40ff-a9fd-99c168e556e8</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1754" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F1754" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1754" t="inlineStr">
+        <is>
+          <t>OP-627</t>
+        </is>
+      </c>
+      <c r="I1754" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1754" s="2" t="n">
+        <v>46064.5689722331</v>
+      </c>
+      <c r="K1754" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>f5018482-a5d2-4694-8ad6-b990cf80d5a5</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>309975ad-3945-4359-ac5a-1c4708531910</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1755" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1755" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1755" t="inlineStr">
+        <is>
+          <t>OP-396</t>
+        </is>
+      </c>
+      <c r="I1755" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1755" s="2" t="n">
+        <v>46063.36063890303</v>
+      </c>
+      <c r="K1755" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>3bde84f3-e3d5-4ff9-b46c-f14056e83ea2</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>3e705212-95fa-4880-9718-7c822acdfc81</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1756" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1756" t="inlineStr">
+        <is>
+          <t>OP-965</t>
+        </is>
+      </c>
+      <c r="I1756" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1756" s="2" t="n">
+        <v>46086.4856389063</v>
+      </c>
+      <c r="K1756" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>b8b12bbb-b59e-4ddb-9795-eac3aefb5184</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>93c4aec4-4b3a-4f6a-bc3e-37905c7c39fc</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1757" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1757" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1757" t="inlineStr">
+        <is>
+          <t>OP-839</t>
+        </is>
+      </c>
+      <c r="I1757" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1757" s="2" t="n">
+        <v>46087.3606389095</v>
+      </c>
+      <c r="K1757" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>90b7d6b1-b853-45c2-8b2b-5251f019be37</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>c0cfd944-c7cd-4ca1-9deb-08176c2352d6</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1758" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1758" t="inlineStr">
+        <is>
+          <t>OP-274</t>
+        </is>
+      </c>
+      <c r="I1758" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1758" s="2" t="n">
+        <v>46073.36063891259</v>
+      </c>
+      <c r="K1758" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>79b31f6b-21aa-4bfc-b56d-ff4bc2bc9c93</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>bae82fd6-0baf-466c-8e7c-3ea79860b08e</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1759" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1759" t="inlineStr">
+        <is>
+          <t>OP-386</t>
+        </is>
+      </c>
+      <c r="I1759" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1759" s="2" t="n">
+        <v>46078.44397224948</v>
+      </c>
+      <c r="K1759" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>71da297c-eca1-490e-88e0-cf2306ca9537</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>25c0c2b8-392c-4765-a339-cb3086ab747b</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1760" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1760" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1760" t="inlineStr">
+        <is>
+          <t>OP-910</t>
+        </is>
+      </c>
+      <c r="I1760" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1760" s="2" t="n">
+        <v>46079.61063891928</v>
+      </c>
+      <c r="K1760" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>959b2935-a098-4779-9e9d-831d20af9e83</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>dce08e91-42b2-4729-a4e0-5c1d7c860654</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1761" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G1761" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1761" t="inlineStr">
+        <is>
+          <t>OP-951</t>
+        </is>
+      </c>
+      <c r="I1761" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1761" s="2" t="n">
+        <v>46088.65230558906</v>
+      </c>
+      <c r="K1761" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>c48a581c-5f26-4691-b3fa-55679bf5c091</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>12c64a62-689d-4657-9b7d-84f5ffde97c6</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1762" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="F1762" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1762" t="inlineStr">
+        <is>
+          <t>OP-348</t>
+        </is>
+      </c>
+      <c r="I1762" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1762" s="2" t="n">
+        <v>46068.52730559234</v>
+      </c>
+      <c r="K1762" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>55c4bbe0-de81-43bc-b43f-922c44540d41</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>f9d666aa-c4de-43a8-9fa3-7865d5fccc56</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1763" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F1763" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1763" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1763" t="inlineStr">
+        <is>
+          <t>OP-509</t>
+        </is>
+      </c>
+      <c r="I1763" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1763" s="2" t="n">
+        <v>46089.61063892905</v>
+      </c>
+      <c r="K1763" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>cbd987ee-067f-4f69-bb93-96f9dbb2ba0a</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>27fe8019-fd17-4109-b75a-128ed57b18fa</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1764" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1764" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1764" t="inlineStr">
+        <is>
+          <t>OP-332</t>
+        </is>
+      </c>
+      <c r="I1764" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1764" s="2" t="n">
+        <v>46090.27730559898</v>
+      </c>
+      <c r="K1764" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>ac062050-3f7d-4da2-a187-e238ba6facea</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>17ee1e1e-5681-422b-89e0-b3484743d9fc</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1765" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F1765" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1765" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1765" t="inlineStr">
+        <is>
+          <t>OP-153</t>
+        </is>
+      </c>
+      <c r="I1765" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1765" s="2" t="n">
+        <v>46087.61063893538</v>
+      </c>
+      <c r="K1765" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>31721fbd-d589-4fb1-93c2-eaccb592406d</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>2634c01f-3652-4f11-9402-abde766bbb0f</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1766" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F1766" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1766" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1766" t="inlineStr">
+        <is>
+          <t>OP-298</t>
+        </is>
+      </c>
+      <c r="I1766" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1766" s="2" t="n">
+        <v>46086.40230560513</v>
+      </c>
+      <c r="K1766" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>bd8f0397-6cdf-4420-bac0-9117fbf6770e</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>d4f38b3c-241b-46aa-8d95-9f7aedd15fe4</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1767" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F1767" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G1767" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1767" t="inlineStr">
+        <is>
+          <t>OP-734</t>
+        </is>
+      </c>
+      <c r="I1767" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1767" s="2" t="n">
+        <v>46069.31897227523</v>
+      </c>
+      <c r="K1767" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>650836a0-c537-4e6e-85d8-272d1fb07a31</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>11c08e16-1dce-482f-ad40-d8be8b67cdbf</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1768" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F1768" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G1768" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1768" t="inlineStr">
+        <is>
+          <t>OP-660</t>
+        </is>
+      </c>
+      <c r="I1768" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1768" s="2" t="n">
+        <v>46077.56897227832</v>
+      </c>
+      <c r="K1768" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>06982d40-0c8a-409c-aa16-25aa8447bfbe</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>2d02b18a-3ade-402f-bf3b-9e23c29e5d3e</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1769" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="G1769" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1769" t="inlineStr">
+        <is>
+          <t>OP-207</t>
+        </is>
+      </c>
+      <c r="I1769" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1769" s="2" t="n">
+        <v>46088.44397228152</v>
+      </c>
+      <c r="K1769" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>1e0e5992-2df7-4947-b2c0-e2e67c60ba1d</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>bd660620-205f-4836-9c1e-2ed6c5f3abc5</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1770" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F1770" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1770" t="inlineStr">
+        <is>
+          <t>OP-676</t>
+        </is>
+      </c>
+      <c r="I1770" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1770" s="2" t="n">
+        <v>46068.36063895162</v>
+      </c>
+      <c r="K1770" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>5563aae8-8f32-43a7-ad0a-1b8e07a24bad</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>b110d69b-4f13-47ee-8847-fa4568bba672</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1771" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1771" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1771" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1771" t="inlineStr">
+        <is>
+          <t>OP-682</t>
+        </is>
+      </c>
+      <c r="I1771" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1771" s="2" t="n">
+        <v>46079.31897228803</v>
+      </c>
+      <c r="K1771" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>95f6cfde-4061-4090-8319-eba1d991f221</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>c6e116af-5ee1-4d4a-a1b3-1118a5b9a178</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1772" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G1772" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1772" t="inlineStr">
+        <is>
+          <t>OP-263</t>
+        </is>
+      </c>
+      <c r="I1772" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1772" s="2" t="n">
+        <v>46066.52730562443</v>
+      </c>
+      <c r="K1772" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>4c38160f-8963-45e9-a5e6-37377342d53e</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>7ee40d22-1f4f-4583-9500-9dcb76fe803b</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1773" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F1773" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G1773" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1773" t="inlineStr">
+        <is>
+          <t>OP-103</t>
+        </is>
+      </c>
+      <c r="I1773" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1773" s="2" t="n">
+        <v>46074.48563896103</v>
+      </c>
+      <c r="K1773" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>f0a1fdf0-e776-41fb-b47b-41ce79ba5b76</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>11be0600-7eb2-41dc-883c-5d6090a9087c</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1774" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F1774" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G1774" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1774" t="inlineStr">
+        <is>
+          <t>OP-581</t>
+        </is>
+      </c>
+      <c r="I1774" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1774" s="2" t="n">
+        <v>46066.31897229792</v>
+      </c>
+      <c r="K1774" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>d00c4de8-0e14-49db-9da2-63998a09ab9b</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>7e3b4db0-f84f-4eb6-9510-e8aac1dddf25</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1775" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1775" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1775" t="inlineStr">
+        <is>
+          <t>OP-644</t>
+        </is>
+      </c>
+      <c r="I1775" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1775" s="2" t="n">
+        <v>46063.44397230096</v>
+      </c>
+      <c r="K1775" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>35254e4a-8a46-4501-a16b-c46cd65e4eaa</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>4f9aea4b-0c8d-405c-8433-600df2917004</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1776" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1776" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1776" t="inlineStr">
+        <is>
+          <t>OP-547</t>
+        </is>
+      </c>
+      <c r="I1776" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1776" s="2" t="n">
+        <v>46063.40230563734</v>
+      </c>
+      <c r="K1776" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>70e39483-95a1-46cd-b497-b6711a23b31a</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>401392e4-960b-49f7-bfdd-07258dfd613e</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1777" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F1777" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G1777" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1777" t="inlineStr">
+        <is>
+          <t>OP-315</t>
+        </is>
+      </c>
+      <c r="I1777" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1777" s="2" t="n">
+        <v>46064.65230564065</v>
+      </c>
+      <c r="K1777" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>fad8bd19-6335-4293-9f7f-fcec7ecf1fe6</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>5d5483b9-ee6e-4948-a0c2-7b561658513b</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1778" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G1778" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1778" t="inlineStr">
+        <is>
+          <t>OP-817</t>
+        </is>
+      </c>
+      <c r="I1778" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1778" s="2" t="n">
+        <v>46071.52730564376</v>
+      </c>
+      <c r="K1778" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>15d53e48-83c1-4b0c-8e6f-968b1c34897e</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>ed14d143-ae93-484f-95bb-f116b5c90a01</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1779" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F1779" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1779" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1779" t="inlineStr">
+        <is>
+          <t>OP-992</t>
+        </is>
+      </c>
+      <c r="I1779" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1779" s="2" t="n">
+        <v>46082.48563898017</v>
+      </c>
+      <c r="K1779" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>140fecb5-2c96-4caf-a13f-a1acbbbc834f</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>d941bab9-52f1-4092-9841-a7d35ae84bd1</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1780" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="F1780" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G1780" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1780" t="inlineStr">
+        <is>
+          <t>OP-996</t>
+        </is>
+      </c>
+      <c r="I1780" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1780" s="2" t="n">
+        <v>46062.61063898334</v>
+      </c>
+      <c r="K1780" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>0796397a-0436-4398-8b5f-f7153f71f062</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>060cd397-9116-416f-8aa7-a068b6214d57</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1781" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="F1781" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G1781" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1781" t="inlineStr">
+        <is>
+          <t>OP-789</t>
+        </is>
+      </c>
+      <c r="I1781" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1781" s="2" t="n">
+        <v>46072.65230565325</v>
+      </c>
+      <c r="K1781" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>00f64b1b-85fa-4fc6-93ea-6033c7d1cca4</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>b200f386-6524-48b2-a742-872dc159a39e</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1782" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F1782" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G1782" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1782" t="inlineStr">
+        <is>
+          <t>OP-768</t>
+        </is>
+      </c>
+      <c r="I1782" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1782" s="2" t="n">
+        <v>46077.48563898979</v>
+      </c>
+      <c r="K1782" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>7ecaa836-eacb-4b62-9a0b-19fc6ff9bd8d</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>d0f5c278-22ae-4133-af70-2cda565a1164</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1783" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F1783" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G1783" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1783" t="inlineStr">
+        <is>
+          <t>OP-307</t>
+        </is>
+      </c>
+      <c r="I1783" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1783" s="2" t="n">
+        <v>46061.44397232634</v>
+      </c>
+      <c r="K1783" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>ab3a80d7-29b6-4b66-8845-48f3f3b70297</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>3a6c35cf-7172-4b73-8bcd-867ea1c5358d</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1784" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F1784" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1784" t="inlineStr">
+        <is>
+          <t>OP-372</t>
+        </is>
+      </c>
+      <c r="I1784" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1784" s="2" t="n">
+        <v>46066.48563899614</v>
+      </c>
+      <c r="K1784" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>d6edf995-4699-4b01-91ce-f14c956bd75f</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>3ce9dee6-577f-4c46-b3f0-9459bf39048b</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1785" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="F1785" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1785" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1785" t="inlineStr">
+        <is>
+          <t>OP-259</t>
+        </is>
+      </c>
+      <c r="I1785" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1785" s="2" t="n">
+        <v>46063.27730566607</v>
+      </c>
+      <c r="K1785" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>98b961b5-3a92-48d0-a732-e94893255e34</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>eac6d24d-5ce9-42e5-8402-1346ecbc5adf</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1786" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1786" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1786" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1786" t="inlineStr">
+        <is>
+          <t>OP-347</t>
+        </is>
+      </c>
+      <c r="I1786" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1786" s="2" t="n">
+        <v>46063.27730566918</v>
+      </c>
+      <c r="K1786" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>6f293c2b-a950-45d8-aa2a-a8455eeb1227</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>98c9891a-f135-435f-8625-5bf2356d80d8</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1787" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1787" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G1787" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1787" t="inlineStr">
+        <is>
+          <t>OP-128</t>
+        </is>
+      </c>
+      <c r="I1787" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1787" s="2" t="n">
+        <v>46062.31897233897</v>
+      </c>
+      <c r="K1787" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>a7d4d18b-7413-441a-b9e2-7e4116144479</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>543d97e5-a22a-4276-8b0f-9ec6eb408028</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1788" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F1788" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G1788" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1788" t="inlineStr">
+        <is>
+          <t>OP-517</t>
+        </is>
+      </c>
+      <c r="I1788" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1788" s="2" t="n">
+        <v>46061.27730567561</v>
+      </c>
+      <c r="K1788" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>c770eab8-db68-44bf-96af-bc99f457c367</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>86a1dc05-25d8-4ed1-8c8c-f3a46379ddf2</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1789" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F1789" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1789" t="inlineStr">
+        <is>
+          <t>OP-886</t>
+        </is>
+      </c>
+      <c r="I1789" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1789" s="2" t="n">
+        <v>46090.2773056788</v>
+      </c>
+      <c r="K1789" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>6f77b5bd-ebaa-4f0a-912f-b51c2fa596cb</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>f7a792c3-13e8-46eb-b89b-6277ab4aa0a1</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1790" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F1790" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1790" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1790" t="inlineStr">
+        <is>
+          <t>OP-155</t>
+        </is>
+      </c>
+      <c r="I1790" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1790" s="2" t="n">
+        <v>46067.44397234862</v>
+      </c>
+      <c r="K1790" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>c27ec3a7-3081-4684-9f9b-579f6b77f9be</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>e4d30515-7fae-41b8-ba0c-0d3f0a8bcc21</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1791" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F1791" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G1791" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1791" t="inlineStr">
+        <is>
+          <t>OP-450</t>
+        </is>
+      </c>
+      <c r="I1791" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1791" s="2" t="n">
+        <v>46066.31897235187</v>
+      </c>
+      <c r="K1791" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>a9ac8fe2-e6de-45b8-a7c5-794dcc5647e8</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>d14ade62-f764-487b-be12-7082714670a2</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1792" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F1792" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G1792" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1792" t="inlineStr">
+        <is>
+          <t>OP-895</t>
+        </is>
+      </c>
+      <c r="I1792" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1792" s="2" t="n">
+        <v>46061.4439723551</v>
+      </c>
+      <c r="K1792" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>4bad5f53-95b6-410d-9f81-12c6f3b04437</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>070eff3b-2627-4eb9-9830-9728777ba993</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1793" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="F1793" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1793" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1793" t="inlineStr">
+        <is>
+          <t>OP-859</t>
+        </is>
+      </c>
+      <c r="I1793" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1793" s="2" t="n">
+        <v>46090.48563902505</v>
+      </c>
+      <c r="K1793" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>0202bff8-0b65-410b-885a-fef1abf5bfc5</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>067ba303-2e1f-440d-b282-609925848884</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1794" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1794" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G1794" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1794" t="inlineStr">
+        <is>
+          <t>OP-284</t>
+        </is>
+      </c>
+      <c r="I1794" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1794" s="2" t="n">
+        <v>46070.27730569477</v>
+      </c>
+      <c r="K1794" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>ddfe9a0c-b0f7-41b5-a5ed-f75f0c0136b5</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>c1c850de-9c05-4e3c-a681-66c9f6257780</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1795" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F1795" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G1795" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1795" t="inlineStr">
+        <is>
+          <t>OP-522</t>
+        </is>
+      </c>
+      <c r="I1795" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1795" s="2" t="n">
+        <v>46089.52730569797</v>
+      </c>
+      <c r="K1795" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>641ce147-2b63-4017-b2cf-ce0f68197b8b</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>4a98c36d-6ad8-42d6-9f86-8b6bcd2bc3e8</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1796" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F1796" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1796" t="inlineStr">
+        <is>
+          <t>OP-778</t>
+        </is>
+      </c>
+      <c r="I1796" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1796" s="2" t="n">
+        <v>46088.36063903548</v>
+      </c>
+      <c r="K1796" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>d2159490-270f-4a52-9371-d185ab87c81a</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>6444ecc5-7444-4971-8cfe-63fe21a8719f</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>RiskAgent</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1797" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F1797" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G1797" t="inlineStr">
+        <is>
+          <t>rejected</t>
+        </is>
+      </c>
+      <c r="H1797" t="inlineStr">
+        <is>
+          <t>OP-783</t>
+        </is>
+      </c>
+      <c r="I1797" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1797" s="2" t="n">
+        <v>46084.36063903856</v>
+      </c>
+      <c r="K1797" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>780da106-caed-43e6-b092-7ebea55e107e</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>f1188708-c6c6-42ae-affd-e5a13c8ec51a</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1798" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="F1798" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1798" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1798" t="inlineStr">
+        <is>
+          <t>OP-554</t>
+        </is>
+      </c>
+      <c r="I1798" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1798" s="2" t="n">
+        <v>46066.52730570827</v>
+      </c>
+      <c r="K1798" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>c82072ed-68c1-412b-90f5-1c9db71a0df6</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>7ea5d8ab-8fe9-4c66-9331-654bfd286b63</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>ComplianceAgent</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1799" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F1799" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="H1799" t="inlineStr">
+        <is>
+          <t>OP-636</t>
+        </is>
+      </c>
+      <c r="I1799" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1799" s="2" t="n">
+        <v>46073.48563904529</v>
+      </c>
+      <c r="K1799" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>3346ba08-011d-48e0-98d6-6e34c122f554</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>ce63100e-276e-447c-8b35-2088592499f9</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1800" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F1800" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G1800" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1800" t="inlineStr">
+        <is>
+          <t>OP-427</t>
+        </is>
+      </c>
+      <c r="I1800" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1800" s="2" t="n">
+        <v>46062.4439723817</v>
+      </c>
+      <c r="K1800" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>c12a72fb-30da-4433-a700-b3f4623bb6cf</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>592cd027-c468-4054-824b-dbc7b81af69a</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>MonitoringAgent</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>Increase cooling / reroute shipment</t>
+        </is>
+      </c>
+      <c r="E1801" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F1801" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="H1801" t="inlineStr">
+        <is>
+          <t>OP-128</t>
+        </is>
+      </c>
+      <c r="I1801" t="inlineStr">
+        <is>
+          <t>Synthetic operator note</t>
+        </is>
+      </c>
+      <c r="J1801" s="2" t="n">
+        <v>46062.36063905143</v>
+      </c>
+      <c r="K1801" t="inlineStr">
+        <is>
+          <t>poor</t>
         </is>
       </c>
     </row>
